--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A88DEBB-6F34-4028-99FD-B862124A6999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9DFEAD-5232-4C77-BBE5-8221A20DC632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2022" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="741">
   <si>
     <t>類型</t>
   </si>
@@ -291,1708 +291,2072 @@
     <t>r01</t>
   </si>
   <si>
+    <t>hit</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>evasion</t>
+  </si>
+  <si>
+    <t>r02</t>
+  </si>
+  <si>
+    <t>餘燼</t>
+  </si>
+  <si>
+    <t>atkFlat</t>
+  </si>
+  <si>
+    <t>defFlat</t>
+  </si>
+  <si>
+    <t>r03</t>
+  </si>
+  <si>
+    <t>霜痕</t>
+  </si>
+  <si>
+    <t>elemDmgIce</t>
+  </si>
+  <si>
+    <t>resIce</t>
+  </si>
+  <si>
+    <t>r04</t>
+  </si>
+  <si>
+    <t>風語</t>
+  </si>
+  <si>
+    <t>aspd</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>r05</t>
+  </si>
+  <si>
+    <t>巖心</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>pPen</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>defPct</t>
+  </si>
+  <si>
+    <t>r06</t>
+  </si>
+  <si>
+    <t>毒牙</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>elemDmgPoison</t>
+  </si>
+  <si>
+    <t>resPoison</t>
+  </si>
+  <si>
+    <t>r07</t>
+  </si>
+  <si>
+    <t>雷鳴</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>elemDmgLightning</t>
+  </si>
+  <si>
+    <t>resLightning</t>
+  </si>
+  <si>
+    <t>r08</t>
+  </si>
+  <si>
+    <t>暗影</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>lifesteal</t>
+  </si>
+  <si>
+    <t>hpRegen</t>
+  </si>
+  <si>
+    <t>r09</t>
+  </si>
+  <si>
+    <t>聖輝</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>elemDmgLight</t>
+  </si>
+  <si>
+    <t>resLight</t>
+  </si>
+  <si>
+    <t>r10</t>
+  </si>
+  <si>
+    <t>血誓</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>atkPct</t>
+  </si>
+  <si>
+    <t>hpPct</t>
+  </si>
+  <si>
+    <t>r11</t>
+  </si>
+  <si>
+    <t>鋼魄</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>critDmg</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>pRes</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>r12</t>
+  </si>
+  <si>
+    <t>靈泉</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>matkPct</t>
+  </si>
+  <si>
+    <t>mpFlat</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>r13</t>
+  </si>
+  <si>
+    <t>疾影</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>critRate</t>
+  </si>
+  <si>
+    <t>r14</t>
+  </si>
+  <si>
+    <t>磐石</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>eliteDmg</t>
+  </si>
+  <si>
+    <t>blockRate</t>
+  </si>
+  <si>
+    <t>r15</t>
+  </si>
+  <si>
+    <t>曙光</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>mPen</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>mRes</t>
+  </si>
+  <si>
+    <t>r16</t>
+  </si>
+  <si>
+    <t>夜幕</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>elemDmgDark</t>
+  </si>
+  <si>
+    <t>resDark</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>r17</t>
+  </si>
+  <si>
+    <t>烈陽</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>elemDmgFire</t>
+  </si>
+  <si>
+    <t>resFire</t>
+  </si>
+  <si>
+    <t>r18</t>
+  </si>
+  <si>
+    <t>寒月</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>cdr</t>
+  </si>
+  <si>
+    <t>mdefPct</t>
+  </si>
+  <si>
+    <t>r19</t>
+  </si>
+  <si>
+    <t>驚蟄</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>tenacity</t>
+  </si>
+  <si>
+    <t>r20</t>
+  </si>
+  <si>
+    <t>嵐</t>
+  </si>
+  <si>
+    <t>elemDmgWind</t>
+  </si>
+  <si>
+    <t>resWind</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>r21</t>
+  </si>
+  <si>
+    <t>蒼穹</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>bossDmg</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>shieldEff</t>
+  </si>
+  <si>
+    <t>r22</t>
+  </si>
+  <si>
+    <t>厚土</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>elemDmgEarth</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>r23</t>
+  </si>
+  <si>
+    <t>熔岩</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>globalDmgRed</t>
+  </si>
+  <si>
+    <t>r24</t>
+  </si>
+  <si>
+    <t>冰魄</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>resAll</t>
+  </si>
+  <si>
+    <t>r25</t>
+  </si>
+  <si>
+    <t>雷霆</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>blockDmgRed</t>
+  </si>
+  <si>
+    <t>r26</t>
+  </si>
+  <si>
+    <t>虛空</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>aoeDmg</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>ccRed</t>
+  </si>
+  <si>
+    <t>r27</t>
+  </si>
+  <si>
+    <t>星辰</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>luck</t>
+  </si>
+  <si>
+    <t>r28</t>
+  </si>
+  <si>
+    <t>命運</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>normalDmg</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>r29</t>
+  </si>
+  <si>
+    <t>輪迴</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>r30</t>
+  </si>
+  <si>
+    <t>永恆</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>r31</t>
+  </si>
+  <si>
+    <t>混沌</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>r32</t>
+  </si>
+  <si>
+    <t>創生</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>r33</t>
+  </si>
+  <si>
+    <t>終焉</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>符文之語</t>
+  </si>
+  <si>
+    <t>rw_firstcry</t>
+  </si>
+  <si>
+    <t>初啼</t>
+  </si>
+  <si>
+    <t>微光;餘燼</t>
+  </si>
+  <si>
+    <t>mainHand</t>
+  </si>
+  <si>
+    <t>atkFlat:2;matkFlat:2;hit:1</t>
+  </si>
+  <si>
+    <t>第一聲啼鳴，劃破長夜的寂靜。</t>
+  </si>
+  <si>
+    <t>rw_nightwatch</t>
+  </si>
+  <si>
+    <t>守夜</t>
+  </si>
+  <si>
+    <t>餘燼;巖心</t>
+  </si>
+  <si>
+    <t>chest</t>
+  </si>
+  <si>
+    <t>defFlat:2.5;hpFlat:2.5;hpRegen:1</t>
+  </si>
+  <si>
+    <t>燈火不滅，守夜人便不眠。</t>
+  </si>
+  <si>
+    <t>rw_frostwhisper</t>
+  </si>
+  <si>
+    <t>霜語</t>
+  </si>
+  <si>
+    <t>霜痕;風語</t>
+  </si>
+  <si>
+    <t>caster</t>
+  </si>
+  <si>
+    <t>matkFlat:2.5;elemDmgIce:1.5</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":10,"acts":[{"act":"slow","sec":2}]}]</t>
+  </si>
+  <si>
+    <t>寒風低語，敵人的腳步便慢了下來。</t>
+  </si>
+  <si>
+    <t>rw_windwalk</t>
+  </si>
+  <si>
+    <t>行雲</t>
+  </si>
+  <si>
+    <t>風語;微光;暗影</t>
+  </si>
+  <si>
+    <t>boots</t>
+  </si>
+  <si>
+    <t>evasion:2;hpFlat:2;hit:1</t>
+  </si>
+  <si>
+    <t>步履如雲，不留痕跡。</t>
+  </si>
+  <si>
+    <t>rw_stoneskin</t>
+  </si>
+  <si>
+    <t>石膚</t>
+  </si>
+  <si>
+    <t>巖心;霜痕</t>
+  </si>
+  <si>
+    <t>shoulder;legs</t>
+  </si>
+  <si>
+    <t>defPct:1.5;hpPct:1.2;pRes:0.8</t>
+  </si>
+  <si>
+    <t>thorns:3</t>
+  </si>
+  <si>
+    <t>皮膚堅如岩層，觸碰者必受其傷。</t>
+  </si>
+  <si>
+    <t>rw_viperkiss</t>
+  </si>
+  <si>
+    <t>蛇吻</t>
+  </si>
+  <si>
+    <t>毒牙;暗影</t>
+  </si>
+  <si>
+    <t>sword1h;dagger1h;magicSword1h</t>
+  </si>
+  <si>
+    <t>atkPct:1.2;elemDmgPoison:1.5;critRate:1</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":15,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison"}]}]</t>
+  </si>
+  <si>
+    <t>毒蛇的一吻，慢慢收走對手的生命。</t>
+  </si>
+  <si>
+    <t>rw_minorthunder</t>
+  </si>
+  <si>
+    <t>輕雷</t>
+  </si>
+  <si>
+    <t>雷鳴;風語</t>
+  </si>
+  <si>
+    <t>oneHand</t>
+  </si>
+  <si>
+    <t>matkPct:1.5;elemDmgLightning:2</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":90,"elem":"lightning","to":"target"}]}]</t>
+  </si>
+  <si>
+    <t>一聲輕雷，落在不經意的地方。</t>
+  </si>
+  <si>
+    <t>rw_lightguard</t>
+  </si>
+  <si>
+    <t>聖光之守</t>
+  </si>
+  <si>
+    <t>微光;聖輝</t>
+  </si>
+  <si>
+    <t>helmet</t>
+  </si>
+  <si>
+    <t>mpFlat:2;resLight:1.5;hpPct:1</t>
+  </si>
+  <si>
+    <t>killManaPct:1</t>
+  </si>
+  <si>
+    <t>以聖光為冠，心神澄明。</t>
+  </si>
+  <si>
+    <t>rw_bloodring</t>
+  </si>
+  <si>
+    <t>血誓之環</t>
+  </si>
+  <si>
+    <t>血誓;暗影</t>
+  </si>
+  <si>
+    <t>ring</t>
+  </si>
+  <si>
+    <t>lifesteal:2;atkPct:1;hit:1</t>
+  </si>
+  <si>
+    <t>killHealPct:1</t>
+  </si>
+  <si>
+    <t>以血起誓，生者共飲。</t>
+  </si>
+  <si>
+    <t>rw_steelheart</t>
+  </si>
+  <si>
+    <t>鋼心</t>
+  </si>
+  <si>
+    <t>巖心;血誓</t>
+  </si>
+  <si>
+    <t>belt</t>
+  </si>
+  <si>
+    <t>hpPct:1.5;defPct:1.5;tenacity:1</t>
+  </si>
+  <si>
+    <t>腰繫鋼索，心不動搖。</t>
+  </si>
+  <si>
+    <t>rw_springflow</t>
+  </si>
+  <si>
+    <t>泉湧</t>
+  </si>
+  <si>
+    <t>微光;餘燼;暗影</t>
+  </si>
+  <si>
+    <t>amulet</t>
+  </si>
+  <si>
+    <t>mpRegen:2;hpRegen:2;mpFlat:1.5</t>
+  </si>
+  <si>
+    <t>killManaPct:2</t>
+  </si>
+  <si>
+    <t>源源不絕，如山間清泉。</t>
+  </si>
+  <si>
+    <t>rw_scavenger</t>
+  </si>
+  <si>
+    <t>拾荒者</t>
+  </si>
+  <si>
+    <t>微光;風語</t>
+  </si>
+  <si>
+    <t>jewelry</t>
+  </si>
+  <si>
+    <t>goldBonus:2;xpBonus:1.5;loot:1.2</t>
+  </si>
+  <si>
+    <t>runeFindPct:8</t>
+  </si>
+  <si>
+    <t>連廢墟裡的一粒塵埃，也要翻過三遍。</t>
+  </si>
+  <si>
+    <t>rw_breaker</t>
+  </si>
+  <si>
+    <t>破軍</t>
+  </si>
+  <si>
+    <t>餘燼;血誓;巖心</t>
+  </si>
+  <si>
+    <t>twoHand</t>
+  </si>
+  <si>
+    <t>atkPct:1.2;critDmg:1.2;pPen:0.2</t>
+  </si>
+  <si>
+    <t>重兵一落，軍陣自潰。</t>
+  </si>
+  <si>
+    <t>rw_burnstar</t>
+  </si>
+  <si>
+    <t>燃星</t>
+  </si>
+  <si>
+    <t>餘燼;聖輝</t>
+  </si>
+  <si>
+    <t>matkPct:1.5;elemDmgFire:1.5;mpFlat:1.5</t>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":15,"acts":[{"act":"mana","pctMax":12}]}]</t>
+  </si>
+  <si>
+    <t>星火燎原，施法者的靈感湧現。</t>
+  </si>
+  <si>
+    <t>rw_galeblade</t>
+  </si>
+  <si>
+    <t>疾風烈刃</t>
+  </si>
+  <si>
+    <t>疾影;風語;雷鳴;磐石</t>
+  </si>
+  <si>
+    <t>aspd:2.5;critRate:1.5;atkPct:1.5</t>
+  </si>
+  <si>
+    <t>aspdMult:8</t>
+  </si>
+  <si>
+    <t>快過風的刃，連風聲都追不上。</t>
+  </si>
+  <si>
+    <t>rw_thundergod</t>
+  </si>
+  <si>
+    <t>雷神之怒</t>
+  </si>
+  <si>
+    <t>雷鳴;血誓;鋼魄;夜幕</t>
+  </si>
+  <si>
+    <t>atkPct:1.5;elemDmgLightning:2.5;critDmg:1.5</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":15,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>神怒所至，雷霆不擇敵我之外。</t>
+  </si>
+  <si>
+    <t>rw_winterherald</t>
+  </si>
+  <si>
+    <t>凜冬使者</t>
+  </si>
+  <si>
+    <t>霜痕;霜痕;靈泉</t>
+  </si>
+  <si>
+    <t>matkPct:2;elemDmgIce:3;cdr:1</t>
+  </si>
+  <si>
+    <t>dmgCtrlPct:15</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":20,"acts":[{"act":"stun","sec":1.5}]}]</t>
+  </si>
+  <si>
+    <t>冬天來了，所過之處萬物凝結。</t>
+  </si>
+  <si>
+    <t>rw_bloodgulp</t>
+  </si>
+  <si>
+    <t>血飲者</t>
+  </si>
+  <si>
+    <t>血誓;暗影;血誓;疾影</t>
+  </si>
+  <si>
+    <t>lifesteal:3;atkPct:2;critRate:1</t>
+  </si>
+  <si>
+    <t>killHealPct:3;dmgSelfLowPct:25</t>
+  </si>
+  <si>
+    <t>越是瀕死，越是渴血。</t>
+  </si>
+  <si>
+    <t>rw_unmoving</t>
+  </si>
+  <si>
+    <t>不動山</t>
+  </si>
+  <si>
+    <t>巖心;磐石;鋼魄</t>
+  </si>
+  <si>
+    <t>hpPct:3;defPct:3;pRes:1</t>
+  </si>
+  <si>
+    <t>maxHitPct:40</t>
+  </si>
+  <si>
+    <t>任憑千鈞一擊，山自巍然。</t>
+  </si>
+  <si>
+    <t>rw_shadowstep</t>
+  </si>
+  <si>
+    <t>影步</t>
+  </si>
+  <si>
+    <t>暗影;疾影;夜幕</t>
+  </si>
+  <si>
+    <t>boots;legs</t>
+  </si>
+  <si>
+    <t>evasion:3.5;hit:2;hpPct:1.5</t>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":15,"cd":10,"acts":[{"act":"invuln","sec":1}]}]</t>
+  </si>
+  <si>
+    <t>一步踏入影中，攻擊落了空。</t>
+  </si>
+  <si>
+    <t>rw_dawncrown</t>
+  </si>
+  <si>
+    <t>旭日之冠</t>
+  </si>
+  <si>
+    <t>曙光;聖輝;靈泉</t>
+  </si>
+  <si>
+    <t>hpPct:2;mpFlat:3;resAll:1</t>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":10,"acts":[{"act":"heal","pctMax":8},{"act":"mana","pctMax":8}]}]</t>
+  </si>
+  <si>
+    <t>戴上旭日，每一刻都是黎明。</t>
+  </si>
+  <si>
+    <t>rw_poisoncloud</t>
+  </si>
+  <si>
+    <t>毒雲</t>
+  </si>
+  <si>
+    <t>毒牙;毒牙;暗影;靈泉</t>
+  </si>
+  <si>
+    <t>matkPct:2;elemDmgPoison:3;mPen:0.3</t>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":25,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison","to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>施法之後，毒霧久久不散。</t>
+  </si>
+  <si>
+    <t>rw_awakening</t>
+  </si>
+  <si>
+    <t>風語;雷鳴;疾影</t>
+  </si>
+  <si>
+    <t>gloves</t>
+  </si>
+  <si>
+    <t>aspd:3;critRate:2;atkPct:1.5</t>
+  </si>
+  <si>
+    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":3,"max":3}]}]</t>
+  </si>
+  <si>
+    <t>一聲春雷，萬蟲驚動。</t>
+  </si>
+  <si>
+    <t>rw_ironoath</t>
+  </si>
+  <si>
+    <t>重甲鐵誓</t>
+  </si>
+  <si>
+    <t>磐石;巖心;鋼魄;血誓</t>
+  </si>
+  <si>
+    <t>shoulder</t>
+  </si>
+  <si>
+    <t>hpPct:2.5;defPct:2;pRes:1</t>
+  </si>
+  <si>
+    <t>thorns:12</t>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":20,"cd":3,"acts":[{"act":"dmg","pct":100,"type":"phys","to":"attacker"}]}]</t>
+  </si>
+  <si>
+    <t>以鐵起誓，傷我者必以鐵還之。</t>
+  </si>
+  <si>
+    <t>rw_gambler</t>
+  </si>
+  <si>
+    <t>賭徒之戒</t>
+  </si>
+  <si>
+    <t>微光;疾影;夜幕;鋼魄</t>
+  </si>
+  <si>
+    <t>luck:3;critRate:2;critDmg:2.5;loot:2</t>
+  </si>
+  <si>
+    <t>runeFindPct:15</t>
+  </si>
+  <si>
+    <t>全押。贏了拿走一切，輸了也不過一場好戲。</t>
+  </si>
+  <si>
+    <t>rw_guardian</t>
+  </si>
+  <si>
+    <t>守護者之盾</t>
+  </si>
+  <si>
+    <t>磐石;鋼魄;巖心;曙光</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>blockRate:3;blockDmgRed:3;hpPct:2</t>
+  </si>
+  <si>
+    <t>[{"on":"block","chance":40,"acts":[{"act":"dmg","pct":200,"type":"phys","to":"attacker"}]}]</t>
+  </si>
+  <si>
+    <t>盾不是為了後退，是為了把力量還給對方。</t>
+  </si>
+  <si>
+    <t>rw_arcaneecho</t>
+  </si>
+  <si>
+    <t>奧術迴響</t>
+  </si>
+  <si>
+    <t>靈泉;曙光;靈泉;聖輝</t>
+  </si>
+  <si>
+    <t>focus;spellbook;orb</t>
+  </si>
+  <si>
+    <t>matkPct:3;mpFlat:3;cdr:2</t>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":20,"acts":[{"act":"cdr","sec":1.5}]}]</t>
+  </si>
+  <si>
+    <t>咒語落下之後，還在空氣裡迴盪。</t>
+  </si>
+  <si>
+    <t>rw_smith</t>
+  </si>
+  <si>
+    <t>鐵匠之魂</t>
+  </si>
+  <si>
+    <t>靈泉;鋼魄;磐石</t>
+  </si>
+  <si>
+    <t>gemEff:3;affixCap:2;enhanceSuccess:3</t>
+  </si>
+  <si>
+    <t>鎚聲不絕，鋼與靈魂同鍛。</t>
+  </si>
+  <si>
+    <t>rw_apocalypse</t>
+  </si>
+  <si>
+    <t>天啟</t>
+  </si>
+  <si>
+    <t>血誓;鋼魄;蒼穹;熔岩</t>
+  </si>
+  <si>
+    <t>atkPct:3;matkPct:3;critDmg:3;bossDmg:3</t>
+  </si>
+  <si>
+    <t>dmgPct:18;aspdMult:10</t>
+  </si>
+  <si>
+    <t>號角響起，審判降臨。</t>
+  </si>
+  <si>
+    <t>rw_soulcleaver</t>
+  </si>
+  <si>
+    <t>斷魂</t>
+  </si>
+  <si>
+    <t>鋼魄;驚蟄;嵐;厚土</t>
+  </si>
+  <si>
+    <t>atkPct:4;critDmg:4;eliteDmg:3;pPen:0.5</t>
+  </si>
+  <si>
+    <t>dmgLoHpPct:60</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":8,"acts":[{"act":"execute","hpBelow":15}]}]</t>
+  </si>
+  <si>
+    <t>一刀兩斷，魂亦分離。</t>
+  </si>
+  <si>
+    <t>rw_chainstorm</t>
+  </si>
+  <si>
+    <t>連環雷暴</t>
+  </si>
+  <si>
+    <t>雷鳴;疾影;雷鳴;烈陽</t>
+  </si>
+  <si>
+    <t>matkPct:3;elemDmgLightning:3;elemDmgWind:2;mPen:0.5</t>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":30,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]},{"on":"cast","chance":25,"acts":[{"act":"dmg","pct":100,"elem":"lightning","to":"rand","n":3}]}]</t>
+  </si>
+  <si>
+    <t>雷與風相纏，一環扣一環。</t>
+  </si>
+  <si>
+    <t>rw_timewarden</t>
+  </si>
+  <si>
+    <t>時之守望</t>
+  </si>
+  <si>
+    <t>寒月;嵐;寒月;靈泉</t>
+  </si>
+  <si>
+    <t>cdr:4;matkPct:3;mpRegen:3;hpPct:2</t>
+  </si>
+  <si>
+    <t>cdPct:20</t>
+  </si>
+  <si>
+    <t>[{"on":"kill","acts":[{"act":"cdr","sec":1}]}]</t>
+  </si>
+  <si>
+    <t>守望者拾起墜落的時間，替你多留一點。</t>
+  </si>
+  <si>
+    <t>rw_lastbreath</t>
+  </si>
+  <si>
+    <t>絕境</t>
+  </si>
+  <si>
+    <t>磐石;鋼魄;厚土;寒月</t>
+  </si>
+  <si>
+    <t>hpPct:4;defPct:3.5;mdefPct:3.5;globalDmgRed:2</t>
+  </si>
+  <si>
+    <t>[{"on":"lowhp","below":30,"cd":90,"acts":[{"act":"invuln","sec":3},{"act":"heal","pctMax":30},{"act":"cleanse"}]}]</t>
+  </si>
+  <si>
+    <t>退無可退之處，才是真正的開始。</t>
+  </si>
+  <si>
+    <t>rw_swarmhunter</t>
+  </si>
+  <si>
+    <t>群獵</t>
+  </si>
+  <si>
+    <t>疾影;驚蟄;熔岩;夜幕</t>
+  </si>
+  <si>
+    <t>aspd:2.5;atkPct:2.5;critRate:1.5;aoeDmg:2</t>
+  </si>
+  <si>
+    <t>dmgPerFoePct:5;splashPct:20</t>
+  </si>
+  <si>
+    <t>獸群越多，獵人越是興奮。</t>
+  </si>
+  <si>
+    <t>rw_assassin</t>
+  </si>
+  <si>
+    <t>影殺</t>
+  </si>
+  <si>
+    <t>暗影;夜幕;疾影;厚土</t>
+  </si>
+  <si>
+    <t>dagger1h</t>
+  </si>
+  <si>
+    <t>critRate:1.5;critDmg:2;atkPct:2;evasion:1.5</t>
+  </si>
+  <si>
+    <t>knifeShadowblade;knifeChain</t>
+  </si>
+  <si>
+    <t>dmgHiHpPct:20</t>
+  </si>
+  <si>
+    <t>刀影分裂成雙，雙影各自找到了喉嚨。</t>
+  </si>
+  <si>
+    <t>rw_manafountain</t>
+  </si>
+  <si>
+    <t>魔泉</t>
+  </si>
+  <si>
+    <t>靈泉;靈泉;寒月;蒼穹</t>
+  </si>
+  <si>
+    <t>helmet;amulet</t>
+  </si>
+  <si>
+    <t>mpFlat:4;mpRegen:4;matkPct:2.5</t>
+  </si>
+  <si>
+    <t>manaCostRedPct:40;killManaPct:3</t>
+  </si>
+  <si>
+    <t>魔力不是用完的，是流過的。</t>
+  </si>
+  <si>
+    <t>rw_thornedfury</t>
+  </si>
+  <si>
+    <t>荊棘之怒</t>
+  </si>
+  <si>
+    <t>磐石;熔岩;厚土;鋼魄</t>
+  </si>
+  <si>
+    <t>chest;shield</t>
+  </si>
+  <si>
+    <t>hpPct:3.5;defPct:3.5;pRes:2</t>
+  </si>
+  <si>
+    <t>thorns:35</t>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":25,"cd":2,"acts":[{"act":"dmg","pct":150,"type":"phys","to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>怒意生出荊棘，連空氣都帶刺。</t>
+  </si>
+  <si>
+    <t>rw_bossbane</t>
+  </si>
+  <si>
+    <t>弒王者</t>
+  </si>
+  <si>
+    <t>蒼穹;血誓;疾影;鋼魄</t>
+  </si>
+  <si>
+    <t>bossDmg:5;eliteDmg:4;atkPct:2.5;matkPct:2.5</t>
+  </si>
+  <si>
+    <t>dmgHiHpPct:40;dmgSoloPct:40</t>
+  </si>
+  <si>
+    <t>王座再高，也有人要把它拆了。</t>
+  </si>
+  <si>
+    <t>rw_vitalpact</t>
+  </si>
+  <si>
+    <t>生命契約</t>
+  </si>
+  <si>
+    <t>血誓;暗影;厚土;厚土</t>
+  </si>
+  <si>
+    <t>hpPct:4;lifesteal:4;hpRegen:4</t>
+  </si>
+  <si>
+    <t>killHealPct:6;dmgSelfFullPct:25</t>
+  </si>
+  <si>
+    <t>契約的對價是活著，且活得很好。</t>
+  </si>
+  <si>
+    <t>rw_shieldwall</t>
+  </si>
+  <si>
+    <t>護盾牆</t>
+  </si>
+  <si>
+    <t>蒼穹;磐石;蒼穹;厚土</t>
+  </si>
+  <si>
+    <t>chest;shoulder;helmet</t>
+  </si>
+  <si>
+    <t>shieldEff:5;hpPct:3;globalDmgRed:2.5</t>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":8,"acts":[{"act":"shield","pctMax":20,"sec":8}]}]</t>
+  </si>
+  <si>
+    <t>牆起，風止。</t>
+  </si>
+  <si>
+    <t>rw_elemental</t>
+  </si>
+  <si>
+    <t>元素之環</t>
+  </si>
+  <si>
+    <t>霜痕;烈陽;雷鳴;寒月</t>
+  </si>
+  <si>
+    <t>elemDmgFire:1.8;elemDmgIce:1.8;elemDmgLightning:1.8;elemDmgWind:1.8;elemDmgPoison:1.8</t>
+  </si>
+  <si>
+    <t>dmgPct:10</t>
+  </si>
+  <si>
+    <t>五元素各執一角，在指尖上取得平衡。</t>
+  </si>
+  <si>
+    <t>rw_blitz</t>
+  </si>
+  <si>
+    <t>閃擊</t>
+  </si>
+  <si>
+    <t>疾影;驚蟄;驚蟄;風語</t>
+  </si>
+  <si>
+    <t>aspd:4;critRate:3;hit:2</t>
+  </si>
+  <si>
+    <t>aspdMult:15</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","every":6,"acts":[{"act":"castRandom"}]}]</t>
+  </si>
+  <si>
+    <t>揮刀太快，連技能都被牽著走。</t>
+  </si>
+  <si>
+    <t>rw_reincarnation</t>
+  </si>
+  <si>
+    <t>命運;輪迴;永恆;創生</t>
+  </si>
+  <si>
+    <t>hpPct:4;defPct:4;mdefPct:4</t>
+  </si>
+  <si>
+    <t>reviveHpPct:60;reviveCdSec:180;reviveInvulnSec:3;reviveDmgPct:60;reviveDmgSec:10;reviveRefresh:1</t>
+  </si>
+  <si>
+    <t>死亡只是下一次輪迴的開場白。</t>
+  </si>
+  <si>
+    <t>rw_timeloop</t>
+  </si>
+  <si>
+    <t>時之沙</t>
+  </si>
+  <si>
+    <t>命運;輪迴;虛空;永恆</t>
+  </si>
+  <si>
+    <t>cdr:5;mpRegen:5;matkPct:3</t>
+  </si>
+  <si>
+    <t>cdPct:45;maxHpPct:-20</t>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":25,"acts":[{"act":"recast"}]}]</t>
+  </si>
+  <si>
+    <t>沙漏倒過來了。代價是你的生命，也在一起流。</t>
+  </si>
+  <si>
+    <t>rw_bloodmoon</t>
+  </si>
+  <si>
+    <t>血月</t>
+  </si>
+  <si>
+    <t>夜幕;熔岩;雷霆;命運</t>
+  </si>
+  <si>
+    <t>atkPct:3;matkPct:3;critDmg:3;lifesteal:2</t>
+  </si>
+  <si>
+    <t>dmgPct:60;selfDrainPct:2;killHealPct:8;maxHpPct:-30</t>
+  </si>
+  <si>
+    <t>血月當空，誰先流盡誰先倒下。</t>
+  </si>
+  <si>
+    <t>rw_arsenal</t>
+  </si>
+  <si>
+    <t>武庫</t>
+  </si>
+  <si>
+    <t>疾影;嵐;虛空;星辰</t>
+  </si>
+  <si>
+    <t>aspd:3;atkPct:3;matkPct:3</t>
+  </si>
+  <si>
+    <t>skillDmgPct:40</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","every":4,"acts":[{"act":"castRandom"}]},{"on":"cast","chance":15,"acts":[{"act":"recast"}]}]</t>
+  </si>
+  <si>
+    <t>每一次揮擊，都從武器庫裡抽出另一招。</t>
+  </si>
+  <si>
+    <t>rw_thunderemperor</t>
+  </si>
+  <si>
+    <t>雷帝</t>
+  </si>
+  <si>
+    <t>雷霆;雷鳴;虛空;創生</t>
+  </si>
+  <si>
+    <t>matkPct:3;elemDmgLightning:3.5;critRate:2</t>
+  </si>
+  <si>
+    <t>dmgCtrlPct:25</t>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":2,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"rand","n":3}]},{"on":"crit","acts":[{"act":"stun","sec":1,"to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>帝王不需親自出手，雷霆自會代勞。</t>
+  </si>
+  <si>
+    <t>rw_lonewolf</t>
+  </si>
+  <si>
+    <t>孤狼</t>
+  </si>
+  <si>
+    <t>蒼穹;熔岩;冰魄;雷霆</t>
+  </si>
+  <si>
+    <t>critDmg:3.5;atkPct:3;bossDmg:3.5</t>
+  </si>
+  <si>
+    <t>dmgSoloPct:80;dmgHiHpPct:40;cdPct:15</t>
+  </si>
+  <si>
+    <t>孤狼只獵王者。獵物以外，一概不理。</t>
+  </si>
+  <si>
+    <t>rw_starfall</t>
+  </si>
+  <si>
+    <t>星墜</t>
+  </si>
+  <si>
+    <t>虛空;冰魄;星辰;輪迴</t>
+  </si>
+  <si>
+    <t>staff2h</t>
+  </si>
+  <si>
+    <t>matkPct:3.5;elemDmgFire:2.5;elemDmgIce:2.5;mPen:0.6</t>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":150,"elem":"random","to":"rand","n":5}]}]</t>
+  </si>
+  <si>
+    <t>夜空翻面，群星墜落成雨。</t>
+  </si>
+  <si>
+    <t>rw_chaoslord</t>
+  </si>
+  <si>
+    <t>混沌之主</t>
+  </si>
+  <si>
+    <t>混沌;虛空;輪迴;永恆</t>
+  </si>
+  <si>
+    <t>resAll:3;luck:4;critRate:3</t>
+  </si>
+  <si>
+    <t>skillDmgPct:25</t>
+  </si>
+  <si>
+    <t>[{"on":"cast","acts":[{"act":"buffRandom","sec":8,"from":[{"sid":"atkUp","val":25},{"sid":"aspdUp","val":25},{"sid":"critDmgUp","val":60},{"sid":"defUp","val":40},{"sid":"evasionUp","val":30},{"sid":"allDmgUp","val":20}]}]}]</t>
+  </si>
+  <si>
+    <t>混沌不問因果，每一次施法都是一場賭局。</t>
+  </si>
+  <si>
+    <t>rw_dragonslayer</t>
+  </si>
+  <si>
+    <t>屠龍者</t>
+  </si>
+  <si>
+    <t>熔岩;星辰;永恆;混沌</t>
+  </si>
+  <si>
+    <t>atkPct:2.5;bossDmg:5;critDmg:2.5;pPen:0.8</t>
+  </si>
+  <si>
+    <t>dmgHiHpPct:50;dmgPct:25</t>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":20,"acts":[{"act":"dmg","pct":250,"type":"phys","to":"target"}]}]</t>
+  </si>
+  <si>
+    <t>巨龍的鱗片，就是為了被一劍貫穿而生。</t>
+  </si>
+  <si>
+    <t>rw_immortalbody</t>
+  </si>
+  <si>
+    <t>不朽之軀</t>
+  </si>
+  <si>
+    <t>永恆;終焉;輪迴;創生</t>
+  </si>
+  <si>
+    <t>armor</t>
+  </si>
+  <si>
+    <t>hpPct:5;globalDmgRed:3;resAll:3</t>
+  </si>
+  <si>
+    <t>maxHitPct:15;dmgPct:-20</t>
+  </si>
+  <si>
+    <t>[{"on":"lowhp","below":40,"cd":60,"acts":[{"act":"shield","pctMax":40,"sec":6},{"act":"invuln","sec":2}]}]</t>
+  </si>
+  <si>
+    <t>以出手的力量，換不會倒下的身軀。</t>
+  </si>
+  <si>
+    <t>rw_legion</t>
+  </si>
+  <si>
+    <t>萬軍</t>
+  </si>
+  <si>
+    <t>嵐;虛空;命運;永恆</t>
+  </si>
+  <si>
+    <t>greatsword2h;axe2h</t>
+  </si>
+  <si>
+    <t>atkPct:3;aspd:3;aoeDmg:2</t>
+  </si>
+  <si>
+    <t>skyrendSlash;gatheringVortex</t>
+  </si>
+  <si>
+    <t>splashPct:50;dmgPerFoePct:6</t>
+  </si>
+  <si>
+    <t>一人成軍，一劍橫掃萬軍。</t>
+  </si>
+  <si>
+    <t>rw_bladedancer</t>
+  </si>
+  <si>
+    <t>劍舞者</t>
+  </si>
+  <si>
+    <t>驚蟄;嵐;熔岩;冰魄</t>
+  </si>
+  <si>
+    <t>aspd:3;critRate:3;atkPct:3</t>
+  </si>
+  <si>
+    <t>danceTwinBlades;danceThousandCuts;danceUnyielding</t>
+  </si>
+  <si>
+    <t>舞到最後一步時，才知道這是一場不能停的舞。</t>
+  </si>
+  <si>
+    <t>rw_voidwalker</t>
+  </si>
+  <si>
+    <t>虛空行者</t>
+  </si>
+  <si>
+    <t>虛空;星辰;命運;輪迴</t>
+  </si>
+  <si>
+    <t>evasion:6;hit:4;hpPct:3</t>
+  </si>
+  <si>
+    <t>dmgPct:25</t>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":30,"cd":4,"acts":[{"act":"invuln","sec":1.5},{"act":"dmg","pct":150,"elem":"dark","to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>走進虛空的人，被攻擊的永遠是上一個位置。</t>
+  </si>
+  <si>
+    <t>rw_genesis</t>
+  </si>
+  <si>
+    <t>創世紀</t>
+  </si>
+  <si>
+    <t>永恆;混沌;創生;終焉</t>
+  </si>
+  <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>atkPct:3;matkPct:3;elemDmgFire:1.5;elemDmgIce:1.5;elemDmgLightning:1.5;elemDmgPoison:1.5;elemDmgLight:1.5;elemDmgDark:1.5;elemDmgEarth:1.5;elemDmgWind:1.5</t>
+  </si>
+  <si>
+    <t>dmgPct:50;cdPct:20;aspdMult:15;manaCostRedPct:30</t>
+  </si>
+  <si>
+    <t>最後一顆符文落下時，世界從頭開始。</t>
+  </si>
+  <si>
+    <t>符文表（Runes）欄位與規則說明</t>
+  </si>
+  <si>
+    <t>本頁為說明頁，程式不讀取；第一頁「Runes」才是資料來源。改完存檔（Ctrl+S）後雙擊「套用參數.bat」套用，本機開著的遊戲約 2 秒自動重載。</t>
+  </si>
+  <si>
+    <t>套用時會檢查：詞條鍵、符文名稱、適用裝備、效果鍵、事件觸發 JSON、孔數上限等；任何一格打錯都會整次中止並指出是哪一列哪一格，遊戲程式不會被改到。</t>
+  </si>
+  <si>
+    <t>── 三種列（「類型」欄；用篩選看各自的那一段）──</t>
+  </si>
+  <si>
+    <t>設定：全域設定。id 是鑰匙欄，不可改名；數值填在「設定值」。</t>
+  </si>
+  <si>
+    <t>符文：33 種符文。列的先後順序＝階數（第 1 列＝第 1 階），id 依序為 r01～r33，不可重排、不可增刪。</t>
+  </si>
+  <si>
+    <t>符文之語：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
+  </si>
+  <si>
+    <t>── 設定列 ──</t>
+  </si>
+  <si>
+    <t>maxSlots：符文孔數上限，同時也是符文之語最多能有幾顆符文（設計上限 4）。</t>
+  </si>
+  <si>
+    <t>slots_&lt;稀有度&gt;：該稀有度裝備的符文孔數；0～上限，不可隨稀有度變少，最高稀有度必須等於上限。符文孔取代原本的附魔欄位，與寶石鑲孔分開，雙手武器沒有額外加成。</t>
+  </si>
+  <si>
+    <t>composeCount／composeMaxTier／dismantleYield：合成（同種幾顆→下一階 1 顆）、最高合成階（更高階只能掉落）、拆解產出（必須小於合成所需顆數；預設 1＝只能降階頂替、不會變多）。</t>
+  </si>
+  <si>
+    <t>statScale：全域屬性縮放，符文與符文之語的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
+  </si>
+  <si>
+    <t>drop_*：掉落。basePct 野外每次擊殺的基礎掉落率(%)（再乘掉寶率與地圖獎勵倍率）、towerBossPct 封魔塔通關的基礎掉落率(%)、tierSpread 階數稀有度（相鄰兩階的機率比，0~1，越小高階越稀有）、progressPerTier 每 +1 進度對應的最高掉落階增量。</t>
+  </si>
+  <si>
+    <t>　　取得難度只由「配方最高階那顆符文」決定；各級距的最高階區間與估算小時數見 docs/RUNEWORD_DESIGN.md，估算用 node tools/rw_econ_probe.cjs。</t>
+  </si>
+  <si>
+    <t>── 符文列 ──</t>
+  </si>
+  <si>
+    <t>武器詞條／武器倍率：符文鑲在主手或雙手武器時給的屬性（詞條鍵見 Equipment_Affix 表的詞條池）。倍率＝這件裝備上「一條滿刻度中位數詞條」的幾倍；數值隨裝備等級、稀有度、強化成長，與詞條同一套算法。</t>
+  </si>
+  <si>
+    <t>　　是「額外附加」的一條屬性，直接加進角色該屬性的加總，不是乘在裝備原有詞條上，也不是乘整個角色的數值。</t>
+  </si>
+  <si>
+    <t>防具詞條／防具倍率：符文鑲在防具、飾品、副手時給的屬性，規則同上。</t>
+  </si>
+  <si>
+    <t>單獨鑲著就有效；組成符文之語時，符文之語的屬性與能力另外並存。</t>
+  </si>
+  <si>
+    <t>── 符文之語列 ──</t>
+  </si>
+  <si>
+    <t>級距：1 普通／2 強力／3 非常強力／4 極度特殊。只影響圖鑑的分組與顏色，不影響數值（強度要自己調屬性加成與效果）。</t>
+  </si>
+  <si>
+    <t>配方：符文名稱依序用「;」分隔（也可填 id）。至少 2 顆、最多＝符文孔數上限；順序不同就是不同配方，不得與別的符文之語完全相同。成形條件＝依序放進連續的符文孔，且裝備類型符合。</t>
+  </si>
+  <si>
+    <t>適用裝備：用「;」分隔，多項為「或」。標記：any 任意、armor 八件防具、jewelry 戒指＋項鍊、mainHand 主手與雙手武器、twoHand 雙手武器、oneHand 單手武器、offHand 副手、melee 近戰武器、caster 施法類武器／副手；</t>
+  </si>
+  <si>
+    <t>　　也可填裝備欄位（weapon、helmet、shoulder、chest、belt、gloves、wrist、legs、boots、ring、amulet）或武器類型鍵（sword1h、dagger1h、staff2h、shield、focus… 見 data.js WEAPON_TYPES）。</t>
+  </si>
+  <si>
+    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率意義同符文列；負數＝代價。同一組符文之語穿在多件裝備上時，各件的屬性都計。</t>
+  </si>
+  <si>
+    <t>被動：「鍵:數值」用「;」分隔，鍵限 thorns（反震）、smite（天罰）、undying（不朽）、sunder（破甲）、trueDmg（真傷）、omniDrain（萬象汲取）、soulEater、annihilate、sanctuary、godWrath；並入既有被動。</t>
+  </si>
+  <si>
+    <t>傳奇特效：借用既有傳奇特效（Equipment_Affix 表傳奇特效池的 id，用「;」分隔），不受該特效原本的武器類型限制，但仍需要配戴對應技能才有感。</t>
+  </si>
+  <si>
+    <t>靜態效果：「鍵:數值」用「;」分隔，數字固定、不隨稀有度成長。可用鍵：</t>
+  </si>
+  <si>
+    <t>　　dmgPct 造成傷害%、skillDmgPct 技能傷害%、basicDmgPct 普攻傷害%、aspdMult 攻速額外乘算%、cdPct 技能冷卻-%（乘算）、manaCostRedPct 法力消耗-%、maxHitPct 單次受傷上限（最大生命%）、maxHpPct 最大生命%（乘算，負數＝代價）、</t>
+  </si>
+  <si>
+    <t>　　dmgHiHpPct 對高血(&gt;70%)敵人增傷%、dmgLoHpPct 對低血(&lt;30%)敵人增傷%、dmgSoloPct 只有一隻敵人時增傷%、dmgPerFoePct 每多一隻敵人增傷%、dmgSelfFullPct 自身高血增傷%、dmgSelfLowPct 自身低血增傷%、dmgCtrlPct 對被控場敵人增傷%、</t>
+  </si>
+  <si>
+    <t>　　killHealPct 擊殺回血%、killManaPct 擊殺回魔%、runeFindPct 符文掉落率+%、selfDrainPct 每秒損失最大生命%（代價）、splashPct 普攻擴散給其他敵人%、</t>
+  </si>
+  <si>
+    <t>　　reviveHpPct／reviveCdSec／reviveInvulnSec／reviveDmgPct／reviveDmgSec／reviveRefresh 死亡復活（生命%、冷卻秒、無敵秒、之後增傷%與秒數、是否重置技能冷卻）。</t>
+  </si>
+  <si>
+    <t>事件觸發(JSON)：JSON 陣列，每條 { "on": 觸發, "chance": 機率%, "every": 秒（tick）或次數, "cd": 內建冷卻秒, "below": 生命%（lowhp）, "acts": [動作…] }。</t>
+  </si>
+  <si>
+    <t>　　觸發 on：hit 普攻命中、crit 普攻暴擊、kill 擊殺、hurt 受傷、block 格擋、cast 施放技能、tick 每 every 秒、lowhp 生命低於 below%。</t>
+  </si>
+  <si>
+    <t>　　動作 act：dmg {pct, elem?, type?(magic/phys), to?(target/all/rand/attacker), n?}、heal {pctMax}、shield {pctMax, sec}、mana {pctMax}、buff {sid, val, sec, max?}、buffRandom {sec, from:[{sid,val}]}、stun {sec, to?}、slow {sec, to?}、</t>
+  </si>
+  <si>
+    <t>　　dot {pct, sec, name(poison/burn/bleed/corrode), to?}、cdr {sec}、refresh {n?}、recast、castRandom、invuln {sec}、execute {hpBelow}、cleanse。elem 可填 fire/ice/lightning/poison/light/dark/earth/wind/random。</t>
+  </si>
+  <si>
+    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。效果說明文字由資料自動產生，不需要另外寫。</t>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>微光</t>
-  </si>
-  <si>
-    <t>hit</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>evasion</t>
-  </si>
-  <si>
-    <t>r02</t>
-  </si>
-  <si>
-    <t>餘燼</t>
-  </si>
-  <si>
-    <t>atkFlat</t>
-  </si>
-  <si>
-    <t>defFlat</t>
-  </si>
-  <si>
-    <t>r03</t>
-  </si>
-  <si>
-    <t>霜痕</t>
-  </si>
-  <si>
-    <t>elemDmgIce</t>
-  </si>
-  <si>
-    <t>resIce</t>
-  </si>
-  <si>
-    <t>r04</t>
-  </si>
-  <si>
-    <t>風語</t>
-  </si>
-  <si>
-    <t>aspd</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>r05</t>
-  </si>
-  <si>
-    <t>巖心</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>pPen</t>
-  </si>
-  <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>defPct</t>
-  </si>
-  <si>
-    <t>r06</t>
-  </si>
-  <si>
-    <t>毒牙</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>elemDmgPoison</t>
-  </si>
-  <si>
-    <t>resPoison</t>
-  </si>
-  <si>
-    <t>r07</t>
-  </si>
-  <si>
-    <t>雷鳴</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>elemDmgLightning</t>
-  </si>
-  <si>
-    <t>resLightning</t>
-  </si>
-  <si>
-    <t>r08</t>
-  </si>
-  <si>
-    <t>暗影</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>lifesteal</t>
-  </si>
-  <si>
-    <t>hpRegen</t>
-  </si>
-  <si>
-    <t>r09</t>
-  </si>
-  <si>
-    <t>聖輝</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>elemDmgLight</t>
-  </si>
-  <si>
-    <t>resLight</t>
-  </si>
-  <si>
-    <t>r10</t>
-  </si>
-  <si>
-    <t>血誓</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>atkPct</t>
-  </si>
-  <si>
-    <t>hpPct</t>
-  </si>
-  <si>
-    <t>r11</t>
-  </si>
-  <si>
-    <t>鋼魄</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>critDmg</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>pRes</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>r12</t>
-  </si>
-  <si>
-    <t>靈泉</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>matkPct</t>
-  </si>
-  <si>
-    <t>mpFlat</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>r13</t>
-  </si>
-  <si>
-    <t>疾影</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>critRate</t>
-  </si>
-  <si>
-    <t>r14</t>
-  </si>
-  <si>
-    <t>磐石</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>eliteDmg</t>
-  </si>
-  <si>
-    <t>blockRate</t>
-  </si>
-  <si>
-    <t>r15</t>
-  </si>
-  <si>
-    <t>曙光</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>mPen</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>mRes</t>
-  </si>
-  <si>
-    <t>r16</t>
-  </si>
-  <si>
-    <t>夜幕</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>elemDmgDark</t>
-  </si>
-  <si>
-    <t>resDark</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>r17</t>
-  </si>
-  <si>
-    <t>烈陽</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>elemDmgFire</t>
-  </si>
-  <si>
-    <t>resFire</t>
-  </si>
-  <si>
-    <t>r18</t>
-  </si>
-  <si>
-    <t>寒月</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>cdr</t>
-  </si>
-  <si>
-    <t>mdefPct</t>
-  </si>
-  <si>
-    <t>r19</t>
-  </si>
-  <si>
-    <t>驚蟄</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>tenacity</t>
-  </si>
-  <si>
-    <t>r20</t>
-  </si>
-  <si>
-    <t>嵐</t>
-  </si>
-  <si>
-    <t>elemDmgWind</t>
-  </si>
-  <si>
-    <t>resWind</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>r21</t>
-  </si>
-  <si>
-    <t>蒼穹</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>bossDmg</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>shieldEff</t>
-  </si>
-  <si>
-    <t>r22</t>
-  </si>
-  <si>
-    <t>厚土</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>elemDmgEarth</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>r23</t>
-  </si>
-  <si>
-    <t>熔岩</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>globalDmgRed</t>
-  </si>
-  <si>
-    <t>r24</t>
-  </si>
-  <si>
-    <t>冰魄</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>resAll</t>
-  </si>
-  <si>
-    <t>r25</t>
-  </si>
-  <si>
-    <t>雷霆</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>blockDmgRed</t>
-  </si>
-  <si>
-    <t>r26</t>
-  </si>
-  <si>
-    <t>虛空</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>aoeDmg</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>ccRed</t>
-  </si>
-  <si>
-    <t>r27</t>
-  </si>
-  <si>
-    <t>星辰</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>luck</t>
-  </si>
-  <si>
-    <t>r28</t>
-  </si>
-  <si>
-    <t>命運</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>normalDmg</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
-    <t>r29</t>
-  </si>
-  <si>
-    <t>輪迴</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>r30</t>
-  </si>
-  <si>
-    <t>永恆</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1.9</t>
-  </si>
-  <si>
-    <t>r31</t>
-  </si>
-  <si>
-    <t>混沌</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>r32</t>
-  </si>
-  <si>
-    <t>創生</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2.2</t>
-  </si>
-  <si>
-    <t>r33</t>
-  </si>
-  <si>
-    <t>終焉</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>符文之語</t>
-  </si>
-  <si>
-    <t>rw_firstcry</t>
-  </si>
-  <si>
-    <t>初啼</t>
-  </si>
-  <si>
-    <t>微光;餘燼</t>
-  </si>
-  <si>
-    <t>mainHand</t>
-  </si>
-  <si>
-    <t>atkFlat:2;matkFlat:2;hit:1</t>
-  </si>
-  <si>
-    <t>第一聲啼鳴，劃破長夜的寂靜。</t>
-  </si>
-  <si>
-    <t>rw_nightwatch</t>
-  </si>
-  <si>
-    <t>守夜</t>
-  </si>
-  <si>
-    <t>餘燼;巖心</t>
-  </si>
-  <si>
-    <t>chest</t>
-  </si>
-  <si>
-    <t>defFlat:2.5;hpFlat:2.5;hpRegen:1</t>
-  </si>
-  <si>
-    <t>燈火不滅，守夜人便不眠。</t>
-  </si>
-  <si>
-    <t>rw_frostwhisper</t>
-  </si>
-  <si>
-    <t>霜語</t>
-  </si>
-  <si>
-    <t>霜痕;風語</t>
-  </si>
-  <si>
-    <t>caster</t>
-  </si>
-  <si>
-    <t>matkFlat:2.5;elemDmgIce:1.5</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":10,"acts":[{"act":"slow","sec":2}]}]</t>
-  </si>
-  <si>
-    <t>寒風低語，敵人的腳步便慢了下來。</t>
-  </si>
-  <si>
-    <t>rw_windwalk</t>
-  </si>
-  <si>
-    <t>行雲</t>
-  </si>
-  <si>
-    <t>風語;微光;暗影</t>
-  </si>
-  <si>
-    <t>boots</t>
-  </si>
-  <si>
-    <t>evasion:2;hpFlat:2;hit:1</t>
-  </si>
-  <si>
-    <t>步履如雲，不留痕跡。</t>
-  </si>
-  <si>
-    <t>rw_stoneskin</t>
-  </si>
-  <si>
-    <t>石膚</t>
-  </si>
-  <si>
-    <t>巖心;霜痕</t>
-  </si>
-  <si>
-    <t>shoulder;legs</t>
-  </si>
-  <si>
-    <t>defPct:1.5;hpPct:1.2;pRes:0.8</t>
-  </si>
-  <si>
-    <t>thorns:3</t>
-  </si>
-  <si>
-    <t>皮膚堅如岩層，觸碰者必受其傷。</t>
-  </si>
-  <si>
-    <t>rw_viperkiss</t>
-  </si>
-  <si>
-    <t>蛇吻</t>
-  </si>
-  <si>
-    <t>毒牙;暗影</t>
-  </si>
-  <si>
-    <t>sword1h;dagger1h;magicSword1h</t>
-  </si>
-  <si>
-    <t>atkPct:1.2;elemDmgPoison:1.5;critRate:1</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":15,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison"}]}]</t>
-  </si>
-  <si>
-    <t>毒蛇的一吻，慢慢收走對手的生命。</t>
-  </si>
-  <si>
-    <t>rw_minorthunder</t>
-  </si>
-  <si>
-    <t>輕雷</t>
-  </si>
-  <si>
-    <t>雷鳴;風語</t>
-  </si>
-  <si>
-    <t>oneHand</t>
-  </si>
-  <si>
-    <t>matkPct:1.5;elemDmgLightning:2</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":90,"elem":"lightning","to":"target"}]}]</t>
-  </si>
-  <si>
-    <t>一聲輕雷，落在不經意的地方。</t>
-  </si>
-  <si>
-    <t>rw_lightguard</t>
-  </si>
-  <si>
-    <t>聖光之守</t>
-  </si>
-  <si>
-    <t>微光;聖輝</t>
-  </si>
-  <si>
-    <t>helmet</t>
-  </si>
-  <si>
-    <t>mpFlat:2;resLight:1.5;hpPct:1</t>
-  </si>
-  <si>
-    <t>killManaPct:1</t>
-  </si>
-  <si>
-    <t>以聖光為冠，心神澄明。</t>
-  </si>
-  <si>
-    <t>rw_bloodring</t>
-  </si>
-  <si>
-    <t>血誓之環</t>
-  </si>
-  <si>
-    <t>血誓;暗影</t>
-  </si>
-  <si>
-    <t>ring</t>
-  </si>
-  <si>
-    <t>lifesteal:2;atkPct:1;hit:1</t>
-  </si>
-  <si>
-    <t>killHealPct:1</t>
-  </si>
-  <si>
-    <t>以血起誓，生者共飲。</t>
-  </si>
-  <si>
-    <t>rw_steelheart</t>
-  </si>
-  <si>
-    <t>鋼心</t>
-  </si>
-  <si>
-    <t>巖心;血誓</t>
-  </si>
-  <si>
-    <t>belt</t>
-  </si>
-  <si>
-    <t>hpPct:1.5;defPct:1.5;tenacity:1</t>
-  </si>
-  <si>
-    <t>腰繫鋼索，心不動搖。</t>
-  </si>
-  <si>
-    <t>rw_springflow</t>
-  </si>
-  <si>
-    <t>泉湧</t>
-  </si>
-  <si>
-    <t>微光;餘燼;暗影</t>
-  </si>
-  <si>
-    <t>amulet</t>
-  </si>
-  <si>
-    <t>mpRegen:2;hpRegen:2;mpFlat:1.5</t>
-  </si>
-  <si>
-    <t>killManaPct:2</t>
-  </si>
-  <si>
-    <t>源源不絕，如山間清泉。</t>
-  </si>
-  <si>
-    <t>rw_scavenger</t>
-  </si>
-  <si>
-    <t>拾荒者</t>
-  </si>
-  <si>
-    <t>微光;風語</t>
-  </si>
-  <si>
-    <t>jewelry</t>
-  </si>
-  <si>
-    <t>goldBonus:2;xpBonus:1.5;loot:1.2</t>
-  </si>
-  <si>
-    <t>runeFindPct:8</t>
-  </si>
-  <si>
-    <t>連廢墟裡的一粒塵埃，也要翻過三遍。</t>
-  </si>
-  <si>
-    <t>rw_breaker</t>
-  </si>
-  <si>
-    <t>破軍</t>
-  </si>
-  <si>
-    <t>餘燼;血誓;巖心</t>
-  </si>
-  <si>
-    <t>twoHand</t>
-  </si>
-  <si>
-    <t>atkPct:1.2;critDmg:1.2;pPen:0.2</t>
-  </si>
-  <si>
-    <t>重兵一落，軍陣自潰。</t>
-  </si>
-  <si>
-    <t>rw_burnstar</t>
-  </si>
-  <si>
-    <t>燃星</t>
-  </si>
-  <si>
-    <t>餘燼;聖輝</t>
-  </si>
-  <si>
-    <t>matkPct:1.5;elemDmgFire:1.5;mpFlat:1.5</t>
-  </si>
-  <si>
-    <t>[{"on":"cast","chance":15,"acts":[{"act":"mana","pctMax":12}]}]</t>
-  </si>
-  <si>
-    <t>星火燎原，施法者的靈感湧現。</t>
-  </si>
-  <si>
-    <t>rw_galeblade</t>
-  </si>
-  <si>
-    <t>疾風烈刃</t>
-  </si>
-  <si>
-    <t>疾影;風語;雷鳴;磐石</t>
-  </si>
-  <si>
-    <t>aspd:2.5;critRate:1.5;atkPct:1.5</t>
-  </si>
-  <si>
-    <t>aspdMult:8</t>
-  </si>
-  <si>
-    <t>快過風的刃，連風聲都追不上。</t>
-  </si>
-  <si>
-    <t>rw_thundergod</t>
-  </si>
-  <si>
-    <t>雷神之怒</t>
-  </si>
-  <si>
-    <t>雷鳴;血誓;鋼魄;夜幕</t>
-  </si>
-  <si>
-    <t>atkPct:1.5;elemDmgLightning:2.5;critDmg:1.5</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":15,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]}]</t>
-  </si>
-  <si>
-    <t>神怒所至，雷霆不擇敵我之外。</t>
-  </si>
-  <si>
-    <t>rw_winterherald</t>
-  </si>
-  <si>
-    <t>凜冬使者</t>
-  </si>
-  <si>
-    <t>霜痕;霜痕;靈泉</t>
-  </si>
-  <si>
-    <t>matkPct:2;elemDmgIce:3;cdr:1</t>
-  </si>
-  <si>
-    <t>dmgCtrlPct:15</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":20,"acts":[{"act":"stun","sec":1.5}]}]</t>
-  </si>
-  <si>
-    <t>冬天來了，所過之處萬物凝結。</t>
-  </si>
-  <si>
-    <t>rw_bloodgulp</t>
-  </si>
-  <si>
-    <t>血飲者</t>
-  </si>
-  <si>
-    <t>血誓;暗影;血誓;疾影</t>
-  </si>
-  <si>
-    <t>lifesteal:3;atkPct:2;critRate:1</t>
-  </si>
-  <si>
-    <t>killHealPct:3;dmgSelfLowPct:25</t>
-  </si>
-  <si>
-    <t>越是瀕死，越是渴血。</t>
-  </si>
-  <si>
-    <t>rw_unmoving</t>
-  </si>
-  <si>
-    <t>不動山</t>
-  </si>
-  <si>
-    <t>巖心;磐石;鋼魄</t>
-  </si>
-  <si>
-    <t>hpPct:3;defPct:3;pRes:1</t>
-  </si>
-  <si>
-    <t>maxHitPct:40</t>
-  </si>
-  <si>
-    <t>任憑千鈞一擊，山自巍然。</t>
-  </si>
-  <si>
-    <t>rw_shadowstep</t>
-  </si>
-  <si>
-    <t>影步</t>
-  </si>
-  <si>
-    <t>暗影;疾影;夜幕</t>
-  </si>
-  <si>
-    <t>boots;legs</t>
-  </si>
-  <si>
-    <t>evasion:3.5;hit:2;hpPct:1.5</t>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":15,"cd":10,"acts":[{"act":"invuln","sec":1}]}]</t>
-  </si>
-  <si>
-    <t>一步踏入影中，攻擊落了空。</t>
-  </si>
-  <si>
-    <t>rw_dawncrown</t>
-  </si>
-  <si>
-    <t>旭日之冠</t>
-  </si>
-  <si>
-    <t>曙光;聖輝;靈泉</t>
-  </si>
-  <si>
-    <t>hpPct:2;mpFlat:3;resAll:1</t>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":10,"acts":[{"act":"heal","pctMax":8},{"act":"mana","pctMax":8}]}]</t>
-  </si>
-  <si>
-    <t>戴上旭日，每一刻都是黎明。</t>
-  </si>
-  <si>
-    <t>rw_poisoncloud</t>
-  </si>
-  <si>
-    <t>毒雲</t>
-  </si>
-  <si>
-    <t>毒牙;毒牙;暗影;靈泉</t>
-  </si>
-  <si>
-    <t>matkPct:2;elemDmgPoison:3;mPen:0.3</t>
-  </si>
-  <si>
-    <t>[{"on":"cast","chance":25,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison","to":"all"}]}]</t>
-  </si>
-  <si>
-    <t>施法之後，毒霧久久不散。</t>
-  </si>
-  <si>
-    <t>rw_awakening</t>
-  </si>
-  <si>
-    <t>風語;雷鳴;疾影</t>
-  </si>
-  <si>
-    <t>gloves</t>
-  </si>
-  <si>
-    <t>aspd:3;critRate:2;atkPct:1.5</t>
-  </si>
-  <si>
-    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":3,"max":3}]}]</t>
-  </si>
-  <si>
-    <t>一聲春雷，萬蟲驚動。</t>
-  </si>
-  <si>
-    <t>rw_ironoath</t>
-  </si>
-  <si>
-    <t>重甲鐵誓</t>
-  </si>
-  <si>
-    <t>磐石;巖心;鋼魄;血誓</t>
-  </si>
-  <si>
-    <t>shoulder</t>
-  </si>
-  <si>
-    <t>hpPct:2.5;defPct:2;pRes:1</t>
-  </si>
-  <si>
-    <t>thorns:12</t>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":20,"cd":3,"acts":[{"act":"dmg","pct":100,"type":"phys","to":"attacker"}]}]</t>
-  </si>
-  <si>
-    <t>以鐵起誓，傷我者必以鐵還之。</t>
-  </si>
-  <si>
-    <t>rw_gambler</t>
-  </si>
-  <si>
-    <t>賭徒之戒</t>
-  </si>
-  <si>
-    <t>微光;疾影;夜幕;鋼魄</t>
-  </si>
-  <si>
-    <t>luck:3;critRate:2;critDmg:2.5;loot:2</t>
-  </si>
-  <si>
-    <t>runeFindPct:15</t>
-  </si>
-  <si>
-    <t>全押。贏了拿走一切，輸了也不過一場好戲。</t>
-  </si>
-  <si>
-    <t>rw_guardian</t>
-  </si>
-  <si>
-    <t>守護者之盾</t>
-  </si>
-  <si>
-    <t>磐石;鋼魄;巖心;曙光</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>blockRate:3;blockDmgRed:3;hpPct:2</t>
-  </si>
-  <si>
-    <t>[{"on":"block","chance":40,"acts":[{"act":"dmg","pct":200,"type":"phys","to":"attacker"}]}]</t>
-  </si>
-  <si>
-    <t>盾不是為了後退，是為了把力量還給對方。</t>
-  </si>
-  <si>
-    <t>rw_arcaneecho</t>
-  </si>
-  <si>
-    <t>奧術迴響</t>
-  </si>
-  <si>
-    <t>靈泉;曙光;靈泉;聖輝</t>
-  </si>
-  <si>
-    <t>focus;spellbook;orb</t>
-  </si>
-  <si>
-    <t>matkPct:3;mpFlat:3;cdr:2</t>
-  </si>
-  <si>
-    <t>[{"on":"cast","chance":20,"acts":[{"act":"cdr","sec":1.5}]}]</t>
-  </si>
-  <si>
-    <t>咒語落下之後，還在空氣裡迴盪。</t>
-  </si>
-  <si>
-    <t>rw_smith</t>
-  </si>
-  <si>
-    <t>鐵匠之魂</t>
-  </si>
-  <si>
-    <t>靈泉;鋼魄;磐石</t>
-  </si>
-  <si>
-    <t>gemEff:3;affixCap:2;enhanceSuccess:3</t>
-  </si>
-  <si>
-    <t>鎚聲不絕，鋼與靈魂同鍛。</t>
-  </si>
-  <si>
-    <t>rw_apocalypse</t>
-  </si>
-  <si>
-    <t>天啟</t>
-  </si>
-  <si>
-    <t>血誓;鋼魄;蒼穹;熔岩</t>
-  </si>
-  <si>
-    <t>atkPct:3;matkPct:3;critDmg:3;bossDmg:3</t>
-  </si>
-  <si>
-    <t>dmgPct:18;aspdMult:10</t>
-  </si>
-  <si>
-    <t>號角響起，審判降臨。</t>
-  </si>
-  <si>
-    <t>rw_soulcleaver</t>
-  </si>
-  <si>
-    <t>斷魂</t>
-  </si>
-  <si>
-    <t>鋼魄;驚蟄;嵐;厚土</t>
-  </si>
-  <si>
-    <t>atkPct:4;critDmg:4;eliteDmg:3;pPen:0.5</t>
-  </si>
-  <si>
-    <t>dmgLoHpPct:60</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":8,"acts":[{"act":"execute","hpBelow":15}]}]</t>
-  </si>
-  <si>
-    <t>一刀兩斷，魂亦分離。</t>
-  </si>
-  <si>
-    <t>rw_chainstorm</t>
-  </si>
-  <si>
-    <t>連環雷暴</t>
-  </si>
-  <si>
-    <t>雷鳴;疾影;雷鳴;烈陽</t>
-  </si>
-  <si>
-    <t>matkPct:3;elemDmgLightning:3;elemDmgWind:2;mPen:0.5</t>
-  </si>
-  <si>
-    <t>[{"on":"crit","chance":30,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]},{"on":"cast","chance":25,"acts":[{"act":"dmg","pct":100,"elem":"lightning","to":"rand","n":3}]}]</t>
-  </si>
-  <si>
-    <t>雷與風相纏，一環扣一環。</t>
-  </si>
-  <si>
-    <t>rw_timewarden</t>
-  </si>
-  <si>
-    <t>時之守望</t>
-  </si>
-  <si>
-    <t>寒月;嵐;寒月;靈泉</t>
-  </si>
-  <si>
-    <t>cdr:4;matkPct:3;mpRegen:3;hpPct:2</t>
-  </si>
-  <si>
-    <t>cdPct:20</t>
-  </si>
-  <si>
-    <t>[{"on":"kill","acts":[{"act":"cdr","sec":1}]}]</t>
-  </si>
-  <si>
-    <t>守望者拾起墜落的時間，替你多留一點。</t>
-  </si>
-  <si>
-    <t>rw_lastbreath</t>
-  </si>
-  <si>
-    <t>絕境</t>
-  </si>
-  <si>
-    <t>磐石;鋼魄;厚土;寒月</t>
-  </si>
-  <si>
-    <t>hpPct:4;defPct:3.5;mdefPct:3.5;globalDmgRed:2</t>
-  </si>
-  <si>
-    <t>[{"on":"lowhp","below":30,"cd":90,"acts":[{"act":"invuln","sec":3},{"act":"heal","pctMax":30},{"act":"cleanse"}]}]</t>
-  </si>
-  <si>
-    <t>退無可退之處，才是真正的開始。</t>
-  </si>
-  <si>
-    <t>rw_swarmhunter</t>
-  </si>
-  <si>
-    <t>群獵</t>
-  </si>
-  <si>
-    <t>疾影;驚蟄;熔岩;夜幕</t>
-  </si>
-  <si>
-    <t>aspd:2.5;atkPct:2.5;critRate:1.5;aoeDmg:2</t>
-  </si>
-  <si>
-    <t>dmgPerFoePct:5;splashPct:20</t>
-  </si>
-  <si>
-    <t>獸群越多，獵人越是興奮。</t>
-  </si>
-  <si>
-    <t>rw_assassin</t>
-  </si>
-  <si>
-    <t>影殺</t>
-  </si>
-  <si>
-    <t>暗影;夜幕;疾影;厚土</t>
-  </si>
-  <si>
-    <t>dagger1h</t>
-  </si>
-  <si>
-    <t>critRate:1.5;critDmg:2;atkPct:2;evasion:1.5</t>
-  </si>
-  <si>
-    <t>knifeShadowblade;knifeChain</t>
-  </si>
-  <si>
-    <t>dmgHiHpPct:20</t>
-  </si>
-  <si>
-    <t>刀影分裂成雙，雙影各自找到了喉嚨。</t>
-  </si>
-  <si>
-    <t>rw_manafountain</t>
-  </si>
-  <si>
-    <t>魔泉</t>
-  </si>
-  <si>
-    <t>靈泉;靈泉;寒月;蒼穹</t>
-  </si>
-  <si>
-    <t>helmet;amulet</t>
-  </si>
-  <si>
-    <t>mpFlat:4;mpRegen:4;matkPct:2.5</t>
-  </si>
-  <si>
-    <t>manaCostRedPct:40;killManaPct:3</t>
-  </si>
-  <si>
-    <t>魔力不是用完的，是流過的。</t>
-  </si>
-  <si>
-    <t>rw_thornedfury</t>
-  </si>
-  <si>
-    <t>荊棘之怒</t>
-  </si>
-  <si>
-    <t>磐石;熔岩;厚土;鋼魄</t>
-  </si>
-  <si>
-    <t>chest;shield</t>
-  </si>
-  <si>
-    <t>hpPct:3.5;defPct:3.5;pRes:2</t>
-  </si>
-  <si>
-    <t>thorns:35</t>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":25,"cd":2,"acts":[{"act":"dmg","pct":150,"type":"phys","to":"all"}]}]</t>
-  </si>
-  <si>
-    <t>怒意生出荊棘，連空氣都帶刺。</t>
-  </si>
-  <si>
-    <t>rw_bossbane</t>
-  </si>
-  <si>
-    <t>弒王者</t>
-  </si>
-  <si>
-    <t>蒼穹;血誓;疾影;鋼魄</t>
-  </si>
-  <si>
-    <t>bossDmg:5;eliteDmg:4;atkPct:2.5;matkPct:2.5</t>
-  </si>
-  <si>
-    <t>dmgHiHpPct:40;dmgSoloPct:40</t>
-  </si>
-  <si>
-    <t>王座再高，也有人要把它拆了。</t>
-  </si>
-  <si>
-    <t>rw_vitalpact</t>
-  </si>
-  <si>
-    <t>生命契約</t>
-  </si>
-  <si>
-    <t>血誓;暗影;厚土;厚土</t>
-  </si>
-  <si>
-    <t>hpPct:4;lifesteal:4;hpRegen:4</t>
-  </si>
-  <si>
-    <t>killHealPct:6;dmgSelfFullPct:25</t>
-  </si>
-  <si>
-    <t>契約的對價是活著，且活得很好。</t>
-  </si>
-  <si>
-    <t>rw_shieldwall</t>
-  </si>
-  <si>
-    <t>護盾牆</t>
-  </si>
-  <si>
-    <t>蒼穹;磐石;蒼穹;厚土</t>
-  </si>
-  <si>
-    <t>chest;shoulder;helmet</t>
-  </si>
-  <si>
-    <t>shieldEff:5;hpPct:3;globalDmgRed:2.5</t>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":8,"acts":[{"act":"shield","pctMax":20,"sec":8}]}]</t>
-  </si>
-  <si>
-    <t>牆起，風止。</t>
-  </si>
-  <si>
-    <t>rw_elemental</t>
-  </si>
-  <si>
-    <t>元素之環</t>
-  </si>
-  <si>
-    <t>霜痕;烈陽;雷鳴;寒月</t>
-  </si>
-  <si>
-    <t>elemDmgFire:1.8;elemDmgIce:1.8;elemDmgLightning:1.8;elemDmgWind:1.8;elemDmgPoison:1.8</t>
-  </si>
-  <si>
-    <t>dmgPct:10</t>
-  </si>
-  <si>
-    <t>五元素各執一角，在指尖上取得平衡。</t>
-  </si>
-  <si>
-    <t>rw_blitz</t>
-  </si>
-  <si>
-    <t>閃擊</t>
-  </si>
-  <si>
-    <t>疾影;驚蟄;驚蟄;風語</t>
-  </si>
-  <si>
-    <t>aspd:4;critRate:3;hit:2</t>
-  </si>
-  <si>
-    <t>aspdMult:15</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","every":6,"acts":[{"act":"castRandom"}]}]</t>
-  </si>
-  <si>
-    <t>揮刀太快，連技能都被牽著走。</t>
-  </si>
-  <si>
-    <t>rw_reincarnation</t>
-  </si>
-  <si>
-    <t>命運;輪迴;永恆;創生</t>
-  </si>
-  <si>
-    <t>hpPct:4;defPct:4;mdefPct:4</t>
-  </si>
-  <si>
-    <t>reviveHpPct:60;reviveCdSec:180;reviveInvulnSec:3;reviveDmgPct:60;reviveDmgSec:10;reviveRefresh:1</t>
-  </si>
-  <si>
-    <t>死亡只是下一次輪迴的開場白。</t>
-  </si>
-  <si>
-    <t>rw_timeloop</t>
-  </si>
-  <si>
-    <t>時之沙</t>
-  </si>
-  <si>
-    <t>命運;輪迴;虛空;永恆</t>
-  </si>
-  <si>
-    <t>cdr:5;mpRegen:5;matkPct:3</t>
-  </si>
-  <si>
-    <t>cdPct:45;maxHpPct:-20</t>
-  </si>
-  <si>
-    <t>[{"on":"cast","chance":25,"acts":[{"act":"recast"}]}]</t>
-  </si>
-  <si>
-    <t>沙漏倒過來了。代價是你的生命，也在一起流。</t>
-  </si>
-  <si>
-    <t>rw_bloodmoon</t>
-  </si>
-  <si>
-    <t>血月</t>
-  </si>
-  <si>
-    <t>夜幕;熔岩;雷霆;命運</t>
-  </si>
-  <si>
-    <t>atkPct:3;matkPct:3;critDmg:3;lifesteal:2</t>
-  </si>
-  <si>
-    <t>dmgPct:60;selfDrainPct:2;killHealPct:8;maxHpPct:-30</t>
-  </si>
-  <si>
-    <t>血月當空，誰先流盡誰先倒下。</t>
-  </si>
-  <si>
-    <t>rw_arsenal</t>
-  </si>
-  <si>
-    <t>武庫</t>
-  </si>
-  <si>
-    <t>疾影;嵐;虛空;星辰</t>
-  </si>
-  <si>
-    <t>aspd:3;atkPct:3;matkPct:3</t>
-  </si>
-  <si>
-    <t>skillDmgPct:40</t>
-  </si>
-  <si>
-    <t>[{"on":"hit","every":4,"acts":[{"act":"castRandom"}]},{"on":"cast","chance":15,"acts":[{"act":"recast"}]}]</t>
-  </si>
-  <si>
-    <t>每一次揮擊，都從武器庫裡抽出另一招。</t>
-  </si>
-  <si>
-    <t>rw_thunderemperor</t>
-  </si>
-  <si>
-    <t>雷帝</t>
-  </si>
-  <si>
-    <t>雷霆;雷鳴;虛空;創生</t>
-  </si>
-  <si>
-    <t>matkPct:3;elemDmgLightning:3.5;critRate:2</t>
-  </si>
-  <si>
-    <t>dmgCtrlPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":2,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"rand","n":3}]},{"on":"crit","acts":[{"act":"stun","sec":1,"to":"all"}]}]</t>
-  </si>
-  <si>
-    <t>帝王不需親自出手，雷霆自會代勞。</t>
-  </si>
-  <si>
-    <t>rw_lonewolf</t>
-  </si>
-  <si>
-    <t>孤狼</t>
-  </si>
-  <si>
-    <t>蒼穹;熔岩;冰魄;雷霆</t>
-  </si>
-  <si>
-    <t>critDmg:3.5;atkPct:3;bossDmg:3.5</t>
-  </si>
-  <si>
-    <t>dmgSoloPct:80;dmgHiHpPct:40;cdPct:15</t>
-  </si>
-  <si>
-    <t>孤狼只獵王者。獵物以外，一概不理。</t>
-  </si>
-  <si>
-    <t>rw_starfall</t>
-  </si>
-  <si>
-    <t>星墜</t>
-  </si>
-  <si>
-    <t>虛空;冰魄;星辰;輪迴</t>
-  </si>
-  <si>
-    <t>staff2h</t>
-  </si>
-  <si>
-    <t>matkPct:3.5;elemDmgFire:2.5;elemDmgIce:2.5;mPen:0.6</t>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":150,"elem":"random","to":"rand","n":5}]}]</t>
-  </si>
-  <si>
-    <t>夜空翻面，群星墜落成雨。</t>
-  </si>
-  <si>
-    <t>rw_chaoslord</t>
-  </si>
-  <si>
-    <t>混沌之主</t>
-  </si>
-  <si>
-    <t>混沌;虛空;輪迴;永恆</t>
-  </si>
-  <si>
-    <t>resAll:3;luck:4;critRate:3</t>
-  </si>
-  <si>
-    <t>skillDmgPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"cast","acts":[{"act":"buffRandom","sec":8,"from":[{"sid":"atkUp","val":25},{"sid":"aspdUp","val":25},{"sid":"critDmgUp","val":60},{"sid":"defUp","val":40},{"sid":"evasionUp","val":30},{"sid":"allDmgUp","val":20}]}]}]</t>
-  </si>
-  <si>
-    <t>混沌不問因果，每一次施法都是一場賭局。</t>
-  </si>
-  <si>
-    <t>rw_dragonslayer</t>
-  </si>
-  <si>
-    <t>屠龍者</t>
-  </si>
-  <si>
-    <t>熔岩;星辰;永恆;混沌</t>
-  </si>
-  <si>
-    <t>atkPct:2.5;bossDmg:5;critDmg:2.5;pPen:0.8</t>
-  </si>
-  <si>
-    <t>dmgHiHpPct:50;dmgPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"crit","chance":20,"acts":[{"act":"dmg","pct":250,"type":"phys","to":"target"}]}]</t>
-  </si>
-  <si>
-    <t>巨龍的鱗片，就是為了被一劍貫穿而生。</t>
-  </si>
-  <si>
-    <t>rw_immortalbody</t>
-  </si>
-  <si>
-    <t>不朽之軀</t>
-  </si>
-  <si>
-    <t>永恆;終焉;輪迴;創生</t>
-  </si>
-  <si>
-    <t>armor</t>
-  </si>
-  <si>
-    <t>hpPct:5;globalDmgRed:3;resAll:3</t>
-  </si>
-  <si>
-    <t>maxHitPct:15;dmgPct:-20</t>
-  </si>
-  <si>
-    <t>[{"on":"lowhp","below":40,"cd":60,"acts":[{"act":"shield","pctMax":40,"sec":6},{"act":"invuln","sec":2}]}]</t>
-  </si>
-  <si>
-    <t>以出手的力量，換不會倒下的身軀。</t>
-  </si>
-  <si>
-    <t>rw_legion</t>
-  </si>
-  <si>
-    <t>萬軍</t>
-  </si>
-  <si>
-    <t>嵐;虛空;命運;永恆</t>
-  </si>
-  <si>
-    <t>greatsword2h;axe2h</t>
-  </si>
-  <si>
-    <t>atkPct:3;aspd:3;aoeDmg:2</t>
-  </si>
-  <si>
-    <t>skyrendSlash;gatheringVortex</t>
-  </si>
-  <si>
-    <t>splashPct:50;dmgPerFoePct:6</t>
-  </si>
-  <si>
-    <t>一人成軍，一劍橫掃萬軍。</t>
-  </si>
-  <si>
-    <t>rw_bladedancer</t>
-  </si>
-  <si>
-    <t>劍舞者</t>
-  </si>
-  <si>
-    <t>驚蟄;嵐;熔岩;冰魄</t>
-  </si>
-  <si>
-    <t>aspd:3;critRate:3;atkPct:3</t>
-  </si>
-  <si>
-    <t>danceTwinBlades;danceThousandCuts;danceUnyielding</t>
-  </si>
-  <si>
-    <t>舞到最後一步時，才知道這是一場不能停的舞。</t>
-  </si>
-  <si>
-    <t>rw_voidwalker</t>
-  </si>
-  <si>
-    <t>虛空行者</t>
-  </si>
-  <si>
-    <t>虛空;星辰;命運;輪迴</t>
-  </si>
-  <si>
-    <t>evasion:6;hit:4;hpPct:3</t>
-  </si>
-  <si>
-    <t>dmgPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":30,"cd":4,"acts":[{"act":"invuln","sec":1.5},{"act":"dmg","pct":150,"elem":"dark","to":"all"}]}]</t>
-  </si>
-  <si>
-    <t>走進虛空的人，被攻擊的永遠是上一個位置。</t>
-  </si>
-  <si>
-    <t>rw_genesis</t>
-  </si>
-  <si>
-    <t>創世紀</t>
-  </si>
-  <si>
-    <t>永恆;混沌;創生;終焉</t>
-  </si>
-  <si>
-    <t>any</t>
-  </si>
-  <si>
-    <t>atkPct:3;matkPct:3;elemDmgFire:1.5;elemDmgIce:1.5;elemDmgLightning:1.5;elemDmgPoison:1.5;elemDmgLight:1.5;elemDmgDark:1.5;elemDmgEarth:1.5;elemDmgWind:1.5</t>
-  </si>
-  <si>
-    <t>dmgPct:50;cdPct:20;aspdMult:15;manaCostRedPct:30</t>
-  </si>
-  <si>
-    <t>最後一顆符文落下時，世界從頭開始。</t>
-  </si>
-  <si>
-    <t>符文表（Runes）欄位與規則說明</t>
-  </si>
-  <si>
-    <t>本頁為說明頁，程式不讀取；第一頁「Runes」才是資料來源。改完存檔（Ctrl+S）後雙擊「套用參數.bat」套用，本機開著的遊戲約 2 秒自動重載。</t>
-  </si>
-  <si>
-    <t>套用時會檢查：詞條鍵、符文名稱、適用裝備、效果鍵、事件觸發 JSON、孔數上限等；任何一格打錯都會整次中止並指出是哪一列哪一格，遊戲程式不會被改到。</t>
-  </si>
-  <si>
-    <t>── 三種列（「類型」欄；用篩選看各自的那一段）──</t>
-  </si>
-  <si>
-    <t>設定：全域設定。id 是鑰匙欄，不可改名；數值填在「設定值」。</t>
-  </si>
-  <si>
-    <t>符文：33 種符文。列的先後順序＝階數（第 1 列＝第 1 階），id 依序為 r01～r33，不可重排、不可增刪。</t>
-  </si>
-  <si>
-    <t>符文之語：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
-  </si>
-  <si>
-    <t>── 設定列 ──</t>
-  </si>
-  <si>
-    <t>maxSlots：符文孔數上限，同時也是符文之語最多能有幾顆符文（設計上限 4）。</t>
-  </si>
-  <si>
-    <t>slots_&lt;稀有度&gt;：該稀有度裝備的符文孔數；0～上限，不可隨稀有度變少，最高稀有度必須等於上限。符文孔取代原本的附魔欄位，與寶石鑲孔分開，雙手武器沒有額外加成。</t>
-  </si>
-  <si>
-    <t>composeCount／composeMaxTier／dismantleYield：合成（同種幾顆→下一階 1 顆）、最高合成階（更高階只能掉落）、拆解產出（必須小於合成所需顆數；預設 1＝只能降階頂替、不會變多）。</t>
-  </si>
-  <si>
-    <t>statScale：全域屬性縮放，符文與符文之語的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
-  </si>
-  <si>
-    <t>drop_*：掉落。basePct 野外每次擊殺的基礎掉落率(%)（再乘掉寶率與地圖獎勵倍率）、towerBossPct 封魔塔通關的基礎掉落率(%)、tierSpread 階數稀有度（相鄰兩階的機率比，0~1，越小高階越稀有）、progressPerTier 每 +1 進度對應的最高掉落階增量。</t>
-  </si>
-  <si>
-    <t>　　取得難度只由「配方最高階那顆符文」決定；各級距的最高階區間與估算小時數見 docs/RUNEWORD_DESIGN.md，估算用 node tools/rw_econ_probe.cjs。</t>
-  </si>
-  <si>
-    <t>── 符文列 ──</t>
-  </si>
-  <si>
-    <t>武器詞條／武器倍率：符文鑲在主手或雙手武器時給的屬性（詞條鍵見 Equipment_Affix 表的詞條池）。倍率＝這件裝備上「一條滿刻度中位數詞條」的幾倍；數值隨裝備等級、稀有度、強化成長，與詞條同一套算法。</t>
-  </si>
-  <si>
-    <t>　　是「額外附加」的一條屬性，直接加進角色該屬性的加總，不是乘在裝備原有詞條上，也不是乘整個角色的數值。</t>
-  </si>
-  <si>
-    <t>防具詞條／防具倍率：符文鑲在防具、飾品、副手時給的屬性，規則同上。</t>
-  </si>
-  <si>
-    <t>單獨鑲著就有效；組成符文之語時，符文之語的屬性與能力另外並存。</t>
-  </si>
-  <si>
-    <t>── 符文之語列 ──</t>
-  </si>
-  <si>
-    <t>級距：1 普通／2 強力／3 非常強力／4 極度特殊。只影響圖鑑的分組與顏色，不影響數值（強度要自己調屬性加成與效果）。</t>
-  </si>
-  <si>
-    <t>配方：符文名稱依序用「;」分隔（也可填 id）。至少 2 顆、最多＝符文孔數上限；順序不同就是不同配方，不得與別的符文之語完全相同。成形條件＝依序放進連續的符文孔，且裝備類型符合。</t>
-  </si>
-  <si>
-    <t>適用裝備：用「;」分隔，多項為「或」。標記：any 任意、armor 八件防具、jewelry 戒指＋項鍊、mainHand 主手與雙手武器、twoHand 雙手武器、oneHand 單手武器、offHand 副手、melee 近戰武器、caster 施法類武器／副手；</t>
-  </si>
-  <si>
-    <t>　　也可填裝備欄位（weapon、helmet、shoulder、chest、belt、gloves、wrist、legs、boots、ring、amulet）或武器類型鍵（sword1h、dagger1h、staff2h、shield、focus… 見 data.js WEAPON_TYPES）。</t>
-  </si>
-  <si>
-    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率意義同符文列；負數＝代價。同一組符文之語穿在多件裝備上時，各件的屬性都計。</t>
-  </si>
-  <si>
-    <t>被動：「鍵:數值」用「;」分隔，鍵限 thorns（反震）、smite（天罰）、undying（不朽）、sunder（破甲）、trueDmg（真傷）、omniDrain（萬象汲取）、soulEater、annihilate、sanctuary、godWrath；並入既有被動。</t>
-  </si>
-  <si>
-    <t>傳奇特效：借用既有傳奇特效（Equipment_Affix 表傳奇特效池的 id，用「;」分隔），不受該特效原本的武器類型限制，但仍需要配戴對應技能才有感。</t>
-  </si>
-  <si>
-    <t>靜態效果：「鍵:數值」用「;」分隔，數字固定、不隨稀有度成長。可用鍵：</t>
-  </si>
-  <si>
-    <t>　　dmgPct 造成傷害%、skillDmgPct 技能傷害%、basicDmgPct 普攻傷害%、aspdMult 攻速額外乘算%、cdPct 技能冷卻-%（乘算）、manaCostRedPct 法力消耗-%、maxHitPct 單次受傷上限（最大生命%）、maxHpPct 最大生命%（乘算，負數＝代價）、</t>
-  </si>
-  <si>
-    <t>　　dmgHiHpPct 對高血(&gt;70%)敵人增傷%、dmgLoHpPct 對低血(&lt;30%)敵人增傷%、dmgSoloPct 只有一隻敵人時增傷%、dmgPerFoePct 每多一隻敵人增傷%、dmgSelfFullPct 自身高血增傷%、dmgSelfLowPct 自身低血增傷%、dmgCtrlPct 對被控場敵人增傷%、</t>
-  </si>
-  <si>
-    <t>　　killHealPct 擊殺回血%、killManaPct 擊殺回魔%、runeFindPct 符文掉落率+%、selfDrainPct 每秒損失最大生命%（代價）、splashPct 普攻擴散給其他敵人%、</t>
-  </si>
-  <si>
-    <t>　　reviveHpPct／reviveCdSec／reviveInvulnSec／reviveDmgPct／reviveDmgSec／reviveRefresh 死亡復活（生命%、冷卻秒、無敵秒、之後增傷%與秒數、是否重置技能冷卻）。</t>
-  </si>
-  <si>
-    <t>事件觸發(JSON)：JSON 陣列，每條 { "on": 觸發, "chance": 機率%, "every": 秒（tick）或次數, "cd": 內建冷卻秒, "below": 生命%（lowhp）, "acts": [動作…] }。</t>
-  </si>
-  <si>
-    <t>　　觸發 on：hit 普攻命中、crit 普攻暴擊、kill 擊殺、hurt 受傷、block 格擋、cast 施放技能、tick 每 every 秒、lowhp 生命低於 below%。</t>
-  </si>
-  <si>
-    <t>　　動作 act：dmg {pct, elem?, type?(magic/phys), to?(target/all/rand/attacker), n?}、heal {pctMax}、shield {pctMax, sec}、mana {pctMax}、buff {sid, val, sec, max?}、buffRandom {sec, from:[{sid,val}]}、stun {sec, to?}、slow {sec, to?}、</t>
-  </si>
-  <si>
-    <t>　　dot {pct, sec, name(poison/burn/bleed/corrode), to?}、cdr {sec}、refresh {n?}、recast、castRandom、invuln {sec}、execute {hpBelow}、cleanse。elem 可填 fire/ice/lightning/poison/light/dark/earth/wind/random。</t>
-  </si>
-  <si>
-    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。效果說明文字由資料自動產生，不需要另外寫。</t>
-  </si>
-  <si>
-    <t>備註：純說明欄，不進遊戲。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：命中率×2｜防具・飾品・副手：閃避率×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×2｜防具・飾品・副手：物理防禦×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：冰屬性傷害提升×0.6｜防具・飾品・副手：冰霜抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：攻擊速度×0.6｜防具・飾品・副手：閃避率×0.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理穿透×0.12｜防具・飾品・副手：物理防禦×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：毒屬性傷害提升×0.6｜防具・飾品・副手：劇毒抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：雷屬性傷害提升×0.6｜防具・飾品・副手：雷電抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：吸血×0.7｜防具・飾品・副手：生命恢復/秒×0.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：聖屬性傷害提升×0.6｜防具・飾品・副手：聖光抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×0.7｜防具・飾品・副手：生命值×0.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×0.8｜防具・飾品・副手：物理抗性×0.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×0.7｜防具・飾品・副手：法力值×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊率×0.8｜防具・飾品・副手：命中率×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對菁英傷害×0.8｜防具・飾品・副手：格擋率×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法穿透×0.15｜防具・飾品・副手：魔法抗性×0.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暗屬性傷害提升×0.8｜防具・飾品・副手：暗影抗性×0.4（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：火屬性傷害提升×0.8｜防具・飾品・副手：火焰抗性×0.4（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：冷卻縮減×0.9｜防具・飾品・副手：魔法防禦×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：攻擊速度×1｜防具・飾品・副手：韌性×1（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：風屬性傷害提升×1｜防具・飾品・副手：疾風抗性×0.5（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對BOSS傷害×1.1｜防具・飾品・副手：護盾效率×1.1（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：地屬性傷害提升×1.1｜防具・飾品・副手：生命值×1.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×1.3｜防具・飾品・副手：全局減傷×1.1（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×1.4｜防具・飾品・副手：全屬性抗性×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×1.4｜防具・飾品・副手：格擋減傷×1.4（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：範圍傷害×1.5｜防具・飾品・副手：控制時間縮減×1.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊率×1.6｜防具・飾品・副手：幸運值×1.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對普通敵人傷害×1.7｜防具・飾品・副手：閃避率×1.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：吸血×1.8｜防具・飾品・副手：生命恢復/秒×1.8（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×1.9｜防具・飾品・副手：生命值×1.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×2｜防具・飾品・副手：全屬性抗性×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×2.2｜防具・飾品・副手：護盾效率×2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對BOSS傷害×2.5｜防具・飾品・副手：全局減傷×1.8（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×2、魔法攻擊×2、命中率×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×2.5、生命值×2.5、生命恢復/秒×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×2.5、冰屬性傷害提升×1.5｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×2、生命值×2、命中率×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×1.5、生命值×1.2、物理抗性×0.8｜反震 3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.2、毒屬性傷害提升×1.5、暴擊率×1｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 60% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.5、雷屬性傷害提升×2｜普通攻擊命中時有 8% 機率：對目標造成 90% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×2、聖光抗性×1.5、生命值×1｜擊殺敵人時回復 1% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×2、物理攻擊×1、命中率×1｜擊殺敵人時回復 1% 最大生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.5、物理防禦×1.5、韌性×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×2、生命恢復/秒×2、法力值×1.5｜擊殺敵人時回復 2% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：金幣加成×2、經驗加成×1.5、掉寶率×1.2｜符文掉落率 +8%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.2、暴擊傷害×1.2、物理穿透×0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.5、火屬性傷害提升×1.5、法力值×1.5｜施放技能時有 15% 機率：回復 12% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×2.5、暴擊率×1.5、物理攻擊×1.5｜攻擊速度額外乘算 +8%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.5、雷屬性傷害提升×2.5、暴擊傷害×1.5｜普通攻擊命中時有 15% 機率：對所有敵人造成 120% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×2、冰屬性傷害提升×3、冷卻縮減×1｜對暈眩或緩速中的敵人傷害 +15%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×3、物理攻擊×2、暴擊率×1｜擊殺敵人時回復 3% 最大生命；生命低於 35% 時，傷害 +25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×3、物理防禦×3、物理抗性×1｜單次受到的傷害最多只會是最大生命的 40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×3.5、命中率×2、生命值×1.5｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×2、法力值×3、全屬性抗性×1｜每 10 秒：回復 8% 最大生命，回復 8% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×2、毒屬性傷害提升×3、魔法穿透×0.3｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 60% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×3、暴擊率×2、物理攻擊×1.5｜普通攻擊暴擊時：獲得「攻速」+12%（3 秒，最多 3 層）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×2.5、物理防禦×2、物理抗性×1｜反震 12%；受到傷害時有 20% 機率：對攻擊者造成 100% 物理傷害（內建冷卻 3 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：幸運值×3、暴擊率×2、暴擊傷害×2.5、掉寶率×2｜符文掉落率 +15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：格擋率×3、格擋減傷×3、生命值×2｜格擋成功時有 40% 機率：對攻擊者造成 200% 物理傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3、法力值×3、冷卻縮減×2｜施放技能時有 20% 機率：所有技能冷卻縮短 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：寶石鑲嵌效率×3、詞條上限率×2、強化成功率×3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、對BOSS傷害×3｜造成的所有傷害 +18%；攻擊速度額外乘算 +10%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×4、暴擊傷害×4、對菁英傷害×3、物理穿透×0.5｜對生命低於 30% 的敵人傷害 +60%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 15% 的非 BOSS 敵人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3、風屬性傷害提升×2、魔法穿透×0.5｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 120% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 100% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×4、魔法攻擊×3、法力恢復/秒×3、生命值×2｜所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 1 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×4、物理防禦×3.5、魔法防禦×3.5、全局減傷×2｜生命低於 30% 時：無敵 3 秒，回復 30% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×2.5、物理攻擊×2.5、暴擊率×1.5、範圍傷害×2｜場上每多一名敵人，傷害 +5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 20% 的傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊率×1.5、暴擊傷害×2、物理攻擊×2、閃避率×1.5｜對生命高於 70% 的敵人傷害 +20%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：飛刀的彈射數 +2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×4、法力恢復/秒×4、魔法攻擊×2.5｜技能法力消耗 -40%；擊殺敵人時回復 3% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×3.5、物理防禦×3.5、物理抗性×2｜反震 35%；受到傷害時有 25% 機率：對所有敵人造成 150% 物理傷害（內建冷卻 2 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：對BOSS傷害×5、對菁英傷害×4、物理攻擊×2.5、魔法攻擊×2.5｜對生命高於 70% 的敵人傷害 +40%；場上只有一名敵人時，傷害 +40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×4、吸血×4、生命恢復/秒×4｜擊殺敵人時回復 6% 最大生命；生命高於 90% 時，傷害 +25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：護盾效率×5、生命值×3、全局減傷×2.5｜每 8 秒：獲得相當於 20% 最大生命的護盾（8 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：火屬性傷害提升×1.8、冰屬性傷害提升×1.8、雷屬性傷害提升×1.8、風屬性傷害提升×1.8、毒屬性傷害提升×1.8｜造成的所有傷害 +10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×4、暴擊率×3、命中率×2｜攻擊速度額外乘算 +15%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×4、物理防禦×4、魔法防禦×4｜死亡時以 60% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +60%，冷卻 180 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×5、法力恢復/秒×5、魔法攻擊×3｜所有技能冷卻時間 -45%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、吸血×2｜造成的所有傷害 +60%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 8% 最大生命；最大生命 -30%（乘算，代價）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×3、物理攻擊×3、魔法攻擊×3｜技能傷害 +40%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3.5、暴擊率×2｜對暈眩或緩速中的敵人傷害 +25%；每 2 秒：對隨機 3 名敵人造成 120% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊傷害×3.5、物理攻擊×3、對BOSS傷害×3.5｜場上只有一名敵人時，傷害 +80%；對生命高於 70% 的敵人傷害 +40%；所有技能冷卻時間 -15%（乘算，突破冷卻縮減上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3.5、火屬性傷害提升×2.5、冰屬性傷害提升×2.5、魔法穿透×0.6｜每 3 秒：對隨機 5 名敵人造成 150% 隨機元素傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：全屬性抗性×3、幸運值×4、暴擊率×3｜技能傷害 +25%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×2.5、對BOSS傷害×5、暴擊傷害×2.5、物理穿透×0.8｜對生命高於 70% 的敵人傷害 +50%；造成的所有傷害 +25%；普通攻擊暴擊時有 20% 機率：對目標造成 250% 物理傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×5、全局減傷×3、全屬性抗性×3｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、攻擊速度×3、範圍傷害×2｜普通攻擊同時對其他所有敵人造成 50% 的傷害；場上每多一名敵人，傷害 +6%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。；傳奇特效【聚敵旋渦】：迴旋斬會將 60 米內的所有敵人拉近至身邊 10 米範圍內。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×3、暴擊率×3、物理攻擊×3｜攻擊速度額外乘算 +15%（突破攻速上限）；傳奇特效【雙生刃】：雙刀亂舞的擊中目標數量 +2 個。；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。；傳奇特效【不屈之誓】：暴風之舞持續期間你的死亡延後 10 秒才生效，且這 10 秒內你的傷害提高 100%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×6、命中率×4、生命值×3｜造成的所有傷害 +25%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 150% 暗影傷害（內建冷卻 4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、魔法攻擊×3、火屬性傷害提升×1.5、冰屬性傷害提升×1.5、雷屬性傷害提升×1.5、毒屬性傷害提升×1.5、聖屬性傷害提升×1.5、暗屬性傷害提升×1.5、地屬性傷害提升×1.5、風屬性傷害提升×1.5｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註：設定列＝該設定的說明；符文列＝兩側屬性的中文名稱與倍率；符文之語列＝屬性中文名稱與倍率，加上被動／靜態效果／事件觸發／借用傳奇特效的中文說明（與遊戲內圖鑑同一份文字）。</t>
+  </si>
+  <si>
+    <t>　　備註是自動產生的參考，不進遊戲、不影響套用；你改了能力之後，備註不會自動更新（請 AI 重新產生），以左邊各欄實際內容為準。</t>
   </si>
 </sst>
 </file>
@@ -2402,7 +2766,7 @@
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
     <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.625" customWidth="1"/>
     <col min="5" max="5" width="14.625" customWidth="1"/>
     <col min="6" max="6" width="9.625" customWidth="1"/>
@@ -3603,23 +3967,23 @@
         <v>81</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
       </c>
@@ -3648,7 +4012,7 @@
         <v>21</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>21</v>
+        <v>650</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -3656,25 +4020,25 @@
         <v>80</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
@@ -3704,7 +4068,7 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>21</v>
+        <v>651</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -3712,22 +4076,22 @@
         <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>38</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>66</v>
@@ -3760,7 +4124,7 @@
         <v>21</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>21</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -3768,26 +4132,26 @@
         <v>80</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
@@ -3816,7 +4180,7 @@
         <v>21</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>21</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -3824,25 +4188,25 @@
         <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -3872,7 +4236,7 @@
         <v>21</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>21</v>
+        <v>654</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -3880,22 +4244,22 @@
         <v>80</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>66</v>
@@ -3928,7 +4292,7 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>21</v>
+        <v>655</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -3936,22 +4300,22 @@
         <v>80</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>66</v>
@@ -3984,7 +4348,7 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>21</v>
+        <v>656</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -3992,25 +4356,25 @@
         <v>80</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="H29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -4040,7 +4404,7 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>21</v>
+        <v>657</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -4048,22 +4412,22 @@
         <v>80</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>66</v>
@@ -4096,7 +4460,7 @@
         <v>21</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>21</v>
+        <v>658</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -4104,25 +4468,25 @@
         <v>80</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="H31" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>21</v>
@@ -4152,7 +4516,7 @@
         <v>21</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>21</v>
+        <v>659</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -4160,26 +4524,26 @@
         <v>80</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
       </c>
@@ -4208,7 +4572,7 @@
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>21</v>
+        <v>660</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -4216,26 +4580,26 @@
         <v>80</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>21</v>
       </c>
@@ -4264,7 +4628,7 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>21</v>
+        <v>661</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -4272,25 +4636,25 @@
         <v>80</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>21</v>
@@ -4320,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>21</v>
+        <v>662</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -4328,25 +4692,25 @@
         <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="H35" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>21</v>
@@ -4376,7 +4740,7 @@
         <v>21</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>21</v>
+        <v>663</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -4384,25 +4748,25 @@
         <v>80</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="H36" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
@@ -4432,7 +4796,7 @@
         <v>21</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>21</v>
+        <v>664</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -4440,26 +4804,26 @@
         <v>80</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
       </c>
@@ -4488,7 +4852,7 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>21</v>
+        <v>665</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -4496,25 +4860,25 @@
         <v>80</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="H38" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>21</v>
@@ -4544,7 +4908,7 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>21</v>
+        <v>666</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -4552,25 +4916,25 @@
         <v>80</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="H39" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>21</v>
@@ -4600,7 +4964,7 @@
         <v>21</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>21</v>
+        <v>667</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -4608,22 +4972,22 @@
         <v>80</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>30</v>
@@ -4656,7 +5020,7 @@
         <v>21</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>21</v>
+        <v>668</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -4664,26 +5028,26 @@
         <v>80</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>56</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G41" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
       </c>
@@ -4712,7 +5076,7 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>21</v>
+        <v>669</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -4720,25 +5084,25 @@
         <v>80</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="H42" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>21</v>
@@ -4768,7 +5132,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>21</v>
+        <v>670</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -4776,26 +5140,26 @@
         <v>80</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>21</v>
       </c>
@@ -4824,7 +5188,7 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>21</v>
+        <v>671</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -4832,25 +5196,25 @@
         <v>80</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="H44" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>21</v>
@@ -4880,7 +5244,7 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>21</v>
+        <v>672</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -4888,25 +5252,25 @@
         <v>80</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="H45" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>21</v>
@@ -4936,7 +5300,7 @@
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>21</v>
+        <v>673</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -4944,25 +5308,25 @@
         <v>80</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="H46" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>21</v>
@@ -4992,7 +5356,7 @@
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>21</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -5000,25 +5364,25 @@
         <v>80</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="H47" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>21</v>
@@ -5048,7 +5412,7 @@
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>21</v>
+        <v>675</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -5056,25 +5420,25 @@
         <v>80</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="E48" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="H48" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>21</v>
@@ -5104,7 +5468,7 @@
         <v>21</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>21</v>
+        <v>676</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -5112,25 +5476,25 @@
         <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>21</v>
@@ -5160,7 +5524,7 @@
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>21</v>
+        <v>677</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -5168,25 +5532,25 @@
         <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F50" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="H50" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>21</v>
@@ -5216,7 +5580,7 @@
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>21</v>
+        <v>678</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -5224,25 +5588,25 @@
         <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F51" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="H51" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>21</v>
@@ -5272,7 +5636,7 @@
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>21</v>
+        <v>679</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -5280,25 +5644,25 @@
         <v>80</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>35</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>21</v>
@@ -5328,7 +5692,7 @@
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>21</v>
+        <v>680</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -5336,22 +5700,22 @@
         <v>80</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="G53" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>35</v>
@@ -5384,7 +5748,7 @@
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>21</v>
+        <v>681</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -5392,25 +5756,25 @@
         <v>80</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="G54" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>21</v>
@@ -5440,18 +5804,18 @@
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>21</v>
+        <v>682</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>30</v>
@@ -5469,45 +5833,45 @@
         <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="K55" s="3" t="s">
+      <c r="L55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P55" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>21</v>
+        <v>683</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>30</v>
@@ -5525,45 +5889,45 @@
         <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="K56" s="3" t="s">
+      <c r="L56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>21</v>
+        <v>684</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>30</v>
@@ -5581,45 +5945,45 @@
         <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="K57" s="3" t="s">
+      <c r="L57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O57" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O57" s="3" t="s">
+      <c r="P57" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>21</v>
+        <v>685</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>30</v>
@@ -5637,45 +6001,45 @@
         <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="K58" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="L58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>21</v>
+        <v>686</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>30</v>
@@ -5693,45 +6057,45 @@
         <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J59" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>21</v>
+        <v>687</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>30</v>
@@ -5749,45 +6113,45 @@
         <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="K60" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="K60" s="3" t="s">
+      <c r="L60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O60" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" s="3" t="s">
+      <c r="P60" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>281</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>21</v>
+        <v>688</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>30</v>
@@ -5805,45 +6169,45 @@
         <v>21</v>
       </c>
       <c r="I61" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="J61" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="K61" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="L61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="L61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O61" s="3" t="s">
+      <c r="P61" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="P61" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>21</v>
+        <v>689</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>30</v>
@@ -5861,45 +6225,45 @@
         <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J62" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="K62" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="L62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N62" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N62" s="3" t="s">
+      <c r="O62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P62" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>21</v>
+        <v>690</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>30</v>
@@ -5917,45 +6281,45 @@
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="K63" s="3" t="s">
+      <c r="L63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="L63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N63" s="3" t="s">
+      <c r="O63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P63" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="O63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>302</v>
-      </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>21</v>
+        <v>691</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>30</v>
@@ -5973,45 +6337,45 @@
         <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="J64" s="3" t="s">
+      <c r="K64" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="L64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="L64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>308</v>
-      </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>21</v>
+        <v>692</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>30</v>
@@ -6029,45 +6393,45 @@
         <v>21</v>
       </c>
       <c r="I65" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J65" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="K65" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="L65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N65" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N65" s="3" t="s">
+      <c r="O65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="O65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>315</v>
-      </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>21</v>
+        <v>693</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>30</v>
@@ -6085,45 +6449,45 @@
         <v>21</v>
       </c>
       <c r="I66" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="L66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N66" s="3" t="s">
+      <c r="O66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>322</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>21</v>
+        <v>694</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>30</v>
@@ -6141,45 +6505,45 @@
         <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="L67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="L67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>328</v>
-      </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>21</v>
+        <v>695</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>30</v>
@@ -6197,45 +6561,45 @@
         <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="J68" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K68" s="3" t="s">
+      <c r="L68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O68" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="L68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O68" s="3" t="s">
+      <c r="P68" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="P68" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>21</v>
+        <v>696</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>336</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>35</v>
@@ -6253,45 +6617,45 @@
         <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="K69" s="3" t="s">
+      <c r="L69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N69" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N69" s="3" t="s">
+      <c r="O69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="O69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>21</v>
+        <v>697</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>35</v>
@@ -6309,45 +6673,45 @@
         <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K70" s="3" t="s">
+      <c r="L70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O70" s="3" t="s">
+      <c r="P70" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>346</v>
-      </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>21</v>
+        <v>698</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>35</v>
@@ -6365,45 +6729,45 @@
         <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="J71" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K71" s="3" t="s">
+      <c r="L71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N71" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="L71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N71" s="3" t="s">
+      <c r="O71" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="O71" s="3" t="s">
+      <c r="P71" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="P71" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>21</v>
+        <v>699</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>35</v>
@@ -6421,45 +6785,45 @@
         <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K72" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K72" s="3" t="s">
+      <c r="L72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N72" s="3" t="s">
+      <c r="O72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>359</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>21</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>360</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>361</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>35</v>
@@ -6477,45 +6841,45 @@
         <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K73" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="J73" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K73" s="3" t="s">
+      <c r="L73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N73" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="L73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N73" s="3" t="s">
+      <c r="O73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P73" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="O73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>21</v>
+        <v>701</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>35</v>
@@ -6533,45 +6897,45 @@
         <v>21</v>
       </c>
       <c r="I74" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="K74" s="3" t="s">
+      <c r="L74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O74" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="L74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="P74" s="3" t="s">
-        <v>372</v>
-      </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>21</v>
+        <v>702</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>374</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>35</v>
@@ -6589,45 +6953,45 @@
         <v>21</v>
       </c>
       <c r="I75" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="J75" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="K75" s="3" t="s">
+      <c r="L75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O75" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O75" s="3" t="s">
+      <c r="P75" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="P75" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>21</v>
+        <v>703</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>35</v>
@@ -6645,45 +7009,45 @@
         <v>21</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K76" s="3" t="s">
+      <c r="L76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O76" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O76" s="3" t="s">
+      <c r="P76" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>384</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>21</v>
+        <v>704</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>35</v>
@@ -6701,45 +7065,45 @@
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="K77" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="K77" s="3" t="s">
+      <c r="L77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O77" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O77" s="3" t="s">
+      <c r="P77" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="P77" s="3" t="s">
-        <v>390</v>
-      </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>21</v>
+        <v>705</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>391</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>35</v>
@@ -6757,45 +7121,45 @@
         <v>21</v>
       </c>
       <c r="I78" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="K78" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="L78" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="L78" s="3" t="s">
+      <c r="M78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O78" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="M78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O78" s="3" t="s">
+      <c r="P78" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="P78" s="3" t="s">
-        <v>398</v>
-      </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>21</v>
+        <v>706</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>35</v>
@@ -6813,45 +7177,45 @@
         <v>21</v>
       </c>
       <c r="I79" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="J79" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K79" s="3" t="s">
+      <c r="L79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N79" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="L79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N79" s="3" t="s">
+      <c r="O79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P79" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="O79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>21</v>
+        <v>707</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>35</v>
@@ -6869,45 +7233,45 @@
         <v>21</v>
       </c>
       <c r="I80" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J80" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="K80" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K80" s="3" t="s">
+      <c r="L80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O80" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="L80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O80" s="3" t="s">
+      <c r="P80" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="P80" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>21</v>
+        <v>708</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>35</v>
@@ -6925,45 +7289,45 @@
         <v>21</v>
       </c>
       <c r="I81" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="K81" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="K81" s="3" t="s">
+      <c r="L81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O81" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O81" s="3" t="s">
+      <c r="P81" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>21</v>
+        <v>709</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>35</v>
@@ -6981,45 +7345,45 @@
         <v>21</v>
       </c>
       <c r="I82" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="J82" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="K82" s="3" t="s">
+      <c r="L82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P82" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="L82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P82" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>21</v>
+        <v>710</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>38</v>
@@ -7037,45 +7401,45 @@
         <v>21</v>
       </c>
       <c r="I83" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N83" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P83" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>429</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>21</v>
+        <v>711</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>38</v>
@@ -7093,45 +7457,45 @@
         <v>21</v>
       </c>
       <c r="I84" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K84" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="J84" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="K84" s="3" t="s">
+      <c r="L84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N84" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="L84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N84" s="3" t="s">
+      <c r="O84" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="O84" s="3" t="s">
+      <c r="P84" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="P84" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>21</v>
+        <v>712</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>38</v>
@@ -7149,45 +7513,45 @@
         <v>21</v>
       </c>
       <c r="I85" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K85" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="J85" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K85" s="3" t="s">
+      <c r="L85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O85" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="L85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O85" s="3" t="s">
+      <c r="P85" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="P85" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>21</v>
+        <v>713</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>38</v>
@@ -7205,45 +7569,45 @@
         <v>21</v>
       </c>
       <c r="I86" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="K86" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="K86" s="3" t="s">
+      <c r="L86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="L86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N86" s="3" t="s">
+      <c r="O86" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="O86" s="3" t="s">
+      <c r="P86" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="P86" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>21</v>
+        <v>714</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>38</v>
@@ -7261,45 +7625,45 @@
         <v>21</v>
       </c>
       <c r="I87" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K87" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K87" s="3" t="s">
+      <c r="L87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="L87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O87" s="3" t="s">
+      <c r="P87" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="P87" s="3" t="s">
-        <v>455</v>
-      </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>21</v>
+        <v>715</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>38</v>
@@ -7317,45 +7681,45 @@
         <v>21</v>
       </c>
       <c r="I88" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K88" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="J88" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K88" s="3" t="s">
+      <c r="L88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="L88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N88" s="3" t="s">
+      <c r="O88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P88" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="O88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>21</v>
+        <v>716</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>38</v>
@@ -7373,45 +7737,45 @@
         <v>21</v>
       </c>
       <c r="I89" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="J89" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="O89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P89" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>469</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>21</v>
+        <v>717</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>38</v>
@@ -7429,45 +7793,45 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J90" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="K90" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="K90" s="3" t="s">
+      <c r="L90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N90" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="L90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N90" s="3" t="s">
+      <c r="O90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P90" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="O90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>476</v>
-      </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>21</v>
+        <v>718</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>38</v>
@@ -7485,45 +7849,45 @@
         <v>21</v>
       </c>
       <c r="I91" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="J91" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="L91" s="3" t="s">
+      <c r="M91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>21</v>
+        <v>719</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>38</v>
@@ -7541,45 +7905,45 @@
         <v>21</v>
       </c>
       <c r="I92" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K92" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K92" s="3" t="s">
+      <c r="L92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="L92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N92" s="3" t="s">
+      <c r="O92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P92" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="O92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>490</v>
-      </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>21</v>
+        <v>720</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>38</v>
@@ -7597,45 +7961,45 @@
         <v>21</v>
       </c>
       <c r="I93" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K93" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="J93" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K93" s="3" t="s">
+      <c r="L93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N93" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="L93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N93" s="3" t="s">
+      <c r="O93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P93" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="O93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>21</v>
+        <v>721</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>497</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>498</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>38</v>
@@ -7653,45 +8017,45 @@
         <v>21</v>
       </c>
       <c r="I94" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="J94" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="K94" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O94" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>503</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>21</v>
+        <v>722</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>505</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>38</v>
@@ -7709,45 +8073,45 @@
         <v>21</v>
       </c>
       <c r="I95" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="J95" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K95" s="3" t="s">
+      <c r="L95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="L95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N95" s="3" t="s">
+      <c r="O95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P95" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="O95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>509</v>
-      </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>21</v>
+        <v>723</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>38</v>
@@ -7765,45 +8129,45 @@
         <v>21</v>
       </c>
       <c r="I96" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>516</v>
-      </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>21</v>
+        <v>724</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>22</v>
@@ -7821,45 +8185,45 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K97" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="J97" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="K97" s="3" t="s">
+      <c r="L97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N97" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="L97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N97" s="3" t="s">
+      <c r="O97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P97" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="O97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P97" s="3" t="s">
-        <v>521</v>
-      </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>21</v>
+        <v>725</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>523</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -7877,45 +8241,45 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="K98" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="J98" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="K98" s="3" t="s">
+      <c r="L98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="L98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N98" s="3" t="s">
+      <c r="O98" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="O98" s="3" t="s">
+      <c r="P98" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="P98" s="3" t="s">
-        <v>528</v>
-      </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>21</v>
+        <v>726</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>530</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -7933,45 +8297,45 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K99" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="J99" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K99" s="3" t="s">
+      <c r="L99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N99" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="L99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N99" s="3" t="s">
+      <c r="O99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P99" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="O99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>534</v>
-      </c>
       <c r="Q99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>21</v>
+        <v>727</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>22</v>
@@ -7989,45 +8353,45 @@
         <v>21</v>
       </c>
       <c r="I100" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N100" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>541</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>21</v>
+        <v>728</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>543</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>22</v>
@@ -8045,45 +8409,45 @@
         <v>21</v>
       </c>
       <c r="I101" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N101" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>548</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>21</v>
+        <v>729</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>549</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>550</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>22</v>
@@ -8101,45 +8465,45 @@
         <v>21</v>
       </c>
       <c r="I102" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K102" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="K102" s="3" t="s">
+      <c r="L102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N102" s="3" t="s">
+      <c r="O102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>21</v>
+        <v>730</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>22</v>
@@ -8157,45 +8521,45 @@
         <v>21</v>
       </c>
       <c r="I103" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="J103" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="K103" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="K103" s="3" t="s">
+      <c r="L103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O103" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="L103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O103" s="3" t="s">
+      <c r="P103" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="P103" s="3" t="s">
-        <v>561</v>
-      </c>
       <c r="Q103" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>21</v>
+        <v>731</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B104" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>563</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>22</v>
@@ -8213,45 +8577,45 @@
         <v>21</v>
       </c>
       <c r="I104" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="K104" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="J104" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K104" s="3" t="s">
+      <c r="L104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="L104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N104" s="3" t="s">
+      <c r="O104" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="O104" s="3" t="s">
+      <c r="P104" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="P104" s="3" t="s">
-        <v>568</v>
-      </c>
       <c r="Q104" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R104" s="3" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>22</v>
@@ -8269,45 +8633,45 @@
         <v>21</v>
       </c>
       <c r="I105" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K105" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="J105" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="K105" s="3" t="s">
+      <c r="L105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N105" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="L105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N105" s="3" t="s">
+      <c r="O105" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="O105" s="3" t="s">
+      <c r="P105" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="P105" s="3" t="s">
-        <v>575</v>
-      </c>
       <c r="Q105" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>21</v>
+        <v>733</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>22</v>
@@ -8325,45 +8689,45 @@
         <v>21</v>
       </c>
       <c r="I106" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J106" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="J106" s="3" t="s">
+      <c r="K106" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="K106" s="3" t="s">
+      <c r="L106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N106" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="L106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="O106" s="3" t="s">
+      <c r="P106" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="P106" s="3" t="s">
-        <v>583</v>
-      </c>
       <c r="Q106" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R106" s="3" t="s">
-        <v>21</v>
+        <v>734</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>22</v>
@@ -8381,45 +8745,45 @@
         <v>21</v>
       </c>
       <c r="I107" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="J107" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="K107" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="K107" s="3" t="s">
+      <c r="L107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M107" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="L107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M107" s="3" t="s">
+      <c r="N107" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="N107" s="3" t="s">
+      <c r="O107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P107" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="O107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P107" s="3" t="s">
-        <v>591</v>
-      </c>
       <c r="Q107" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R107" s="3" t="s">
-        <v>21</v>
+        <v>735</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>593</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>22</v>
@@ -8437,45 +8801,45 @@
         <v>21</v>
       </c>
       <c r="I108" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="K108" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="J108" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="K108" s="3" t="s">
+      <c r="L108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M108" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="L108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M108" s="3" t="s">
+      <c r="N108" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P108" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="N108" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="O108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P108" s="3" t="s">
-        <v>597</v>
-      </c>
       <c r="Q108" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R108" s="3" t="s">
-        <v>21</v>
+        <v>736</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>599</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>22</v>
@@ -8493,45 +8857,45 @@
         <v>21</v>
       </c>
       <c r="I109" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K109" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="J109" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K109" s="3" t="s">
+      <c r="L109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N109" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="L109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N109" s="3" t="s">
+      <c r="O109" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="O109" s="3" t="s">
+      <c r="P109" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="P109" s="3" t="s">
-        <v>604</v>
-      </c>
       <c r="Q109" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>21</v>
+        <v>737</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>22</v>
@@ -8549,34 +8913,34 @@
         <v>21</v>
       </c>
       <c r="I110" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="J110" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="K110" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="K110" s="3" t="s">
+      <c r="L110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N110" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="L110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N110" s="3" t="s">
+      <c r="O110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P110" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="O110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P110" s="3" t="s">
-        <v>611</v>
-      </c>
       <c r="Q110" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R110" s="3" t="s">
-        <v>21</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -8588,7 +8952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.625" customWidth="1"/>
@@ -8596,17 +8960,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -8616,22 +8980,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -8641,37 +9005,37 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -8681,27 +9045,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -8711,97 +9075,102 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>649</v>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>740</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9DFEAD-5232-4C77-BBE5-8221A20DC632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7735472D-0E61-4833-A640-BED65EED2CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -114,9 +114,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>符文孔數的硬上限，也是符文之語最多能有幾顆符文。</t>
-  </si>
-  <si>
     <t>slots_common</t>
   </si>
   <si>
@@ -234,9 +231,6 @@
     <t>全域屬性縮放</t>
   </si>
   <si>
-    <t>全域縮放：符文與符文之語的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
-  </si>
-  <si>
     <t>drop_basePct</t>
   </si>
   <si>
@@ -768,9 +762,6 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>符文之語</t>
-  </si>
-  <si>
     <t>rw_firstcry</t>
   </si>
   <si>
@@ -1896,24 +1887,15 @@
     <t>符文：33 種符文。列的先後順序＝階數（第 1 列＝第 1 階），id 依序為 r01～r33，不可重排、不可增刪。</t>
   </si>
   <si>
-    <t>符文之語：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
-  </si>
-  <si>
     <t>── 設定列 ──</t>
   </si>
   <si>
-    <t>maxSlots：符文孔數上限，同時也是符文之語最多能有幾顆符文（設計上限 4）。</t>
-  </si>
-  <si>
     <t>slots_&lt;稀有度&gt;：該稀有度裝備的符文孔數；0～上限，不可隨稀有度變少，最高稀有度必須等於上限。符文孔取代原本的附魔欄位，與寶石鑲孔分開，雙手武器沒有額外加成。</t>
   </si>
   <si>
     <t>composeCount／composeMaxTier／dismantleYield：合成（同種幾顆→下一階 1 顆）、最高合成階（更高階只能掉落）、拆解產出（必須小於合成所需顆數；預設 1＝只能降階頂替、不會變多）。</t>
   </si>
   <si>
-    <t>statScale：全域屬性縮放，符文與符文之語的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
-  </si>
-  <si>
     <t>drop_*：掉落。basePct 野外每次擊殺的基礎掉落率(%)（再乘掉寶率與地圖獎勵倍率）、towerBossPct 封魔塔通關的基礎掉落率(%)、tierSpread 階數稀有度（相鄰兩階的機率比，0~1，越小高階越稀有）、progressPerTier 每 +1 進度對應的最高掉落階增量。</t>
   </si>
   <si>
@@ -1932,27 +1914,12 @@
     <t>防具詞條／防具倍率：符文鑲在防具、飾品、副手時給的屬性，規則同上。</t>
   </si>
   <si>
-    <t>單獨鑲著就有效；組成符文之語時，符文之語的屬性與能力另外並存。</t>
-  </si>
-  <si>
-    <t>── 符文之語列 ──</t>
-  </si>
-  <si>
-    <t>級距：1 普通／2 強力／3 非常強力／4 極度特殊。只影響圖鑑的分組與顏色，不影響數值（強度要自己調屬性加成與效果）。</t>
-  </si>
-  <si>
-    <t>配方：符文名稱依序用「;」分隔（也可填 id）。至少 2 顆、最多＝符文孔數上限；順序不同就是不同配方，不得與別的符文之語完全相同。成形條件＝依序放進連續的符文孔，且裝備類型符合。</t>
-  </si>
-  <si>
     <t>適用裝備：用「;」分隔，多項為「或」。標記：any 任意、armor 八件防具、jewelry 戒指＋項鍊、mainHand 主手與雙手武器、twoHand 雙手武器、oneHand 單手武器、offHand 副手、melee 近戰武器、caster 施法類武器／副手；</t>
   </si>
   <si>
     <t>　　也可填裝備欄位（weapon、helmet、shoulder、chest、belt、gloves、wrist、legs、boots、ring、amulet）或武器類型鍵（sword1h、dagger1h、staff2h、shield、focus… 見 data.js WEAPON_TYPES）。</t>
   </si>
   <si>
-    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率意義同符文列；負數＝代價。同一組符文之語穿在多件裝備上時，各件的屬性都計。</t>
-  </si>
-  <si>
     <t>被動：「鍵:數值」用「;」分隔，鍵限 thorns（反震）、smite（天罰）、undying（不朽）、sunder（破甲）、trueDmg（真傷）、omniDrain（萬象汲取）、soulEater、annihilate、sanctuary、godWrath；並入既有被動。</t>
   </si>
   <si>
@@ -2353,10 +2320,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>備註：設定列＝該設定的說明；符文列＝兩側屬性的中文名稱與倍率；符文之語列＝屬性中文名稱與倍率，加上被動／靜態效果／事件觸發／借用傳奇特效的中文說明（與遊戲內圖鑑同一份文字）。</t>
-  </si>
-  <si>
     <t>　　備註是自動產生的參考，不進遊戲、不影響套用；你改了能力之後，備註不會自動更新（請 AI 重新產生），以左邊各欄實際內容為準。</t>
+  </si>
+  <si>
+    <t>符文孔數的硬上限，也是符文真言最多能有幾顆符文。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全域縮放：符文與符文真言的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符文真言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符文真言：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxSlots：符文孔數上限，同時也是符文真言最多能有幾顆符文（設計上限 4）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>statScale：全域屬性縮放，符文與符文真言的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>單獨鑲著就有效；組成符文真言時，符文真言的屬性與能力另外並存。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>── 符文真言列 ──</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>級距：1 普通／2 精良／3 史詩／4 傳說（沿用裝備品質的名稱與顏色）。只影響圖鑑的分組與顏色，不影響數值（強度要自己調屬性加成與效果）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配方：符文名稱依序用「;」分隔（也可填 id）。至少 2 顆、最多＝符文孔數上限；順序不同就是不同配方，不得與別的符文真言完全相同。成形條件＝依序放進連續的符文孔，且裝備類型符合。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率意義同符文列；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註：設定列＝該設定的說明；符文列＝兩側屬性的中文名稱與倍率；符文真言列＝屬性中文名稱與倍率，加上被動／靜態效果／事件觸發／借用傳奇特效的中文說明（與遊戲內圖鑑同一份文字）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2892,7 +2904,7 @@
         <v>22</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>23</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -2900,55 +2912,55 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -2956,55 +2968,55 @@
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="R4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3012,11 +3024,11 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
@@ -3057,10 +3069,10 @@
         <v>21</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3068,55 +3080,55 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="R6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3124,55 +3136,55 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="R7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -3180,10 +3192,10 @@
         <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
@@ -3228,7 +3240,7 @@
         <v>22</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -3236,10 +3248,10 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
@@ -3284,7 +3296,7 @@
         <v>22</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -3292,10 +3304,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
@@ -3340,7 +3352,7 @@
         <v>22</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -3348,10 +3360,10 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>46</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -3396,7 +3408,7 @@
         <v>22</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -3404,10 +3416,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -3452,7 +3464,7 @@
         <v>22</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -3460,10 +3472,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>21</v>
@@ -3508,7 +3520,7 @@
         <v>22</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -3516,55 +3528,55 @@
         <v>18</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -3572,55 +3584,55 @@
         <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -3628,55 +3640,55 @@
         <v>18</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R16" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -3684,11 +3696,11 @@
         <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="D17" s="3" t="s">
         <v>21</v>
       </c>
@@ -3729,10 +3741,10 @@
         <v>21</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>63</v>
+        <v>730</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -3740,55 +3752,55 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="R18" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -3796,55 +3808,55 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="R19" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -3852,55 +3864,55 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="R20" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -3908,82 +3920,82 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="F22" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
       </c>
@@ -4012,33 +4024,33 @@
         <v>21</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="F23" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
@@ -4068,33 +4080,33 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="H24" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
@@ -4124,33 +4136,33 @@
         <v>21</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -4180,33 +4192,33 @@
         <v>21</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -4236,33 +4248,33 @@
         <v>21</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="F27" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="H27" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
@@ -4292,33 +4304,33 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="H28" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
@@ -4348,33 +4360,33 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="F29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="H29" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -4404,33 +4416,33 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="F30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="H30" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>21</v>
@@ -4460,33 +4472,33 @@
         <v>21</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="H31" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>21</v>
@@ -4516,34 +4528,34 @@
         <v>21</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
       </c>
@@ -4572,34 +4584,34 @@
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="F33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="H33" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>21</v>
       </c>
@@ -4628,33 +4640,33 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="H34" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>21</v>
@@ -4684,33 +4696,33 @@
         <v>21</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="F35" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="H35" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>21</v>
@@ -4740,33 +4752,33 @@
         <v>21</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="G36" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="H36" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
@@ -4796,34 +4808,34 @@
         <v>21</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="F37" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="H37" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
       </c>
@@ -4852,33 +4864,33 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="F38" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="H38" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>21</v>
@@ -4908,33 +4920,33 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="F39" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="H39" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>21</v>
@@ -4964,33 +4976,33 @@
         <v>21</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="E40" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="H40" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>21</v>
@@ -5020,34 +5032,34 @@
         <v>21</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="F41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
       </c>
@@ -5076,33 +5088,33 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="G42" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="H42" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>21</v>
@@ -5132,34 +5144,34 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="F43" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>21</v>
       </c>
@@ -5188,33 +5200,33 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="E44" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="G44" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="H44" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>21</v>
@@ -5244,33 +5256,33 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="E45" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="H45" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>21</v>
@@ -5300,33 +5312,33 @@
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="H46" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>21</v>
@@ -5356,33 +5368,33 @@
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="H47" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>21</v>
@@ -5412,33 +5424,33 @@
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="E48" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="H48" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>21</v>
@@ -5468,33 +5480,33 @@
         <v>21</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>221</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>21</v>
@@ -5524,33 +5536,33 @@
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="E50" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>225</v>
-      </c>
       <c r="G50" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>21</v>
@@ -5580,33 +5592,33 @@
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="G51" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>21</v>
@@ -5636,34 +5648,34 @@
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="E52" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>21</v>
       </c>
@@ -5692,33 +5704,33 @@
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="E53" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="G53" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>21</v>
@@ -5748,33 +5760,33 @@
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="E54" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="G54" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>21</v>
@@ -5804,2370 +5816,2370 @@
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="J55" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="K55" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="3" t="s">
+      <c r="L55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P55" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J55" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="K56" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I56" s="3" t="s">
+      <c r="L56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="K57" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" s="3" t="s">
+      <c r="L57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O57" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="P57" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="K58" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I58" s="3" t="s">
+      <c r="L58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="J59" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="M59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="K60" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I60" s="3" t="s">
+      <c r="L60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O60" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="P60" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="J61" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="K61" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="3" t="s">
+      <c r="L61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="J61" s="3" t="s">
+      <c r="P61" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="K61" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="P61" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="J62" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="K62" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I62" s="3" t="s">
+      <c r="L62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N62" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="J62" s="3" t="s">
+      <c r="O62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P62" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J63" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I63" s="3" t="s">
+      <c r="L63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="J63" s="3" t="s">
+      <c r="O63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P63" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="K63" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>301</v>
-      </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="K64" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I64" s="3" t="s">
+      <c r="L64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>307</v>
-      </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="J65" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="K65" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I65" s="3" t="s">
+      <c r="L65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N65" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="O65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="K65" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N65" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I66" s="3" t="s">
+      <c r="L66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="J66" s="3" t="s">
+      <c r="O66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67" s="3" t="s">
+      <c r="L67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P67" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="L68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O68" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I68" s="3" t="s">
+      <c r="P68" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="J68" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="L69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N69" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69" s="3" t="s">
+      <c r="O69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P69" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="L70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70" s="3" t="s">
+      <c r="P70" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>345</v>
-      </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="L71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N71" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I71" s="3" t="s">
+      <c r="O71" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="J71" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K71" s="3" t="s">
+      <c r="P71" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="L71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K72" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="L72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="3" t="s">
+      <c r="O72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K73" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="L73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N73" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I73" s="3" t="s">
+      <c r="O73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P73" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="J73" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74" s="3" t="s">
+      <c r="L74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O74" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O74" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="L75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O75" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75" s="3" t="s">
+      <c r="P75" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J75" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O75" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="P75" s="3" t="s">
-        <v>377</v>
-      </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="L76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O76" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76" s="3" t="s">
+      <c r="P76" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>383</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" s="3" t="s">
+      <c r="L77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O77" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="J77" s="3" t="s">
+      <c r="P77" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="K77" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O77" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="P77" s="3" t="s">
-        <v>389</v>
-      </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="K78" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I78" s="3" t="s">
+      <c r="L78" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="J78" s="3" t="s">
+      <c r="M78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O78" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="K78" s="3" t="s">
+      <c r="P78" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="L78" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="M78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="P78" s="3" t="s">
-        <v>397</v>
-      </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="L79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N79" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79" s="3" t="s">
+      <c r="O79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P79" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="J79" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="O79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>403</v>
-      </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="J80" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="K80" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I80" s="3" t="s">
+      <c r="L80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O80" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="J80" s="3" t="s">
+      <c r="P80" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="K80" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O80" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="K81" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I81" s="3" t="s">
+      <c r="L81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O81" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="P81" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="L82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P82" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P82" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="L83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N83" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I83" s="3" t="s">
+      <c r="O83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P83" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>428</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K84" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="L84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N84" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I84" s="3" t="s">
+      <c r="O84" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="J84" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K84" s="3" t="s">
+      <c r="P84" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="L84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N84" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="O84" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="P84" s="3" t="s">
-        <v>435</v>
-      </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K85" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="L85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O85" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I85" s="3" t="s">
+      <c r="P85" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="J85" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="L85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O85" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="P85" s="3" t="s">
-        <v>441</v>
-      </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="K86" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="L86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I86" s="3" t="s">
+      <c r="O86" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="K86" s="3" t="s">
+      <c r="P86" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="L86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N86" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="O86" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="P86" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K87" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="L87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="3" t="s">
+      <c r="P87" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="J87" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K88" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="L88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" s="3" t="s">
+      <c r="O88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P88" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="J88" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>460</v>
-      </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J89" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="K89" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="3" t="s">
+      <c r="L89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="J89" s="3" t="s">
+      <c r="N89" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="O89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P89" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>468</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J90" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="K90" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" s="3" t="s">
+      <c r="L90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N90" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="J90" s="3" t="s">
+      <c r="O90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P90" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="K90" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N90" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J91" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="K91" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="J91" s="3" t="s">
+      <c r="M91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K92" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="L92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92" s="3" t="s">
+      <c r="O92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P92" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N92" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K93" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="L93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N93" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" s="3" t="s">
+      <c r="O93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P93" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="J93" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N93" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="O93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>495</v>
-      </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="J94" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="K94" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I94" s="3" t="s">
+      <c r="L94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O94" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="J94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="L95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95" s="3" t="s">
+      <c r="O95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P95" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="J95" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N95" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="O95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>508</v>
-      </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="L96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>515</v>
-      </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>22</v>
@@ -8185,45 +8197,45 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P97" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="J97" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N97" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="O97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P97" s="3" t="s">
-        <v>520</v>
-      </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -8241,45 +8253,45 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="J98" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="K98" s="3" t="s">
+      <c r="P98" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="L98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N98" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="O98" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="P98" s="3" t="s">
-        <v>527</v>
-      </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -8297,45 +8309,45 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P99" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="J99" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N99" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>533</v>
-      </c>
       <c r="Q99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>22</v>
@@ -8353,45 +8365,45 @@
         <v>21</v>
       </c>
       <c r="I100" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="O100" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>540</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>22</v>
@@ -8409,45 +8421,45 @@
         <v>21</v>
       </c>
       <c r="I101" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="O101" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="K101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>547</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>22</v>
@@ -8465,45 +8477,45 @@
         <v>21</v>
       </c>
       <c r="I102" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>553</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>22</v>
@@ -8521,45 +8533,45 @@
         <v>21</v>
       </c>
       <c r="I103" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="K103" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="L103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N103" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O103" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="J103" s="3" t="s">
+      <c r="P103" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="K103" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="L103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O103" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="P103" s="3" t="s">
-        <v>560</v>
-      </c>
       <c r="Q103" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>22</v>
@@ -8577,45 +8589,45 @@
         <v>21</v>
       </c>
       <c r="I104" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="L104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="O104" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="J104" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="K104" s="3" t="s">
+      <c r="P104" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="L104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="O104" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="P104" s="3" t="s">
-        <v>567</v>
-      </c>
       <c r="Q104" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R104" s="3" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>22</v>
@@ -8633,45 +8645,45 @@
         <v>21</v>
       </c>
       <c r="I105" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K105" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="L105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M105" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N105" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="O105" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="J105" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K105" s="3" t="s">
+      <c r="P105" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="L105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="O105" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="P105" s="3" t="s">
-        <v>574</v>
-      </c>
       <c r="Q105" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>22</v>
@@ -8689,45 +8701,45 @@
         <v>21</v>
       </c>
       <c r="I106" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="L106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N106" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="J106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="K106" s="3" t="s">
+      <c r="P106" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="L106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N106" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="P106" s="3" t="s">
-        <v>582</v>
-      </c>
       <c r="Q106" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R106" s="3" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>22</v>
@@ -8745,45 +8757,45 @@
         <v>21</v>
       </c>
       <c r="I107" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="K107" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="L107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M107" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="J107" s="3" t="s">
+      <c r="N107" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="K107" s="3" t="s">
+      <c r="O107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P107" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="L107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M107" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="N107" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="O107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P107" s="3" t="s">
-        <v>590</v>
-      </c>
       <c r="Q107" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R107" s="3" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>22</v>
@@ -8801,45 +8813,45 @@
         <v>21</v>
       </c>
       <c r="I108" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="L108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M108" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="N108" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P108" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="J108" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="K108" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="L108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M108" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="N108" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="O108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P108" s="3" t="s">
-        <v>596</v>
-      </c>
       <c r="Q108" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R108" s="3" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>22</v>
@@ -8857,45 +8869,45 @@
         <v>21</v>
       </c>
       <c r="I109" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="K109" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N109" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="O109" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="J109" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="K109" s="3" t="s">
+      <c r="P109" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="L109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N109" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="O109" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="P109" s="3" t="s">
-        <v>603</v>
-      </c>
       <c r="Q109" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>241</v>
+        <v>731</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>22</v>
@@ -8913,34 +8925,34 @@
         <v>21</v>
       </c>
       <c r="I110" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="L110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N110" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="J110" s="3" t="s">
+      <c r="O110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P110" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="K110" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P110" s="3" t="s">
-        <v>610</v>
-      </c>
       <c r="Q110" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R110" s="3" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -8960,17 +8972,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -8980,22 +8992,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>617</v>
+        <v>732</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -9005,37 +9017,37 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>619</v>
+        <v>733</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>622</v>
+        <v>734</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
@@ -9045,27 +9057,27 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>629</v>
+        <v>735</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -9075,102 +9087,102 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>631</v>
+        <v>737</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>632</v>
+        <v>738</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>635</v>
+        <v>739</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7735472D-0E61-4833-A640-BED65EED2CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578D2905-1597-495C-8C1D-F7F0FAEB51A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="859">
   <si>
     <t>類型</t>
   </si>
@@ -195,2180 +195,3096 @@
     <t>符文孔數：神鑄混沌</t>
   </si>
   <si>
+    <t>0.3</t>
+  </si>
+  <si>
+    <t>符文</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>caster</t>
+  </si>
+  <si>
+    <t>boots</t>
+  </si>
+  <si>
+    <t>jewelry</t>
+  </si>
+  <si>
+    <t>twoHand</t>
+  </si>
+  <si>
+    <t>aspdMult:15</t>
+  </si>
+  <si>
+    <t>staff2h</t>
+  </si>
+  <si>
+    <t>rw_legion</t>
+  </si>
+  <si>
+    <t>萬軍</t>
+  </si>
+  <si>
+    <t>嵐;虛空;命運;永恆</t>
+  </si>
+  <si>
+    <t>greatsword2h;axe2h</t>
+  </si>
+  <si>
+    <t>atkPct:3;aspd:3;aoeDmg:2</t>
+  </si>
+  <si>
+    <t>splashPct:50;dmgPerFoePct:6</t>
+  </si>
+  <si>
+    <t>一人成軍，一劍橫掃萬軍。</t>
+  </si>
+  <si>
+    <t>rw_bladedancer</t>
+  </si>
+  <si>
+    <t>劍舞者</t>
+  </si>
+  <si>
+    <t>aspd:3;critRate:3;atkPct:3</t>
+  </si>
+  <si>
+    <t>舞到最後一步時，才知道這是一場不能停的舞。</t>
+  </si>
+  <si>
+    <t>rw_voidwalker</t>
+  </si>
+  <si>
+    <t>虛空行者</t>
+  </si>
+  <si>
+    <t>evasion:6;hit:4;hpPct:3</t>
+  </si>
+  <si>
+    <t>dmgPct:25</t>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":30,"cd":4,"acts":[{"act":"invuln","sec":1.5},{"act":"dmg","pct":150,"elem":"dark","to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>走進虛空的人，被攻擊的永遠是上一個位置。</t>
+  </si>
+  <si>
+    <t>rw_genesis</t>
+  </si>
+  <si>
+    <t>創世紀</t>
+  </si>
+  <si>
+    <t>永恆;混沌;創生;終焉</t>
+  </si>
+  <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>atkPct:3;matkPct:3;elemDmgFire:1.5;elemDmgIce:1.5;elemDmgLightning:1.5;elemDmgPoison:1.5;elemDmgLight:1.5;elemDmgDark:1.5;elemDmgEarth:1.5;elemDmgWind:1.5</t>
+  </si>
+  <si>
+    <t>dmgPct:50;cdPct:20;aspdMult:15;manaCostRedPct:30</t>
+  </si>
+  <si>
+    <t>最後一顆符文落下時，世界從頭開始。</t>
+  </si>
+  <si>
+    <t>符文表（Runes）欄位與規則說明</t>
+  </si>
+  <si>
+    <t>本頁為說明頁，程式不讀取；第一頁「Runes」才是資料來源。改完存檔（Ctrl+S）後雙擊「套用參數.bat」套用，本機開著的遊戲約 2 秒自動重載。</t>
+  </si>
+  <si>
+    <t>套用時會檢查：詞條鍵、符文名稱、適用裝備、效果鍵、事件觸發 JSON、孔數上限等；任何一格打錯都會整次中止並指出是哪一列哪一格，遊戲程式不會被改到。</t>
+  </si>
+  <si>
+    <t>── 三種列（「類型」欄；用篩選看各自的那一段）──</t>
+  </si>
+  <si>
+    <t>設定：全域設定。id 是鑰匙欄，不可改名；數值填在「設定值」。</t>
+  </si>
+  <si>
+    <t>符文：33 種符文。列的先後順序＝階數（第 1 列＝第 1 階），id 依序為 r01～r33，不可重排、不可增刪。</t>
+  </si>
+  <si>
+    <t>── 設定列 ──</t>
+  </si>
+  <si>
+    <t>composeCount／composeMaxTier／dismantleYield：合成（同種幾顆→下一階 1 顆）、最高合成階（更高階只能掉落）、拆解產出（必須小於合成所需顆數；預設 1＝只能降階頂替、不會變多）。</t>
+  </si>
+  <si>
+    <t>drop_*：掉落。basePct 野外每次擊殺的基礎掉落率(%)（再乘掉寶率與地圖獎勵倍率）、towerBossPct 封魔塔通關的基礎掉落率(%)、tierSpread 階數稀有度（相鄰兩階的機率比，0~1，越小高階越稀有）、progressPerTier 每 +1 進度對應的最高掉落階增量。</t>
+  </si>
+  <si>
+    <t>　　取得難度只由「配方最高階那顆符文」決定；各級距的最高階區間與估算小時數見 docs/RUNEWORD_DESIGN.md，估算用 node tools/rw_econ_probe.cjs。</t>
+  </si>
+  <si>
+    <t>── 符文列 ──</t>
+  </si>
+  <si>
+    <t>武器詞條／武器倍率：符文鑲在主手或雙手武器時給的屬性（詞條鍵見 Equipment_Affix 表的詞條池）。倍率＝這件裝備上「一條滿刻度中位數詞條」的幾倍；數值隨裝備等級、稀有度、強化成長，與詞條同一套算法。</t>
+  </si>
+  <si>
+    <t>　　是「額外附加」的一條屬性，直接加進角色該屬性的加總，不是乘在裝備原有詞條上，也不是乘整個角色的數值。</t>
+  </si>
+  <si>
+    <t>防具詞條／防具倍率：符文鑲在防具、飾品、副手時給的屬性，規則同上。</t>
+  </si>
+  <si>
+    <t>適用裝備：用「;」分隔，多項為「或」。標記：any 任意、armor 八件防具、jewelry 戒指＋項鍊、mainHand 主手與雙手武器、twoHand 雙手武器、oneHand 單手武器、offHand 副手、melee 近戰武器、caster 施法類武器／副手；</t>
+  </si>
+  <si>
+    <t>　　也可填裝備欄位（weapon、helmet、shoulder、chest、belt、gloves、wrist、legs、boots、ring、amulet）或武器類型鍵（sword1h、dagger1h、staff2h、shield、focus… 見 data.js WEAPON_TYPES）。</t>
+  </si>
+  <si>
+    <t>被動：「鍵:數值」用「;」分隔，鍵限 thorns（反震）、smite（天罰）、undying（不朽）、sunder（破甲）、trueDmg（真傷）、omniDrain（萬象汲取）、soulEater、annihilate、sanctuary、godWrath；並入既有被動。</t>
+  </si>
+  <si>
+    <t>傳奇特效：借用既有傳奇特效（Equipment_Affix 表傳奇特效池的 id，用「;」分隔），不受該特效原本的武器類型限制，但仍需要配戴對應技能才有感。</t>
+  </si>
+  <si>
+    <t>靜態效果：「鍵:數值」用「;」分隔，數字固定、不隨稀有度成長。可用鍵：</t>
+  </si>
+  <si>
+    <t>　　dmgPct 造成傷害%、skillDmgPct 技能傷害%、basicDmgPct 普攻傷害%、aspdMult 攻速額外乘算%、cdPct 技能冷卻-%（乘算）、manaCostRedPct 法力消耗-%、maxHitPct 單次受傷上限（最大生命%）、maxHpPct 最大生命%（乘算，負數＝代價）、</t>
+  </si>
+  <si>
+    <t>　　dmgHiHpPct 對高血(&gt;70%)敵人增傷%、dmgLoHpPct 對低血(&lt;30%)敵人增傷%、dmgSoloPct 只有一隻敵人時增傷%、dmgPerFoePct 每多一隻敵人增傷%、dmgSelfFullPct 自身高血增傷%、dmgSelfLowPct 自身低血增傷%、dmgCtrlPct 對被控場敵人增傷%、</t>
+  </si>
+  <si>
+    <t>　　killHealPct 擊殺回血%、killManaPct 擊殺回魔%、runeFindPct 符文掉落率+%、selfDrainPct 每秒損失最大生命%（代價）、splashPct 普攻擴散給其他敵人%、</t>
+  </si>
+  <si>
+    <t>　　reviveHpPct／reviveCdSec／reviveInvulnSec／reviveDmgPct／reviveDmgSec／reviveRefresh 死亡復活（生命%、冷卻秒、無敵秒、之後增傷%與秒數、是否重置技能冷卻）。</t>
+  </si>
+  <si>
+    <t>事件觸發(JSON)：JSON 陣列，每條 { "on": 觸發, "chance": 機率%, "every": 秒（tick）或次數, "cd": 內建冷卻秒, "below": 生命%（lowhp）, "acts": [動作…] }。</t>
+  </si>
+  <si>
+    <t>　　觸發 on：hit 普攻命中、crit 普攻暴擊、kill 擊殺、hurt 受傷、block 格擋、cast 施放技能、tick 每 every 秒、lowhp 生命低於 below%。</t>
+  </si>
+  <si>
+    <t>　　動作 act：dmg {pct, elem?, type?(magic/phys), to?(target/all/rand/attacker), n?}、heal {pctMax}、shield {pctMax, sec}、mana {pctMax}、buff {sid, val, sec, max?}、buffRandom {sec, from:[{sid,val}]}、stun {sec, to?}、slow {sec, to?}、</t>
+  </si>
+  <si>
+    <t>　　dot {pct, sec, name(poison/burn/bleed/corrode), to?}、cdr {sec}、refresh {n?}、recast、castRandom、invuln {sec}、execute {hpBelow}、cleanse。elem 可填 fire/ice/lightning/poison/light/dark/earth/wind/random。</t>
+  </si>
+  <si>
+    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。效果說明文字由資料自動產生，不需要另外寫。</t>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：命中率×2｜防具・飾品・副手：閃避率×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×2｜防具・飾品・副手：物理防禦×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：冰屬性傷害提升×0.6｜防具・飾品・副手：冰霜抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：攻擊速度×0.6｜防具・飾品・副手：閃避率×0.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理穿透×0.12｜防具・飾品・副手：物理防禦×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：毒屬性傷害提升×0.6｜防具・飾品・副手：劇毒抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：雷屬性傷害提升×0.6｜防具・飾品・副手：雷電抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：吸血×0.7｜防具・飾品・副手：生命恢復/秒×0.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：聖屬性傷害提升×0.6｜防具・飾品・副手：聖光抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×0.7｜防具・飾品・副手：生命值×0.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×0.8｜防具・飾品・副手：物理抗性×0.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×0.7｜防具・飾品・副手：法力值×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊率×0.8｜防具・飾品・副手：命中率×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對菁英傷害×0.8｜防具・飾品・副手：格擋率×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法穿透×0.15｜防具・飾品・副手：魔法抗性×0.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暗屬性傷害提升×0.8｜防具・飾品・副手：暗影抗性×0.4（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：火屬性傷害提升×0.8｜防具・飾品・副手：火焰抗性×0.4（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：冷卻縮減×0.9｜防具・飾品・副手：魔法防禦×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：攻擊速度×1｜防具・飾品・副手：韌性×1（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：風屬性傷害提升×1｜防具・飾品・副手：疾風抗性×0.5（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對BOSS傷害×1.1｜防具・飾品・副手：護盾效率×1.1（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：地屬性傷害提升×1.1｜防具・飾品・副手：生命值×1.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×1.3｜防具・飾品・副手：全局減傷×1.1（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×1.4｜防具・飾品・副手：全屬性抗性×0.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×1.4｜防具・飾品・副手：格擋減傷×1.4（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：範圍傷害×1.5｜防具・飾品・副手：控制時間縮減×1.2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊率×1.6｜防具・飾品・副手：幸運值×1.6（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對普通敵人傷害×1.7｜防具・飾品・副手：閃避率×1.7（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：吸血×1.8｜防具・飾品・副手：生命恢復/秒×1.8（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×1.9｜防具・飾品・副手：生命值×1.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×2｜防具・飾品・副手：全屬性抗性×0.9（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×2.2｜防具・飾品・副手：護盾效率×2（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對BOSS傷害×2.5｜防具・飾品・副手：全局減傷×1.8（×倍＝一條滿刻度詞條的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×2、魔法攻擊×2、命中率×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×2.5、生命值×2.5、生命恢復/秒×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×2.5、冰屬性傷害提升×1.5｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×2、生命值×2、命中率×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×1.5、生命值×1.2、物理抗性×0.8｜反震 3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.2、毒屬性傷害提升×1.5、暴擊率×1｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 60% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.5、雷屬性傷害提升×2｜普通攻擊命中時有 8% 機率：對目標造成 90% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×2、聖光抗性×1.5、生命值×1｜擊殺敵人時回復 1% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×2、物理攻擊×1、命中率×1｜擊殺敵人時回復 1% 最大生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.5、物理防禦×1.5、韌性×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×2、生命恢復/秒×2、法力值×1.5｜擊殺敵人時回復 2% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：金幣加成×2、經驗加成×1.5、掉寶率×1.2｜符文掉落率 +8%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.2、暴擊傷害×1.2、物理穿透×0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.5、火屬性傷害提升×1.5、法力值×1.5｜施放技能時有 15% 機率：回復 12% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×2.5、暴擊率×1.5、物理攻擊×1.5｜攻擊速度額外乘算 +8%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.5、雷屬性傷害提升×2.5、暴擊傷害×1.5｜普通攻擊命中時有 15% 機率：對所有敵人造成 120% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×2、冰屬性傷害提升×3、冷卻縮減×1｜對暈眩或緩速中的敵人傷害 +15%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×3、物理攻擊×2、暴擊率×1｜擊殺敵人時回復 3% 最大生命；生命低於 35% 時，傷害 +25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×3、物理防禦×3、物理抗性×1｜單次受到的傷害最多只會是最大生命的 40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×3.5、命中率×2、生命值×1.5｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×2、法力值×3、全屬性抗性×1｜每 10 秒：回復 8% 最大生命，回復 8% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×2、毒屬性傷害提升×3、魔法穿透×0.3｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 60% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×3、暴擊率×2、物理攻擊×1.5｜普通攻擊暴擊時：獲得「攻速」+12%（3 秒，最多 3 層）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×2.5、物理防禦×2、物理抗性×1｜反震 12%；受到傷害時有 20% 機率：對攻擊者造成 100% 物理傷害（內建冷卻 3 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：幸運值×3、暴擊率×2、暴擊傷害×2.5、掉寶率×2｜符文掉落率 +15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：格擋率×3、格擋減傷×3、生命值×2｜格擋成功時有 40% 機率：對攻擊者造成 200% 物理傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3、法力值×3、冷卻縮減×2｜施放技能時有 20% 機率：所有技能冷卻縮短 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：寶石鑲嵌效率×3、詞條上限率×2、強化成功率×3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、對BOSS傷害×3｜造成的所有傷害 +18%；攻擊速度額外乘算 +10%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×4、暴擊傷害×4、對菁英傷害×3、物理穿透×0.5｜對生命低於 30% 的敵人傷害 +60%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 15% 的非 BOSS 敵人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3、風屬性傷害提升×2、魔法穿透×0.5｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 120% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 100% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×4、魔法攻擊×3、法力恢復/秒×3、生命值×2｜所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 1 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×4、物理防禦×3.5、魔法防禦×3.5、全局減傷×2｜生命低於 30% 時：無敵 3 秒，回復 30% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×2.5、物理攻擊×2.5、暴擊率×1.5、範圍傷害×2｜場上每多一名敵人，傷害 +5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 20% 的傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊率×1.5、暴擊傷害×2、物理攻擊×2、閃避率×1.5｜對生命高於 70% 的敵人傷害 +20%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：飛刀的彈射數 +2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×4、法力恢復/秒×4、魔法攻擊×2.5｜技能法力消耗 -40%；擊殺敵人時回復 3% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×3.5、物理防禦×3.5、物理抗性×2｜反震 35%；受到傷害時有 25% 機率：對所有敵人造成 150% 物理傷害（內建冷卻 2 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：對BOSS傷害×5、對菁英傷害×4、物理攻擊×2.5、魔法攻擊×2.5｜對生命高於 70% 的敵人傷害 +40%；場上只有一名敵人時，傷害 +40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×4、吸血×4、生命恢復/秒×4｜擊殺敵人時回復 6% 最大生命；生命高於 90% 時，傷害 +25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：護盾效率×5、生命值×3、全局減傷×2.5｜每 8 秒：獲得相當於 20% 最大生命的護盾（8 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：火屬性傷害提升×1.8、冰屬性傷害提升×1.8、雷屬性傷害提升×1.8、風屬性傷害提升×1.8、毒屬性傷害提升×1.8｜造成的所有傷害 +10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×4、暴擊率×3、命中率×2｜攻擊速度額外乘算 +15%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>　　備註是自動產生的參考，不進遊戲、不影響套用；你改了能力之後，備註不會自動更新（請 AI 重新產生），以左邊各欄實際內容為準。</t>
+  </si>
+  <si>
+    <t>符文真言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符文孔數的硬上限，也是符文真言最多能有幾顆符文。目前 5：一般裝備最多 4 孔，5 顆符文的真言是為「雙手武器之後最多 5 孔」預留的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twoHandBonusSlots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙手武器額外符文孔數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙手武器的符文孔比一般裝備多幾個（0＝一樣多）。設成 1，傳說以上的雙手武器就有 5 孔，5 顆符文的真言（只能用在雙手武器）才做得出來。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>composeCount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>合成所需顆數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>合成：同種符文幾顆合成下一階 1 顆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>composeMaxTier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>最高合成階</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>能合成到第幾階；更高階的符文只能靠擊殺與封魔塔掉落。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dismantleYield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>拆解產出顆數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>拆解 1 顆得到低一階符文幾顆；必須小於合成所需顆數。≥2 會讓一顆高階符文拆出指數倍的低階符文、破壞稀有度，所以預設 1（只能降階頂替、不會變多）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>statScale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>全域屬性縮放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全域縮放：符文與符文真言的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_basePct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>野外基礎掉落率(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>野外每次擊殺的基礎掉落率（%），再乘掉寶率、地圖倍率與敵種倍率。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_towerBossPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>封魔塔基礎掉落率(%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>封魔塔通關時的基礎掉落機率（%）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_tierSpread</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落階數分佈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0.74</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>階數稀有度：第 t+1 階的出現機率是第 t 階的這個倍數（0~1，越小高階越稀有）。階越高越稀有，與進度無關；進度只決定能掉到幾階。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>drop_progressPerTier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>每進度的最高階增量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>4.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>進度（地圖序號＋關卡比例）每 +1 對應的最高掉落階增量（解鎖速度，不影響稀有度）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>微光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>餘燼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkFlat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defFlat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜痕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgIce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resIce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巖心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pPen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒牙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgPoison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resPoison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷鳴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgLightning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resLightning</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifesteal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpRegen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聖輝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgLight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resLight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血誓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鋼魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pRes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靈泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpFlat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磐石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eliteDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>曙光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mPen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mRes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgDark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resDark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈陽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgFire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resFire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mdefPct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驚蟄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tenacity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgWind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resWind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒼穹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bossDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shieldEff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgEarth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>熔岩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>globalDmgRed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resAll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷霆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockDmgRed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虛空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aoeDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ccRed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命運</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>normalDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輪迴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>永恆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>混沌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>創生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>符文</t>
-  </si>
-  <si>
-    <t>r01</t>
-  </si>
-  <si>
-    <t>hit</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>evasion</t>
-  </si>
-  <si>
-    <t>r02</t>
-  </si>
-  <si>
-    <t>餘燼</t>
-  </si>
-  <si>
-    <t>atkFlat</t>
-  </si>
-  <si>
-    <t>defFlat</t>
-  </si>
-  <si>
-    <t>r03</t>
-  </si>
-  <si>
-    <t>霜痕</t>
-  </si>
-  <si>
-    <t>elemDmgIce</t>
-  </si>
-  <si>
-    <t>resIce</t>
-  </si>
-  <si>
-    <t>r04</t>
-  </si>
-  <si>
-    <t>風語</t>
-  </si>
-  <si>
-    <t>aspd</t>
-  </si>
-  <si>
-    <t>0.7</t>
-  </si>
-  <si>
-    <t>r05</t>
-  </si>
-  <si>
-    <t>巖心</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>pPen</t>
-  </si>
-  <si>
-    <t>0.12</t>
-  </si>
-  <si>
-    <t>defPct</t>
-  </si>
-  <si>
-    <t>r06</t>
-  </si>
-  <si>
-    <t>毒牙</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>elemDmgPoison</t>
-  </si>
-  <si>
-    <t>resPoison</t>
-  </si>
-  <si>
-    <t>r07</t>
-  </si>
-  <si>
-    <t>雷鳴</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>elemDmgLightning</t>
-  </si>
-  <si>
-    <t>resLightning</t>
-  </si>
-  <si>
-    <t>r08</t>
-  </si>
-  <si>
-    <t>暗影</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>lifesteal</t>
-  </si>
-  <si>
-    <t>hpRegen</t>
-  </si>
-  <si>
-    <t>r09</t>
-  </si>
-  <si>
-    <t>聖輝</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>elemDmgLight</t>
-  </si>
-  <si>
-    <t>resLight</t>
-  </si>
-  <si>
-    <t>r10</t>
-  </si>
-  <si>
-    <t>血誓</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>atkPct</t>
-  </si>
-  <si>
-    <t>hpPct</t>
-  </si>
-  <si>
-    <t>r11</t>
-  </si>
-  <si>
-    <t>鋼魄</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>critDmg</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>pRes</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
-    <t>r12</t>
-  </si>
-  <si>
-    <t>靈泉</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>matkPct</t>
-  </si>
-  <si>
-    <t>mpFlat</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>r13</t>
-  </si>
-  <si>
-    <t>疾影</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>critRate</t>
-  </si>
-  <si>
-    <t>r14</t>
-  </si>
-  <si>
-    <t>磐石</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>eliteDmg</t>
-  </si>
-  <si>
-    <t>blockRate</t>
-  </si>
-  <si>
-    <t>r15</t>
-  </si>
-  <si>
-    <t>曙光</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>mPen</t>
-  </si>
-  <si>
-    <t>0.15</t>
-  </si>
-  <si>
-    <t>mRes</t>
-  </si>
-  <si>
-    <t>r16</t>
-  </si>
-  <si>
-    <t>夜幕</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>elemDmgDark</t>
-  </si>
-  <si>
-    <t>resDark</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>r17</t>
-  </si>
-  <si>
-    <t>烈陽</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>elemDmgFire</t>
-  </si>
-  <si>
-    <t>resFire</t>
-  </si>
-  <si>
-    <t>r18</t>
-  </si>
-  <si>
-    <t>寒月</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>cdr</t>
-  </si>
-  <si>
-    <t>mdefPct</t>
-  </si>
-  <si>
-    <t>r19</t>
-  </si>
-  <si>
-    <t>驚蟄</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>tenacity</t>
-  </si>
-  <si>
-    <t>r20</t>
-  </si>
-  <si>
-    <t>嵐</t>
-  </si>
-  <si>
-    <t>elemDmgWind</t>
-  </si>
-  <si>
-    <t>resWind</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>r21</t>
-  </si>
-  <si>
-    <t>蒼穹</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>bossDmg</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>shieldEff</t>
-  </si>
-  <si>
-    <t>r22</t>
-  </si>
-  <si>
-    <t>厚土</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>elemDmgEarth</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>r23</t>
-  </si>
-  <si>
-    <t>熔岩</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>globalDmgRed</t>
-  </si>
-  <si>
-    <t>r24</t>
-  </si>
-  <si>
-    <t>冰魄</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>resAll</t>
-  </si>
-  <si>
-    <t>r25</t>
-  </si>
-  <si>
-    <t>雷霆</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>blockDmgRed</t>
-  </si>
-  <si>
-    <t>r26</t>
-  </si>
-  <si>
-    <t>虛空</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>aoeDmg</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>ccRed</t>
-  </si>
-  <si>
-    <t>r27</t>
-  </si>
-  <si>
-    <t>星辰</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>luck</t>
-  </si>
-  <si>
-    <t>r28</t>
-  </si>
-  <si>
-    <t>命運</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>normalDmg</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
-    <t>r29</t>
-  </si>
-  <si>
-    <t>輪迴</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>r30</t>
-  </si>
-  <si>
-    <t>永恆</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1.9</t>
-  </si>
-  <si>
-    <t>r31</t>
-  </si>
-  <si>
-    <t>混沌</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>r32</t>
-  </si>
-  <si>
-    <t>創生</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>r33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>終焉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_firstcry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>初啼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>微光;餘燼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>mainHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkFlat:2;matkFlat:2;hit:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>第一聲啼鳴，劃破長夜的寂靜。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_nightwatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>守夜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>餘燼;巖心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>chest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>defFlat:2.5;hpFlat:2.5;hpRegen:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>燈火不滅，守夜人便不眠。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_frostwhisper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>霜語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>霜痕;風語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>caster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkFlat:2.5;elemDmgIce:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","chance":10,"acts":[{"act":"slow","sec":2}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>寒風低語，敵人的腳步便慢了下來。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_windwalk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>行雲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>風語;微光;暗影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>boots</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>evasion:2;hpFlat:2;hit:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>步履如雲，不留痕跡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_stoneskin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>石膚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>巖心;霜痕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>shoulder;legs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>defPct:1.5;hpPct:1.2;pRes:0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>thorns:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>皮膚堅如岩層，觸碰者必受其傷。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_viperkiss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>蛇吻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>毒牙;暗影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>sword1h;dagger1h;magicSword1h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:1.2;elemDmgPoison:1.5;critRate:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","chance":15,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>毒蛇的一吻，慢慢收走對手的生命。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_minorthunder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>輕雷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷鳴;風語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>oneHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:1.5;elemDmgLightning:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":90,"elem":"lightning","to":"target"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一聲輕雷，落在不經意的地方。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_lightguard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>聖光之守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>微光;聖輝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>helmet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>mpFlat:2;resLight:1.5;hpPct:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>killManaPct:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>以聖光為冠，心神澄明。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_bloodring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血誓之環</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血誓;暗影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>ring</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>lifesteal:2;atkPct:1;hit:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>killHealPct:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>以血起誓，生者共飲。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_steelheart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>鋼心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>巖心;血誓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>belt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:1.5;defPct:1.5;tenacity:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>腰繫鋼索，心不動搖。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_springflow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>泉湧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>微光;餘燼;暗影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>amulet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>mpRegen:2;hpRegen:2;mpFlat:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>killManaPct:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>源源不絕，如山間清泉。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_scavenger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>拾荒者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>微光;風語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>jewelry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>goldBonus:2;xpBonus:1.5;loot:1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>runeFindPct:8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>連廢墟裡的一粒塵埃，也要翻過三遍。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_breaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>破軍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>餘燼;血誓;巖心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>twoHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:1.2;critDmg:1.2;pPen:0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>重兵一落，軍陣自潰。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_burnstar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>燃星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>餘燼;聖輝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:1.5;elemDmgFire:1.5;mpFlat:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"cast","chance":15,"acts":[{"act":"mana","pctMax":12}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>星火燎原，施法者的靈感湧現。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_galeblade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>疾風烈刃</t>
-  </si>
-  <si>
-    <t>疾影;風語;雷鳴;磐石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風語;疾影;磐石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspd:2.5;critRate:1.5;atkPct:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspdMult:8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>快過風的刃，連風聲都追不上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_thundergod</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷神之怒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷鳴;血誓;鋼魄;夜幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:1.5;elemDmgLightning:2.5;critDmg:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","chance":15,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>神怒所至，雷霆不擇敵我之外。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_winterherald</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>凜冬使者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>霜痕;霜痕;靈泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:2;elemDmgIce:3;cdr:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgCtrlPct:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","chance":20,"acts":[{"act":"stun","sec":1.5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>冬天來了，所過之處萬物凝結。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_bloodgulp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血飲者</t>
-  </si>
-  <si>
-    <t>血誓;暗影;血誓;疾影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血誓;暗影;疾影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>lifesteal:3;atkPct:2;critRate:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>killHealPct:3;dmgSelfLowPct:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>越是瀕死，越是渴血。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_unmoving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>不動山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>巖心;磐石;鋼魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:3;defPct:3;pRes:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>maxHitPct:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>任憑千鈞一擊，山自巍然。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_shadowstep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>影步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>暗影;疾影;夜幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>boots;legs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>evasion:3.5;hit:2;hpPct:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hurt","chance":15,"cd":10,"acts":[{"act":"invuln","sec":1}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一步踏入影中，攻擊落了空。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_dawncrown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>旭日之冠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>曙光;聖輝;靈泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:2;mpFlat:3;resAll:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"tick","every":10,"acts":[{"act":"heal","pctMax":8},{"act":"mana","pctMax":8}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>戴上旭日，每一刻都是黎明。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_poisoncloud</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>毒雲</t>
-  </si>
-  <si>
-    <t>毒牙;毒牙;暗影;靈泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒牙;毒牙;靈泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:2;elemDmgPoison:3;mPen:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"cast","chance":25,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>施法之後，毒霧久久不散。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_awakening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>風語;雷鳴;疾影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>gloves</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspd:3;critRate:2;atkPct:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":3,"max":3}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一聲春雷，萬蟲驚動。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_ironoath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>重甲鐵誓</t>
-  </si>
-  <si>
-    <t>磐石;巖心;鋼魄;血誓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磐石;鋼魄;血誓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>shoulder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:2.5;defPct:2;pRes:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>thorns:12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hurt","chance":20,"cd":3,"acts":[{"act":"dmg","pct":100,"type":"phys","to":"attacker"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>以鐵起誓，傷我者必以鐵還之。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_gambler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>賭徒之戒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>微光;疾影;夜幕;鋼魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>luck:3;critRate:2;critDmg:2.5;loot:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>runeFindPct:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>全押。贏了拿走一切，輸了也不過一場好戲。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_guardian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>守護者之盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>磐石;鋼魄;巖心;曙光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>blockRate:3;blockDmgRed:3;hpPct:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"block","chance":40,"acts":[{"act":"dmg","pct":200,"type":"phys","to":"attacker"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>盾不是為了後退，是為了把力量還給對方。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_arcaneecho</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>奧術迴響</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>靈泉;曙光;靈泉;聖輝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>focus;spellbook;orb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:3;mpFlat:3;cdr:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"cast","chance":20,"acts":[{"act":"cdr","sec":1.5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>咒語落下之後，還在空氣裡迴盪。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_smith</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>鐵匠之魂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>靈泉;鋼魄;磐石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>gemEff:3;affixCap:2;enhanceSuccess:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>鎚聲不絕，鋼與靈魂同鍛。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_apocalypse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>天啟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血誓;鋼魄;蒼穹;熔岩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:3;matkPct:3;critDmg:3;bossDmg:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgPct:18;aspdMult:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>號角響起，審判降臨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_soulcleaver</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>斷魂</t>
-  </si>
-  <si>
-    <t>鋼魄;驚蟄;嵐;厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鋼魄;嵐;厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:4;critDmg:4;eliteDmg:3;pPen:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgLoHpPct:60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","chance":8,"acts":[{"act":"execute","hpBelow":15}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一刀兩斷，魂亦分離。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_chainstorm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>連環雷暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷鳴;疾影;雷鳴;烈陽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:3;elemDmgLightning:3;elemDmgWind:2;mPen:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"crit","chance":30,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]},{"on":"cast","chance":25,"acts":[{"act":"dmg","pct":100,"elem":"lightning","to":"rand","n":3}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷與風相纏，一環扣一環。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_timewarden</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>時之守望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>寒月;嵐;寒月;靈泉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>cdr:4;matkPct:3;mpRegen:3;hpPct:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>cdPct:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"kill","acts":[{"act":"cdr","sec":1}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>守望者拾起墜落的時間，替你多留一點。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_lastbreath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>絕境</t>
-  </si>
-  <si>
-    <t>磐石;鋼魄;厚土;寒月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磐石;厚土;寒月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:4;defPct:3.5;mdefPct:3.5;globalDmgRed:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"lowhp","below":30,"cd":90,"acts":[{"act":"invuln","sec":3},{"act":"heal","pctMax":30},{"act":"cleanse"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>退無可退之處，才是真正的開始。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_swarmhunter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>群獵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>疾影;驚蟄;熔岩;夜幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspd:2.5;atkPct:2.5;critRate:1.5;aoeDmg:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgPerFoePct:5;splashPct:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>獸群越多，獵人越是興奮。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_assassin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>影殺</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>暗影;夜幕;疾影;厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dagger1h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>critRate:1.5;critDmg:2;atkPct:2;evasion:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>knifeShadowblade;knifeChain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgHiHpPct:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>刀影分裂成雙，雙影各自找到了喉嚨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_manafountain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>魔泉</t>
-  </si>
-  <si>
-    <t>靈泉;靈泉;寒月;蒼穹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靈泉;寒月;蒼穹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>helmet;amulet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>mpFlat:4;mpRegen:4;matkPct:2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>manaCostRedPct:40;killManaPct:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>魔力不是用完的，是流過的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_thornedfury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>荊棘之怒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>磐石;熔岩;厚土;鋼魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>chest;shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:3.5;defPct:3.5;pRes:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>thorns:35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hurt","chance":25,"cd":2,"acts":[{"act":"dmg","pct":150,"type":"phys","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>怒意生出荊棘，連空氣都帶刺。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_bossbane</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>弒王者</t>
-  </si>
-  <si>
-    <t>蒼穹;血誓;疾影;鋼魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒼穹;血誓;鋼魄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>bossDmg:5;eliteDmg:4;atkPct:2.5;matkPct:2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgHiHpPct:40;dmgSoloPct:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>王座再高，也有人要把它拆了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_vitalpact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>生命契約</t>
-  </si>
-  <si>
-    <t>血誓;暗影;厚土;厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血誓;暗影;厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:4;lifesteal:4;hpRegen:4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>killHealPct:6;dmgSelfFullPct:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>契約的對價是活著，且活得很好。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_shieldwall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>護盾牆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>蒼穹;磐石;蒼穹;厚土</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>chest;shoulder;helmet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>shieldEff:5;hpPct:3;globalDmgRed:2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"tick","every":8,"acts":[{"act":"shield","pctMax":20,"sec":8}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>牆起，風止。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_elemental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>元素之環</t>
-  </si>
-  <si>
-    <t>霜痕;烈陽;雷鳴;寒月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜痕;烈陽;嵐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>elemDmgFire:1.8;elemDmgIce:1.8;elemDmgLightning:1.8;elemDmgWind:1.8;elemDmgPoison:1.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgPct:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>五元素各執一角，在指尖上取得平衡。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_blitz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>閃擊</t>
-  </si>
-  <si>
-    <t>疾影;驚蟄;驚蟄;風語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>疾影;驚蟄;風語</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspd:4;critRate:3;hit:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspdMult:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","every":6,"acts":[{"act":"castRandom"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>揮刀太快，連技能都被牽著走。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rw_quake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地裂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巖心;磐石;厚土;雷霆;星辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:4;eliteDmg:3;pPen:0.6;critDmg:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rockEarthHeart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgHiHpPct:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":220,"type":"phys","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地在刀下裂開，裂縫一路追著敵人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×4、對菁英傷害×3、物理穿透×0.6、暴擊傷害×3｜對生命高於 70% 的敵人傷害 +30%；普通攻擊命中時有 8% 機率：對所有敵人造成 220% 物理傷害；傳奇特效【大地之心】：當你的生命護盾降至 0 時獲得無敵 2 秒；此效果每 30 秒只能觸發 1 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rw_galeeye</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風暴之眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風語;驚蟄;嵐;虛空;命運</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:4.5;critRate:3.5;atkPct:3.5;aoeDmg:2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stormbarrierCore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspdMult:18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":4,"max":4}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風暴中央最安靜，刀卻最快。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×4.5、暴擊率×3.5、物理攻擊×3.5、範圍傷害×2.5｜攻擊速度額外乘算 +18%（突破攻速上限）；普通攻擊暴擊時：獲得「攻速」+12%（4 秒，最多 4 層）；傳奇特效【風暴核心】：【暴風神體】的持續時間 +50%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rw_bloodrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血祭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血誓;暗影;厚土;冰魄;虛空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:4.5;lifesteal:4.5;critDmg:4.5;hpPct:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bloodVenomRite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killHealPct:8;dmgSelfLowPct:60;dmgPct:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以血為祭，戰場上的每一滴都算數。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×4.5、吸血×4.5、暴擊傷害×4.5、生命值×3｜擊殺敵人時回復 8% 最大生命；生命低於 35% 時，傷害 +60%；造成的所有傷害 +30%；傳奇特效【毒血祭】：血刃斬的中毒每感染 1 個敵人就使自身生命值 -1%，但造成的中毒與流血傷害提高 50%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_reincarnation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>命運;輪迴;永恆;創生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:4;defPct:4;mdefPct:4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counterOath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>reviveHpPct:60;reviveCdSec:180;reviveInvulnSec:3;reviveDmgPct:60;reviveDmgSec:10;reviveRefresh:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>死亡只是下一次輪迴的開場白。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×4、物理防禦×4、魔法防禦×4｜死亡時以 60% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +60%，冷卻 180 秒；傳奇特效【堅韌誓言】：反擊 100 次後獲得無敵狀態，持續 3 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_timeloop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>時之沙</t>
-  </si>
-  <si>
-    <t>命運;輪迴;虛空;永恆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虛空;輪迴;永恆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>cdr:5;mpRegen:5;matkPct:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacuumFlux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>cdPct:45;maxHpPct:-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"cast","chance":25,"acts":[{"act":"recast"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>沙漏倒過來了。代價是你的生命，也在一起流。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×5、法力恢復/秒×5、魔法攻擊×3｜所有技能冷卻時間 -45%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能；傳奇特效【虛空漲落】：【虛空斬】的持續時間 +3 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_bloodmoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血月</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>夜幕;熔岩;雷霆;命運</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:3;matkPct:3;critDmg:3;lifesteal:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rageBurnBlood</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgPct:60;selfDrainPct:2;killHealPct:8;maxHpPct:-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>血月當空，誰先流盡誰先倒下。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、吸血×2｜造成的所有傷害 +60%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 8% 最大生命；最大生命 -30%（乘算，代價）；傳奇特效【燃血】：【血飲術】每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_arsenal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>武庫</t>
-  </si>
-  <si>
-    <t>疾影;嵐;虛空;星辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵐;虛空;星辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>aspd:3;atkPct:3;matkPct:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>knifeSplitter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skillDmgPct:40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"hit","every":4,"acts":[{"act":"castRandom"}]},{"on":"cast","chance":15,"acts":[{"act":"recast"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>每一次揮擊，都從武器庫裡抽出另一招。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×3、物理攻擊×3、魔法攻擊×3｜技能傷害 +40%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能；傳奇特效【分裂者】：飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_thunderemperor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷帝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>雷霆;雷鳴;虛空;創生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:3;elemDmgLightning:3.5;critRate:2</t>
-  </si>
-  <si>
-    <t>dmgCtrlPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":2,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"rand","n":3}]},{"on":"crit","acts":[{"act":"stun","sec":1,"to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chainlightningOverload</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgCtrlPct:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"rand","n":3}]},{"on":"crit","acts":[{"act":"stun","sec":1,"to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>帝王不需親自出手，雷霆自會代勞。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3.5、暴擊率×2｜對暈眩或緩速中的敵人傷害 +10%；每 3 秒：對隨機 3 名敵人造成 120% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒；傳奇特效【過載】：同一個敵人受到 5 次連鎖閃電的彈射後產生爆炸，對周圍 6 米內的敵人造成 200% 雷電傷害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_lonewolf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>孤狼</t>
-  </si>
-  <si>
-    <t>蒼穹;熔岩;冰魄;雷霆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒼穹;雷霆;星辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>critDmg:3.5;atkPct:3;bossDmg:3.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sunpiercerLance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgSoloPct:80;dmgHiHpPct:40;cdPct:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>孤狼只獵王者。獵物以外，一概不理。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊傷害×3.5、物理攻擊×3、對BOSS傷害×3.5｜場上只有一名敵人時，傷害 +80%；對生命高於 70% 的敵人傷害 +40%；所有技能冷卻時間 -15%（乘算，突破冷卻縮減上限）；傳奇特效【貫日之刺】：四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_starfall</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>星墜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>虛空;冰魄;星辰;輪迴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>staff2h</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>matkPct:3.5;elemDmgFire:2.5;elemDmgIce:2.5;mPen:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fireballBurst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":150,"elem":"random","to":"rand","n":5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>夜空翻面，群星墜落成雨。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3.5、火屬性傷害提升×2.5、冰屬性傷害提升×2.5、魔法穿透×0.6｜每 3 秒：對隨機 5 名敵人造成 150% 隨機元素傷害；傳奇特效【爆裂】：【火球爆裂】會額外產生 3 個小火球。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_chaoslord</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>混沌之主</t>
-  </si>
-  <si>
-    <t>混沌;虛空;輪迴;永恆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>虛空;永恆;混沌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>resAll:3;luck:4;critRate:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mireCorrupt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>skillDmgPct:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"cast","acts":[{"act":"buffRandom","sec":8,"from":[{"sid":"atkUp","val":25},{"sid":"aspdUp","val":25},{"sid":"critDmgUp","val":60},{"sid":"defUp","val":40},{"sid":"evasionUp","val":30},{"sid":"allDmgUp","val":20}]}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>混沌不問因果，每一次施法都是一場賭局。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：全屬性抗性×3、幸運值×4、暴擊率×3｜技能傷害 +25%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）；傳奇特效【腐化】：在泥沼術範圍內所有受到控場的敵人，受到的傷害 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_dragonslayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>屠龍者</t>
-  </si>
-  <si>
-    <t>熔岩;星辰;永恆;混沌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星辰;永恆;混沌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>atkPct:2.5;bossDmg:5;critDmg:2.5;pPen:0.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>galeExecute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>dmgHiHpPct:50;dmgPct:25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"crit","chance":20,"acts":[{"act":"dmg","pct":250,"type":"phys","to":"target"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>巨龍的鱗片，就是為了被一劍貫穿而生。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×2.5、對BOSS傷害×5、暴擊傷害×2.5、物理穿透×0.8｜對生命高於 70% 的敵人傷害 +50%；造成的所有傷害 +25%；普通攻擊暴擊時有 20% 機率：對目標造成 250% 物理傷害；傳奇特效【斬殺】：疾風斬有 35% 機率可立即殺死生命值 20% 以下的非 BOSS 敵人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>rw_immortalbody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>不朽之軀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>永恆;終焉;輪迴;創生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>hpPct:5;globalDmgRed:3;resAll:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earthguardUndyingWill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>maxHitPct:15;dmgPct:-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>[{"on":"lowhp","below":40,"cd":60,"acts":[{"act":"shield","pctMax":40,"sec":6},{"act":"invuln","sec":2}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>以出手的力量，換不會倒下的身軀。</t>
-  </si>
-  <si>
-    <t>rw_legion</t>
-  </si>
-  <si>
-    <t>萬軍</t>
-  </si>
-  <si>
-    <t>嵐;虛空;命運;永恆</t>
-  </si>
-  <si>
-    <t>greatsword2h;axe2h</t>
-  </si>
-  <si>
-    <t>atkPct:3;aspd:3;aoeDmg:2</t>
-  </si>
-  <si>
-    <t>skyrendSlash;gatheringVortex</t>
-  </si>
-  <si>
-    <t>splashPct:50;dmgPerFoePct:6</t>
-  </si>
-  <si>
-    <t>一人成軍，一劍橫掃萬軍。</t>
-  </si>
-  <si>
-    <t>rw_bladedancer</t>
-  </si>
-  <si>
-    <t>劍舞者</t>
-  </si>
-  <si>
-    <t>驚蟄;嵐;熔岩;冰魄</t>
-  </si>
-  <si>
-    <t>aspd:3;critRate:3;atkPct:3</t>
-  </si>
-  <si>
-    <t>danceTwinBlades;danceThousandCuts;danceUnyielding</t>
-  </si>
-  <si>
-    <t>舞到最後一步時，才知道這是一場不能停的舞。</t>
-  </si>
-  <si>
-    <t>rw_voidwalker</t>
-  </si>
-  <si>
-    <t>虛空行者</t>
-  </si>
-  <si>
-    <t>虛空;星辰;命運;輪迴</t>
-  </si>
-  <si>
-    <t>evasion:6;hit:4;hpPct:3</t>
-  </si>
-  <si>
-    <t>dmgPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":30,"cd":4,"acts":[{"act":"invuln","sec":1.5},{"act":"dmg","pct":150,"elem":"dark","to":"all"}]}]</t>
-  </si>
-  <si>
-    <t>走進虛空的人，被攻擊的永遠是上一個位置。</t>
-  </si>
-  <si>
-    <t>rw_genesis</t>
-  </si>
-  <si>
-    <t>創世紀</t>
-  </si>
-  <si>
-    <t>永恆;混沌;創生;終焉</t>
-  </si>
-  <si>
-    <t>any</t>
-  </si>
-  <si>
-    <t>atkPct:3;matkPct:3;elemDmgFire:1.5;elemDmgIce:1.5;elemDmgLightning:1.5;elemDmgPoison:1.5;elemDmgLight:1.5;elemDmgDark:1.5;elemDmgEarth:1.5;elemDmgWind:1.5</t>
-  </si>
-  <si>
-    <t>dmgPct:50;cdPct:20;aspdMult:15;manaCostRedPct:30</t>
-  </si>
-  <si>
-    <t>最後一顆符文落下時，世界從頭開始。</t>
-  </si>
-  <si>
-    <t>符文表（Runes）欄位與規則說明</t>
-  </si>
-  <si>
-    <t>本頁為說明頁，程式不讀取；第一頁「Runes」才是資料來源。改完存檔（Ctrl+S）後雙擊「套用參數.bat」套用，本機開著的遊戲約 2 秒自動重載。</t>
-  </si>
-  <si>
-    <t>套用時會檢查：詞條鍵、符文名稱、適用裝備、效果鍵、事件觸發 JSON、孔數上限等；任何一格打錯都會整次中止並指出是哪一列哪一格，遊戲程式不會被改到。</t>
-  </si>
-  <si>
-    <t>── 三種列（「類型」欄；用篩選看各自的那一段）──</t>
-  </si>
-  <si>
-    <t>設定：全域設定。id 是鑰匙欄，不可改名；數值填在「設定值」。</t>
-  </si>
-  <si>
-    <t>符文：33 種符文。列的先後順序＝階數（第 1 列＝第 1 階），id 依序為 r01～r33，不可重排、不可增刪。</t>
-  </si>
-  <si>
-    <t>── 設定列 ──</t>
-  </si>
-  <si>
-    <t>slots_&lt;稀有度&gt;：該稀有度裝備的符文孔數；0～上限，不可隨稀有度變少，最高稀有度必須等於上限。符文孔取代原本的附魔欄位，與寶石鑲孔分開，雙手武器沒有額外加成。</t>
-  </si>
-  <si>
-    <t>composeCount／composeMaxTier／dismantleYield：合成（同種幾顆→下一階 1 顆）、最高合成階（更高階只能掉落）、拆解產出（必須小於合成所需顆數；預設 1＝只能降階頂替、不會變多）。</t>
-  </si>
-  <si>
-    <t>drop_*：掉落。basePct 野外每次擊殺的基礎掉落率(%)（再乘掉寶率與地圖獎勵倍率）、towerBossPct 封魔塔通關的基礎掉落率(%)、tierSpread 階數稀有度（相鄰兩階的機率比，0~1，越小高階越稀有）、progressPerTier 每 +1 進度對應的最高掉落階增量。</t>
-  </si>
-  <si>
-    <t>　　取得難度只由「配方最高階那顆符文」決定；各級距的最高階區間與估算小時數見 docs/RUNEWORD_DESIGN.md，估算用 node tools/rw_econ_probe.cjs。</t>
-  </si>
-  <si>
-    <t>── 符文列 ──</t>
-  </si>
-  <si>
-    <t>武器詞條／武器倍率：符文鑲在主手或雙手武器時給的屬性（詞條鍵見 Equipment_Affix 表的詞條池）。倍率＝這件裝備上「一條滿刻度中位數詞條」的幾倍；數值隨裝備等級、稀有度、強化成長，與詞條同一套算法。</t>
-  </si>
-  <si>
-    <t>　　是「額外附加」的一條屬性，直接加進角色該屬性的加總，不是乘在裝備原有詞條上，也不是乘整個角色的數值。</t>
-  </si>
-  <si>
-    <t>防具詞條／防具倍率：符文鑲在防具、飾品、副手時給的屬性，規則同上。</t>
-  </si>
-  <si>
-    <t>適用裝備：用「;」分隔，多項為「或」。標記：any 任意、armor 八件防具、jewelry 戒指＋項鍊、mainHand 主手與雙手武器、twoHand 雙手武器、oneHand 單手武器、offHand 副手、melee 近戰武器、caster 施法類武器／副手；</t>
-  </si>
-  <si>
-    <t>　　也可填裝備欄位（weapon、helmet、shoulder、chest、belt、gloves、wrist、legs、boots、ring、amulet）或武器類型鍵（sword1h、dagger1h、staff2h、shield、focus… 見 data.js WEAPON_TYPES）。</t>
-  </si>
-  <si>
-    <t>被動：「鍵:數值」用「;」分隔，鍵限 thorns（反震）、smite（天罰）、undying（不朽）、sunder（破甲）、trueDmg（真傷）、omniDrain（萬象汲取）、soulEater、annihilate、sanctuary、godWrath；並入既有被動。</t>
-  </si>
-  <si>
-    <t>傳奇特效：借用既有傳奇特效（Equipment_Affix 表傳奇特效池的 id，用「;」分隔），不受該特效原本的武器類型限制，但仍需要配戴對應技能才有感。</t>
-  </si>
-  <si>
-    <t>靜態效果：「鍵:數值」用「;」分隔，數字固定、不隨稀有度成長。可用鍵：</t>
-  </si>
-  <si>
-    <t>　　dmgPct 造成傷害%、skillDmgPct 技能傷害%、basicDmgPct 普攻傷害%、aspdMult 攻速額外乘算%、cdPct 技能冷卻-%（乘算）、manaCostRedPct 法力消耗-%、maxHitPct 單次受傷上限（最大生命%）、maxHpPct 最大生命%（乘算，負數＝代價）、</t>
-  </si>
-  <si>
-    <t>　　dmgHiHpPct 對高血(&gt;70%)敵人增傷%、dmgLoHpPct 對低血(&lt;30%)敵人增傷%、dmgSoloPct 只有一隻敵人時增傷%、dmgPerFoePct 每多一隻敵人增傷%、dmgSelfFullPct 自身高血增傷%、dmgSelfLowPct 自身低血增傷%、dmgCtrlPct 對被控場敵人增傷%、</t>
-  </si>
-  <si>
-    <t>　　killHealPct 擊殺回血%、killManaPct 擊殺回魔%、runeFindPct 符文掉落率+%、selfDrainPct 每秒損失最大生命%（代價）、splashPct 普攻擴散給其他敵人%、</t>
-  </si>
-  <si>
-    <t>　　reviveHpPct／reviveCdSec／reviveInvulnSec／reviveDmgPct／reviveDmgSec／reviveRefresh 死亡復活（生命%、冷卻秒、無敵秒、之後增傷%與秒數、是否重置技能冷卻）。</t>
-  </si>
-  <si>
-    <t>事件觸發(JSON)：JSON 陣列，每條 { "on": 觸發, "chance": 機率%, "every": 秒（tick）或次數, "cd": 內建冷卻秒, "below": 生命%（lowhp）, "acts": [動作…] }。</t>
-  </si>
-  <si>
-    <t>　　觸發 on：hit 普攻命中、crit 普攻暴擊、kill 擊殺、hurt 受傷、block 格擋、cast 施放技能、tick 每 every 秒、lowhp 生命低於 below%。</t>
-  </si>
-  <si>
-    <t>　　動作 act：dmg {pct, elem?, type?(magic/phys), to?(target/all/rand/attacker), n?}、heal {pctMax}、shield {pctMax, sec}、mana {pctMax}、buff {sid, val, sec, max?}、buffRandom {sec, from:[{sid,val}]}、stun {sec, to?}、slow {sec, to?}、</t>
-  </si>
-  <si>
-    <t>　　dot {pct, sec, name(poison/burn/bleed/corrode), to?}、cdr {sec}、refresh {n?}、recast、castRandom、invuln {sec}、execute {hpBelow}、cleanse。elem 可填 fire/ice/lightning/poison/light/dark/earth/wind/random。</t>
-  </si>
-  <si>
-    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。效果說明文字由資料自動產生，不需要另外寫。</t>
-  </si>
-  <si>
-    <t>2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>微光</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：命中率×2｜防具・飾品・副手：閃避率×0.6（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：物理攻擊×2｜防具・飾品・副手：物理防禦×0.6（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：冰屬性傷害提升×0.6｜防具・飾品・副手：冰霜抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：攻擊速度×0.6｜防具・飾品・副手：閃避率×0.7（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：物理穿透×0.12｜防具・飾品・副手：物理防禦×0.6（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：毒屬性傷害提升×0.6｜防具・飾品・副手：劇毒抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：雷屬性傷害提升×0.6｜防具・飾品・副手：雷電抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：吸血×0.7｜防具・飾品・副手：生命恢復/秒×0.7（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：聖屬性傷害提升×0.6｜防具・飾品・副手：聖光抗性×0.3（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：物理攻擊×0.7｜防具・飾品・副手：生命值×0.7（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暴擊傷害×0.8｜防具・飾品・副手：物理抗性×0.2（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：魔法攻擊×0.7｜防具・飾品・副手：法力值×0.9（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暴擊率×0.8｜防具・飾品・副手：命中率×0.9（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：對菁英傷害×0.8｜防具・飾品・副手：格擋率×0.9（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：魔法穿透×0.15｜防具・飾品・副手：魔法抗性×0.2（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暗屬性傷害提升×0.8｜防具・飾品・副手：暗影抗性×0.4（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：火屬性傷害提升×0.8｜防具・飾品・副手：火焰抗性×0.4（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：冷卻縮減×0.9｜防具・飾品・副手：魔法防禦×0.9（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：攻擊速度×1｜防具・飾品・副手：韌性×1（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：風屬性傷害提升×1｜防具・飾品・副手：疾風抗性×0.5（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：對BOSS傷害×1.1｜防具・飾品・副手：護盾效率×1.1（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：地屬性傷害提升×1.1｜防具・飾品・副手：生命值×1.2（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：物理攻擊×1.3｜防具・飾品・副手：全局減傷×1.1（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暴擊傷害×1.4｜防具・飾品・副手：全屬性抗性×0.6（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：魔法攻擊×1.4｜防具・飾品・副手：格擋減傷×1.4（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：範圍傷害×1.5｜防具・飾品・副手：控制時間縮減×1.2（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暴擊率×1.6｜防具・飾品・副手：幸運值×1.6（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：對普通敵人傷害×1.7｜防具・飾品・副手：閃避率×1.7（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：吸血×1.8｜防具・飾品・副手：生命恢復/秒×1.8（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：物理攻擊×1.9｜防具・飾品・副手：生命值×1.9（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：魔法攻擊×2｜防具・飾品・副手：全屬性抗性×0.9（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暴擊傷害×2.2｜防具・飾品・副手：護盾效率×2（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：對BOSS傷害×2.5｜防具・飾品・副手：全局減傷×1.8（×倍＝一條滿刻度詞條的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×2、魔法攻擊×2、命中率×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理防禦×2.5、生命值×2.5、生命恢復/秒×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×2.5、冰屬性傷害提升×1.5｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×2、生命值×2、命中率×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理防禦×1.5、生命值×1.2、物理抗性×0.8｜反震 3%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.2、毒屬性傷害提升×1.5、暴擊率×1｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 60% 攻擊力，4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.5、雷屬性傷害提升×2｜普通攻擊命中時有 8% 機率：對目標造成 90% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力值×2、聖光抗性×1.5、生命值×1｜擊殺敵人時回復 1% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：吸血×2、物理攻擊×1、命中率×1｜擊殺敵人時回復 1% 最大生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.5、物理防禦×1.5、韌性×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力恢復/秒×2、生命恢復/秒×2、法力值×1.5｜擊殺敵人時回復 2% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：金幣加成×2、經驗加成×1.5、掉寶率×1.2｜符文掉落率 +8%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.2、暴擊傷害×1.2、物理穿透×0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.5、火屬性傷害提升×1.5、法力值×1.5｜施放技能時有 15% 機率：回復 12% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×2.5、暴擊率×1.5、物理攻擊×1.5｜攻擊速度額外乘算 +8%（突破攻速上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.5、雷屬性傷害提升×2.5、暴擊傷害×1.5｜普通攻擊命中時有 15% 機率：對所有敵人造成 120% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×2、冰屬性傷害提升×3、冷卻縮減×1｜對暈眩或緩速中的敵人傷害 +15%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：吸血×3、物理攻擊×2、暴擊率×1｜擊殺敵人時回復 3% 最大生命；生命低於 35% 時，傷害 +25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×3、物理防禦×3、物理抗性×1｜單次受到的傷害最多只會是最大生命的 40%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×3.5、命中率×2、生命值×1.5｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×2、法力值×3、全屬性抗性×1｜每 10 秒：回復 8% 最大生命，回復 8% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×2、毒屬性傷害提升×3、魔法穿透×0.3｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 60% 攻擊力，4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×3、暴擊率×2、物理攻擊×1.5｜普通攻擊暴擊時：獲得「攻速」+12%（3 秒，最多 3 層）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×2.5、物理防禦×2、物理抗性×1｜反震 12%；受到傷害時有 20% 機率：對攻擊者造成 100% 物理傷害（內建冷卻 3 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：幸運值×3、暴擊率×2、暴擊傷害×2.5、掉寶率×2｜符文掉落率 +15%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：格擋率×3、格擋減傷×3、生命值×2｜格擋成功時有 40% 機率：對攻擊者造成 200% 物理傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×3、法力值×3、冷卻縮減×2｜施放技能時有 20% 機率：所有技能冷卻縮短 1.5 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：寶石鑲嵌效率×3、詞條上限率×2、強化成功率×3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、對BOSS傷害×3｜造成的所有傷害 +18%；攻擊速度額外乘算 +10%（突破攻速上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×4、暴擊傷害×4、對菁英傷害×3、物理穿透×0.5｜對生命低於 30% 的敵人傷害 +60%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 15% 的非 BOSS 敵人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3、風屬性傷害提升×2、魔法穿透×0.5｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 120% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 100% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：冷卻縮減×4、魔法攻擊×3、法力恢復/秒×3、生命值×2｜所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 1 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×4、物理防禦×3.5、魔法防禦×3.5、全局減傷×2｜生命低於 30% 時：無敵 3 秒，回復 30% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×2.5、物理攻擊×2.5、暴擊率×1.5、範圍傷害×2｜場上每多一名敵人，傷害 +5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 20% 的傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：暴擊率×1.5、暴擊傷害×2、物理攻擊×2、閃避率×1.5｜對生命高於 70% 的敵人傷害 +20%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：飛刀的彈射數 +2 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力值×4、法力恢復/秒×4、魔法攻擊×2.5｜技能法力消耗 -40%；擊殺敵人時回復 3% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×3.5、物理防禦×3.5、物理抗性×2｜反震 35%；受到傷害時有 25% 機率：對所有敵人造成 150% 物理傷害（內建冷卻 2 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：對BOSS傷害×5、對菁英傷害×4、物理攻擊×2.5、魔法攻擊×2.5｜對生命高於 70% 的敵人傷害 +40%；場上只有一名敵人時，傷害 +40%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×4、吸血×4、生命恢復/秒×4｜擊殺敵人時回復 6% 最大生命；生命高於 90% 時，傷害 +25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：護盾效率×5、生命值×3、全局減傷×2.5｜每 8 秒：獲得相當於 20% 最大生命的護盾（8 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：火屬性傷害提升×1.8、冰屬性傷害提升×1.8、雷屬性傷害提升×1.8、風屬性傷害提升×1.8、毒屬性傷害提升×1.8｜造成的所有傷害 +10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×4、暴擊率×3、命中率×2｜攻擊速度額外乘算 +15%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×4、物理防禦×4、魔法防禦×4｜死亡時以 60% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +60%，冷卻 180 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：冷卻縮減×5、法力恢復/秒×5、魔法攻擊×3｜所有技能冷卻時間 -45%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、吸血×2｜造成的所有傷害 +60%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 8% 最大生命；最大生命 -30%（乘算，代價）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×3、物理攻擊×3、魔法攻擊×3｜技能傷害 +40%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3.5、暴擊率×2｜對暈眩或緩速中的敵人傷害 +25%；每 2 秒：對隨機 3 名敵人造成 120% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：暴擊傷害×3.5、物理攻擊×3、對BOSS傷害×3.5｜場上只有一名敵人時，傷害 +80%；對生命高於 70% 的敵人傷害 +40%；所有技能冷卻時間 -15%（乘算，突破冷卻縮減上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×3.5、火屬性傷害提升×2.5、冰屬性傷害提升×2.5、魔法穿透×0.6｜每 3 秒：對隨機 5 名敵人造成 150% 隨機元素傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：全屬性抗性×3、幸運值×4、暴擊率×3｜技能傷害 +25%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×2.5、對BOSS傷害×5、暴擊傷害×2.5、物理穿透×0.8｜對生命高於 70% 的敵人傷害 +50%；造成的所有傷害 +25%；普通攻擊暴擊時有 20% 機率：對目標造成 250% 物理傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×5、全局減傷×3、全屬性抗性×3｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×3、攻擊速度×3、範圍傷害×2｜普通攻擊同時對其他所有敵人造成 50% 的傷害；場上每多一名敵人，傷害 +6%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。；傳奇特效【聚敵旋渦】：迴旋斬會將 60 米內的所有敵人拉近至身邊 10 米範圍內。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×3、暴擊率×3、物理攻擊×3｜攻擊速度額外乘算 +15%（突破攻速上限）；傳奇特效【雙生刃】：雙刀亂舞的擊中目標數量 +2 個。；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。；傳奇特效【不屈之誓】：暴風之舞持續期間你的死亡延後 10 秒才生效，且這 10 秒內你的傷害提高 100%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×6、命中率×4、生命值×3｜造成的所有傷害 +25%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 150% 暗影傷害（內建冷卻 4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×3、魔法攻擊×3、火屬性傷害提升×1.5、冰屬性傷害提升×1.5、雷屬性傷害提升×1.5、毒屬性傷害提升×1.5、聖屬性傷害提升×1.5、暗屬性傷害提升×1.5、地屬性傷害提升×1.5、風屬性傷害提升×1.5｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>　　備註是自動產生的參考，不進遊戲、不影響套用；你改了能力之後，備註不會自動更新（請 AI 重新產生），以左邊各欄實際內容為準。</t>
-  </si>
-  <si>
-    <t>符文孔數的硬上限，也是符文真言最多能有幾顆符文。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>全域縮放：符文與符文真言的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×5、全局減傷×3、全屬性抗性×3｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的無敵時間內，每殺死 1 個敵人則無敵時間 +0.5 秒。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>符文真言</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skyrendSlash</t>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、攻擊速度×3、範圍傷害×2｜普通攻擊同時對其他所有敵人造成 50% 的傷害；場上每多一名敵人，傷害 +6%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
+  </si>
+  <si>
+    <t>驚蟄;冰魄;虛空</t>
+  </si>
+  <si>
+    <t>danceThousandCuts</t>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×3、暴擊率×3、物理攻擊×3｜攻擊速度額外乘算 +15%（突破攻速上限）；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。</t>
+  </si>
+  <si>
+    <t>虛空;命運;輪迴</t>
+  </si>
+  <si>
+    <t>windbladeVoidCut</t>
+  </si>
+  <si>
+    <t>屬性：閃避率×6、命中率×4、生命值×3｜造成的所有傷害 +25%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 150% 暗影傷害（內建冷卻 4 秒）；傳奇特效【斷空刃】：【暴風真空刃】每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
+  </si>
+  <si>
+    <t>firepillarResonance</t>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、魔法攻擊×3、火屬性傷害提升×1.5、冰屬性傷害提升×1.5、雷屬性傷害提升×1.5、毒屬性傷害提升×1.5、聖屬性傷害提升×1.5、暗屬性傷害提升×1.5、地屬性傷害提升×1.5、風屬性傷害提升×1.5｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
+  </si>
+  <si>
+    <t>rw_worldend</t>
+  </si>
+  <si>
+    <t>滅世</t>
+  </si>
+  <si>
+    <t>熔岩;虛空;命運;永恆;混沌</t>
+  </si>
+  <si>
+    <t>atkPct:3.5;critDmg:3.5;bossDmg:3.5;aoeDmg:2</t>
+  </si>
+  <si>
+    <t>thunderorbFallCount</t>
+  </si>
+  <si>
+    <t>dmgPct:18;splashPct:15</t>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":10,"acts":[{"act":"dmg","pct":250,"type":"phys","to":"all"}]}]</t>
+  </si>
+  <si>
+    <t>舉刀之時，終局已定。</t>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3.5、暴擊傷害×3.5、對BOSS傷害×3.5、範圍傷害×2｜造成的所有傷害 +18%；普通攻擊同時對其他所有敵人造成 15% 的傷害；普通攻擊暴擊時有 10% 機率：對所有敵人造成 250% 物理傷害；傳奇特效【雷殞落】：【雷殞天落】降下的雷球數量 +1 顆。</t>
+  </si>
+  <si>
+    <t>rw_stargate</t>
+  </si>
+  <si>
+    <t>星門</t>
+  </si>
+  <si>
+    <t>嵐;雷霆;星辰;輪迴;永恆</t>
+  </si>
+  <si>
+    <t>matkPct:5;elemDmgLightning:2.5;elemDmgWind:2.5;cdr:3.5;mPen:0.6</t>
+  </si>
+  <si>
+    <t>thunderstrikeRebirth</t>
+  </si>
+  <si>
+    <t>cdPct:25;skillDmgPct:40</t>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":20,"acts":[{"act":"recast"}]}]</t>
+  </si>
+  <si>
+    <t>星門開啟，咒語在兩端同時落下。</t>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×5、雷屬性傷害提升×2.5、風屬性傷害提升×2.5、冷卻縮減×3.5、魔法穿透×0.6｜所有技能冷卻時間 -25%（乘算，突破冷卻縮減上限）；技能傷害 +40%；施放技能時有 20% 機率：免費再施放一次剛施放的技能；傳奇特效【雷之再生】：【迅雷重生】的機率提高至 100%。</t>
+  </si>
+  <si>
+    <t>rw_divinewrath</t>
+  </si>
+  <si>
+    <t>神罰</t>
+  </si>
+  <si>
+    <t>蒼穹;冰魄;輪迴;混沌;終焉</t>
+  </si>
+  <si>
+    <t>atkPct:3;bossDmg:5;elemDmgLight:3;critRate:2</t>
+  </si>
+  <si>
+    <t>smite:20</t>
+  </si>
+  <si>
+    <t>firehuntHunter</t>
+  </si>
+  <si>
+    <t>dmgHiHpPct:40</t>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":15,"acts":[{"act":"dmg","pct":350,"elem":"light","to":"target"}]}]</t>
+  </si>
+  <si>
+    <t>審判不問理由，只問罪行。</t>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×3、對BOSS傷害×5、聖屬性傷害提升×3、暴擊率×2｜天罰 20%；對生命高於 70% 的敵人傷害 +40%；普通攻擊暴擊時有 15% 機率：對目標造成 350% 聖光傷害；傳奇特效【狩獵者】：你的火狩數量減半（無條件進位，至少 1 團），但造成的傷害額外 +150%。</t>
+  </si>
+  <si>
+    <t>rw_permafrost</t>
+  </si>
+  <si>
+    <t>永凍</t>
+  </si>
+  <si>
+    <t>寒月;冰魄;永恆</t>
+  </si>
+  <si>
+    <t>matkPct:4.5;elemDmgIce:5;cdr:3</t>
+  </si>
+  <si>
+    <t>frostnovaWinterFrost</t>
+  </si>
+  <si>
+    <t>dmgCtrlPct:45</t>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":15,"acts":[{"act":"stun","sec":1.5}]}]</t>
+  </si>
+  <si>
+    <t>時間在這裡結了冰，連呼吸都慢了下來。</t>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×4.5、冰屬性傷害提升×5、冷卻縮減×3｜對暈眩或緩速中的敵人傷害 +45%；普通攻擊命中時有 15% 機率：目標暈眩 1.5 秒；傳奇特效【凜冬寒霜】：暴風雪持續時間內會不斷對範圍內的敵人施加寒霜狀態，且寒霜狀態傷害 +30%。</t>
+  </si>
+  <si>
+    <t>rw_glacier</t>
+  </si>
+  <si>
+    <t>冰川</t>
+  </si>
+  <si>
+    <t>霜痕;雷霆;命運</t>
+  </si>
+  <si>
+    <t>matkPct:3.5;elemDmgIce:3;critDmg:3;bossDmg:3</t>
+  </si>
+  <si>
+    <t>icearrowDeepFreeze</t>
+  </si>
+  <si>
+    <t>dmgHiHpPct:40;dmgCtrlPct:20</t>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":25,"acts":[{"act":"dmg","pct":200,"elem":"ice","to":"target"}]}]</t>
+  </si>
+  <si>
+    <t>冰川緩慢，但它走過的地方什麼都不剩。</t>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×3.5、冰屬性傷害提升×3、暴擊傷害×3、對BOSS傷害×3｜對生命高於 70% 的敵人傷害 +40%；對暈眩或緩速中的敵人傷害 +20%；普通攻擊暴擊時有 25% 機率：對目標造成 200% 冰霜傷害；傳奇特效【深度凍結】：寒冰箭擊中暈眩或凍結的敵人造成的傷害 +50%。</t>
+  </si>
+  <si>
+    <t>rw_tidecall</t>
+  </si>
+  <si>
+    <t>潮汐</t>
+  </si>
+  <si>
+    <t>暗影;靈泉;永恆</t>
+  </si>
+  <si>
+    <t>mpRegen:5;hpRegen:5;matkPct:3;cdr:3</t>
+  </si>
+  <si>
+    <t>waterballTornado</t>
+  </si>
+  <si>
+    <t>killManaPct:4;manaCostRedPct:25</t>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":6,"acts":[{"act":"heal","pctMax":6},{"act":"mana","pctMax":10}]}]</t>
+  </si>
+  <si>
+    <t>潮來潮去，每一次都帶走疲憊、留下力量。</t>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×5、生命恢復/秒×5、魔法攻擊×3、冷卻縮減×3｜擊殺敵人時回復 4% 最大法力；技能法力消耗 -25%；每 6 秒：回復 6% 最大生命，回復 10% 最大法力；傳奇特效【水龍勢】：水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
   </si>
   <si>
     <t>符文真言：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>maxSlots：符文孔數上限，同時也是符文真言最多能有幾顆符文（設計上限 4）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxSlots：符文孔數上限，同時也是符文真言最多能有幾顆符文。目前 5：一般裝備最多 4 孔，5 顆符文的真言是為「雙手武器之後最多 5 孔」預留的（它們只能用在雙手武器，現在還做不出來）。</t>
+  </si>
+  <si>
+    <t>twoHandBonusSlots：雙手武器的符文孔比一般裝備多幾個（0＝一樣多）。把它設成 1，傳說以上的雙手武器就有 5 孔，5 顆符文的真言就做得出來。</t>
+  </si>
+  <si>
+    <t>slots_&lt;稀有度&gt;：該稀有度裝備的符文孔數；0～上限，不可隨稀有度變少；最高稀有度的孔數加上雙手加成不得超過上限。符文孔取代原本的附魔欄位，與寶石鑲孔分開，雙手武器沒有額外加成。</t>
   </si>
   <si>
     <t>statScale：全域屬性縮放，符文與符文真言的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>單獨鑲著就有效；組成符文真言時，符文真言的屬性與能力另外並存。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>── 符文真言列 ──</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>級距：1 普通／2 精良／3 史詩／4 傳說（沿用裝備品質的名稱與顏色）。只影響圖鑑的分組與顏色，不影響數值（強度要自己調屬性加成與效果）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>配方：符文名稱依序用「;」分隔（也可填 id）。至少 2 顆、最多＝符文孔數上限；順序不同就是不同配方，不得與別的符文真言完全相同。成形條件＝依序放進連續的符文孔，且裝備類型符合。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率意義同符文列；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>備註：設定列＝該設定的說明；符文列＝兩側屬性的中文名稱與倍率；符文真言列＝屬性中文名稱與倍率，加上被動／靜態效果／事件觸發／借用傳奇特效的中文說明（與遊戲內圖鑑同一份文字）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2423,7 +3339,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2438,6 +3354,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2773,7 +3692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}">
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:R120"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -2901,10 +3820,10 @@
         <v>21</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>22</v>
+        <v>194</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>729</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3528,10 +4447,10 @@
         <v>18</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>196</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>51</v>
+        <v>197</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>21</v>
@@ -3573,10 +4492,10 @@
         <v>21</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>52</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -3584,10 +4503,10 @@
         <v>18</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>200</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>21</v>
@@ -3629,10 +4548,10 @@
         <v>21</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>56</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -3640,10 +4559,10 @@
         <v>18</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>57</v>
+        <v>204</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>58</v>
+        <v>205</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>21</v>
@@ -3685,10 +4604,10 @@
         <v>21</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>59</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -3696,10 +4615,10 @@
         <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>60</v>
+        <v>208</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>61</v>
+        <v>209</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>21</v>
@@ -3744,7 +4663,7 @@
         <v>29</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>730</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -3752,10 +4671,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>21</v>
@@ -3797,10 +4716,10 @@
         <v>21</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>64</v>
+        <v>213</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -3808,10 +4727,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>66</v>
+        <v>215</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>21</v>
@@ -3853,10 +4772,10 @@
         <v>21</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>68</v>
+        <v>217</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -3864,10 +4783,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>70</v>
+        <v>219</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>21</v>
@@ -3909,10 +4828,10 @@
         <v>21</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>72</v>
+        <v>221</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>73</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -3920,10 +4839,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>21</v>
@@ -3965,36 +4884,36 @@
         <v>21</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>77</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>78</v>
+        <v>227</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>638</v>
+        <v>229</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>637</v>
+        <v>21</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>82</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
@@ -4021,36 +4940,36 @@
         <v>21</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>639</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>232</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>84</v>
+        <v>233</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>85</v>
+        <v>234</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>637</v>
+        <v>116</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
@@ -4080,33 +4999,33 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>640</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>87</v>
+        <v>236</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>88</v>
+        <v>237</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>89</v>
+        <v>239</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>81</v>
+        <v>238</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>64</v>
+        <v>241</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
@@ -4136,33 +5055,33 @@
         <v>21</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>242</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>92</v>
+        <v>243</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>244</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -4192,33 +5111,33 @@
         <v>21</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>642</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>96</v>
+        <v>247</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>100</v>
+        <v>235</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -4248,33 +5167,33 @@
         <v>21</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>643</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>101</v>
+        <v>251</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>102</v>
+        <v>252</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>104</v>
+        <v>253</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>81</v>
+        <v>254</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>64</v>
+        <v>241</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
@@ -4304,33 +5223,33 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>644</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>106</v>
+        <v>256</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>107</v>
+        <v>257</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>108</v>
+        <v>258</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
@@ -4360,33 +5279,33 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>645</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>112</v>
+        <v>262</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>113</v>
+        <v>263</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>114</v>
+        <v>264</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>115</v>
+        <v>265</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>94</v>
+        <v>217</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -4416,33 +5335,33 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>646</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>116</v>
+        <v>266</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>117</v>
+        <v>267</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>119</v>
+        <v>269</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>21</v>
@@ -4472,145 +5391,145 @@
         <v>21</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>647</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>121</v>
+        <v>271</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>122</v>
+        <v>272</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>123</v>
+        <v>273</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>124</v>
+        <v>274</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>94</v>
+        <v>241</v>
       </c>
       <c r="G31" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R32" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>133</v>
+        <v>281</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>134</v>
+        <v>282</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>135</v>
+        <v>283</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>137</v>
+        <v>286</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>138</v>
+        <v>287</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>21</v>
@@ -4640,33 +5559,33 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>650</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>139</v>
+        <v>288</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>140</v>
+        <v>289</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>141</v>
+        <v>290</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>142</v>
+        <v>291</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>21</v>
@@ -4696,33 +5615,33 @@
         <v>21</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>651</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>143</v>
+        <v>293</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>144</v>
+        <v>294</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>145</v>
+        <v>295</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>146</v>
+        <v>296</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>147</v>
+        <v>234</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>138</v>
+        <v>54</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>21</v>
@@ -4752,33 +5671,33 @@
         <v>21</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>652</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>148</v>
+        <v>297</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>149</v>
+        <v>298</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>150</v>
+        <v>299</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>151</v>
+        <v>300</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>153</v>
+        <v>301</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>132</v>
+        <v>302</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
@@ -4808,33 +5727,33 @@
         <v>21</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>653</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>154</v>
+        <v>303</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>155</v>
+        <v>304</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>156</v>
+        <v>305</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>130</v>
+        <v>307</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>158</v>
+        <v>308</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>159</v>
+        <v>287</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
@@ -4864,33 +5783,33 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>654</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>160</v>
+        <v>309</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>161</v>
+        <v>310</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>164</v>
+        <v>313</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>21</v>
@@ -4920,33 +5839,33 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>655</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>165</v>
+        <v>314</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>166</v>
+        <v>315</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>167</v>
+        <v>316</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>168</v>
+        <v>317</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>138</v>
+        <v>285</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>169</v>
+        <v>318</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>138</v>
+        <v>319</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>21</v>
@@ -4976,33 +5895,33 @@
         <v>21</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>656</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>170</v>
+        <v>320</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>171</v>
+        <v>321</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>172</v>
+        <v>322</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>93</v>
+        <v>323</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>29</v>
+        <v>302</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>173</v>
+        <v>324</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>29</v>
+        <v>302</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>21</v>
@@ -5032,33 +5951,33 @@
         <v>21</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>657</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>174</v>
+        <v>325</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>175</v>
+        <v>326</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>55</v>
+        <v>327</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>176</v>
+        <v>249</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>328</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
@@ -5088,33 +6007,33 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>658</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>179</v>
+        <v>329</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>180</v>
+        <v>330</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>182</v>
+        <v>331</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>184</v>
+        <v>332</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>183</v>
+        <v>333</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>21</v>
@@ -5144,33 +6063,33 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>659</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>185</v>
+        <v>334</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>186</v>
+        <v>335</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>187</v>
+        <v>336</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>188</v>
+        <v>337</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>125</v>
+        <v>338</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>189</v>
+        <v>339</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>21</v>
@@ -5200,33 +6119,33 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>660</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>190</v>
+        <v>340</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>191</v>
+        <v>341</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>192</v>
+        <v>342</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>124</v>
+        <v>343</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>193</v>
+        <v>339</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>183</v>
+        <v>344</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>21</v>
@@ -5256,33 +6175,33 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>661</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>195</v>
+        <v>345</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>196</v>
+        <v>346</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>197</v>
+        <v>347</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>129</v>
+        <v>279</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>198</v>
+        <v>348</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>199</v>
+        <v>349</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>21</v>
@@ -5312,33 +6231,33 @@
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>662</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>201</v>
+        <v>351</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>202</v>
+        <v>352</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>198</v>
+        <v>57</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>203</v>
+        <v>353</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>198</v>
+        <v>241</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>21</v>
@@ -5368,33 +6287,33 @@
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>663</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>204</v>
+        <v>354</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>205</v>
+        <v>355</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>206</v>
+        <v>356</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>207</v>
+        <v>291</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>208</v>
+        <v>357</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>209</v>
+        <v>358</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>189</v>
+        <v>357</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>21</v>
@@ -5424,89 +6343,89 @@
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>664</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>210</v>
+        <v>359</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>211</v>
+        <v>360</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>212</v>
+        <v>361</v>
       </c>
       <c r="E48" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R48" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>365</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>216</v>
+        <v>366</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>217</v>
+        <v>367</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>219</v>
+        <v>368</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>368</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>21</v>
@@ -5536,33 +6455,33 @@
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>666</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>370</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>221</v>
+        <v>371</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>222</v>
+        <v>372</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>114</v>
+        <v>373</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>21</v>
@@ -5592,33 +6511,33 @@
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>667</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>224</v>
+        <v>375</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>225</v>
+        <v>376</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>226</v>
+        <v>377</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>227</v>
+        <v>378</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>125</v>
+        <v>270</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>378</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>21</v>
@@ -5648,33 +6567,33 @@
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>668</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>136</v>
+        <v>279</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>34</v>
+        <v>382</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>199</v>
+        <v>280</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>138</v>
+        <v>382</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>21</v>
@@ -5704,33 +6623,33 @@
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>669</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>231</v>
+        <v>383</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>232</v>
+        <v>384</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>233</v>
+        <v>385</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>129</v>
+        <v>291</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>184</v>
+        <v>353</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>34</v>
+        <v>302</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>21</v>
@@ -5760,34 +6679,34 @@
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>670</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>235</v>
+        <v>386</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>236</v>
+        <v>387</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>237</v>
+        <v>388</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>182</v>
+        <v>284</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>21</v>
       </c>
@@ -5816,42 +6735,42 @@
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>671</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>731</v>
+        <v>390</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>239</v>
+        <v>391</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>240</v>
+        <v>392</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>29</v>
+        <v>393</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>21</v>
+        <v>394</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>21</v>
@@ -5866,24 +6785,24 @@
         <v>21</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>672</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>245</v>
+        <v>395</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>246</v>
+        <v>396</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>29</v>
@@ -5901,13 +6820,13 @@
         <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>247</v>
+        <v>397</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>248</v>
+        <v>398</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>249</v>
+        <v>399</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>21</v>
@@ -5922,24 +6841,24 @@
         <v>21</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>673</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>251</v>
+        <v>401</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>252</v>
+        <v>402</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>29</v>
@@ -5957,13 +6876,13 @@
         <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>253</v>
+        <v>403</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>254</v>
+        <v>404</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>255</v>
+        <v>405</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>21</v>
@@ -5975,27 +6894,27 @@
         <v>21</v>
       </c>
       <c r="O57" s="3" t="s">
-        <v>256</v>
+        <v>21</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>257</v>
+        <v>406</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>674</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>258</v>
+        <v>407</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>259</v>
+        <v>408</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>29</v>
@@ -6013,13 +6932,13 @@
         <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>260</v>
+        <v>409</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>261</v>
+        <v>410</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>262</v>
+        <v>411</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>21</v>
@@ -6031,27 +6950,27 @@
         <v>21</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>263</v>
+        <v>413</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>675</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>264</v>
+        <v>414</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>265</v>
+        <v>415</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>29</v>
@@ -6069,16 +6988,16 @@
         <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>266</v>
+        <v>416</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>267</v>
+        <v>417</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>268</v>
+        <v>418</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>21</v>
@@ -6090,24 +7009,24 @@
         <v>21</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>270</v>
+        <v>419</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>676</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>271</v>
+        <v>420</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>272</v>
+        <v>421</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>29</v>
@@ -6125,16 +7044,16 @@
         <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>273</v>
+        <v>422</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>274</v>
+        <v>423</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>275</v>
+        <v>424</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>21</v>
@@ -6143,27 +7062,27 @@
         <v>21</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>277</v>
+        <v>426</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>677</v>
+        <v>154</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>278</v>
+        <v>427</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>279</v>
+        <v>428</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>29</v>
@@ -6181,13 +7100,13 @@
         <v>21</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>280</v>
+        <v>429</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>281</v>
+        <v>430</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>282</v>
+        <v>431</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>21</v>
@@ -6199,27 +7118,27 @@
         <v>21</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>283</v>
+        <v>432</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>284</v>
+        <v>433</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>678</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>285</v>
+        <v>434</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>286</v>
+        <v>435</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>29</v>
@@ -6237,13 +7156,13 @@
         <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>287</v>
+        <v>436</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>288</v>
+        <v>437</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>289</v>
+        <v>438</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>21</v>
@@ -6252,30 +7171,30 @@
         <v>21</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>679</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>292</v>
+        <v>441</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>293</v>
+        <v>442</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>29</v>
@@ -6293,13 +7212,13 @@
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>294</v>
+        <v>443</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>295</v>
+        <v>444</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>296</v>
+        <v>445</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>21</v>
@@ -6308,30 +7227,30 @@
         <v>21</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>297</v>
+        <v>446</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>298</v>
+        <v>447</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>680</v>
+        <v>157</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>299</v>
+        <v>448</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>300</v>
+        <v>449</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>29</v>
@@ -6349,13 +7268,13 @@
         <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>301</v>
+        <v>450</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>302</v>
+        <v>451</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>303</v>
+        <v>452</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>21</v>
@@ -6364,30 +7283,30 @@
         <v>21</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>21</v>
+        <v>453</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>304</v>
+        <v>454</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>681</v>
+        <v>158</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>305</v>
+        <v>455</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>306</v>
+        <v>456</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>29</v>
@@ -6405,13 +7324,13 @@
         <v>21</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>307</v>
+        <v>457</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>308</v>
+        <v>458</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>309</v>
+        <v>459</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>21</v>
@@ -6420,30 +7339,30 @@
         <v>21</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>311</v>
+        <v>460</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>682</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>312</v>
+        <v>461</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>313</v>
+        <v>462</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>29</v>
@@ -6461,13 +7380,13 @@
         <v>21</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>314</v>
+        <v>463</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>315</v>
+        <v>464</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>316</v>
+        <v>465</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>21</v>
@@ -6476,30 +7395,30 @@
         <v>21</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>317</v>
+        <v>466</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>318</v>
+        <v>467</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>683</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>319</v>
+        <v>468</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>320</v>
+        <v>469</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>29</v>
@@ -6517,13 +7436,13 @@
         <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>321</v>
+        <v>470</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>322</v>
+        <v>471</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>323</v>
+        <v>472</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>21</v>
@@ -6532,30 +7451,30 @@
         <v>21</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>21</v>
+        <v>473</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>324</v>
+        <v>474</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>684</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>325</v>
+        <v>475</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>326</v>
+        <v>476</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>29</v>
@@ -6573,13 +7492,13 @@
         <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>327</v>
+        <v>477</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>254</v>
+        <v>478</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>328</v>
+        <v>479</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>21</v>
@@ -6591,30 +7510,30 @@
         <v>21</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>685</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>331</v>
+        <v>481</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>332</v>
+        <v>482</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>21</v>
@@ -6629,13 +7548,13 @@
         <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>333</v>
+        <v>483</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>274</v>
+        <v>410</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>334</v>
+        <v>484</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>21</v>
@@ -6644,30 +7563,30 @@
         <v>21</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>21</v>
+        <v>485</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>336</v>
+        <v>486</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>686</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>337</v>
+        <v>487</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>338</v>
+        <v>488</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>34</v>
@@ -6685,13 +7604,13 @@
         <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>339</v>
+        <v>489</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>242</v>
+        <v>430</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>340</v>
+        <v>490</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>21</v>
@@ -6700,30 +7619,30 @@
         <v>21</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>21</v>
+        <v>491</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>342</v>
+        <v>492</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>687</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>343</v>
+        <v>493</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>344</v>
+        <v>494</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>34</v>
@@ -6741,13 +7660,13 @@
         <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>345</v>
+        <v>495</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>346</v>
+        <v>496</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>21</v>
@@ -6756,30 +7675,30 @@
         <v>21</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>347</v>
+        <v>21</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>348</v>
+        <v>497</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>349</v>
+        <v>498</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>688</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>350</v>
+        <v>499</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>351</v>
+        <v>500</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>34</v>
@@ -6797,13 +7716,13 @@
         <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>352</v>
+        <v>501</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>242</v>
+        <v>410</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>353</v>
+        <v>502</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>21</v>
@@ -6812,30 +7731,30 @@
         <v>21</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>354</v>
+        <v>503</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>21</v>
+        <v>504</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>355</v>
+        <v>505</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>689</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>356</v>
+        <v>506</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>357</v>
+        <v>507</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>34</v>
@@ -6853,13 +7772,13 @@
         <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>358</v>
+        <v>508</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>248</v>
+        <v>398</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>359</v>
+        <v>509</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>21</v>
@@ -6868,30 +7787,30 @@
         <v>21</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>360</v>
+        <v>510</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>361</v>
+        <v>511</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>690</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>362</v>
+        <v>512</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>363</v>
+        <v>513</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>34</v>
@@ -6909,13 +7828,13 @@
         <v>21</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>364</v>
+        <v>514</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>365</v>
+        <v>404</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>366</v>
+        <v>515</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>21</v>
@@ -6924,30 +7843,30 @@
         <v>21</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>21</v>
+        <v>516</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>367</v>
+        <v>21</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>368</v>
+        <v>517</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>691</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>369</v>
+        <v>518</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>370</v>
+        <v>519</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>34</v>
@@ -6965,13 +7884,13 @@
         <v>21</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>371</v>
+        <v>520</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>288</v>
+        <v>521</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>372</v>
+        <v>522</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>21</v>
@@ -6983,27 +7902,27 @@
         <v>21</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>373</v>
+        <v>523</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>374</v>
+        <v>524</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>692</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>375</v>
+        <v>525</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>376</v>
+        <v>526</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>34</v>
@@ -7021,13 +7940,13 @@
         <v>21</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>377</v>
+        <v>527</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>254</v>
+        <v>444</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>378</v>
+        <v>528</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>21</v>
@@ -7039,27 +7958,27 @@
         <v>21</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>379</v>
+        <v>529</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>380</v>
+        <v>530</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>693</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>381</v>
+        <v>531</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>171</v>
+        <v>532</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>34</v>
@@ -7077,13 +7996,13 @@
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>382</v>
+        <v>533</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>384</v>
+        <v>534</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>21</v>
@@ -7095,27 +8014,27 @@
         <v>21</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>385</v>
+        <v>535</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>386</v>
+        <v>536</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>694</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>387</v>
+        <v>537</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>388</v>
+        <v>326</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>34</v>
@@ -7133,16 +8052,16 @@
         <v>21</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>389</v>
+        <v>538</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>390</v>
+        <v>539</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>391</v>
+        <v>540</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>392</v>
+        <v>21</v>
       </c>
       <c r="M78" s="3" t="s">
         <v>21</v>
@@ -7151,27 +8070,27 @@
         <v>21</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>393</v>
+        <v>541</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>394</v>
+        <v>542</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>695</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>395</v>
+        <v>543</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>396</v>
+        <v>544</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>34</v>
@@ -7189,45 +8108,45 @@
         <v>21</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>397</v>
+        <v>545</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>295</v>
+        <v>546</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>398</v>
+        <v>547</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>21</v>
+        <v>548</v>
       </c>
       <c r="M79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>399</v>
+        <v>21</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>21</v>
+        <v>549</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>696</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>402</v>
+        <v>552</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>34</v>
@@ -7245,13 +8164,13 @@
         <v>21</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>403</v>
+        <v>553</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>405</v>
+        <v>554</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>21</v>
@@ -7260,30 +8179,30 @@
         <v>21</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>21</v>
+        <v>555</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>407</v>
+        <v>556</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>697</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>408</v>
+        <v>557</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>409</v>
+        <v>558</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>34</v>
@@ -7301,13 +8220,13 @@
         <v>21</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>410</v>
+        <v>559</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>411</v>
+        <v>560</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>412</v>
+        <v>561</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>21</v>
@@ -7319,27 +8238,27 @@
         <v>21</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>413</v>
+        <v>562</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>698</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>415</v>
+        <v>564</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>416</v>
+        <v>565</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>34</v>
@@ -7357,13 +8276,13 @@
         <v>21</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>417</v>
+        <v>566</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>308</v>
+        <v>567</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>418</v>
+        <v>568</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>21</v>
@@ -7375,30 +8294,30 @@
         <v>21</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>21</v>
+        <v>569</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>419</v>
+        <v>570</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>699</v>
+        <v>176</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>420</v>
+        <v>571</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>421</v>
+        <v>572</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>21</v>
@@ -7413,13 +8332,13 @@
         <v>21</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>422</v>
+        <v>573</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>242</v>
+        <v>464</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>423</v>
+        <v>574</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>21</v>
@@ -7428,30 +8347,30 @@
         <v>21</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>424</v>
+        <v>21</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>425</v>
+        <v>575</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>700</v>
+        <v>177</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>426</v>
+        <v>576</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>427</v>
+        <v>577</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>37</v>
@@ -7469,13 +8388,13 @@
         <v>21</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>428</v>
+        <v>578</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>322</v>
+        <v>398</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>429</v>
+        <v>579</v>
       </c>
       <c r="L84" s="3" t="s">
         <v>21</v>
@@ -7484,30 +8403,30 @@
         <v>21</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>432</v>
+        <v>581</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>701</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>433</v>
+        <v>582</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>434</v>
+        <v>583</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>37</v>
@@ -7525,13 +8444,13 @@
         <v>21</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>435</v>
+        <v>584</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>254</v>
+        <v>478</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>436</v>
+        <v>585</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>21</v>
@@ -7540,30 +8459,30 @@
         <v>21</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>21</v>
+        <v>586</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>437</v>
+        <v>587</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>438</v>
+        <v>588</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>702</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>439</v>
+        <v>589</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>440</v>
+        <v>590</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>37</v>
@@ -7581,13 +8500,13 @@
         <v>21</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>441</v>
+        <v>591</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>442</v>
+        <v>592</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>21</v>
@@ -7596,30 +8515,30 @@
         <v>21</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>443</v>
+        <v>21</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>444</v>
+        <v>593</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>445</v>
+        <v>594</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>703</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>446</v>
+        <v>595</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>447</v>
+        <v>596</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>37</v>
@@ -7637,13 +8556,13 @@
         <v>21</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>448</v>
+        <v>597</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>248</v>
+        <v>567</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>449</v>
+        <v>598</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>21</v>
@@ -7652,30 +8571,30 @@
         <v>21</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>21</v>
+        <v>599</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>450</v>
+        <v>600</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>451</v>
+        <v>601</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>704</v>
+        <v>181</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>452</v>
+        <v>602</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>453</v>
+        <v>603</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>37</v>
@@ -7693,13 +8612,13 @@
         <v>21</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>454</v>
+        <v>604</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>242</v>
+        <v>404</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>455</v>
+        <v>605</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>21</v>
@@ -7708,30 +8627,30 @@
         <v>21</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>456</v>
+        <v>21</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>21</v>
+        <v>606</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>457</v>
+        <v>607</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>705</v>
+        <v>182</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>458</v>
+        <v>608</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>459</v>
+        <v>609</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>37</v>
@@ -7749,45 +8668,45 @@
         <v>21</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>460</v>
+        <v>610</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>461</v>
+        <v>398</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>462</v>
+        <v>611</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>463</v>
+        <v>21</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>464</v>
+        <v>612</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>465</v>
+        <v>613</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>706</v>
+        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>466</v>
+        <v>614</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>467</v>
+        <v>615</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>37</v>
@@ -7805,45 +8724,45 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>468</v>
+        <v>616</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>469</v>
+        <v>617</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>470</v>
+        <v>618</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>21</v>
+        <v>619</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>471</v>
+        <v>620</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>472</v>
+        <v>621</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>707</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>473</v>
+        <v>622</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>474</v>
+        <v>623</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>37</v>
@@ -7861,45 +8780,45 @@
         <v>21</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>475</v>
+        <v>624</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>476</v>
+        <v>625</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>477</v>
+        <v>626</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>478</v>
+        <v>21</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>21</v>
+        <v>627</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>479</v>
+        <v>21</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>480</v>
+        <v>628</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>708</v>
+        <v>185</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>481</v>
+        <v>629</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>482</v>
+        <v>630</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>37</v>
@@ -7917,45 +8836,45 @@
         <v>21</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>483</v>
+        <v>631</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>242</v>
+        <v>632</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>484</v>
+        <v>633</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>21</v>
+        <v>634</v>
       </c>
       <c r="M92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>21</v>
+        <v>635</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>486</v>
+        <v>636</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>709</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>487</v>
+        <v>637</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>488</v>
+        <v>638</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>37</v>
@@ -7973,13 +8892,13 @@
         <v>21</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>489</v>
+        <v>639</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>315</v>
+        <v>398</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>490</v>
+        <v>640</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>21</v>
@@ -7988,30 +8907,30 @@
         <v>21</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>491</v>
+        <v>641</v>
       </c>
       <c r="O93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>492</v>
+        <v>642</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>710</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>493</v>
+        <v>643</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>494</v>
+        <v>644</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>37</v>
@@ -8029,13 +8948,13 @@
         <v>21</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>495</v>
+        <v>645</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>497</v>
+        <v>646</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>21</v>
@@ -8044,30 +8963,30 @@
         <v>21</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>21</v>
+        <v>647</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>498</v>
+        <v>21</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>499</v>
+        <v>648</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>711</v>
+        <v>188</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>500</v>
+        <v>649</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>501</v>
+        <v>650</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>37</v>
@@ -8085,13 +9004,13 @@
         <v>21</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>502</v>
+        <v>651</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>295</v>
+        <v>652</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>503</v>
+        <v>653</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>21</v>
@@ -8100,30 +9019,30 @@
         <v>21</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>504</v>
+        <v>21</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>21</v>
+        <v>654</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>505</v>
+        <v>655</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>712</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>506</v>
+        <v>656</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>507</v>
+        <v>657</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>37</v>
@@ -8141,13 +9060,13 @@
         <v>21</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>508</v>
+        <v>658</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>242</v>
+        <v>451</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>509</v>
+        <v>659</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>21</v>
@@ -8156,33 +9075,33 @@
         <v>21</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>510</v>
+        <v>660</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>511</v>
+        <v>21</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>512</v>
+        <v>661</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>713</v>
+        <v>190</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>513</v>
+        <v>662</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>221</v>
+        <v>663</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>21</v>
@@ -8197,13 +9116,13 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>514</v>
+        <v>664</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>248</v>
+        <v>398</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>515</v>
+        <v>665</v>
       </c>
       <c r="L97" s="3" t="s">
         <v>21</v>
@@ -8212,30 +9131,30 @@
         <v>21</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>516</v>
+        <v>666</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>21</v>
+        <v>667</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>517</v>
+        <v>668</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>714</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>518</v>
+        <v>669</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>519</v>
+        <v>670</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -8253,45 +9172,45 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>520</v>
+        <v>671</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>521</v>
+        <v>672</v>
       </c>
       <c r="L98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>21</v>
+        <v>673</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>522</v>
+        <v>674</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>523</v>
+        <v>675</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>524</v>
+        <v>676</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>715</v>
+        <v>677</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>525</v>
+        <v>678</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>526</v>
+        <v>679</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -8309,45 +9228,45 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>527</v>
+        <v>680</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>242</v>
+        <v>478</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>528</v>
+        <v>681</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>21</v>
+        <v>682</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>529</v>
+        <v>683</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>21</v>
+        <v>684</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>530</v>
+        <v>685</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>716</v>
+        <v>686</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>531</v>
+        <v>687</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>532</v>
+        <v>688</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>22</v>
@@ -8365,45 +9284,45 @@
         <v>21</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>533</v>
+        <v>689</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>242</v>
+        <v>478</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>534</v>
+        <v>690</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>21</v>
+        <v>691</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>535</v>
+        <v>692</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>536</v>
+        <v>21</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>537</v>
+        <v>693</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>717</v>
+        <v>694</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>538</v>
+        <v>695</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>539</v>
+        <v>376</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>22</v>
@@ -8421,45 +9340,45 @@
         <v>21</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>540</v>
+        <v>696</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>254</v>
+        <v>404</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>541</v>
+        <v>697</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>542</v>
+        <v>699</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>543</v>
+        <v>21</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>544</v>
+        <v>700</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>545</v>
+        <v>702</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>546</v>
+        <v>703</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>22</v>
@@ -8477,45 +9396,45 @@
         <v>21</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>547</v>
+        <v>704</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>242</v>
+        <v>464</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>548</v>
+        <v>705</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>21</v>
+        <v>706</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>549</v>
+        <v>707</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>21</v>
+        <v>708</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>550</v>
+        <v>709</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>551</v>
+        <v>711</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>552</v>
+        <v>712</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>22</v>
@@ -8533,45 +9452,45 @@
         <v>21</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>553</v>
+        <v>713</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>554</v>
+        <v>398</v>
       </c>
       <c r="K103" s="3" t="s">
-        <v>555</v>
+        <v>714</v>
       </c>
       <c r="L103" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>21</v>
+        <v>715</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>21</v>
+        <v>716</v>
       </c>
       <c r="O103" s="3" t="s">
-        <v>556</v>
+        <v>21</v>
       </c>
       <c r="P103" s="3" t="s">
-        <v>557</v>
+        <v>717</v>
       </c>
       <c r="Q103" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R103" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>558</v>
+        <v>719</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>559</v>
+        <v>720</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>22</v>
@@ -8589,45 +9508,45 @@
         <v>21</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>560</v>
+        <v>721</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>315</v>
+        <v>398</v>
       </c>
       <c r="K104" s="3" t="s">
-        <v>561</v>
+        <v>722</v>
       </c>
       <c r="L104" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>21</v>
+        <v>723</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>562</v>
+        <v>724</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>563</v>
+        <v>725</v>
       </c>
       <c r="P104" s="3" t="s">
-        <v>564</v>
+        <v>726</v>
       </c>
       <c r="Q104" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R104" s="3" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>565</v>
+        <v>728</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>566</v>
+        <v>729</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>22</v>
@@ -8645,45 +9564,45 @@
         <v>21</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>567</v>
+        <v>730</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>322</v>
+        <v>410</v>
       </c>
       <c r="K105" s="3" t="s">
-        <v>568</v>
+        <v>731</v>
       </c>
       <c r="L105" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>21</v>
+        <v>732</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>569</v>
+        <v>733</v>
       </c>
       <c r="O105" s="3" t="s">
-        <v>570</v>
+        <v>734</v>
       </c>
       <c r="P105" s="3" t="s">
-        <v>571</v>
+        <v>735</v>
       </c>
       <c r="Q105" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R105" s="3" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>572</v>
+        <v>737</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>573</v>
+        <v>738</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>22</v>
@@ -8701,45 +9620,45 @@
         <v>21</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>574</v>
+        <v>739</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>575</v>
+        <v>398</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>576</v>
+        <v>740</v>
       </c>
       <c r="L106" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>21</v>
+        <v>741</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>577</v>
+        <v>742</v>
       </c>
       <c r="O106" s="3" t="s">
-        <v>578</v>
+        <v>21</v>
       </c>
       <c r="P106" s="3" t="s">
-        <v>579</v>
+        <v>743</v>
       </c>
       <c r="Q106" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R106" s="3" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>580</v>
+        <v>745</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>581</v>
+        <v>746</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>22</v>
@@ -8757,45 +9676,45 @@
         <v>21</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>582</v>
+        <v>747</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>583</v>
+        <v>748</v>
       </c>
       <c r="K107" s="3" t="s">
-        <v>584</v>
+        <v>749</v>
       </c>
       <c r="L107" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>585</v>
+        <v>750</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>586</v>
+        <v>21</v>
       </c>
       <c r="O107" s="3" t="s">
-        <v>21</v>
+        <v>751</v>
       </c>
       <c r="P107" s="3" t="s">
-        <v>587</v>
+        <v>752</v>
       </c>
       <c r="Q107" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R107" s="3" t="s">
-        <v>724</v>
+        <v>753</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>588</v>
+        <v>754</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>589</v>
+        <v>755</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>22</v>
@@ -8813,45 +9732,45 @@
         <v>21</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>590</v>
+        <v>756</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>322</v>
+        <v>471</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>591</v>
+        <v>757</v>
       </c>
       <c r="L108" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>592</v>
+        <v>758</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>510</v>
+        <v>759</v>
       </c>
       <c r="O108" s="3" t="s">
-        <v>21</v>
+        <v>760</v>
       </c>
       <c r="P108" s="3" t="s">
-        <v>593</v>
+        <v>761</v>
       </c>
       <c r="Q108" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R108" s="3" t="s">
-        <v>725</v>
+        <v>762</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>594</v>
+        <v>763</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>595</v>
+        <v>764</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>22</v>
@@ -8869,45 +9788,45 @@
         <v>21</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>596</v>
+        <v>765</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>261</v>
+        <v>478</v>
       </c>
       <c r="K109" s="3" t="s">
-        <v>597</v>
+        <v>766</v>
       </c>
       <c r="L109" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>21</v>
+        <v>767</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>598</v>
+        <v>768</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>599</v>
+        <v>769</v>
       </c>
       <c r="P109" s="3" t="s">
-        <v>600</v>
+        <v>770</v>
       </c>
       <c r="Q109" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R109" s="3" t="s">
-        <v>726</v>
+        <v>771</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>731</v>
+        <v>193</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>601</v>
+        <v>772</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>602</v>
+        <v>773</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>22</v>
@@ -8925,34 +9844,408 @@
         <v>21</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>603</v>
+        <v>774</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>604</v>
+        <v>775</v>
       </c>
       <c r="K110" s="3" t="s">
-        <v>605</v>
+        <v>776</v>
       </c>
       <c r="L110" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>21</v>
+        <v>777</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>606</v>
+        <v>778</v>
       </c>
       <c r="O110" s="3" t="s">
-        <v>21</v>
+        <v>779</v>
       </c>
       <c r="P110" s="3" t="s">
-        <v>607</v>
+        <v>780</v>
       </c>
       <c r="Q110" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R110" s="3" t="s">
-        <v>727</v>
+        <v>781</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M111" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="N111" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="P111" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="R111" s="5" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="M112" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="N112" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P112" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="R112" s="5" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M113" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="N113" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="O113" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="P113" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="R113" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K114" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="M114" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="N114" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="P114" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="R114" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K115" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="M115" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="N115" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="O115" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="P115" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="R115" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>802</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="K116" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="M116" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="N116" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="O116" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="P116" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="R116" s="5" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="J117" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K117" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="L117" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="M117" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="N117" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="O117" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="P117" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="R117" s="5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A118" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K118" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="M118" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="N118" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="O118" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="P118" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="R118" s="5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="J119" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K119" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="M119" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="N119" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="O119" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="P119" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="R119" s="5" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K120" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="M120" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="N120" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="O120" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="P120" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="R120" s="5" t="s">
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -8964,7 +10257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.625" customWidth="1"/>
@@ -8972,17 +10265,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>608</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>609</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>610</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -8992,22 +10285,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>611</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>612</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>613</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>732</v>
+        <v>848</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -9017,172 +10310,177 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>733</v>
+        <v>849</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>615</v>
+        <v>850</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>617</v>
+        <v>852</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>621</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>622</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>735</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>21</v>
+        <v>853</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>737</v>
+        <v>854</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>738</v>
+        <v>855</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>623</v>
+        <v>856</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>624</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>739</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>625</v>
+        <v>857</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>628</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>629</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>630</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>631</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>634</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>728</v>
+        <v>858</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578D2905-1597-495C-8C1D-F7F0FAEB51A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89777818-AD64-4933-83B2-3A7000BAEBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="欄位說明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runes!$A$1:$R$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runes!$A$1:$R$99</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="834">
   <si>
     <t>類型</t>
   </si>
@@ -114,87 +114,15 @@
     <t>4</t>
   </si>
   <si>
-    <t>slots_common</t>
-  </si>
-  <si>
-    <t>符文孔數：普通</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>該稀有度的裝備有幾個符文孔（不得超過符文孔數上限）。</t>
-  </si>
-  <si>
-    <t>slots_uncommon</t>
-  </si>
-  <si>
-    <t>符文孔數：精良</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>slots_rare</t>
-  </si>
-  <si>
-    <t>符文孔數：稀有</t>
-  </si>
-  <si>
-    <t>slots_unique</t>
-  </si>
-  <si>
-    <t>符文孔數：獨特</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>slots_epic</t>
-  </si>
-  <si>
-    <t>符文孔數：史詩</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
-    <t>slots_legendary</t>
-  </si>
-  <si>
-    <t>符文孔數：傳說</t>
-  </si>
-  <si>
-    <t>slots_mythic</t>
-  </si>
-  <si>
-    <t>符文孔數：神話</t>
-  </si>
-  <si>
-    <t>slots_genesis</t>
-  </si>
-  <si>
-    <t>符文孔數：創世</t>
-  </si>
-  <si>
-    <t>slots_godforged</t>
-  </si>
-  <si>
-    <t>符文孔數：神鑄創世</t>
-  </si>
-  <si>
-    <t>slots_chaos</t>
-  </si>
-  <si>
-    <t>符文孔數：混沌</t>
-  </si>
-  <si>
-    <t>slots_chaosGodforged</t>
-  </si>
-  <si>
-    <t>符文孔數：神鑄混沌</t>
-  </si>
-  <si>
     <t>0.3</t>
   </si>
   <si>
@@ -708,10 +636,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>符文孔數的硬上限，也是符文真言最多能有幾顆符文。目前 5：一般裝備最多 4 孔，5 顆符文的真言是為「雙手武器之後最多 5 孔」預留的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>twoHandBonusSlots</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -720,14 +644,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雙手武器的符文孔比一般裝備多幾個（0＝一樣多）。設成 1，傳說以上的雙手武器就有 5 孔，5 顆符文的真言（只能用在雙手武器）才做得出來。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>composeCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3257,15 +3173,6 @@
     <t>符文真言：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
   </si>
   <si>
-    <t>maxSlots：符文孔數上限，同時也是符文真言最多能有幾顆符文。目前 5：一般裝備最多 4 孔，5 顆符文的真言是為「雙手武器之後最多 5 孔」預留的（它們只能用在雙手武器，現在還做不出來）。</t>
-  </si>
-  <si>
-    <t>twoHandBonusSlots：雙手武器的符文孔比一般裝備多幾個（0＝一樣多）。把它設成 1，傳說以上的雙手武器就有 5 孔，5 顆符文的真言就做得出來。</t>
-  </si>
-  <si>
-    <t>slots_&lt;稀有度&gt;：該稀有度裝備的符文孔數；0～上限，不可隨稀有度變少；最高稀有度的孔數加上雙手加成不得超過上限。符文孔取代原本的附魔欄位，與寶石鑲孔分開，雙手武器沒有額外加成。</t>
-  </si>
-  <si>
     <t>statScale：全域屬性縮放，符文與符文真言的屬性加成一律乘此值（平衡用旋鈕，1＝不縮放）。</t>
   </si>
   <si>
@@ -3285,6 +3192,23 @@
   </si>
   <si>
     <t>備註：設定列＝該設定的說明；符文列＝兩側屬性的中文名稱與倍率；符文真言列＝屬性中文名稱與倍率，加上被動／靜態效果／事件觸發／借用傳奇特效的中文說明（與遊戲內圖鑑同一份文字）。</t>
+  </si>
+  <si>
+    <t>符文孔數的硬上限，也是符文真言最多能有幾顆符文。各稀有度的符文孔數不在這張表：在 game_parameters.xlsx「表-稀有度」各列的參數g。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙手武器的符文孔比一般裝備多幾個（加法，不是倍數；0＝一樣多）。只加在本來就有符文孔的稀有度上（孔數 0 的稀有度，雙手武器也沒有符文孔）；最多孔稀有度的孔數加上它不得超過符文孔數上限。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxSlots：符文孔數上限，同時也是符文真言最多能有幾顆符文。</t>
+  </si>
+  <si>
+    <t>各稀有度的符文孔數：不在這張表。在 config/Excel/game_parameters.xlsx 的「表-稀有度」各列（編號 321～331）的「參數g」；0～上限，不可隨稀有度變少。符文孔取代原本的附魔欄位，與寶石鑲孔分開。</t>
+  </si>
+  <si>
+    <t>twoHandBonusSlots：雙手武器的符文孔比一般裝備多幾個（加法，不是倍數；0＝一樣多）。只加在本來就有符文孔的稀有度上；最多孔稀有度的孔數加上它不得超過上限。5 顆符文的真言只能用在雙手武器，要靠這一格才做得出來。</t>
   </si>
 </sst>
 </file>
@@ -3692,7 +3616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}">
-  <dimension ref="A1:R120"/>
+  <dimension ref="A1:R109"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3820,10 +3744,10 @@
         <v>21</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>195</v>
+        <v>829</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3831,10 +3755,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>21</v>
@@ -3876,10 +3800,10 @@
         <v>21</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>26</v>
+        <v>830</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3887,10 +3811,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>21</v>
@@ -3932,10 +3856,10 @@
         <v>21</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>29</v>
+        <v>175</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>26</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3943,10 +3867,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>31</v>
+        <v>178</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>21</v>
@@ -3988,10 +3912,10 @@
         <v>21</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>26</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3999,10 +3923,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>21</v>
@@ -4044,10 +3968,10 @@
         <v>21</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -4055,10 +3979,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>184</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>185</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>21</v>
@@ -4100,10 +4024,10 @@
         <v>21</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>37</v>
+        <v>186</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>26</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -4111,10 +4035,10 @@
         <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>38</v>
+        <v>188</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
@@ -4156,10 +4080,10 @@
         <v>21</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -4167,10 +4091,10 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>41</v>
+        <v>193</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
@@ -4212,10 +4136,10 @@
         <v>21</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>22</v>
+        <v>194</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -4223,10 +4147,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
@@ -4268,21 +4192,21 @@
         <v>21</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>22</v>
+        <v>198</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>44</v>
+        <v>201</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>202</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -4324,36 +4248,36 @@
         <v>21</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>203</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>26</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>47</v>
+        <v>206</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>21</v>
@@ -4380,36 +4304,36 @@
         <v>21</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>48</v>
+        <v>209</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>49</v>
+        <v>210</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>21</v>
@@ -4436,36 +4360,36 @@
         <v>21</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>21</v>
@@ -4492,36 +4416,36 @@
         <v>21</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>222</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>21</v>
@@ -4548,36 +4472,36 @@
         <v>21</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>203</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>170</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -4604,36 +4528,36 @@
         <v>21</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>207</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -4660,36 +4584,36 @@
         <v>21</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>210</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>21</v>
+        <v>236</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>21</v>
+        <v>237</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>238</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>21</v>
@@ -4716,36 +4640,36 @@
         <v>21</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>214</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>21</v>
+        <v>243</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
@@ -4772,36 +4696,36 @@
         <v>21</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>218</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>21</v>
+        <v>246</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>21</v>
+        <v>247</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>21</v>
+        <v>214</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>21</v>
+        <v>248</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>21</v>
@@ -4828,36 +4752,36 @@
         <v>21</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>222</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="G21" s="3" t="s">
-        <v>21</v>
+        <v>253</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>21</v>
+        <v>223</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
@@ -4884,36 +4808,36 @@
         <v>21</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>225</v>
+        <v>21</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>226</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>227</v>
+        <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>21</v>
+        <v>258</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>21</v>
+        <v>260</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
@@ -4940,36 +4864,36 @@
         <v>21</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>231</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>116</v>
+        <v>223</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
@@ -4999,33 +4923,33 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>238</v>
+        <v>29</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>241</v>
+        <v>30</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
@@ -5055,33 +4979,33 @@
         <v>21</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>202</v>
+        <v>272</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>52</v>
+        <v>258</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -5111,33 +5035,33 @@
         <v>21</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -5167,33 +5091,33 @@
         <v>21</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>194</v>
+        <v>284</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>254</v>
+        <v>29</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>241</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
@@ -5223,33 +5147,33 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>50</v>
+        <v>292</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
@@ -5279,33 +5203,33 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>217</v>
+        <v>275</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -5335,33 +5259,33 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>250</v>
+        <v>23</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>21</v>
@@ -5391,33 +5315,33 @@
         <v>21</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>273</v>
+        <v>179</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>217</v>
+        <v>306</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>21</v>
@@ -5447,33 +5371,33 @@
         <v>21</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>250</v>
+        <v>32</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>250</v>
+        <v>312</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
@@ -5503,33 +5427,33 @@
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>21</v>
@@ -5559,33 +5483,33 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>250</v>
+        <v>321</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>54</v>
+        <v>312</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>21</v>
@@ -5615,33 +5539,33 @@
         <v>21</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>234</v>
+        <v>326</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>54</v>
+        <v>214</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>21</v>
@@ -5671,33 +5595,33 @@
         <v>21</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>285</v>
+        <v>330</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>302</v>
+        <v>330</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
@@ -5727,33 +5651,33 @@
         <v>21</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>306</v>
+        <v>335</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
@@ -5783,33 +5707,33 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>53</v>
+        <v>341</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>55</v>
+        <v>341</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>21</v>
@@ -5839,33 +5763,33 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>314</v>
+        <v>343</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>285</v>
+        <v>347</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>318</v>
+        <v>208</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>319</v>
+        <v>347</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>21</v>
@@ -5895,33 +5819,33 @@
         <v>21</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>323</v>
+        <v>242</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>324</v>
+        <v>243</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>302</v>
+        <v>351</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>21</v>
@@ -5951,33 +5875,33 @@
         <v>21</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>29</v>
+        <v>355</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>328</v>
+        <v>253</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>213</v>
+        <v>355</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
@@ -6007,33 +5931,33 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>206</v>
+        <v>358</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>331</v>
+        <v>264</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>333</v>
+        <v>275</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>21</v>
@@ -6063,33 +5987,33 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>337</v>
+        <v>257</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>56</v>
+        <v>362</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>339</v>
+        <v>211</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>21</v>
@@ -6119,33 +6043,33 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>51</v>
+        <v>363</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>280</v>
+        <v>322</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>21</v>
@@ -6175,42 +6099,42 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>347</v>
+        <v>23</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>348</v>
+        <v>21</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>339</v>
+        <v>21</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>21</v>
+        <v>371</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>21</v>
@@ -6225,48 +6149,48 @@
         <v>21</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>352</v>
+        <v>23</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>21</v>
@@ -6281,48 +6205,48 @@
         <v>21</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>21</v>
+        <v>379</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>356</v>
+        <v>23</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>21</v>
+        <v>383</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>21</v>
@@ -6334,51 +6258,51 @@
         <v>21</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>21</v>
+        <v>386</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>361</v>
+        <v>23</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>362</v>
+        <v>21</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>364</v>
+        <v>21</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>21</v>
+        <v>389</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>21</v>
+        <v>390</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>21</v>
+        <v>391</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>21</v>
@@ -6393,51 +6317,51 @@
         <v>21</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>367</v>
+        <v>23</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>21</v>
+        <v>395</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>21</v>
+        <v>396</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>21</v>
+        <v>397</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>21</v>
@@ -6449,48 +6373,48 @@
         <v>21</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>21</v>
+        <v>399</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>21</v>
+        <v>403</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>21</v>
+        <v>404</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>21</v>
@@ -6502,51 +6426,51 @@
         <v>21</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>21</v>
+        <v>406</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>377</v>
+        <v>23</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>270</v>
+        <v>21</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>21</v>
+        <v>409</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>21</v>
+        <v>410</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>21</v>
+        <v>411</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>21</v>
@@ -6558,51 +6482,51 @@
         <v>21</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>21</v>
+        <v>413</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>379</v>
+        <v>414</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>381</v>
+        <v>23</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>279</v>
+        <v>21</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>280</v>
+        <v>21</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>21</v>
+        <v>417</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>21</v>
+        <v>418</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>21</v>
@@ -6611,54 +6535,54 @@
         <v>21</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>21</v>
+        <v>419</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>21</v>
+        <v>420</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>383</v>
+        <v>421</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>385</v>
+        <v>23</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>353</v>
+        <v>21</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>302</v>
+        <v>21</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>21</v>
+        <v>424</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>21</v>
+        <v>425</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>21</v>
@@ -6667,54 +6591,54 @@
         <v>21</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>21</v>
+        <v>426</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>21</v>
+        <v>427</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>386</v>
+        <v>428</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>388</v>
+        <v>23</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>284</v>
+        <v>21</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>21</v>
+        <v>430</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>21</v>
+        <v>432</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>21</v>
@@ -6729,48 +6653,48 @@
         <v>21</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>21</v>
+        <v>433</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>390</v>
+        <v>169</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>392</v>
+        <v>435</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>393</v>
+        <v>23</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>337</v>
+        <v>21</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>394</v>
+        <v>21</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>349</v>
+        <v>21</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>21</v>
+        <v>436</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>21</v>
+        <v>437</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>21</v>
+        <v>438</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>21</v>
@@ -6779,33 +6703,33 @@
         <v>21</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>21</v>
+        <v>440</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>395</v>
+        <v>441</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>396</v>
+        <v>442</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>21</v>
@@ -6820,13 +6744,13 @@
         <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>397</v>
+        <v>443</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>399</v>
+        <v>445</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>21</v>
@@ -6835,33 +6759,33 @@
         <v>21</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>21</v>
@@ -6876,13 +6800,13 @@
         <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>403</v>
+        <v>450</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>21</v>
@@ -6897,27 +6821,27 @@
         <v>21</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>407</v>
+        <v>454</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>408</v>
+        <v>455</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>21</v>
@@ -6932,13 +6856,13 @@
         <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>409</v>
+        <v>456</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>411</v>
+        <v>457</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>21</v>
@@ -6950,30 +6874,30 @@
         <v>21</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>412</v>
+        <v>458</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>414</v>
+        <v>460</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>415</v>
+        <v>461</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>21</v>
@@ -6988,13 +6912,13 @@
         <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>416</v>
+        <v>462</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>21</v>
@@ -7003,33 +6927,33 @@
         <v>21</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>419</v>
+        <v>465</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>420</v>
+        <v>466</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>421</v>
+        <v>467</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>21</v>
@@ -7044,16 +6968,16 @@
         <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>423</v>
+        <v>371</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>425</v>
+        <v>21</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>21</v>
@@ -7062,30 +6986,30 @@
         <v>21</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>21</v>
+        <v>470</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>426</v>
+        <v>471</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>427</v>
+        <v>472</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>428</v>
+        <v>473</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>21</v>
@@ -7100,13 +7024,13 @@
         <v>21</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>430</v>
+        <v>383</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>431</v>
+        <v>475</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>21</v>
@@ -7115,33 +7039,33 @@
         <v>21</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>432</v>
+        <v>477</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>433</v>
+        <v>478</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>434</v>
+        <v>479</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>435</v>
+        <v>480</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>21</v>
@@ -7156,13 +7080,13 @@
         <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>436</v>
+        <v>481</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>437</v>
+        <v>371</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>438</v>
+        <v>482</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>21</v>
@@ -7171,33 +7095,33 @@
         <v>21</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>439</v>
+        <v>21</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>442</v>
+        <v>486</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>21</v>
@@ -7212,13 +7136,13 @@
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>443</v>
+        <v>487</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>21</v>
@@ -7227,33 +7151,33 @@
         <v>21</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>447</v>
+        <v>490</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>448</v>
+        <v>491</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>449</v>
+        <v>492</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>21</v>
@@ -7268,13 +7192,13 @@
         <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>450</v>
+        <v>493</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>451</v>
+        <v>494</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>21</v>
@@ -7283,33 +7207,33 @@
         <v>21</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>453</v>
+        <v>21</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>21</v>
+        <v>496</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>456</v>
+        <v>499</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>21</v>
@@ -7324,13 +7248,13 @@
         <v>21</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>457</v>
+        <v>500</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>459</v>
+        <v>501</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>21</v>
@@ -7342,30 +7266,30 @@
         <v>21</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>21</v>
+        <v>502</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>460</v>
+        <v>503</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>21</v>
@@ -7380,13 +7304,13 @@
         <v>21</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>465</v>
+        <v>507</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>21</v>
@@ -7395,33 +7319,33 @@
         <v>21</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>466</v>
+        <v>21</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>467</v>
+        <v>509</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>469</v>
+        <v>299</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>21</v>
@@ -7436,13 +7360,13 @@
         <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>21</v>
@@ -7451,33 +7375,33 @@
         <v>21</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>473</v>
+        <v>21</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>21</v>
+        <v>514</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>21</v>
@@ -7492,16 +7416,16 @@
         <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>21</v>
+        <v>521</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>21</v>
@@ -7510,30 +7434,30 @@
         <v>21</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>21</v>
+        <v>522</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>213</v>
+        <v>24</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>21</v>
@@ -7548,13 +7472,13 @@
         <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>484</v>
+        <v>527</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>21</v>
@@ -7563,33 +7487,33 @@
         <v>21</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>21</v>
+        <v>528</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>21</v>
@@ -7604,13 +7528,13 @@
         <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>430</v>
+        <v>533</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>490</v>
+        <v>534</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>21</v>
@@ -7619,33 +7543,33 @@
         <v>21</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>21</v>
+        <v>535</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>492</v>
+        <v>536</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>493</v>
+        <v>537</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>494</v>
+        <v>538</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>21</v>
@@ -7660,13 +7584,13 @@
         <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>495</v>
+        <v>539</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>398</v>
+        <v>540</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>21</v>
@@ -7678,30 +7602,30 @@
         <v>21</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>497</v>
+        <v>542</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>498</v>
+        <v>543</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>499</v>
+        <v>544</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>500</v>
+        <v>545</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>21</v>
@@ -7716,13 +7640,13 @@
         <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>501</v>
+        <v>546</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>502</v>
+        <v>547</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>21</v>
@@ -7731,33 +7655,33 @@
         <v>21</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>503</v>
+        <v>21</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>504</v>
+        <v>21</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>505</v>
+        <v>548</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>506</v>
+        <v>549</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>507</v>
+        <v>550</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>21</v>
@@ -7772,13 +7696,13 @@
         <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>508</v>
+        <v>551</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>21</v>
@@ -7787,33 +7711,33 @@
         <v>21</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>510</v>
+        <v>553</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>511</v>
+        <v>554</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>512</v>
+        <v>555</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>513</v>
+        <v>556</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>21</v>
@@ -7828,13 +7752,13 @@
         <v>21</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>515</v>
+        <v>558</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>21</v>
@@ -7843,33 +7767,33 @@
         <v>21</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>516</v>
+        <v>559</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>21</v>
+        <v>560</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>517</v>
+        <v>561</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>518</v>
+        <v>562</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>519</v>
+        <v>563</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>21</v>
@@ -7884,13 +7808,13 @@
         <v>21</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>520</v>
+        <v>564</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>521</v>
+        <v>383</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>522</v>
+        <v>565</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>21</v>
@@ -7902,30 +7826,30 @@
         <v>21</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>523</v>
+        <v>566</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>524</v>
+        <v>567</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>525</v>
+        <v>568</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>526</v>
+        <v>569</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>21</v>
@@ -7940,13 +7864,13 @@
         <v>21</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>527</v>
+        <v>570</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>444</v>
+        <v>540</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>21</v>
@@ -7955,33 +7879,33 @@
         <v>21</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>21</v>
+        <v>572</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>529</v>
+        <v>573</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>530</v>
+        <v>574</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>531</v>
+        <v>575</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>532</v>
+        <v>576</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>21</v>
@@ -7996,13 +7920,13 @@
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>534</v>
+        <v>578</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>21</v>
@@ -8014,30 +7938,30 @@
         <v>21</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>535</v>
+        <v>579</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>536</v>
+        <v>580</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>537</v>
+        <v>581</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>326</v>
+        <v>582</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>21</v>
@@ -8052,13 +7976,13 @@
         <v>21</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>538</v>
+        <v>583</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>539</v>
+        <v>371</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>540</v>
+        <v>584</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>21</v>
@@ -8067,33 +7991,33 @@
         <v>21</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>21</v>
+        <v>585</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>541</v>
+        <v>21</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>542</v>
+        <v>586</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>543</v>
+        <v>587</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>544</v>
+        <v>588</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>21</v>
@@ -8108,48 +8032,48 @@
         <v>21</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>545</v>
+        <v>589</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>546</v>
+        <v>590</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>547</v>
+        <v>591</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>548</v>
+        <v>21</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>21</v>
+        <v>592</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>21</v>
+        <v>593</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>549</v>
+        <v>21</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>550</v>
+        <v>594</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>551</v>
+        <v>595</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>21</v>
@@ -8164,13 +8088,13 @@
         <v>21</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>553</v>
+        <v>597</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>451</v>
+        <v>598</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>554</v>
+        <v>599</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>21</v>
@@ -8179,33 +8103,33 @@
         <v>21</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>555</v>
+        <v>600</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>556</v>
+        <v>601</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>557</v>
+        <v>602</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>558</v>
+        <v>603</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>21</v>
@@ -8220,16 +8144,16 @@
         <v>21</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>559</v>
+        <v>604</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>560</v>
+        <v>605</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>561</v>
+        <v>606</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>21</v>
+        <v>607</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>21</v>
@@ -8238,30 +8162,30 @@
         <v>21</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>562</v>
+        <v>608</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>563</v>
+        <v>609</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>564</v>
+        <v>610</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>21</v>
@@ -8276,13 +8200,13 @@
         <v>21</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>566</v>
+        <v>612</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>567</v>
+        <v>371</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>568</v>
+        <v>613</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>21</v>
@@ -8291,33 +8215,33 @@
         <v>21</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>21</v>
+        <v>614</v>
       </c>
       <c r="O82" s="3" t="s">
-        <v>569</v>
+        <v>21</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>570</v>
+        <v>615</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>571</v>
+        <v>616</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>572</v>
+        <v>617</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>238</v>
+        <v>25</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>21</v>
@@ -8332,13 +8256,13 @@
         <v>21</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>573</v>
+        <v>618</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>21</v>
@@ -8347,33 +8271,33 @@
         <v>21</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>21</v>
+        <v>620</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>575</v>
+        <v>621</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>576</v>
+        <v>622</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>21</v>
@@ -8388,13 +8312,13 @@
         <v>21</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>578</v>
+        <v>624</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>398</v>
+        <v>625</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>579</v>
+        <v>626</v>
       </c>
       <c r="L84" s="3" t="s">
         <v>21</v>
@@ -8403,33 +8327,33 @@
         <v>21</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>580</v>
+        <v>21</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>21</v>
+        <v>627</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>581</v>
+        <v>628</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>582</v>
+        <v>629</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>583</v>
+        <v>630</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>21</v>
@@ -8444,13 +8368,13 @@
         <v>21</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>584</v>
+        <v>631</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>478</v>
+        <v>424</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>585</v>
+        <v>632</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>21</v>
@@ -8459,33 +8383,33 @@
         <v>21</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="O85" s="3" t="s">
-        <v>587</v>
+        <v>21</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>588</v>
+        <v>634</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>589</v>
+        <v>635</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>590</v>
+        <v>636</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>37</v>
+        <v>175</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>21</v>
@@ -8500,13 +8424,13 @@
         <v>21</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>591</v>
+        <v>637</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>410</v>
+        <v>371</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>592</v>
+        <v>638</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>21</v>
@@ -8515,33 +8439,33 @@
         <v>21</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>21</v>
+        <v>639</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>593</v>
+        <v>640</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>594</v>
+        <v>641</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>596</v>
+        <v>643</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>21</v>
@@ -8556,48 +8480,48 @@
         <v>21</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>597</v>
+        <v>644</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>567</v>
+        <v>451</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>21</v>
+        <v>646</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>599</v>
+        <v>647</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>600</v>
+        <v>648</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>601</v>
+        <v>649</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>181</v>
+        <v>650</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>602</v>
+        <v>651</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>603</v>
+        <v>652</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>21</v>
@@ -8612,48 +8536,48 @@
         <v>21</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>604</v>
+        <v>653</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>605</v>
+        <v>654</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>21</v>
+        <v>655</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>21</v>
+        <v>656</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>606</v>
+        <v>657</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>607</v>
+        <v>658</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>182</v>
+        <v>659</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>608</v>
+        <v>660</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>609</v>
+        <v>661</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>21</v>
@@ -8668,48 +8592,48 @@
         <v>21</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>610</v>
+        <v>662</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>611</v>
+        <v>663</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>21</v>
+        <v>664</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>612</v>
+        <v>665</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>613</v>
+        <v>666</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>183</v>
+        <v>667</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>614</v>
+        <v>668</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>615</v>
+        <v>349</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>21</v>
@@ -8724,48 +8648,48 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>616</v>
+        <v>669</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>617</v>
+        <v>377</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>618</v>
+        <v>670</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>619</v>
+        <v>671</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>620</v>
+        <v>672</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>621</v>
+        <v>673</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>184</v>
+        <v>674</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>622</v>
+        <v>675</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>623</v>
+        <v>676</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>21</v>
@@ -8780,48 +8704,48 @@
         <v>21</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>624</v>
+        <v>677</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>625</v>
+        <v>437</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>626</v>
+        <v>678</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>21</v>
+        <v>679</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>627</v>
+        <v>680</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>21</v>
+        <v>681</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>628</v>
+        <v>682</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>185</v>
+        <v>683</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>629</v>
+        <v>684</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>630</v>
+        <v>685</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>21</v>
@@ -8836,48 +8760,48 @@
         <v>21</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>631</v>
+        <v>686</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>632</v>
+        <v>371</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>633</v>
+        <v>687</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>634</v>
+        <v>21</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>21</v>
+        <v>688</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>21</v>
+        <v>689</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>635</v>
+        <v>21</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>636</v>
+        <v>690</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>186</v>
+        <v>691</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>637</v>
+        <v>692</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>638</v>
+        <v>693</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>21</v>
@@ -8892,48 +8816,48 @@
         <v>21</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>639</v>
+        <v>694</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>398</v>
+        <v>371</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>640</v>
+        <v>695</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>21</v>
+        <v>696</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>641</v>
+        <v>697</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>642</v>
+        <v>699</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>187</v>
+        <v>700</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>643</v>
+        <v>701</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>644</v>
+        <v>702</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>21</v>
@@ -8948,48 +8872,48 @@
         <v>21</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>645</v>
+        <v>703</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>471</v>
+        <v>383</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>646</v>
+        <v>704</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>21</v>
+        <v>705</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>647</v>
+        <v>706</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>21</v>
+        <v>707</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>188</v>
+        <v>709</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>649</v>
+        <v>710</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>650</v>
+        <v>711</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>21</v>
@@ -9004,48 +8928,48 @@
         <v>21</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>651</v>
+        <v>712</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>652</v>
+        <v>371</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>653</v>
+        <v>713</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>21</v>
+        <v>714</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>21</v>
+        <v>715</v>
       </c>
       <c r="O95" s="3" t="s">
-        <v>654</v>
+        <v>21</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>655</v>
+        <v>716</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>189</v>
+        <v>717</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>656</v>
+        <v>718</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>657</v>
+        <v>719</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>21</v>
@@ -9060,48 +8984,48 @@
         <v>21</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>658</v>
+        <v>720</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>451</v>
+        <v>721</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>659</v>
+        <v>722</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>21</v>
+        <v>723</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>660</v>
+        <v>21</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>21</v>
+        <v>724</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>661</v>
+        <v>725</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>190</v>
+        <v>726</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>662</v>
+        <v>727</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>663</v>
+        <v>728</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>202</v>
+        <v>22</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>21</v>
@@ -9116,45 +9040,45 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>664</v>
+        <v>729</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>665</v>
+        <v>730</v>
       </c>
       <c r="L97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>21</v>
+        <v>731</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>666</v>
+        <v>732</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>667</v>
+        <v>733</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>668</v>
+        <v>734</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>191</v>
+        <v>735</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>669</v>
+        <v>736</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>670</v>
+        <v>737</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -9172,45 +9096,45 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>671</v>
+        <v>738</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>672</v>
+        <v>739</v>
       </c>
       <c r="L98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>673</v>
+        <v>740</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>674</v>
+        <v>741</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>676</v>
+        <v>743</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>677</v>
+        <v>744</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>678</v>
+        <v>745</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>679</v>
+        <v>746</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -9228,1028 +9152,412 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>680</v>
+        <v>747</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>478</v>
+        <v>748</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>681</v>
+        <v>749</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>682</v>
+        <v>750</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>683</v>
+        <v>751</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>684</v>
+        <v>752</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>685</v>
+        <v>753</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>686</v>
+        <v>754</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="D100" s="3" t="s">
+      <c r="A100" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>694</v>
+      <c r="I100" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K100" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M100" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="N100" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P100" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="R100" s="5" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D101" s="3" t="s">
+      <c r="A101" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>701</v>
+      <c r="I101" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K101" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="M101" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="N101" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P101" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R101" s="5" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="D102" s="3" t="s">
+      <c r="A102" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>710</v>
+      <c r="I102" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K102" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M102" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="N102" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="O102" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P102" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="R102" s="5" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="D103" s="3" t="s">
+      <c r="A103" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D103" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="K103" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="L103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M103" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="O103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P103" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="Q103" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R103" s="3" t="s">
-        <v>718</v>
+      <c r="I103" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="K103" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M103" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="N103" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P103" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="R103" s="5" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="D104" s="3" t="s">
+      <c r="A104" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="D104" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="K104" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="L104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M104" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="N104" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="O104" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="P104" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="Q104" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R104" s="3" t="s">
-        <v>727</v>
+      <c r="I104" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K104" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="M104" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="N104" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="O104" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="P104" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="R104" s="5" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="D105" s="3" t="s">
+      <c r="A105" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="D105" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M105" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="O105" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="P105" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="Q105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R105" s="3" t="s">
-        <v>736</v>
+      <c r="I105" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K105" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="M105" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="N105" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="O105" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="P105" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="R105" s="5" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="D106" s="3" t="s">
+      <c r="A106" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="D106" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="K106" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="L106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M106" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="N106" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P106" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="Q106" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R106" s="3" t="s">
-        <v>744</v>
+      <c r="I106" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K106" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="N106" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="O106" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="P106" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="R106" s="5" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="D107" s="3" t="s">
+      <c r="A107" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="D107" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="K107" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="L107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M107" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="N107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O107" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="P107" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="Q107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R107" s="3" t="s">
-        <v>753</v>
+      <c r="I107" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K107" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="M107" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="N107" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="O107" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="P107" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="R107" s="5" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="C108" s="3" t="s">
+      <c r="A108" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="B108" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="J108" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K108" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="L108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M108" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="N108" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="O108" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="P108" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="Q108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R108" s="3" t="s">
-        <v>762</v>
+      <c r="I108" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K108" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="M108" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="N108" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="O108" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="P108" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="R108" s="5" t="s">
+        <v>811</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="D109" s="3" t="s">
+      <c r="A109" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="D109" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="J109" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="K109" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="L109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="N109" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="O109" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="P109" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="Q109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R109" s="3" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="L110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M110" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="N110" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="O110" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="P110" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="Q110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R110" s="3" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A111" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="J111" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="K111" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M111" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="N111" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="P111" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="R111" s="5" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A112" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="J112" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K112" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="M112" s="5" t="s">
-        <v>786</v>
-      </c>
-      <c r="N112" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P112" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="R112" s="5" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A113" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I113" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="J113" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="K113" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="M113" s="5" t="s">
-        <v>789</v>
-      </c>
-      <c r="N113" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="O113" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="P113" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="R113" s="5" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A114" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I114" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J114" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K114" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="M114" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="N114" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="P114" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="R114" s="5" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A115" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>793</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I115" s="5" t="s">
-        <v>795</v>
-      </c>
-      <c r="J115" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K115" s="5" t="s">
-        <v>796</v>
-      </c>
-      <c r="M115" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="N115" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="O115" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="P115" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="R115" s="5" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A116" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I116" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="J116" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K116" s="5" t="s">
-        <v>805</v>
-      </c>
-      <c r="M116" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="N116" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="O116" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="P116" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="R116" s="5" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A117" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I117" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="J117" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K117" s="5" t="s">
+      <c r="I109" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="L117" s="5" t="s">
+      <c r="J109" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="K109" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="M117" s="5" t="s">
+      <c r="M109" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="N117" s="5" t="s">
+      <c r="N109" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="O117" s="5" t="s">
+      <c r="O109" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="P117" s="5" t="s">
+      <c r="P109" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="R117" s="5" t="s">
+      <c r="R109" s="5" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A118" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I118" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="J118" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K118" s="5" t="s">
-        <v>824</v>
-      </c>
-      <c r="M118" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="N118" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="O118" s="5" t="s">
-        <v>827</v>
-      </c>
-      <c r="P118" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="R118" s="5" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A119" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="J119" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K119" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="M119" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="N119" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="O119" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="P119" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="R119" s="5" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A120" s="5" t="s">
-        <v>782</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>839</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I120" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="J120" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="K120" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="M120" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="N120" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="O120" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="P120" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="R120" s="5" t="s">
-        <v>847</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:R110" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}"/>
+  <autoFilter ref="A1:R99" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10265,17 +9573,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -10285,22 +9593,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>848</v>
+        <v>821</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -10310,42 +9618,42 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>849</v>
+        <v>831</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>852</v>
+        <v>822</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -10355,27 +9663,27 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>853</v>
+        <v>823</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -10385,102 +9693,102 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>854</v>
+        <v>824</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>855</v>
+        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>856</v>
+        <v>826</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>857</v>
+        <v>827</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>858</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89777818-AD64-4933-83B2-3A7000BAEBCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3983A9D-CC98-4D79-9CEA-F823384D9206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="欄位說明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runes!$A$1:$R$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runes!$A$1:$R$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="846">
   <si>
     <t>類型</t>
   </si>
@@ -3209,6 +3209,42 @@
   </si>
   <si>
     <t>twoHandBonusSlots：雙手武器的符文孔比一般裝備多幾個（加法，不是倍數；0＝一樣多）。只加在本來就有符文孔的稀有度上；最多孔稀有度的孔數加上它不得超過上限。5 顆符文的真言只能用在雙手武器，要靠這一格才做得出來。</t>
+  </si>
+  <si>
+    <t>erase_scrapPerTier</t>
+  </si>
+  <si>
+    <t>抹除費用：裝備碎片(每階)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>抹除已刻印的符文要付的裝備碎片：每階單價（0＝不收這種幣）。實付＝單價 × 符文階數 × 裝備稀有度倍率（RARITIES 的詞條數值倍率），無條件進位。符文抹除後直接消失、不退還。</t>
+  </si>
+  <si>
+    <t>erase_essencePerTier</t>
+  </si>
+  <si>
+    <t>抹除費用：附魔精華(每階)</t>
+  </si>
+  <si>
+    <t>抹除已刻印的符文要付的附魔精華：每階單價（0＝不收這種幣）。算法同裝備碎片。</t>
+  </si>
+  <si>
+    <t>erase_goldPerTier</t>
+  </si>
+  <si>
+    <t>抹除費用：金幣(每階)</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>抹除已刻印的符文要付的金幣：每階單價（0＝不收這種幣；預設不收）。算法同裝備碎片。</t>
+  </si>
+  <si>
+    <t>erase_scrapPerTier／erase_essencePerTier／erase_goldPerTier：抹除已刻印符文的費用（裝備碎片／附魔精華／金幣各自的每階單價，0＝不收這種幣）。實付＝單價 × 符文階數 × 裝備稀有度倍率，無條件進位；符文抹除後消失、不退還。</t>
   </si>
 </sst>
 </file>
@@ -3616,7 +3652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}">
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:R112"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
@@ -3811,55 +3847,29 @@
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>173</v>
+        <v>834</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>175</v>
+        <v>836</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>176</v>
+        <v>837</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3867,55 +3877,29 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>177</v>
+        <v>838</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>839</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>180</v>
+        <v>840</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3923,55 +3907,29 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>181</v>
+        <v>841</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>21</v>
-      </c>
+        <v>842</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>23</v>
+        <v>843</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>183</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -3979,10 +3937,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>21</v>
@@ -4024,10 +3982,10 @@
         <v>21</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -4035,10 +3993,10 @@
         <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
@@ -4080,10 +4038,10 @@
         <v>21</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -4091,10 +4049,10 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
@@ -4136,10 +4094,10 @@
         <v>21</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>194</v>
+        <v>23</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -4147,10 +4105,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
@@ -4192,21 +4150,21 @@
         <v>21</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>200</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -4248,36 +4206,36 @@
         <v>21</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>21</v>
@@ -4304,36 +4262,36 @@
         <v>21</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>93</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>21</v>
@@ -4360,36 +4318,36 @@
         <v>21</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>94</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>21</v>
@@ -4416,10 +4374,10 @@
         <v>21</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -4427,25 +4385,25 @@
         <v>27</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>214</v>
+        <v>92</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>208</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>21</v>
@@ -4475,7 +4433,7 @@
         <v>21</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -4483,22 +4441,22 @@
         <v>27</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>214</v>
@@ -4531,7 +4489,7 @@
         <v>21</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4539,25 +4497,25 @@
         <v>27</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -4587,7 +4545,7 @@
         <v>21</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4595,25 +4553,25 @@
         <v>27</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>214</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>21</v>
@@ -4643,7 +4601,7 @@
         <v>21</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -4651,25 +4609,25 @@
         <v>27</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
@@ -4699,7 +4657,7 @@
         <v>21</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4707,25 +4665,25 @@
         <v>27</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>214</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>21</v>
@@ -4755,7 +4713,7 @@
         <v>21</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4763,25 +4721,25 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
@@ -4811,7 +4769,7 @@
         <v>21</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4819,25 +4777,25 @@
         <v>27</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
@@ -4867,7 +4825,7 @@
         <v>21</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4875,25 +4833,25 @@
         <v>27</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>190</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
@@ -4923,7 +4881,7 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4931,25 +4889,25 @@
         <v>27</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
@@ -4979,7 +4937,7 @@
         <v>21</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -4987,25 +4945,25 @@
         <v>27</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>258</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -5035,7 +4993,7 @@
         <v>21</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -5043,25 +5001,25 @@
         <v>27</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>260</v>
+        <v>30</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -5091,7 +5049,7 @@
         <v>21</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -5099,25 +5057,25 @@
         <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>286</v>
+        <v>207</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
@@ -5147,7 +5105,7 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -5155,25 +5113,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>258</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
@@ -5203,7 +5161,7 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5211,25 +5169,25 @@
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -5259,7 +5217,7 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5267,25 +5225,25 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>222</v>
+        <v>285</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>21</v>
@@ -5315,7 +5273,7 @@
         <v>21</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5323,25 +5281,25 @@
         <v>27</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>179</v>
+        <v>289</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>186</v>
+        <v>258</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>21</v>
@@ -5371,7 +5329,7 @@
         <v>21</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5379,25 +5337,25 @@
         <v>27</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>32</v>
+        <v>275</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>312</v>
+        <v>275</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
@@ -5427,7 +5385,7 @@
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -5435,25 +5393,25 @@
         <v>27</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>316</v>
+        <v>222</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>312</v>
+        <v>23</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>253</v>
+        <v>301</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>317</v>
+        <v>186</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>21</v>
@@ -5483,7 +5441,7 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -5491,25 +5449,25 @@
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>320</v>
+        <v>179</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>252</v>
+        <v>304</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>321</v>
+        <v>186</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>21</v>
@@ -5539,7 +5497,7 @@
         <v>21</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -5547,25 +5505,25 @@
         <v>27</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>214</v>
+        <v>312</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>21</v>
@@ -5595,7 +5553,7 @@
         <v>21</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -5603,25 +5561,25 @@
         <v>27</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
@@ -5651,7 +5609,7 @@
         <v>21</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -5659,25 +5617,25 @@
         <v>27</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>335</v>
+        <v>252</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
@@ -5707,7 +5665,7 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -5715,25 +5673,25 @@
         <v>27</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>341</v>
+        <v>33</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>341</v>
+        <v>214</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>21</v>
@@ -5763,7 +5721,7 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -5771,25 +5729,25 @@
         <v>27</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>346</v>
+        <v>264</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>208</v>
+        <v>331</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>21</v>
@@ -5819,7 +5777,7 @@
         <v>21</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -5827,25 +5785,25 @@
         <v>27</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>242</v>
+        <v>335</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>243</v>
+        <v>337</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>21</v>
@@ -5875,7 +5833,7 @@
         <v>21</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -5883,25 +5841,25 @@
         <v>27</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>253</v>
+        <v>342</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
@@ -5931,7 +5889,7 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -5939,25 +5897,25 @@
         <v>27</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>264</v>
+        <v>346</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>211</v>
+        <v>347</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>275</v>
+        <v>347</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>21</v>
@@ -5987,7 +5945,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -5995,25 +5953,25 @@
         <v>27</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>311</v>
+        <v>243</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>211</v>
+        <v>351</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>21</v>
@@ -6043,33 +6001,33 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>363</v>
+        <v>27</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>310</v>
+        <v>252</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>322</v>
+        <v>253</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>21</v>
@@ -6099,42 +6057,42 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>23</v>
+        <v>358</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>21</v>
+        <v>264</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>371</v>
+        <v>21</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>21</v>
@@ -6149,48 +6107,48 @@
         <v>21</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>169</v>
+        <v>27</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>23</v>
+        <v>361</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>21</v>
+        <v>362</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>21</v>
+        <v>311</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>376</v>
+        <v>21</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>21</v>
@@ -6205,48 +6163,48 @@
         <v>21</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>379</v>
+        <v>21</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>169</v>
+        <v>363</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>23</v>
+        <v>366</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>21</v>
+        <v>310</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>21</v>
+        <v>367</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>21</v>
+        <v>322</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>382</v>
+        <v>21</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>383</v>
+        <v>21</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>384</v>
+        <v>21</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>21</v>
@@ -6258,16 +6216,16 @@
         <v>21</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>385</v>
+        <v>21</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>386</v>
+        <v>21</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
@@ -6275,10 +6233,10 @@
         <v>169</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>23</v>
@@ -6296,13 +6254,13 @@
         <v>21</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>21</v>
@@ -6317,13 +6275,13 @@
         <v>21</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
@@ -6331,10 +6289,10 @@
         <v>169</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>23</v>
@@ -6352,16 +6310,16 @@
         <v>21</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>398</v>
+        <v>21</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>21</v>
@@ -6373,13 +6331,13 @@
         <v>21</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
@@ -6387,10 +6345,10 @@
         <v>169</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>23</v>
@@ -6408,13 +6366,13 @@
         <v>21</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>21</v>
@@ -6426,16 +6384,16 @@
         <v>21</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
@@ -6443,10 +6401,10 @@
         <v>169</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>23</v>
@@ -6464,13 +6422,13 @@
         <v>21</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>21</v>
@@ -6482,16 +6440,16 @@
         <v>21</v>
       </c>
       <c r="O51" s="3" t="s">
-        <v>412</v>
+        <v>21</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
@@ -6499,10 +6457,10 @@
         <v>169</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>23</v>
@@ -6520,34 +6478,34 @@
         <v>21</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>21</v>
+        <v>398</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
@@ -6555,10 +6513,10 @@
         <v>169</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>23</v>
@@ -6576,13 +6534,13 @@
         <v>21</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>21</v>
@@ -6591,19 +6549,19 @@
         <v>21</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>426</v>
+        <v>21</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>21</v>
+        <v>405</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
@@ -6611,10 +6569,10 @@
         <v>169</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>23</v>
@@ -6632,13 +6590,13 @@
         <v>21</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>21</v>
@@ -6650,16 +6608,16 @@
         <v>21</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
@@ -6667,10 +6625,10 @@
         <v>169</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>23</v>
@@ -6688,13 +6646,13 @@
         <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>21</v>
@@ -6703,19 +6661,19 @@
         <v>21</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
@@ -6723,10 +6681,10 @@
         <v>169</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>23</v>
@@ -6744,13 +6702,13 @@
         <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>21</v>
@@ -6759,19 +6717,19 @@
         <v>21</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
@@ -6779,10 +6737,10 @@
         <v>169</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>23</v>
@@ -6800,13 +6758,13 @@
         <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>21</v>
@@ -6821,13 +6779,13 @@
         <v>21</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
@@ -6835,13 +6793,13 @@
         <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>21</v>
@@ -6856,13 +6814,13 @@
         <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>21</v>
@@ -6871,19 +6829,19 @@
         <v>21</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>21</v>
+        <v>439</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>458</v>
+        <v>21</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
@@ -6891,13 +6849,13 @@
         <v>169</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>21</v>
@@ -6912,13 +6870,13 @@
         <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>21</v>
@@ -6927,19 +6885,19 @@
         <v>21</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
@@ -6947,13 +6905,13 @@
         <v>169</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>21</v>
@@ -6968,13 +6926,13 @@
         <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>371</v>
+        <v>451</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>21</v>
@@ -6986,16 +6944,16 @@
         <v>21</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>470</v>
+        <v>21</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
@@ -7003,13 +6961,13 @@
         <v>169</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>21</v>
@@ -7024,13 +6982,13 @@
         <v>21</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>383</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>21</v>
@@ -7039,19 +6997,19 @@
         <v>21</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>476</v>
+        <v>21</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
@@ -7059,10 +7017,10 @@
         <v>169</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>24</v>
@@ -7080,13 +7038,13 @@
         <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>21</v>
@@ -7095,19 +7053,19 @@
         <v>21</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
@@ -7115,10 +7073,10 @@
         <v>169</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>24</v>
@@ -7136,13 +7094,13 @@
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>21</v>
@@ -7151,19 +7109,19 @@
         <v>21</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>489</v>
+        <v>21</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>21</v>
+        <v>470</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
@@ -7171,10 +7129,10 @@
         <v>169</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>24</v>
@@ -7192,13 +7150,13 @@
         <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>494</v>
+        <v>383</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>21</v>
@@ -7207,19 +7165,19 @@
         <v>21</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>21</v>
+        <v>476</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
@@ -7227,10 +7185,10 @@
         <v>169</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>24</v>
@@ -7248,13 +7206,13 @@
         <v>21</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>417</v>
+        <v>371</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>21</v>
@@ -7263,19 +7221,19 @@
         <v>21</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>21</v>
+        <v>483</v>
       </c>
       <c r="O65" s="3" t="s">
-        <v>502</v>
+        <v>21</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
@@ -7283,10 +7241,10 @@
         <v>169</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>24</v>
@@ -7304,13 +7262,13 @@
         <v>21</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>21</v>
@@ -7319,19 +7277,19 @@
         <v>21</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>21</v>
+        <v>489</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>508</v>
+        <v>21</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
@@ -7339,10 +7297,10 @@
         <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>299</v>
+        <v>492</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>24</v>
@@ -7360,13 +7318,13 @@
         <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>21</v>
@@ -7378,16 +7336,16 @@
         <v>21</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
@@ -7395,10 +7353,10 @@
         <v>169</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>24</v>
@@ -7416,16 +7374,16 @@
         <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>519</v>
+        <v>417</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>521</v>
+        <v>21</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>21</v>
@@ -7434,16 +7392,16 @@
         <v>21</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -7451,10 +7409,10 @@
         <v>169</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>24</v>
@@ -7472,13 +7430,13 @@
         <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>424</v>
+        <v>383</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>21</v>
@@ -7487,19 +7445,19 @@
         <v>21</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>21</v>
+        <v>508</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -7507,10 +7465,10 @@
         <v>169</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>531</v>
+        <v>299</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>24</v>
@@ -7528,13 +7486,13 @@
         <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>21</v>
@@ -7546,16 +7504,16 @@
         <v>21</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -7563,10 +7521,10 @@
         <v>169</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>24</v>
@@ -7584,16 +7542,16 @@
         <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>21</v>
+        <v>521</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>21</v>
@@ -7602,16 +7560,16 @@
         <v>21</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -7619,13 +7577,13 @@
         <v>169</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>21</v>
@@ -7640,13 +7598,13 @@
         <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>21</v>
@@ -7655,19 +7613,19 @@
         <v>21</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>21</v>
+        <v>528</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -7675,13 +7633,13 @@
         <v>169</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>21</v>
@@ -7696,13 +7654,13 @@
         <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>371</v>
+        <v>533</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>21</v>
@@ -7711,19 +7669,19 @@
         <v>21</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>553</v>
+        <v>21</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>21</v>
+        <v>535</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -7731,13 +7689,13 @@
         <v>169</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>21</v>
@@ -7752,13 +7710,13 @@
         <v>21</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>451</v>
+        <v>540</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>21</v>
@@ -7767,19 +7725,19 @@
         <v>21</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>559</v>
+        <v>21</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -7787,13 +7745,13 @@
         <v>169</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>25</v>
+        <v>211</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>21</v>
@@ -7808,13 +7766,13 @@
         <v>21</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>21</v>
@@ -7826,16 +7784,16 @@
         <v>21</v>
       </c>
       <c r="O75" s="3" t="s">
-        <v>566</v>
+        <v>21</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -7843,10 +7801,10 @@
         <v>169</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>25</v>
@@ -7864,13 +7822,13 @@
         <v>21</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>540</v>
+        <v>371</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>21</v>
@@ -7879,19 +7837,19 @@
         <v>21</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>573</v>
+        <v>21</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -7899,10 +7857,10 @@
         <v>169</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>25</v>
@@ -7920,13 +7878,13 @@
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>377</v>
+        <v>451</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>21</v>
@@ -7935,19 +7893,19 @@
         <v>21</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>21</v>
+        <v>559</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -7955,10 +7913,10 @@
         <v>169</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>25</v>
@@ -7976,13 +7934,13 @@
         <v>21</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>21</v>
@@ -7991,19 +7949,19 @@
         <v>21</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>585</v>
+        <v>21</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>21</v>
+        <v>566</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -8011,10 +7969,10 @@
         <v>169</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>25</v>
@@ -8032,34 +7990,34 @@
         <v>21</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>590</v>
+        <v>540</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>592</v>
+        <v>21</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -8067,10 +8025,10 @@
         <v>169</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>25</v>
@@ -8088,13 +8046,13 @@
         <v>21</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>598</v>
+        <v>377</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>21</v>
@@ -8103,19 +8061,19 @@
         <v>21</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>600</v>
+        <v>21</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>21</v>
+        <v>579</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
@@ -8123,10 +8081,10 @@
         <v>169</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>25</v>
@@ -8144,34 +8102,34 @@
         <v>21</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>605</v>
+        <v>371</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>607</v>
+        <v>21</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>21</v>
+        <v>585</v>
       </c>
       <c r="O81" s="3" t="s">
-        <v>608</v>
+        <v>21</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
@@ -8179,10 +8137,10 @@
         <v>169</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>611</v>
+        <v>588</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>25</v>
@@ -8200,34 +8158,34 @@
         <v>21</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>371</v>
+        <v>590</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>613</v>
+        <v>591</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>21</v>
+        <v>592</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
@@ -8235,10 +8193,10 @@
         <v>169</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>25</v>
@@ -8256,13 +8214,13 @@
         <v>21</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>444</v>
+        <v>598</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>21</v>
@@ -8271,19 +8229,19 @@
         <v>21</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
@@ -8291,10 +8249,10 @@
         <v>169</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>25</v>
@@ -8312,16 +8270,16 @@
         <v>21</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>21</v>
+        <v>607</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>21</v>
@@ -8330,16 +8288,16 @@
         <v>21</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
@@ -8347,10 +8305,10 @@
         <v>169</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>25</v>
@@ -8368,13 +8326,13 @@
         <v>21</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>424</v>
+        <v>371</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>21</v>
@@ -8383,19 +8341,19 @@
         <v>21</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
@@ -8403,13 +8361,13 @@
         <v>169</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>635</v>
+        <v>616</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>21</v>
@@ -8424,13 +8382,13 @@
         <v>21</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>371</v>
+        <v>444</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>21</v>
@@ -8439,19 +8397,19 @@
         <v>21</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>640</v>
+        <v>21</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
@@ -8459,13 +8417,13 @@
         <v>169</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>643</v>
+        <v>623</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>21</v>
@@ -8480,34 +8438,34 @@
         <v>21</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>451</v>
+        <v>625</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>645</v>
+        <v>626</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>646</v>
+        <v>21</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>647</v>
+        <v>21</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>650</v>
+        <v>165</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
@@ -8515,13 +8473,13 @@
         <v>169</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>652</v>
+        <v>630</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>21</v>
@@ -8536,34 +8494,34 @@
         <v>21</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>655</v>
+        <v>21</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>656</v>
+        <v>633</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>657</v>
+        <v>21</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>659</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
@@ -8571,13 +8529,13 @@
         <v>169</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>660</v>
+        <v>635</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>661</v>
+        <v>636</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>21</v>
@@ -8592,34 +8550,34 @@
         <v>21</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>662</v>
+        <v>637</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>451</v>
+        <v>371</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>663</v>
+        <v>638</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>664</v>
+        <v>21</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>21</v>
+        <v>640</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>666</v>
+        <v>641</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>667</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
@@ -8627,10 +8585,10 @@
         <v>169</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>668</v>
+        <v>642</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>349</v>
+        <v>643</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>22</v>
@@ -8648,34 +8606,34 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>377</v>
+        <v>451</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>671</v>
+        <v>646</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>672</v>
+        <v>647</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>21</v>
+        <v>648</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
@@ -8683,10 +8641,10 @@
         <v>169</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>22</v>
@@ -8704,34 +8662,34 @@
         <v>21</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>677</v>
+        <v>653</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
@@ -8739,10 +8697,10 @@
         <v>169</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>22</v>
@@ -8760,34 +8718,34 @@
         <v>21</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>371</v>
+        <v>451</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="L92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="O92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>691</v>
+        <v>667</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
@@ -8795,10 +8753,10 @@
         <v>169</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>693</v>
+        <v>349</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>22</v>
@@ -8816,34 +8774,34 @@
         <v>21</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>694</v>
+        <v>669</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>695</v>
+        <v>670</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>696</v>
+        <v>671</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="O93" s="3" t="s">
-        <v>698</v>
+        <v>21</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>699</v>
+        <v>673</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>700</v>
+        <v>674</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
@@ -8851,10 +8809,10 @@
         <v>169</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>701</v>
+        <v>675</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>702</v>
+        <v>676</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>22</v>
@@ -8872,34 +8830,34 @@
         <v>21</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>703</v>
+        <v>677</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>383</v>
+        <v>437</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>704</v>
+        <v>678</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>706</v>
+        <v>680</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>707</v>
+        <v>681</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>708</v>
+        <v>682</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>709</v>
+        <v>683</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
@@ -8907,10 +8865,10 @@
         <v>169</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>710</v>
+        <v>684</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>22</v>
@@ -8928,34 +8886,34 @@
         <v>21</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>712</v>
+        <v>686</v>
       </c>
       <c r="J95" s="3" t="s">
         <v>371</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>713</v>
+        <v>687</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>714</v>
+        <v>688</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>715</v>
+        <v>689</v>
       </c>
       <c r="O95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>716</v>
+        <v>690</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>717</v>
+        <v>691</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
@@ -8963,10 +8921,10 @@
         <v>169</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>718</v>
+        <v>692</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>719</v>
+        <v>693</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>22</v>
@@ -8984,34 +8942,34 @@
         <v>21</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>721</v>
+        <v>371</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>722</v>
+        <v>695</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>723</v>
+        <v>696</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>21</v>
+        <v>697</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>724</v>
+        <v>698</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>726</v>
+        <v>700</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
@@ -9019,10 +8977,10 @@
         <v>169</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>727</v>
+        <v>701</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>728</v>
+        <v>702</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>22</v>
@@ -9040,34 +8998,34 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>729</v>
+        <v>703</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>444</v>
+        <v>383</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>730</v>
+        <v>704</v>
       </c>
       <c r="L97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>731</v>
+        <v>705</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>732</v>
+        <v>706</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>733</v>
+        <v>707</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>734</v>
+        <v>708</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>735</v>
+        <v>709</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
@@ -9075,10 +9033,10 @@
         <v>169</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>736</v>
+        <v>710</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>737</v>
+        <v>711</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -9096,34 +9054,34 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>738</v>
+        <v>712</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>451</v>
+        <v>371</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>739</v>
+        <v>713</v>
       </c>
       <c r="L98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>740</v>
+        <v>714</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>741</v>
+        <v>715</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>742</v>
+        <v>21</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>743</v>
+        <v>716</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>744</v>
+        <v>717</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
@@ -9131,10 +9089,10 @@
         <v>169</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>745</v>
+        <v>718</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -9152,142 +9110,202 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="N99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="P99" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="Q99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R99" s="3" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I102" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="J102" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="K99" s="3" t="s">
+      <c r="K102" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="L99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="3" t="s">
+      <c r="L102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="N99" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="O99" s="3" t="s">
+      <c r="O102" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="P99" s="3" t="s">
+      <c r="P102" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="Q99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R99" s="3" t="s">
+      <c r="Q102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>754</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I100" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="K100" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="M100" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="N100" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P100" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="R100" s="5" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I101" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="J101" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K101" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M101" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="N101" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P101" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="R101" s="5" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A102" s="5" t="s">
-        <v>755</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I102" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="K102" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M102" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="N102" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="O102" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P102" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="R102" s="5" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
@@ -9295,34 +9313,34 @@
         <v>755</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="P103" s="5" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="R103" s="5" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
@@ -9330,37 +9348,34 @@
         <v>755</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>766</v>
+        <v>47</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>767</v>
+        <v>48</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>37</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>769</v>
+        <v>49</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="O104" s="5" t="s">
-        <v>772</v>
+        <v>38</v>
       </c>
       <c r="P104" s="5" t="s">
-        <v>773</v>
+        <v>50</v>
       </c>
       <c r="R104" s="5" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
@@ -9368,37 +9383,37 @@
         <v>755</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>775</v>
+        <v>51</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>776</v>
+        <v>52</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="J105" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>778</v>
+        <v>53</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>779</v>
+        <v>762</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>780</v>
+        <v>54</v>
       </c>
       <c r="O105" s="5" t="s">
-        <v>781</v>
+        <v>55</v>
       </c>
       <c r="P105" s="5" t="s">
-        <v>782</v>
+        <v>56</v>
       </c>
       <c r="R105" s="5" t="s">
-        <v>783</v>
+        <v>763</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
@@ -9406,40 +9421,34 @@
         <v>755</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>784</v>
+        <v>57</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>785</v>
+        <v>58</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>786</v>
+        <v>59</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>787</v>
-      </c>
-      <c r="L106" s="5" t="s">
-        <v>788</v>
+        <v>61</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>789</v>
+        <v>764</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="O106" s="5" t="s">
-        <v>791</v>
+        <v>62</v>
       </c>
       <c r="P106" s="5" t="s">
-        <v>792</v>
+        <v>63</v>
       </c>
       <c r="R106" s="5" t="s">
-        <v>793</v>
+        <v>765</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
@@ -9447,37 +9456,37 @@
         <v>755</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>794</v>
+        <v>766</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>796</v>
+        <v>768</v>
       </c>
       <c r="J107" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>798</v>
+        <v>770</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>799</v>
+        <v>771</v>
       </c>
       <c r="O107" s="5" t="s">
-        <v>800</v>
+        <v>772</v>
       </c>
       <c r="P107" s="5" t="s">
-        <v>801</v>
+        <v>773</v>
       </c>
       <c r="R107" s="5" t="s">
-        <v>802</v>
+        <v>774</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
@@ -9485,37 +9494,37 @@
         <v>755</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>803</v>
+        <v>775</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>804</v>
+        <v>776</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>805</v>
+        <v>777</v>
       </c>
       <c r="J108" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>806</v>
+        <v>778</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>808</v>
+        <v>780</v>
       </c>
       <c r="O108" s="5" t="s">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="P108" s="5" t="s">
-        <v>810</v>
+        <v>782</v>
       </c>
       <c r="R108" s="5" t="s">
-        <v>811</v>
+        <v>783</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
@@ -9523,41 +9532,158 @@
         <v>755</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>812</v>
+        <v>784</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>813</v>
+        <v>785</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I109" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K109" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="L109" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="M109" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="N109" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="O109" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="P109" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="R109" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="M110" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="N110" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="O110" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="P110" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="R110" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="M111" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="N111" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="O111" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="P111" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="R111" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="J109" s="5" t="s">
+      <c r="J112" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K109" s="5" t="s">
+      <c r="K112" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="M109" s="5" t="s">
+      <c r="M112" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="N109" s="5" t="s">
+      <c r="N112" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="O109" s="5" t="s">
+      <c r="O112" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="P109" s="5" t="s">
+      <c r="P112" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="R109" s="5" t="s">
+      <c r="R112" s="5" t="s">
         <v>820</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R99" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}"/>
+  <autoFilter ref="A1:R102" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9565,7 +9691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.625" customWidth="1"/>
@@ -9638,156 +9764,161 @@
     </row>
     <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>822</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="21" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>823</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>21</v>
+        <v>823</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>824</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>78</v>
+        <v>826</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>827</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>80</v>
+        <v>827</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+    <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>168</v>
       </c>
     </row>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFC081B-6A3E-4B73-829F-B8F048714820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B74B51A-927D-40C9-B8B7-27213DCA35EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -156,9 +156,6 @@
     <t>greatsword2h;axe2h</t>
   </si>
   <si>
-    <t>atkPct:3;aspd:3;aoeDmg:2</t>
-  </si>
-  <si>
     <t>splashPct:50;dmgPerFoePct:6</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>劍舞者</t>
   </si>
   <si>
-    <t>aspd:3;critRate:3;atkPct:3</t>
-  </si>
-  <si>
     <t>舞到最後一步時，才知道這是一場不能停的舞。</t>
   </si>
   <si>
@@ -183,9 +177,6 @@
     <t>虛空行者</t>
   </si>
   <si>
-    <t>evasion:6;hit:4;hpPct:3</t>
-  </si>
-  <si>
     <t>dmgPct:25</t>
   </si>
   <si>
@@ -207,9 +198,6 @@
     <t>any</t>
   </si>
   <si>
-    <t>atkPct:3;matkPct:3;elemDmgFire:1.5;elemDmgIce:1.5;elemDmgLightning:1.5;elemDmgPoison:1.5;elemDmgLight:1.5;elemDmgDark:1.5;elemDmgEarth:1.5;elemDmgWind:1.5</t>
-  </si>
-  <si>
     <t>dmgPct:50;cdPct:20;aspdMult:15;manaCostRedPct:30</t>
   </si>
   <si>
@@ -297,174 +285,6 @@
     <t>風味文字：圖鑑與詳情顯示的一句話，可留空。效果說明文字由資料自動產生，不需要另外寫。</t>
   </si>
   <si>
-    <t>屬性：物理攻擊×2、魔法攻擊×2、命中率×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理防禦×2.5、生命值×2.5、生命恢復/秒×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×2.5、冰屬性傷害提升×1.5｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×2、生命值×2、命中率×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理防禦×1.5、生命值×1.2、物理抗性×0.8｜反震 3%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.2、毒屬性傷害提升×1.5、暴擊率×1｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 60% 攻擊力，4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.5、雷屬性傷害提升×2｜普通攻擊命中時有 8% 機率：對目標造成 90% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力值×2、聖光抗性×1.5、生命值×1｜擊殺敵人時回復 1% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：吸血×2、物理攻擊×1、命中率×1｜擊殺敵人時回復 1% 最大生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.5、物理防禦×1.5、韌性×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力恢復/秒×2、生命恢復/秒×2、法力值×1.5｜擊殺敵人時回復 2% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：金幣加成×2、經驗加成×1.5、掉寶率×1.2｜符文掉落率 +8%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.2、暴擊傷害×1.2、物理穿透×0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.5、火屬性傷害提升×1.5、法力值×1.5｜施放技能時有 15% 機率：回復 12% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×2.5、暴擊率×1.5、物理攻擊×1.5｜攻擊速度額外乘算 +8%（突破攻速上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.5、雷屬性傷害提升×2.5、暴擊傷害×1.5｜普通攻擊命中時有 15% 機率：對所有敵人造成 120% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×2、冰屬性傷害提升×3、冷卻縮減×1｜對暈眩或緩速中的敵人傷害 +15%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：吸血×3、物理攻擊×2、暴擊率×1｜擊殺敵人時回復 3% 最大生命；生命低於 35% 時，傷害 +25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×3、物理防禦×3、物理抗性×1｜單次受到的傷害最多只會是最大生命的 40%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×3.5、命中率×2、生命值×1.5｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×2、法力值×3、全屬性抗性×1｜每 10 秒：回復 8% 最大生命，回復 8% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×2、毒屬性傷害提升×3、魔法穿透×0.3｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 60% 攻擊力，4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×3、暴擊率×2、物理攻擊×1.5｜普通攻擊暴擊時：獲得「攻速」+12%（3 秒，最多 3 層）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×2.5、物理防禦×2、物理抗性×1｜反震 12%；受到傷害時有 20% 機率：對攻擊者造成 100% 物理傷害（內建冷卻 3 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：幸運值×3、暴擊率×2、暴擊傷害×2.5、掉寶率×2｜符文掉落率 +15%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：格擋率×3、格擋減傷×3、生命值×2｜格擋成功時有 40% 機率：對攻擊者造成 200% 物理傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×3、法力值×3、冷卻縮減×2｜施放技能時有 20% 機率：所有技能冷卻縮短 1.5 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：寶石鑲嵌效率×3、詞條上限率×2、強化成功率×3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、對BOSS傷害×3｜造成的所有傷害 +18%；攻擊速度額外乘算 +10%（突破攻速上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×4、暴擊傷害×4、對菁英傷害×3、物理穿透×0.5｜對生命低於 30% 的敵人傷害 +60%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 15% 的非 BOSS 敵人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3、風屬性傷害提升×2、魔法穿透×0.5｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 120% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 100% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：冷卻縮減×4、魔法攻擊×3、法力恢復/秒×3、生命值×2｜所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 1 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×4、物理防禦×3.5、魔法防禦×3.5、全局減傷×2｜生命低於 30% 時：無敵 3 秒，回復 30% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×2.5、物理攻擊×2.5、暴擊率×1.5、範圍傷害×2｜場上每多一名敵人，傷害 +5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 20% 的傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：暴擊率×1.5、暴擊傷害×2、物理攻擊×2、閃避率×1.5｜對生命高於 70% 的敵人傷害 +20%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：飛刀的彈射數 +2 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力值×4、法力恢復/秒×4、魔法攻擊×2.5｜技能法力消耗 -40%；擊殺敵人時回復 3% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×3.5、物理防禦×3.5、物理抗性×2｜反震 35%；受到傷害時有 25% 機率：對所有敵人造成 150% 物理傷害（內建冷卻 2 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：對BOSS傷害×5、對菁英傷害×4、物理攻擊×2.5、魔法攻擊×2.5｜對生命高於 70% 的敵人傷害 +40%；場上只有一名敵人時，傷害 +40%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×4、吸血×4、生命恢復/秒×4｜擊殺敵人時回復 6% 最大生命；生命高於 90% 時，傷害 +25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：護盾效率×5、生命值×3、全局減傷×2.5｜每 8 秒：獲得相當於 20% 最大生命的護盾（8 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：火屬性傷害提升×1.8、冰屬性傷害提升×1.8、雷屬性傷害提升×1.8、風屬性傷害提升×1.8、毒屬性傷害提升×1.8｜造成的所有傷害 +10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×4、暴擊率×3、命中率×2｜攻擊速度額外乘算 +15%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>　　備註是自動產生的參考，不進遊戲、不影響套用；你改了能力之後，備註不會自動更新（請 AI 重新產生），以左邊各欄實際內容為準。</t>
   </si>
   <si>
@@ -1208,10 +1028,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkFlat:2;matkFlat:2;hit:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>第一聲啼鳴，劃破長夜的寂靜。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1232,10 +1048,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>defFlat:2.5;hpFlat:2.5;hpRegen:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>燈火不滅，守夜人便不眠。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1256,10 +1068,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkFlat:2.5;elemDmgIce:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","chance":10,"acts":[{"act":"slow","sec":2}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1284,10 +1092,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>evasion:2;hpFlat:2;hit:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>步履如雲，不留痕跡。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1308,10 +1112,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>defPct:1.5;hpPct:1.2;pRes:0.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>thorns:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1336,10 +1136,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:1.2;elemDmgPoison:1.5;critRate:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","chance":15,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1364,10 +1160,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:1.5;elemDmgLightning:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":90,"elem":"lightning","to":"target"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1392,10 +1184,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mpFlat:2;resLight:1.5;hpPct:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>killManaPct:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1420,10 +1208,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lifesteal:2;atkPct:1;hit:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>killHealPct:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1448,10 +1232,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:1.5;defPct:1.5;tenacity:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>腰繫鋼索，心不動搖。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1472,10 +1252,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mpRegen:2;hpRegen:2;mpFlat:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>killManaPct:2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1500,10 +1276,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>goldBonus:2;xpBonus:1.5;loot:1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>runeFindPct:8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1528,10 +1300,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:1.2;critDmg:1.2;pPen:0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重兵一落，軍陣自潰。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1548,10 +1316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:1.5;elemDmgFire:1.5;mpFlat:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"cast","chance":15,"acts":[{"act":"mana","pctMax":12}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1572,10 +1336,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspd:2.5;critRate:1.5;atkPct:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>aspdMult:8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1596,10 +1356,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:1.5;elemDmgLightning:2.5;critDmg:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","chance":15,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1620,10 +1376,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:2;elemDmgIce:3;cdr:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgCtrlPct:15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1648,10 +1400,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>lifesteal:3;atkPct:2;critRate:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>killHealPct:3;dmgSelfLowPct:25</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1672,10 +1420,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:3;defPct:3;pRes:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>maxHitPct:40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1700,10 +1444,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>evasion:3.5;hit:2;hpPct:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hurt","chance":15,"cd":10,"acts":[{"act":"invuln","sec":1}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1724,10 +1464,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:2;mpFlat:3;resAll:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"tick","every":10,"acts":[{"act":"heal","pctMax":8},{"act":"mana","pctMax":8}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1748,10 +1484,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:2;elemDmgPoison:3;mPen:0.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"cast","chance":25,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison","to":"all"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1772,10 +1504,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspd:3;critRate:2;atkPct:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":3,"max":3}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1800,10 +1528,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:2.5;defPct:2;pRes:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>thorns:12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1828,10 +1552,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>luck:3;critRate:2;critDmg:2.5;loot:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>runeFindPct:15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1856,10 +1576,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>blockRate:3;blockDmgRed:3;hpPct:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"block","chance":40,"acts":[{"act":"dmg","pct":200,"type":"phys","to":"attacker"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1884,10 +1600,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:3;mpFlat:3;cdr:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"cast","chance":20,"acts":[{"act":"cdr","sec":1.5}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1908,10 +1620,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gemEff:3;affixCap:2;enhanceSuccess:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鎚聲不絕，鋼與靈魂同鍛。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1928,10 +1636,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:3;matkPct:3;critDmg:3;bossDmg:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgPct:18;aspdMult:10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1952,10 +1656,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:4;critDmg:4;eliteDmg:3;pPen:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgLoHpPct:60</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1980,10 +1680,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:3;elemDmgLightning:3;elemDmgWind:2;mPen:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"crit","chance":30,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]},{"on":"cast","chance":25,"acts":[{"act":"dmg","pct":100,"elem":"lightning","to":"rand","n":3}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2004,10 +1700,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cdr:4;matkPct:3;mpRegen:3;hpPct:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cdPct:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2032,10 +1724,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:4;defPct:3.5;mdefPct:3.5;globalDmgRed:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"lowhp","below":30,"cd":90,"acts":[{"act":"invuln","sec":3},{"act":"heal","pctMax":30},{"act":"cleanse"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2056,10 +1744,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspd:2.5;atkPct:2.5;critRate:1.5;aoeDmg:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgPerFoePct:5;splashPct:20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2084,10 +1768,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>critRate:1.5;critDmg:2;atkPct:2;evasion:1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>knifeShadowblade;knifeChain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2116,10 +1796,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mpFlat:4;mpRegen:4;matkPct:2.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>manaCostRedPct:40;killManaPct:3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2144,10 +1820,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:3.5;defPct:3.5;pRes:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>thorns:35</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2172,10 +1844,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bossDmg:5;eliteDmg:4;atkPct:2.5;matkPct:2.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgHiHpPct:40;dmgSoloPct:40</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2196,10 +1864,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:4;lifesteal:4;hpRegen:4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>killHealPct:6;dmgSelfFullPct:25</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2224,10 +1888,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>shieldEff:5;hpPct:3;globalDmgRed:2.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"tick","every":8,"acts":[{"act":"shield","pctMax":20,"sec":8}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2248,10 +1908,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>elemDmgFire:1.8;elemDmgIce:1.8;elemDmgLightning:1.8;elemDmgWind:1.8;elemDmgPoison:1.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgPct:10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2272,10 +1928,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspd:4;critRate:3;hit:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>aspdMult:15</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2300,10 +1952,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:4;eliteDmg:3;pPen:0.6;critDmg:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rockEarthHeart</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2320,10 +1968,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：物理攻擊×4、對菁英傷害×3、物理穿透×0.6、暴擊傷害×3｜對生命高於 70% 的敵人傷害 +30%；普通攻擊命中時有 8% 機率：對所有敵人造成 220% 物理傷害；傳奇特效【大地之心】：當你的生命護盾降至 0 時獲得無敵 2 秒；此效果每 30 秒只能觸發 1 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_galeeye</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2336,10 +1980,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspd:4.5;critRate:3.5;atkPct:3.5;aoeDmg:2.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>stormbarrierCore</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2356,10 +1996,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：攻擊速度×4.5、暴擊率×3.5、物理攻擊×3.5、範圍傷害×2.5｜攻擊速度額外乘算 +18%（突破攻速上限）；普通攻擊暴擊時：獲得「攻速」+12%（4 秒，最多 4 層）；傳奇特效【風暴核心】：【暴風神體】的持續時間 +50%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_bloodrite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2372,10 +2008,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:4.5;lifesteal:4.5;critDmg:4.5;hpPct:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bloodVenomRite</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2388,10 +2020,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：物理攻擊×4.5、吸血×4.5、暴擊傷害×4.5、生命值×3｜擊殺敵人時回復 8% 最大生命；生命低於 35% 時，傷害 +60%；造成的所有傷害 +30%；傳奇特效【毒血祭】：血刃斬的中毒每感染 1 個敵人就使自身生命值 -1%，但造成的中毒與流血傷害提高 50%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_reincarnation</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2400,10 +2028,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:4;defPct:4;mdefPct:4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>counterOath</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2416,10 +2040,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：生命值×4、物理防禦×4、魔法防禦×4｜死亡時以 60% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +60%，冷卻 180 秒；傳奇特效【堅韌誓言】：反擊 100 次後獲得無敵狀態，持續 3 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_timeloop</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2432,10 +2052,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cdr:5;mpRegen:5;matkPct:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>vacuumFlux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2452,10 +2068,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：冷卻縮減×5、法力恢復/秒×5、魔法攻擊×3｜所有技能冷卻時間 -45%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能；傳奇特效【虛空漲落】：【虛空斬】的持續時間 +3 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_bloodmoon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2468,10 +2080,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:3;matkPct:3;critDmg:3;lifesteal:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rageBurnBlood</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2484,10 +2092,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：物理攻擊×3、魔法攻擊×3、暴擊傷害×3、吸血×2｜造成的所有傷害 +60%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 8% 最大生命；最大生命 -30%（乘算，代價）；傳奇特效【燃血】：【血飲術】每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_arsenal</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2500,10 +2104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspd:3;atkPct:3;matkPct:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>knifeSplitter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2520,10 +2120,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：攻擊速度×3、物理攻擊×3、魔法攻擊×3｜技能傷害 +40%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能；傳奇特效【分裂者】：飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_thunderemperor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2536,10 +2132,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:3;elemDmgLightning:3.5;critRate:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>chainlightningOverload</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2556,10 +2148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：魔法攻擊×3、雷屬性傷害提升×3.5、暴擊率×2｜對暈眩或緩速中的敵人傷害 +10%；每 3 秒：對隨機 3 名敵人造成 120% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒；傳奇特效【過載】：同一個敵人受到 5 次連鎖閃電的彈射後產生爆炸，對周圍 6 米內的敵人造成 200% 雷電傷害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_lonewolf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2572,10 +2160,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>critDmg:3.5;atkPct:3;bossDmg:3.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sunpiercerLance</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2588,10 +2172,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：暴擊傷害×3.5、物理攻擊×3、對BOSS傷害×3.5｜場上只有一名敵人時，傷害 +80%；對生命高於 70% 的敵人傷害 +40%；所有技能冷卻時間 -15%（乘算，突破冷卻縮減上限）；傳奇特效【貫日之刺】：四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_starfall</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2608,10 +2188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>matkPct:3.5;elemDmgFire:2.5;elemDmgIce:2.5;mPen:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>fireballBurst</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2624,10 +2200,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：魔法攻擊×3.5、火屬性傷害提升×2.5、冰屬性傷害提升×2.5、魔法穿透×0.6｜每 3 秒：對隨機 5 名敵人造成 150% 隨機元素傷害；傳奇特效【爆裂】：【火球爆裂】會額外產生 3 個小火球。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_chaoslord</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2640,10 +2212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>resAll:3;luck:4;critRate:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mireCorrupt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2660,10 +2228,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：全屬性抗性×3、幸運值×4、暴擊率×3｜技能傷害 +25%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）；傳奇特效【腐化】：在泥沼術範圍內所有受到控場的敵人，受到的傷害 +30%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_dragonslayer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2676,10 +2240,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:2.5;bossDmg:5;critDmg:2.5;pPen:0.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>galeExecute</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2696,10 +2256,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：物理攻擊×2.5、對BOSS傷害×5、暴擊傷害×2.5、物理穿透×0.8｜對生命高於 70% 的敵人傷害 +50%；造成的所有傷害 +25%；普通攻擊暴擊時有 20% 機率：對目標造成 250% 物理傷害；傳奇特效【斬殺】：疾風斬有 35% 機率可立即殺死生命值 20% 以下的非 BOSS 敵人。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rw_immortalbody</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2716,10 +2272,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hpPct:5;globalDmgRed:3;resAll:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>earthguardUndyingWill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2736,43 +2288,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：生命值×5、全局減傷×3、全屬性抗性×3｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的無敵時間內，每殺死 1 個敵人則無敵時間 +0.5 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>符文真言</t>
   </si>
   <si>
     <t>skyrendSlash</t>
   </si>
   <si>
-    <t>屬性：物理攻擊×3、攻擊速度×3、範圍傷害×2｜普通攻擊同時對其他所有敵人造成 50% 的傷害；場上每多一名敵人，傷害 +6%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
-  </si>
-  <si>
     <t>驚蟄;冰魄;虛空</t>
   </si>
   <si>
     <t>danceThousandCuts</t>
   </si>
   <si>
-    <t>屬性：攻擊速度×3、暴擊率×3、物理攻擊×3｜攻擊速度額外乘算 +15%（突破攻速上限）；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。</t>
-  </si>
-  <si>
     <t>虛空;命運;輪迴</t>
   </si>
   <si>
     <t>windbladeVoidCut</t>
   </si>
   <si>
-    <t>屬性：閃避率×6、命中率×4、生命值×3｜造成的所有傷害 +25%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 150% 暗影傷害（內建冷卻 4 秒）；傳奇特效【斷空刃】：【暴風真空刃】每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
-  </si>
-  <si>
     <t>firepillarResonance</t>
   </si>
   <si>
-    <t>屬性：物理攻擊×3、魔法攻擊×3、火屬性傷害提升×1.5、冰屬性傷害提升×1.5、雷屬性傷害提升×1.5、毒屬性傷害提升×1.5、聖屬性傷害提升×1.5、暗屬性傷害提升×1.5、地屬性傷害提升×1.5、風屬性傷害提升×1.5｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
-  </si>
-  <si>
     <t>rw_worldend</t>
   </si>
   <si>
@@ -2782,9 +2318,6 @@
     <t>熔岩;虛空;命運;永恆;混沌</t>
   </si>
   <si>
-    <t>atkPct:3.5;critDmg:3.5;bossDmg:3.5;aoeDmg:2</t>
-  </si>
-  <si>
     <t>thunderorbFallCount</t>
   </si>
   <si>
@@ -2797,9 +2330,6 @@
     <t>舉刀之時，終局已定。</t>
   </si>
   <si>
-    <t>屬性：物理攻擊×3.5、暴擊傷害×3.5、對BOSS傷害×3.5、範圍傷害×2｜造成的所有傷害 +18%；普通攻擊同時對其他所有敵人造成 15% 的傷害；普通攻擊暴擊時有 10% 機率：對所有敵人造成 250% 物理傷害；傳奇特效【雷殞落】：【雷殞天落】降下的雷球數量 +1 顆。</t>
-  </si>
-  <si>
     <t>rw_stargate</t>
   </si>
   <si>
@@ -2809,9 +2339,6 @@
     <t>嵐;雷霆;星辰;輪迴;永恆</t>
   </si>
   <si>
-    <t>matkPct:5;elemDmgLightning:2.5;elemDmgWind:2.5;cdr:3.5;mPen:0.6</t>
-  </si>
-  <si>
     <t>thunderstrikeRebirth</t>
   </si>
   <si>
@@ -2824,9 +2351,6 @@
     <t>星門開啟，咒語在兩端同時落下。</t>
   </si>
   <si>
-    <t>屬性：魔法攻擊×5、雷屬性傷害提升×2.5、風屬性傷害提升×2.5、冷卻縮減×3.5、魔法穿透×0.6｜所有技能冷卻時間 -25%（乘算，突破冷卻縮減上限）；技能傷害 +40%；施放技能時有 20% 機率：免費再施放一次剛施放的技能；傳奇特效【雷之再生】：【迅雷重生】的機率提高至 100%。</t>
-  </si>
-  <si>
     <t>rw_divinewrath</t>
   </si>
   <si>
@@ -2836,9 +2360,6 @@
     <t>蒼穹;冰魄;輪迴;混沌;終焉</t>
   </si>
   <si>
-    <t>atkPct:3;bossDmg:5;elemDmgLight:3;critRate:2</t>
-  </si>
-  <si>
     <t>smite:20</t>
   </si>
   <si>
@@ -2854,9 +2375,6 @@
     <t>審判不問理由，只問罪行。</t>
   </si>
   <si>
-    <t>屬性：物理攻擊×3、對BOSS傷害×5、聖屬性傷害提升×3、暴擊率×2｜天罰 20%；對生命高於 70% 的敵人傷害 +40%；普通攻擊暴擊時有 15% 機率：對目標造成 350% 聖光傷害；傳奇特效【狩獵者】：你的火狩數量減半（無條件進位，至少 1 團），但造成的傷害額外 +150%。</t>
-  </si>
-  <si>
     <t>rw_permafrost</t>
   </si>
   <si>
@@ -2866,9 +2384,6 @@
     <t>寒月;冰魄;永恆</t>
   </si>
   <si>
-    <t>matkPct:4.5;elemDmgIce:5;cdr:3</t>
-  </si>
-  <si>
     <t>frostnovaWinterFrost</t>
   </si>
   <si>
@@ -2881,9 +2396,6 @@
     <t>時間在這裡結了冰，連呼吸都慢了下來。</t>
   </si>
   <si>
-    <t>屬性：魔法攻擊×4.5、冰屬性傷害提升×5、冷卻縮減×3｜對暈眩或緩速中的敵人傷害 +45%；普通攻擊命中時有 15% 機率：目標暈眩 1.5 秒；傳奇特效【凜冬寒霜】：暴風雪持續時間內會不斷對範圍內的敵人施加寒霜狀態，且寒霜狀態傷害 +30%。</t>
-  </si>
-  <si>
     <t>rw_glacier</t>
   </si>
   <si>
@@ -2893,9 +2405,6 @@
     <t>霜痕;雷霆;命運</t>
   </si>
   <si>
-    <t>matkPct:3.5;elemDmgIce:3;critDmg:3;bossDmg:3</t>
-  </si>
-  <si>
     <t>icearrowDeepFreeze</t>
   </si>
   <si>
@@ -2908,9 +2417,6 @@
     <t>冰川緩慢，但它走過的地方什麼都不剩。</t>
   </si>
   <si>
-    <t>屬性：魔法攻擊×3.5、冰屬性傷害提升×3、暴擊傷害×3、對BOSS傷害×3｜對生命高於 70% 的敵人傷害 +40%；對暈眩或緩速中的敵人傷害 +20%；普通攻擊暴擊時有 25% 機率：對目標造成 200% 冰霜傷害；傳奇特效【深度凍結】：寒冰箭擊中暈眩或凍結的敵人造成的傷害 +50%。</t>
-  </si>
-  <si>
     <t>rw_tidecall</t>
   </si>
   <si>
@@ -2920,9 +2426,6 @@
     <t>暗影;靈泉;永恆</t>
   </si>
   <si>
-    <t>mpRegen:5;hpRegen:5;matkPct:3;cdr:3</t>
-  </si>
-  <si>
     <t>waterballTornado</t>
   </si>
   <si>
@@ -2935,9 +2438,6 @@
     <t>潮來潮去，每一次都帶走疲憊、留下力量。</t>
   </si>
   <si>
-    <t>屬性：法力恢復/秒×5、生命恢復/秒×5、魔法攻擊×3、冷卻縮減×3｜擊殺敵人時回復 4% 最大法力；技能法力消耗 -25%；每 6 秒：回復 6% 最大生命，回復 10% 最大法力；傳奇特效【水龍勢】：水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
-  </si>
-  <si>
     <t>符文真言：符文組合與其全部能力。可以新增列（id 以 rw_ 開頭、英數字、不重複）、刪除列、修改任何欄位。</t>
   </si>
   <si>
@@ -3309,6 +2809,526 @@
   </si>
   <si>
     <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率＝同裝備等級、稀有度「詞條基準值」（詞條範圍的中間值，等於符文倍率 1 的 1.25 倍）的幾倍，不乘雙手倍率；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkFlat:1;matkFlat:1;hit:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1、魔法攻擊×1、命中率×0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defFlat:1.25;hpFlat:1.25;hpRegen:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×1.25、生命值×1.25、生命恢復/秒×0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkFlat:1.25;elemDmgIce:0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.25、冰屬性傷害提升×0.75｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion:1;hpFlat:1;hit:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×1、生命值×1、命中率×0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defPct:0.75;hpPct:0.6;pRes:0.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×0.75、生命值×0.6、物理抗性×0.4｜反震 3%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.6;elemDmgPoison:0.75;critRate:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.6、毒屬性傷害提升×0.75、暴擊率×0.5｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 60% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.75;elemDmgLightning:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.75、雷屬性傷害提升×1｜普通攻擊命中時有 8% 機率：對目標造成 90% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpFlat:1;resLight:0.75;hpPct:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×1、聖光抗性×0.75、生命值×0.5｜擊殺敵人時回復 1% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifesteal:1;atkPct:0.5;hit:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×1、物理攻擊×0.5、命中率×0.5｜擊殺敵人時回復 1% 最大生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.75;defPct:0.75;tenacity:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.75、物理防禦×0.75、韌性×0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpRegen:1;hpRegen:1;mpFlat:0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×1、生命恢復/秒×1、法力值×0.75｜擊殺敵人時回復 2% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goldBonus:1;xpBonus:0.75;loot:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：金幣加成×1、經驗加成×0.75、掉寶率×0.6｜符文掉落率 +8%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.6;critDmg:0.6;pPen:0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.6、暴擊傷害×0.6、物理穿透×0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.75;elemDmgFire:0.75;mpFlat:0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.75、火屬性傷害提升×0.75、法力值×0.75｜施放技能時有 15% 機率：回復 12% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:1.08;critRate:0.65;atkPct:0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×1.08、暴擊率×0.65、物理攻擊×0.65｜攻擊速度額外乘算 +8%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.65;elemDmgLightning:1.08;critDmg:0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.65、雷屬性傷害提升×1.08、暴擊傷害×0.65｜普通攻擊命中時有 15% 機率：對所有敵人造成 120% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.87;elemDmgIce:1.3;cdr:0.43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.87、冰屬性傷害提升×1.3、冷卻縮減×0.43｜對暈眩或緩速中的敵人傷害 +15%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifesteal:1.3;atkPct:0.87;critRate:0.43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×1.3、物理攻擊×0.87、暴擊率×0.43｜擊殺敵人時回復 3% 最大生命；生命低於 35% 時，傷害 +25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.3;defPct:1.3;pRes:0.43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.3、物理防禦×1.3、物理抗性×0.43｜單次受到的傷害最多只會是最大生命的 40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion:1.52;hit:0.87;hpPct:0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×1.52、命中率×0.87、生命值×0.65｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.87;mpFlat:1.3;resAll:0.43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.87、法力值×1.3、全屬性抗性×0.43｜每 10 秒：回復 8% 最大生命，回復 8% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.87;elemDmgPoison:1.3;mPen:0.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.87、毒屬性傷害提升×1.3、魔法穿透×0.13｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 60% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:1.3;critRate:0.87;atkPct:0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×1.3、暴擊率×0.87、物理攻擊×0.65｜普通攻擊暴擊時：獲得「攻速」+12%（3 秒，最多 3 層）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.08;defPct:0.87;pRes:0.43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.08、物理防禦×0.87、物理抗性×0.43｜反震 12%；受到傷害時有 20% 機率：對攻擊者造成 100% 物理傷害（內建冷卻 3 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luck:1.3;critRate:0.87;critDmg:1.08;loot:0.87</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：幸運值×1.3、暴擊率×0.87、暴擊傷害×1.08、掉寶率×0.87｜符文掉落率 +15%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockRate:1.3;blockDmgRed:1.3;hpPct:0.87</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：格擋率×1.3、格擋減傷×1.3、生命值×0.87｜格擋成功時有 40% 機率：對攻擊者造成 200% 物理傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:1.3;mpFlat:1.3;cdr:0.87</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.3、法力值×1.3、冷卻縮減×0.87｜施放技能時有 20% 機率：所有技能冷卻縮短 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gemEff:1.3;affixCap:0.87;enhanceSuccess:1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：寶石鑲嵌效率×1.3、詞條上限率×0.87、強化成功率×1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:1.1;matkPct:1.1;critDmg:1.1;bossDmg:1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.1、魔法攻擊×1.1、暴擊傷害×1.1、對BOSS傷害×1.1｜造成的所有傷害 +18%；攻擊速度額外乘算 +10%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:1.47;critDmg:1.47;eliteDmg:1.1;pPen:0.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.47、暴擊傷害×1.47、對菁英傷害×1.1、物理穿透×0.18｜對生命低於 30% 的敵人傷害 +60%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 15% 的非 BOSS 敵人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:1.1;elemDmgLightning:1.1;elemDmgWind:0.73;mPen:0.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.1、雷屬性傷害提升×1.1、風屬性傷害提升×0.73、魔法穿透×0.18｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 120% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 100% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdr:1.47;matkPct:1.1;mpRegen:1.1;hpPct:0.73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×1.47、魔法攻擊×1.1、法力恢復/秒×1.1、生命值×0.73｜所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 1 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.47;defPct:1.28;mdefPct:1.28;globalDmgRed:0.73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.47、物理防禦×1.28、魔法防禦×1.28、全局減傷×0.73｜生命低於 30% 時：無敵 3 秒，回復 30% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.92;atkPct:0.92;critRate:0.55;aoeDmg:0.73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.92、物理攻擊×0.92、暴擊率×0.55、範圍傷害×0.73｜場上每多一名敵人，傷害 +5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 20% 的傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critRate:0.55;critDmg:0.73;atkPct:0.73;evasion:0.55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊率×0.55、暴擊傷害×0.73、物理攻擊×0.73、閃避率×0.55｜對生命高於 70% 的敵人傷害 +20%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：飛刀的彈射數 +2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpFlat:1.47;mpRegen:1.47;matkPct:0.92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×1.47、法力恢復/秒×1.47、魔法攻擊×0.92｜技能法力消耗 -40%；擊殺敵人時回復 3% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.28;defPct:1.28;pRes:0.73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.28、物理防禦×1.28、物理抗性×0.73｜反震 35%；受到傷害時有 25% 機率：對所有敵人造成 150% 物理傷害（內建冷卻 2 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bossDmg:1.83;eliteDmg:1.47;atkPct:0.92;matkPct:0.92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：對BOSS傷害×1.83、對菁英傷害×1.47、物理攻擊×0.92、魔法攻擊×0.92｜對生命高於 70% 的敵人傷害 +40%；場上只有一名敵人時，傷害 +40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.47;lifesteal:1.47;hpRegen:1.47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.47、吸血×1.47、生命恢復/秒×1.47｜擊殺敵人時回復 6% 最大生命；生命高於 90% 時，傷害 +25%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shieldEff:1.83;hpPct:1.1;globalDmgRed:0.92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：護盾效率×1.83、生命值×1.1、全局減傷×0.92｜每 8 秒：獲得相當於 20% 最大生命的護盾（8 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgFire:0.66;elemDmgIce:0.66;elemDmgLightning:0.66;elemDmgWind:0.66;elemDmgPoison:0.66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：火屬性傷害提升×0.66、冰屬性傷害提升×0.66、雷屬性傷害提升×0.66、風屬性傷害提升×0.66、毒屬性傷害提升×0.66｜造成的所有傷害 +10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:1.47;critRate:1.1;hit:0.73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×1.47、暴擊率×1.1、命中率×0.73｜攻擊速度額外乘算 +15%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:1.2;eliteDmg:0.9;pPen:0.18;critDmg:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.2、對菁英傷害×0.9、物理穿透×0.18、暴擊傷害×0.9｜對生命高於 70% 的敵人傷害 +30%；普通攻擊命中時有 8% 機率：對所有敵人造成 220% 物理傷害；傳奇特效【大地之心】：當你的生命護盾降至 0 時獲得無敵 2 秒；此效果每 30 秒只能觸發 1 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:1.35;critRate:1.05;atkPct:1.05;aoeDmg:0.75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×1.35、暴擊率×1.05、物理攻擊×1.05、範圍傷害×0.75｜攻擊速度額外乘算 +18%（突破攻速上限）；普通攻擊暴擊時：獲得「攻速」+12%（4 秒，最多 4 層）；傳奇特效【風暴核心】：【暴風神體】的持續時間 +50%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:1.35;lifesteal:1.35;critDmg:1.35;hpPct:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.35、吸血×1.35、暴擊傷害×1.35、生命值×0.9｜擊殺敵人時回復 8% 最大生命；生命低於 35% 時，傷害 +60%；造成的所有傷害 +30%；傳奇特效【毒血祭】：血刃斬的中毒每感染 1 個敵人就使自身生命值 -1%，但造成的中毒與流血傷害提高 50%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.2;defPct:1.2;mdefPct:1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.2、物理防禦×1.2、魔法防禦×1.2｜死亡時以 60% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +60%，冷卻 180 秒；傳奇特效【堅韌誓言】：反擊 100 次後獲得無敵狀態，持續 3 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdr:1.5;mpRegen:1.5;matkPct:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×1.5、法力恢復/秒×1.5、魔法攻擊×0.9｜所有技能冷卻時間 -45%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能；傳奇特效【虛空漲落】：【虛空斬】的持續時間 +3 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.9;matkPct:0.9;critDmg:0.9;lifesteal:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.9、魔法攻擊×0.9、暴擊傷害×0.9、吸血×0.6｜造成的所有傷害 +60%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 8% 最大生命；最大生命 -30%（乘算，代價）；傳奇特效【燃血】：【血飲術】每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.9;atkPct:0.9;matkPct:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.9、物理攻擊×0.9、魔法攻擊×0.9｜技能傷害 +40%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能；傳奇特效【分裂者】：飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.9;elemDmgLightning:1.05;critRate:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.9、雷屬性傷害提升×1.05、暴擊率×0.6｜對暈眩或緩速中的敵人傷害 +10%；每 3 秒：對隨機 3 名敵人造成 120% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒；傳奇特效【過載】：同一個敵人受到 5 次連鎖閃電的彈射後產生爆炸，對周圍 6 米內的敵人造成 200% 雷電傷害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critDmg:1.05;atkPct:0.9;bossDmg:1.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊傷害×1.05、物理攻擊×0.9、對BOSS傷害×1.05｜場上只有一名敵人時，傷害 +80%；對生命高於 70% 的敵人傷害 +40%；所有技能冷卻時間 -15%（乘算，突破冷卻縮減上限）；傳奇特效【貫日之刺】：四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:1.05;elemDmgFire:0.75;elemDmgIce:0.75;mPen:0.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.05、火屬性傷害提升×0.75、冰屬性傷害提升×0.75、魔法穿透×0.18｜每 3 秒：對隨機 5 名敵人造成 150% 隨機元素傷害；傳奇特效【爆裂】：【火球爆裂】會額外產生 3 個小火球。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resAll:0.9;luck:1.2;critRate:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：全屬性抗性×0.9、幸運值×1.2、暴擊率×0.9｜技能傷害 +25%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）；傳奇特效【腐化】：在泥沼術範圍內所有受到控場的敵人，受到的傷害 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.75;bossDmg:1.5;critDmg:0.75;pPen:0.24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.75、對BOSS傷害×1.5、暴擊傷害×0.75、物理穿透×0.24｜對生命高於 70% 的敵人傷害 +50%；造成的所有傷害 +25%；普通攻擊暴擊時有 20% 機率：對目標造成 250% 物理傷害；傳奇特效【斬殺】：疾風斬有 35% 機率可立即殺死生命值 20% 以下的非 BOSS 敵人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:1.5;globalDmgRed:0.9;resAll:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.5、全局減傷×0.9、全屬性抗性×0.9｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的無敵時間內，每殺死 1 個敵人則無敵時間 +0.5 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.9;aspd:0.9;aoeDmg:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.9、攻擊速度×0.9、範圍傷害×0.6｜普通攻擊同時對其他所有敵人造成 50% 的傷害；場上每多一名敵人，傷害 +6%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.9;critRate:0.9;atkPct:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.9、暴擊率×0.9、物理攻擊×0.9｜攻擊速度額外乘算 +15%（突破攻速上限）；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion:1.8;hit:1.2;hpPct:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×1.8、命中率×1.2、生命值×0.9｜造成的所有傷害 +25%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 150% 暗影傷害（內建冷卻 4 秒）；傳奇特效【斷空刃】：【暴風真空刃】每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.9;matkPct:0.9;elemDmgFire:0.45;elemDmgIce:0.45;elemDmgLightning:0.45;elemDmgPoison:0.45;elemDmgLight:0.45;elemDmgDark:0.45;elemDmgEarth:0.45;elemDmgWind:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.9、魔法攻擊×0.9、火屬性傷害提升×0.45、冰屬性傷害提升×0.45、雷屬性傷害提升×0.45、毒屬性傷害提升×0.45、聖屬性傷害提升×0.45、暗屬性傷害提升×0.45、地屬性傷害提升×0.45、風屬性傷害提升×0.45｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:1.05;critDmg:1.05;bossDmg:1.05;aoeDmg:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×1.05、暴擊傷害×1.05、對BOSS傷害×1.05、範圍傷害×0.6｜造成的所有傷害 +18%；普通攻擊同時對其他所有敵人造成 15% 的傷害；普通攻擊暴擊時有 10% 機率：對所有敵人造成 250% 物理傷害；傳奇特效【雷殞落】：【雷殞天落】降下的雷球數量 +1 顆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:1.5;elemDmgLightning:0.75;elemDmgWind:0.75;cdr:1.05;mPen:0.18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.5、雷屬性傷害提升×0.75、風屬性傷害提升×0.75、冷卻縮減×1.05、魔法穿透×0.18｜所有技能冷卻時間 -25%（乘算，突破冷卻縮減上限）；技能傷害 +40%；施放技能時有 20% 機率：免費再施放一次剛施放的技能；傳奇特效【雷之再生】：【迅雷重生】的機率提高至 100%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.9;bossDmg:1.5;elemDmgLight:0.9;critRate:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.9、對BOSS傷害×1.5、聖屬性傷害提升×0.9、暴擊率×0.6｜天罰 20%；對生命高於 70% 的敵人傷害 +40%；普通攻擊暴擊時有 15% 機率：對目標造成 350% 聖光傷害；傳奇特效【狩獵者】：你的火狩數量減半（無條件進位，至少 1 團），但造成的傷害額外 +150%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:1.35;elemDmgIce:1.5;cdr:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.35、冰屬性傷害提升×1.5、冷卻縮減×0.9｜對暈眩或緩速中的敵人傷害 +45%；普通攻擊命中時有 15% 機率：目標暈眩 1.5 秒；傳奇特效【凜冬寒霜】：暴風雪持續時間內會不斷對範圍內的敵人施加寒霜狀態，且寒霜狀態傷害 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:1.05;elemDmgIce:0.9;critDmg:0.9;bossDmg:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×1.05、冰屬性傷害提升×0.9、暴擊傷害×0.9、對BOSS傷害×0.9｜對生命高於 70% 的敵人傷害 +40%；對暈眩或緩速中的敵人傷害 +20%；普通攻擊暴擊時有 25% 機率：對目標造成 200% 冰霜傷害；傳奇特效【深度凍結】：寒冰箭擊中暈眩或凍結的敵人造成的傷害 +50%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpRegen:1.5;hpRegen:1.5;matkPct:0.9;cdr:0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×1.5、生命恢復/秒×1.5、魔法攻擊×0.9、冷卻縮減×0.9｜擊殺敵人時回復 4% 最大法力；技能法力消耗 -25%；每 6 秒：回復 6% 最大生命，回復 10% 最大法力；傳奇特效【水龍勢】：水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3845,10 +3865,10 @@
         <v>21</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>768</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3856,10 +3876,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>21</v>
@@ -3901,10 +3921,10 @@
         <v>21</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>769</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3912,10 +3932,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>773</v>
+        <v>643</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>774</v>
+        <v>644</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -3931,10 +3951,10 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>775</v>
+        <v>645</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>776</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3942,10 +3962,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>777</v>
+        <v>647</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>778</v>
+        <v>648</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -3964,7 +3984,7 @@
         <v>23</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>779</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3972,10 +3992,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>780</v>
+        <v>650</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>781</v>
+        <v>651</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -3991,10 +4011,10 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>782</v>
+        <v>652</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>783</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -4002,10 +4022,10 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>131</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>21</v>
@@ -4047,10 +4067,10 @@
         <v>21</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -4058,10 +4078,10 @@
         <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
@@ -4103,10 +4123,10 @@
         <v>21</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -4114,10 +4134,10 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
@@ -4162,7 +4182,7 @@
         <v>23</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -4170,10 +4190,10 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
@@ -4215,10 +4235,10 @@
         <v>21</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -4226,10 +4246,10 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
@@ -4271,10 +4291,10 @@
         <v>21</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>149</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -4282,10 +4302,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>21</v>
@@ -4327,10 +4347,10 @@
         <v>21</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>152</v>
+        <v>106</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -4338,10 +4358,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>21</v>
@@ -4383,21 +4403,21 @@
         <v>21</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>21</v>
@@ -4439,10 +4459,10 @@
         <v>21</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>161</v>
+        <v>115</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -4450,25 +4470,25 @@
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>21</v>
@@ -4498,7 +4518,7 @@
         <v>21</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>786</v>
+        <v>656</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -4506,25 +4526,25 @@
         <v>26</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>167</v>
+        <v>121</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -4554,7 +4574,7 @@
         <v>21</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>787</v>
+        <v>657</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4562,25 +4582,25 @@
         <v>26</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>174</v>
+        <v>128</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>232</v>
+        <v>186</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -4610,7 +4630,7 @@
         <v>21</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>788</v>
+        <v>658</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4618,25 +4638,25 @@
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>789</v>
+        <v>659</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>21</v>
@@ -4666,7 +4686,7 @@
         <v>21</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>790</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -4674,25 +4694,25 @@
         <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>181</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>791</v>
+        <v>661</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>792</v>
+        <v>662</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>21</v>
@@ -4722,7 +4742,7 @@
         <v>21</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>793</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4730,25 +4750,25 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>186</v>
+        <v>140</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>794</v>
+        <v>664</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>188</v>
+        <v>142</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>795</v>
+        <v>665</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>21</v>
@@ -4778,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>796</v>
+        <v>666</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4786,25 +4806,25 @@
         <v>26</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>190</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>192</v>
+        <v>146</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>797</v>
+        <v>667</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>798</v>
+        <v>668</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
@@ -4834,7 +4854,7 @@
         <v>21</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>799</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4842,25 +4862,25 @@
         <v>26</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>800</v>
+        <v>670</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>800</v>
+        <v>670</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>21</v>
@@ -4890,7 +4910,7 @@
         <v>21</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>801</v>
+        <v>671</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4898,25 +4918,25 @@
         <v>26</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>201</v>
+        <v>155</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>797</v>
+        <v>667</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>798</v>
+        <v>668</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
@@ -4946,7 +4966,7 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>802</v>
+        <v>672</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4954,25 +4974,25 @@
         <v>26</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>803</v>
+        <v>673</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>803</v>
+        <v>673</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>21</v>
@@ -5002,7 +5022,7 @@
         <v>21</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>804</v>
+        <v>674</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -5010,25 +5030,25 @@
         <v>26</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>211</v>
+        <v>165</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>805</v>
+        <v>675</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>806</v>
+        <v>676</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>21</v>
@@ -5058,7 +5078,7 @@
         <v>21</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>807</v>
+        <v>677</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -5066,25 +5086,25 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>808</v>
+        <v>678</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>809</v>
+        <v>679</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>21</v>
@@ -5114,7 +5134,7 @@
         <v>21</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>810</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -5122,25 +5142,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>811</v>
+        <v>681</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>812</v>
+        <v>682</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>21</v>
@@ -5170,7 +5190,7 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>813</v>
+        <v>683</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -5178,25 +5198,25 @@
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>814</v>
+        <v>684</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>815</v>
+        <v>685</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>21</v>
@@ -5226,7 +5246,7 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>816</v>
+        <v>686</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5234,25 +5254,25 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>228</v>
+        <v>182</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>791</v>
+        <v>661</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>233</v>
+        <v>187</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>817</v>
+        <v>687</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>21</v>
@@ -5282,7 +5302,7 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>818</v>
+        <v>688</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5290,25 +5310,25 @@
         <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>819</v>
+        <v>689</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>820</v>
+        <v>690</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>21</v>
@@ -5338,7 +5358,7 @@
         <v>21</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>821</v>
+        <v>691</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5346,25 +5366,25 @@
         <v>26</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>239</v>
+        <v>193</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>242</v>
+        <v>196</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>800</v>
+        <v>670</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>822</v>
+        <v>692</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>21</v>
@@ -5394,7 +5414,7 @@
         <v>21</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>823</v>
+        <v>693</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5402,25 +5422,25 @@
         <v>26</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>247</v>
+        <v>201</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>248</v>
+        <v>202</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>805</v>
+        <v>675</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>805</v>
+        <v>675</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
@@ -5450,7 +5470,7 @@
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>824</v>
+        <v>694</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -5458,25 +5478,25 @@
         <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>252</v>
+        <v>206</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>179</v>
+        <v>133</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>812</v>
+        <v>682</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>825</v>
+        <v>695</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>21</v>
@@ -5506,7 +5526,7 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>826</v>
+        <v>696</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -5514,25 +5534,25 @@
         <v>26</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>254</v>
+        <v>208</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>256</v>
+        <v>210</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>825</v>
+        <v>695</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>827</v>
+        <v>697</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>21</v>
@@ -5562,7 +5582,7 @@
         <v>21</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>828</v>
+        <v>698</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -5570,25 +5590,25 @@
         <v>26</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>829</v>
+        <v>699</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>21</v>
@@ -5618,7 +5638,7 @@
         <v>21</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>831</v>
+        <v>701</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -5626,25 +5646,25 @@
         <v>26</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>832</v>
+        <v>702</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>833</v>
+        <v>703</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
@@ -5674,7 +5694,7 @@
         <v>21</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>834</v>
+        <v>704</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -5682,25 +5702,25 @@
         <v>26</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>268</v>
+        <v>222</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>835</v>
+        <v>705</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
@@ -5730,7 +5750,7 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>836</v>
+        <v>706</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -5738,25 +5758,25 @@
         <v>26</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>271</v>
+        <v>225</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>272</v>
+        <v>226</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>837</v>
+        <v>707</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>838</v>
+        <v>708</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>21</v>
@@ -5786,7 +5806,7 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>839</v>
+        <v>709</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -5794,25 +5814,25 @@
         <v>26</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>275</v>
+        <v>229</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>840</v>
+        <v>710</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>840</v>
+        <v>710</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>21</v>
@@ -5842,7 +5862,7 @@
         <v>21</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>841</v>
+        <v>711</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -5850,25 +5870,25 @@
         <v>26</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>842</v>
+        <v>712</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>830</v>
+        <v>700</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>21</v>
@@ -5898,7 +5918,7 @@
         <v>21</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>843</v>
+        <v>713</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -5906,25 +5926,25 @@
         <v>26</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>285</v>
+        <v>239</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>286</v>
+        <v>240</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>844</v>
+        <v>714</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>287</v>
+        <v>241</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>844</v>
+        <v>714</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
@@ -5954,7 +5974,7 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>845</v>
+        <v>715</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -5962,25 +5982,25 @@
         <v>26</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>289</v>
+        <v>243</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>846</v>
+        <v>716</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>166</v>
+        <v>120</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>846</v>
+        <v>716</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>21</v>
@@ -6010,7 +6030,7 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>847</v>
+        <v>717</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -6018,25 +6038,25 @@
         <v>26</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>848</v>
+        <v>718</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>848</v>
+        <v>718</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>21</v>
@@ -6066,7 +6086,7 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>849</v>
+        <v>719</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -6074,25 +6094,25 @@
         <v>26</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>295</v>
+        <v>249</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>296</v>
+        <v>250</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>297</v>
+        <v>251</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>207</v>
+        <v>161</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>850</v>
+        <v>720</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>850</v>
+        <v>720</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>21</v>
@@ -6122,7 +6142,7 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>851</v>
+        <v>721</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -6130,25 +6150,25 @@
         <v>26</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>852</v>
+        <v>722</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>274</v>
+        <v>228</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>797</v>
+        <v>667</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>21</v>
@@ -6178,7 +6198,7 @@
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>853</v>
+        <v>723</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -6186,25 +6206,25 @@
         <v>26</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>301</v>
+        <v>255</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>302</v>
+        <v>256</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>212</v>
+        <v>166</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>854</v>
+        <v>724</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>850</v>
+        <v>720</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>21</v>
@@ -6234,33 +6254,33 @@
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>855</v>
+        <v>725</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>306</v>
+        <v>260</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>261</v>
+        <v>215</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>856</v>
+        <v>726</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>270</v>
+        <v>224</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>844</v>
+        <v>714</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>21</v>
@@ -6290,18 +6310,18 @@
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>857</v>
+        <v>727</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>309</v>
+        <v>263</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>23</v>
@@ -6319,13 +6339,13 @@
         <v>21</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>312</v>
+        <v>730</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>21</v>
@@ -6340,24 +6360,24 @@
         <v>21</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>84</v>
+        <v>731</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>314</v>
+        <v>267</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>315</v>
+        <v>268</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>23</v>
@@ -6375,13 +6395,13 @@
         <v>21</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>318</v>
+        <v>732</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>21</v>
@@ -6396,24 +6416,24 @@
         <v>21</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>85</v>
+        <v>733</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>23</v>
@@ -6431,13 +6451,13 @@
         <v>21</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>322</v>
+        <v>274</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>324</v>
+        <v>734</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>21</v>
@@ -6449,27 +6469,27 @@
         <v>21</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>86</v>
+        <v>735</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>23</v>
@@ -6487,13 +6507,13 @@
         <v>21</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>331</v>
+        <v>736</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>21</v>
@@ -6508,24 +6528,24 @@
         <v>21</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>87</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>23</v>
@@ -6543,16 +6563,16 @@
         <v>21</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>337</v>
+        <v>738</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>21</v>
@@ -6564,24 +6584,24 @@
         <v>21</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>88</v>
+        <v>739</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>23</v>
@@ -6599,13 +6619,13 @@
         <v>21</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>344</v>
+        <v>740</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>21</v>
@@ -6617,27 +6637,27 @@
         <v>21</v>
       </c>
       <c r="O53" s="3" t="s">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>346</v>
+        <v>294</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>89</v>
+        <v>741</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>348</v>
+        <v>296</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>23</v>
@@ -6655,13 +6675,13 @@
         <v>21</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>351</v>
+        <v>742</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>21</v>
@@ -6673,27 +6693,27 @@
         <v>21</v>
       </c>
       <c r="O54" s="3" t="s">
-        <v>352</v>
+        <v>299</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>90</v>
+        <v>743</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>354</v>
+        <v>301</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>355</v>
+        <v>302</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>23</v>
@@ -6711,13 +6731,13 @@
         <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>356</v>
+        <v>303</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>357</v>
+        <v>304</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>358</v>
+        <v>744</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>21</v>
@@ -6726,30 +6746,30 @@
         <v>21</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>359</v>
+        <v>305</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>360</v>
+        <v>306</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>91</v>
+        <v>745</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>361</v>
+        <v>307</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>362</v>
+        <v>308</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>23</v>
@@ -6767,13 +6787,13 @@
         <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>365</v>
+        <v>746</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>21</v>
@@ -6782,30 +6802,30 @@
         <v>21</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>366</v>
+        <v>311</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>367</v>
+        <v>312</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>92</v>
+        <v>747</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>368</v>
+        <v>313</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>369</v>
+        <v>314</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>23</v>
@@ -6823,13 +6843,13 @@
         <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>370</v>
+        <v>315</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>371</v>
+        <v>316</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>372</v>
+        <v>748</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>21</v>
@@ -6844,24 +6864,24 @@
         <v>21</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>373</v>
+        <v>317</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>93</v>
+        <v>749</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>374</v>
+        <v>318</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>375</v>
+        <v>319</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>23</v>
@@ -6879,13 +6899,13 @@
         <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>376</v>
+        <v>320</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>378</v>
+        <v>750</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>21</v>
@@ -6894,30 +6914,30 @@
         <v>21</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>379</v>
+        <v>322</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>94</v>
+        <v>751</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>381</v>
+        <v>324</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>382</v>
+        <v>325</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>23</v>
@@ -6935,13 +6955,13 @@
         <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>383</v>
+        <v>326</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>385</v>
+        <v>752</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>21</v>
@@ -6950,30 +6970,30 @@
         <v>21</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>386</v>
+        <v>328</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>387</v>
+        <v>329</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>95</v>
+        <v>753</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>388</v>
+        <v>330</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>389</v>
+        <v>331</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>23</v>
@@ -6991,13 +7011,13 @@
         <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>390</v>
+        <v>332</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>392</v>
+        <v>754</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>21</v>
@@ -7012,27 +7032,27 @@
         <v>21</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>96</v>
+        <v>755</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>394</v>
+        <v>335</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>21</v>
@@ -7047,13 +7067,13 @@
         <v>21</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>396</v>
+        <v>337</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>397</v>
+        <v>756</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>21</v>
@@ -7065,27 +7085,27 @@
         <v>21</v>
       </c>
       <c r="O61" s="3" t="s">
-        <v>398</v>
+        <v>338</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>399</v>
+        <v>339</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>97</v>
+        <v>757</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>401</v>
+        <v>341</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>24</v>
@@ -7103,45 +7123,45 @@
         <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>402</v>
+        <v>342</v>
       </c>
       <c r="J62" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N62" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>405</v>
+        <v>344</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>98</v>
+        <v>759</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>406</v>
+        <v>345</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>407</v>
+        <v>346</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>24</v>
@@ -7159,13 +7179,13 @@
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>408</v>
+        <v>347</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>409</v>
+        <v>760</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>21</v>
@@ -7177,27 +7197,27 @@
         <v>21</v>
       </c>
       <c r="O63" s="3" t="s">
-        <v>410</v>
+        <v>348</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>411</v>
+        <v>349</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>99</v>
+        <v>761</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>412</v>
+        <v>350</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>413</v>
+        <v>351</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>24</v>
@@ -7215,13 +7235,13 @@
         <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>414</v>
+        <v>352</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>415</v>
+        <v>762</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>21</v>
@@ -7230,30 +7250,30 @@
         <v>21</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>416</v>
+        <v>353</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>417</v>
+        <v>354</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>418</v>
+        <v>355</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>100</v>
+        <v>763</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>419</v>
+        <v>356</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>420</v>
+        <v>357</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>24</v>
@@ -7271,13 +7291,13 @@
         <v>21</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>421</v>
+        <v>358</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>422</v>
+        <v>764</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>21</v>
@@ -7286,30 +7306,30 @@
         <v>21</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>423</v>
+        <v>359</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>424</v>
+        <v>360</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>101</v>
+        <v>765</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>425</v>
+        <v>361</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>426</v>
+        <v>362</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>24</v>
@@ -7327,13 +7347,13 @@
         <v>21</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>427</v>
+        <v>363</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>428</v>
+        <v>766</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>21</v>
@@ -7342,30 +7362,30 @@
         <v>21</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>429</v>
+        <v>364</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>430</v>
+        <v>365</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>102</v>
+        <v>767</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>431</v>
+        <v>366</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>432</v>
+        <v>367</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>24</v>
@@ -7383,13 +7403,13 @@
         <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>433</v>
+        <v>368</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>434</v>
+        <v>369</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>435</v>
+        <v>768</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>21</v>
@@ -7401,27 +7421,27 @@
         <v>21</v>
       </c>
       <c r="O67" s="3" t="s">
-        <v>436</v>
+        <v>370</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>437</v>
+        <v>371</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>103</v>
+        <v>769</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>438</v>
+        <v>372</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>439</v>
+        <v>373</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>24</v>
@@ -7439,13 +7459,13 @@
         <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>440</v>
+        <v>374</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>357</v>
+        <v>304</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>441</v>
+        <v>770</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>21</v>
@@ -7457,27 +7477,27 @@
         <v>21</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>442</v>
+        <v>375</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>443</v>
+        <v>376</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>104</v>
+        <v>771</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>444</v>
+        <v>377</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>445</v>
+        <v>378</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>24</v>
@@ -7495,13 +7515,13 @@
         <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>446</v>
+        <v>379</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>447</v>
+        <v>772</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>21</v>
@@ -7513,27 +7533,27 @@
         <v>21</v>
       </c>
       <c r="O69" s="3" t="s">
-        <v>448</v>
+        <v>380</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>449</v>
+        <v>381</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>105</v>
+        <v>773</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>450</v>
+        <v>382</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>251</v>
+        <v>205</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>24</v>
@@ -7551,13 +7571,13 @@
         <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>451</v>
+        <v>383</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>452</v>
+        <v>384</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>453</v>
+        <v>774</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>21</v>
@@ -7569,27 +7589,27 @@
         <v>21</v>
       </c>
       <c r="O70" s="3" t="s">
-        <v>454</v>
+        <v>385</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>455</v>
+        <v>386</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>106</v>
+        <v>775</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>456</v>
+        <v>387</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>457</v>
+        <v>388</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>24</v>
@@ -7607,16 +7627,16 @@
         <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>458</v>
+        <v>389</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>459</v>
+        <v>390</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>460</v>
+        <v>776</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>461</v>
+        <v>391</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>21</v>
@@ -7625,27 +7645,27 @@
         <v>21</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>462</v>
+        <v>392</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>463</v>
+        <v>393</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>107</v>
+        <v>777</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>464</v>
+        <v>394</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>465</v>
+        <v>395</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>24</v>
@@ -7663,13 +7683,13 @@
         <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>466</v>
+        <v>396</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>467</v>
+        <v>778</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>21</v>
@@ -7678,30 +7698,30 @@
         <v>21</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>468</v>
+        <v>397</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>469</v>
+        <v>398</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>108</v>
+        <v>779</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>470</v>
+        <v>399</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>471</v>
+        <v>400</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>24</v>
@@ -7719,13 +7739,13 @@
         <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>472</v>
+        <v>401</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>473</v>
+        <v>402</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>474</v>
+        <v>780</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>21</v>
@@ -7737,27 +7757,27 @@
         <v>21</v>
       </c>
       <c r="O73" s="3" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>109</v>
+        <v>781</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>477</v>
+        <v>405</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>478</v>
+        <v>406</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>24</v>
@@ -7775,13 +7795,13 @@
         <v>21</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>479</v>
+        <v>407</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>480</v>
+        <v>408</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>481</v>
+        <v>782</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>21</v>
@@ -7793,30 +7813,30 @@
         <v>21</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>482</v>
+        <v>409</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>483</v>
+        <v>410</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>110</v>
+        <v>783</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>484</v>
+        <v>411</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>485</v>
+        <v>412</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>21</v>
@@ -7831,13 +7851,13 @@
         <v>21</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>487</v>
+        <v>784</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>21</v>
@@ -7852,24 +7872,24 @@
         <v>21</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>488</v>
+        <v>414</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>111</v>
+        <v>785</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>489</v>
+        <v>415</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>490</v>
+        <v>416</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>25</v>
@@ -7887,13 +7907,13 @@
         <v>21</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>491</v>
+        <v>417</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>492</v>
+        <v>786</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>21</v>
@@ -7902,30 +7922,30 @@
         <v>21</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>493</v>
+        <v>418</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>494</v>
+        <v>419</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>112</v>
+        <v>787</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>495</v>
+        <v>420</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>496</v>
+        <v>421</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>25</v>
@@ -7943,13 +7963,13 @@
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>497</v>
+        <v>422</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>498</v>
+        <v>788</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>21</v>
@@ -7958,30 +7978,30 @@
         <v>21</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>499</v>
+        <v>423</v>
       </c>
       <c r="O77" s="3" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>501</v>
+        <v>425</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>113</v>
+        <v>789</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>502</v>
+        <v>426</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>25</v>
@@ -7999,13 +8019,13 @@
         <v>21</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>504</v>
+        <v>428</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>505</v>
+        <v>790</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>21</v>
@@ -8017,27 +8037,27 @@
         <v>21</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>506</v>
+        <v>429</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>507</v>
+        <v>430</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>114</v>
+        <v>791</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>508</v>
+        <v>431</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>509</v>
+        <v>432</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>25</v>
@@ -8055,13 +8075,13 @@
         <v>21</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>510</v>
+        <v>433</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>480</v>
+        <v>408</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>511</v>
+        <v>792</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>21</v>
@@ -8070,30 +8090,30 @@
         <v>21</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>512</v>
+        <v>434</v>
       </c>
       <c r="O79" s="3" t="s">
-        <v>513</v>
+        <v>435</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>514</v>
+        <v>436</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>115</v>
+        <v>793</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>515</v>
+        <v>437</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>516</v>
+        <v>438</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>25</v>
@@ -8111,13 +8131,13 @@
         <v>21</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>517</v>
+        <v>439</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>518</v>
+        <v>794</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>21</v>
@@ -8129,27 +8149,27 @@
         <v>21</v>
       </c>
       <c r="O80" s="3" t="s">
-        <v>519</v>
+        <v>440</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>520</v>
+        <v>441</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>116</v>
+        <v>795</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>521</v>
+        <v>442</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>522</v>
+        <v>443</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>25</v>
@@ -8167,13 +8187,13 @@
         <v>21</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>523</v>
+        <v>444</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>524</v>
+        <v>796</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>21</v>
@@ -8182,30 +8202,30 @@
         <v>21</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>525</v>
+        <v>445</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>526</v>
+        <v>446</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>117</v>
+        <v>797</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>527</v>
+        <v>447</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>25</v>
@@ -8223,45 +8243,45 @@
         <v>21</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>529</v>
+        <v>449</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>530</v>
+        <v>450</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>531</v>
+        <v>798</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>532</v>
+        <v>451</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>533</v>
+        <v>452</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>534</v>
+        <v>453</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>118</v>
+        <v>799</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>535</v>
+        <v>454</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>536</v>
+        <v>455</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>25</v>
@@ -8279,13 +8299,13 @@
         <v>21</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>537</v>
+        <v>456</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>538</v>
+        <v>457</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>539</v>
+        <v>800</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>21</v>
@@ -8294,30 +8314,30 @@
         <v>21</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>540</v>
+        <v>458</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>541</v>
+        <v>459</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>119</v>
+        <v>801</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>542</v>
+        <v>460</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>543</v>
+        <v>461</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>25</v>
@@ -8335,16 +8355,16 @@
         <v>21</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>544</v>
+        <v>462</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>545</v>
+        <v>463</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>546</v>
+        <v>802</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>547</v>
+        <v>464</v>
       </c>
       <c r="M84" s="3" t="s">
         <v>21</v>
@@ -8353,27 +8373,27 @@
         <v>21</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>548</v>
+        <v>465</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>549</v>
+        <v>466</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>120</v>
+        <v>803</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>550</v>
+        <v>467</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>551</v>
+        <v>468</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>25</v>
@@ -8391,13 +8411,13 @@
         <v>21</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>552</v>
+        <v>469</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>553</v>
+        <v>804</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>21</v>
@@ -8406,30 +8426,30 @@
         <v>21</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>554</v>
+        <v>470</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>555</v>
+        <v>471</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>121</v>
+        <v>805</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>556</v>
+        <v>472</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>557</v>
+        <v>473</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>25</v>
@@ -8447,13 +8467,13 @@
         <v>21</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>558</v>
+        <v>474</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>559</v>
+        <v>806</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>21</v>
@@ -8462,30 +8482,30 @@
         <v>21</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>560</v>
+        <v>475</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>561</v>
+        <v>476</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>122</v>
+        <v>807</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>562</v>
+        <v>477</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>563</v>
+        <v>478</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>25</v>
@@ -8503,13 +8523,13 @@
         <v>21</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>564</v>
+        <v>479</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>565</v>
+        <v>480</v>
       </c>
       <c r="K87" s="3" t="s">
-        <v>566</v>
+        <v>808</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>21</v>
@@ -8521,27 +8541,27 @@
         <v>21</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>567</v>
+        <v>481</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>568</v>
+        <v>482</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>123</v>
+        <v>809</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>569</v>
+        <v>483</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>570</v>
+        <v>484</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>25</v>
@@ -8559,13 +8579,13 @@
         <v>21</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>571</v>
+        <v>485</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="K88" s="3" t="s">
-        <v>572</v>
+        <v>810</v>
       </c>
       <c r="L88" s="3" t="s">
         <v>21</v>
@@ -8574,33 +8594,33 @@
         <v>21</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>573</v>
+        <v>486</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>574</v>
+        <v>487</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>124</v>
+        <v>811</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>575</v>
+        <v>488</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>576</v>
+        <v>489</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>21</v>
@@ -8615,13 +8635,13 @@
         <v>21</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>577</v>
+        <v>490</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K89" s="3" t="s">
-        <v>578</v>
+        <v>812</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>21</v>
@@ -8630,30 +8650,30 @@
         <v>21</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>579</v>
+        <v>491</v>
       </c>
       <c r="O89" s="3" t="s">
-        <v>580</v>
+        <v>492</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>581</v>
+        <v>493</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>125</v>
+        <v>813</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>582</v>
+        <v>494</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>583</v>
+        <v>495</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>22</v>
@@ -8671,45 +8691,45 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>584</v>
+        <v>496</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>585</v>
+        <v>814</v>
       </c>
       <c r="L90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>586</v>
+        <v>497</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>587</v>
+        <v>498</v>
       </c>
       <c r="O90" s="3" t="s">
-        <v>588</v>
+        <v>499</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>589</v>
+        <v>500</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>590</v>
+        <v>815</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>591</v>
+        <v>501</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>592</v>
+        <v>502</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>22</v>
@@ -8727,45 +8747,45 @@
         <v>21</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>593</v>
+        <v>503</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="K91" s="3" t="s">
-        <v>594</v>
+        <v>816</v>
       </c>
       <c r="L91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>595</v>
+        <v>504</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>596</v>
+        <v>505</v>
       </c>
       <c r="O91" s="3" t="s">
-        <v>597</v>
+        <v>506</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>598</v>
+        <v>507</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>599</v>
+        <v>817</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>601</v>
+        <v>509</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>22</v>
@@ -8783,45 +8803,45 @@
         <v>21</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>602</v>
+        <v>510</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>603</v>
+        <v>818</v>
       </c>
       <c r="L92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>604</v>
+        <v>511</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>605</v>
+        <v>512</v>
       </c>
       <c r="O92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>606</v>
+        <v>513</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>607</v>
+        <v>819</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>608</v>
+        <v>514</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>293</v>
+        <v>247</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>22</v>
@@ -8839,45 +8859,45 @@
         <v>21</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>609</v>
+        <v>515</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>317</v>
+        <v>270</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>610</v>
+        <v>820</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>611</v>
+        <v>516</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>612</v>
+        <v>517</v>
       </c>
       <c r="O93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>613</v>
+        <v>518</v>
       </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>614</v>
+        <v>821</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>615</v>
+        <v>519</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>616</v>
+        <v>520</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>22</v>
@@ -8895,45 +8915,45 @@
         <v>21</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>617</v>
+        <v>521</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>618</v>
+        <v>822</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>619</v>
+        <v>522</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>620</v>
+        <v>523</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>621</v>
+        <v>524</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>622</v>
+        <v>525</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>623</v>
+        <v>823</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>624</v>
+        <v>526</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>625</v>
+        <v>527</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>22</v>
@@ -8951,45 +8971,45 @@
         <v>21</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>626</v>
+        <v>528</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>627</v>
+        <v>824</v>
       </c>
       <c r="L95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>628</v>
+        <v>529</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>629</v>
+        <v>530</v>
       </c>
       <c r="O95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>630</v>
+        <v>531</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>631</v>
+        <v>825</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>632</v>
+        <v>532</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>633</v>
+        <v>533</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>22</v>
@@ -9007,45 +9027,45 @@
         <v>21</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>634</v>
+        <v>534</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>635</v>
+        <v>826</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>636</v>
+        <v>535</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>637</v>
+        <v>536</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>638</v>
+        <v>537</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>639</v>
+        <v>538</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>640</v>
+        <v>827</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>641</v>
+        <v>539</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>642</v>
+        <v>540</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>22</v>
@@ -9063,45 +9083,45 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>643</v>
+        <v>541</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>323</v>
+        <v>275</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>644</v>
+        <v>828</v>
       </c>
       <c r="L97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>645</v>
+        <v>542</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>646</v>
+        <v>543</v>
       </c>
       <c r="O97" s="3" t="s">
-        <v>647</v>
+        <v>544</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>648</v>
+        <v>545</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>649</v>
+        <v>829</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>650</v>
+        <v>546</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>651</v>
+        <v>547</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -9119,45 +9139,45 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>652</v>
+        <v>548</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="K98" s="3" t="s">
-        <v>653</v>
+        <v>830</v>
       </c>
       <c r="L98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>654</v>
+        <v>549</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>655</v>
+        <v>550</v>
       </c>
       <c r="O98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>656</v>
+        <v>551</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>657</v>
+        <v>831</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>658</v>
+        <v>552</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>659</v>
+        <v>553</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -9175,45 +9195,45 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>660</v>
+        <v>554</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>661</v>
+        <v>555</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>662</v>
+        <v>832</v>
       </c>
       <c r="L99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>663</v>
+        <v>556</v>
       </c>
       <c r="N99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="O99" s="3" t="s">
-        <v>664</v>
+        <v>557</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>665</v>
+        <v>558</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>666</v>
+        <v>833</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>667</v>
+        <v>559</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>668</v>
+        <v>560</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>22</v>
@@ -9231,45 +9251,45 @@
         <v>21</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>669</v>
+        <v>561</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>384</v>
+        <v>327</v>
       </c>
       <c r="K100" s="3" t="s">
-        <v>670</v>
+        <v>834</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>671</v>
+        <v>562</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>672</v>
+        <v>563</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>673</v>
+        <v>564</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>674</v>
+        <v>565</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>675</v>
+        <v>835</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>676</v>
+        <v>566</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>677</v>
+        <v>567</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>22</v>
@@ -9287,45 +9307,45 @@
         <v>21</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>678</v>
+        <v>568</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="K101" s="3" t="s">
-        <v>679</v>
+        <v>836</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>680</v>
+        <v>569</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>681</v>
+        <v>570</v>
       </c>
       <c r="O101" s="3" t="s">
-        <v>682</v>
+        <v>571</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>683</v>
+        <v>572</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>684</v>
+        <v>837</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>685</v>
+        <v>573</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>686</v>
+        <v>574</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>22</v>
@@ -9343,39 +9363,39 @@
         <v>21</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>687</v>
+        <v>575</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>688</v>
+        <v>576</v>
       </c>
       <c r="K102" s="3" t="s">
-        <v>689</v>
+        <v>838</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>690</v>
+        <v>577</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>691</v>
+        <v>578</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>692</v>
+        <v>579</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>693</v>
+        <v>580</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>694</v>
+        <v>839</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>33</v>
@@ -9393,358 +9413,358 @@
         <v>36</v>
       </c>
       <c r="K103" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="M103" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="N103" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="M103" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="N103" s="5" t="s">
+      <c r="P103" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P103" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="R103" s="5" t="s">
-        <v>697</v>
+        <v>841</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B104" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>41</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>698</v>
+        <v>583</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>42</v>
+        <v>842</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>699</v>
+        <v>584</v>
       </c>
       <c r="N104" s="5" t="s">
         <v>31</v>
       </c>
       <c r="P104" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R104" s="5" t="s">
-        <v>700</v>
+        <v>843</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>701</v>
+        <v>585</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K105" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="M105" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="N105" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O105" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P105" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="M105" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="N105" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="O105" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="P105" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="R105" s="5" t="s">
-        <v>703</v>
+        <v>845</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I106" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K106" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="N106" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P106" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J106" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K106" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M106" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="N106" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="P106" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="R106" s="5" t="s">
-        <v>705</v>
+        <v>847</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>706</v>
+        <v>588</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>707</v>
+        <v>589</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>708</v>
+        <v>590</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>709</v>
+        <v>848</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>710</v>
+        <v>591</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>711</v>
+        <v>592</v>
       </c>
       <c r="O107" s="5" t="s">
-        <v>712</v>
+        <v>593</v>
       </c>
       <c r="P107" s="5" t="s">
-        <v>713</v>
+        <v>594</v>
       </c>
       <c r="R107" s="5" t="s">
-        <v>714</v>
+        <v>849</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>715</v>
+        <v>595</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>716</v>
+        <v>596</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>717</v>
+        <v>597</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>718</v>
+        <v>850</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>719</v>
+        <v>598</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>720</v>
+        <v>599</v>
       </c>
       <c r="O108" s="5" t="s">
-        <v>721</v>
+        <v>600</v>
       </c>
       <c r="P108" s="5" t="s">
-        <v>722</v>
+        <v>601</v>
       </c>
       <c r="R108" s="5" t="s">
-        <v>723</v>
+        <v>851</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>724</v>
+        <v>602</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>725</v>
+        <v>603</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>726</v>
+        <v>604</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>727</v>
+        <v>852</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>728</v>
+        <v>605</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>729</v>
+        <v>606</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>730</v>
+        <v>607</v>
       </c>
       <c r="O109" s="5" t="s">
-        <v>731</v>
+        <v>608</v>
       </c>
       <c r="P109" s="5" t="s">
-        <v>732</v>
+        <v>609</v>
       </c>
       <c r="R109" s="5" t="s">
-        <v>733</v>
+        <v>853</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>734</v>
+        <v>610</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>735</v>
+        <v>611</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>736</v>
+        <v>612</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>737</v>
+        <v>854</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>738</v>
+        <v>613</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>739</v>
+        <v>614</v>
       </c>
       <c r="O110" s="5" t="s">
-        <v>740</v>
+        <v>615</v>
       </c>
       <c r="P110" s="5" t="s">
-        <v>741</v>
+        <v>616</v>
       </c>
       <c r="R110" s="5" t="s">
-        <v>742</v>
+        <v>855</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>743</v>
+        <v>617</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>744</v>
+        <v>618</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>745</v>
+        <v>619</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>746</v>
+        <v>856</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>747</v>
+        <v>620</v>
       </c>
       <c r="N111" s="5" t="s">
-        <v>748</v>
+        <v>621</v>
       </c>
       <c r="O111" s="5" t="s">
-        <v>749</v>
+        <v>622</v>
       </c>
       <c r="P111" s="5" t="s">
-        <v>750</v>
+        <v>623</v>
       </c>
       <c r="R111" s="5" t="s">
-        <v>751</v>
+        <v>857</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>695</v>
+        <v>581</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>752</v>
+        <v>624</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>753</v>
+        <v>625</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>754</v>
+        <v>626</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>29</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>755</v>
+        <v>858</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>756</v>
+        <v>627</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>757</v>
+        <v>628</v>
       </c>
       <c r="O112" s="5" t="s">
-        <v>758</v>
+        <v>629</v>
       </c>
       <c r="P112" s="5" t="s">
-        <v>759</v>
+        <v>630</v>
       </c>
       <c r="R112" s="5" t="s">
-        <v>760</v>
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -9764,17 +9784,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -9784,22 +9804,22 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>761</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -9809,47 +9829,47 @@
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>770</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>771</v>
+        <v>641</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>772</v>
+        <v>642</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>784</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>762</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
@@ -9859,27 +9879,27 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>858</v>
+        <v>728</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>763</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -9889,102 +9909,102 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>764</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>765</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>766</v>
+        <v>636</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>859</v>
+        <v>729</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>767</v>
+        <v>637</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B74B51A-927D-40C9-B8B7-27213DCA35EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DB0643-10DE-4250-9D42-5082F1FEF134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="893">
   <si>
     <t>類型</t>
   </si>
@@ -282,9 +282,6 @@
     <t>　　dot {pct, sec, name(poison/burn/bleed/corrode), to?}、cdr {sec}、refresh {n?}、recast、castRandom、invuln {sec}、execute {hpBelow}、cleanse。elem 可填 fire/ice/lightning/poison/light/dark/earth/wind/random。</t>
   </si>
   <si>
-    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。效果說明文字由資料自動產生，不需要另外寫。</t>
-  </si>
-  <si>
     <t>　　備註是自動產生的參考，不進遊戲、不影響套用；你改了能力之後，備註不會自動更新（請 AI 重新產生），以左邊各欄實際內容為準。</t>
   </si>
   <si>
@@ -2808,10 +2805,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率＝同裝備等級、稀有度「詞條基準值」（詞條範圍的中間值，等於符文倍率 1 的 1.25 倍）的幾倍，不乘雙手倍率；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>atkFlat:1;matkFlat:1;hit:0.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3329,6 +3322,146 @@
   </si>
   <si>
     <t>屬性：法力恢復/秒×1.5、生命恢復/秒×1.5、魔法攻擊×0.9、冷卻縮減×0.9｜擊殺敵人時回復 4% 最大法力；技能法力消耗 -25%；每 6 秒：回復 6% 最大生命，回復 10% 最大法力；傳奇特效【水龍勢】：水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗裡最先亮起的一點微光，指引落點，也教人閃身而過。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>火熄之後仍未冷去的餘燼，餘溫裡藏著再燃的力量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>霜在石上留下的細痕，一碰便是刺骨的寒意。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風的聲息稍縱即逝，發出嘆息之悲鳴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>埋在山腹最深處的石心，千年不碎，也能穿透一切。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蛇牙上的一滴毒，無聲，卻比刀更準。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遠方的悶雷滾過天際，下一瞬便落在腳邊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影子貼著傷口低語，它拿走的，總會以別的方式還回來。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清晨第一道穿雲的光，照亮之處，黑暗無處容身。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以血立下的誓言，不收回，也不能背棄。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>千錘百鍊的鋼，折不彎，亦藏著致命的鋒芒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山間不竭的靈泉，一掬便潤澤乾涸的心神。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快到只剩殘影，旁人看見時，一切已成定局。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立在洪流中央的巨岩，任它如何沖刷，不退半步。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>長夜將盡時的一線曙光，刺破最厚的迷障。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜幕降下，所有未說出口的恐懼都在其中蠕動。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正午的烈陽毫不留情，所到之處皆成焦土。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寒月高懸，時間在它的清輝下緩緩凝滯。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春雷一響，蟄伏的萬物同時驚醒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>山間升起的嵐氣，輕柔地纏上來，又在轉身間化為利刃。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>穹頂之上的目光，俯視一切傲慢的巨影。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地沉默地承載萬物，也沉默地回報。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地底湧出的熔岩，緩慢，卻吞沒前路上的一切。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萬年玄冰中凝成的魂魄，連時間都被它凍結。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天怒所化的雷霆，一道便足以裁決。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注視虛空太久，虛空也在注視著你。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜空裡每一顆星都是一次機緣，抬頭，便能撞見自己的那一顆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>命運之線纏繞所有人，唯有敢於撥動它的人，才看得見盡頭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生滅不息，終點即是起點，傷口在輪迴中癒合。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在時間之外靜止的片刻，沒有終結，也沒有退讓。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>萬物未成形之前的原初混沌，秩序在其中碎裂重組。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一縷光與第一聲息的源頭，一切由此而起。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有故事的最後一頁，闔上之後，再無下文。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率＝「基礎值」（同符文列：詞條可能範圍的下限）的幾倍，與符文不同的是不乘雙手倍率（雙手武器的優勢是 5 孔）；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。符文列＝符文庫詳情裡形容這顆符文的文字；符文真言列＝圖鑑裡那組真言的一句話。效果說明文字由資料自動產生，不需要另外寫。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3865,10 +3998,10 @@
         <v>21</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -3876,11 +4009,11 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
@@ -3921,10 +4054,10 @@
         <v>21</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -3932,10 +4065,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>644</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -3951,10 +4084,10 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -3962,10 +4095,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>648</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -3984,7 +4117,7 @@
         <v>23</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3992,10 +4125,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>651</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -4011,10 +4144,10 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="R6" s="3" t="s">
         <v>652</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -4022,55 +4155,55 @@
         <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" s="3" t="s">
+      <c r="R7" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -4078,55 +4211,55 @@
         <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -4134,10 +4267,10 @@
         <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
@@ -4182,7 +4315,7 @@
         <v>23</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -4190,55 +4323,55 @@
         <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -4246,55 +4379,55 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q11" s="3" t="s">
+      <c r="R11" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -4302,55 +4435,55 @@
         <v>18</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q12" s="3" t="s">
+      <c r="R12" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -4358,111 +4491,111 @@
         <v>18</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="3" t="s">
+      <c r="R13" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -4470,55 +4603,55 @@
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="H15" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -4526,25 +4659,25 @@
         <v>26</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="H16" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -4568,13 +4701,13 @@
         <v>21</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>21</v>
+        <v>859</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -4582,25 +4715,25 @@
         <v>26</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="H17" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -4624,13 +4757,13 @@
         <v>21</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>21</v>
+        <v>860</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4638,55 +4771,55 @@
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -4694,55 +4827,55 @@
         <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4750,55 +4883,55 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -4806,55 +4939,55 @@
         <v>26</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="s">
         <v>668</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -4862,55 +4995,55 @@
         <v>26</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="H22" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -4918,26 +5051,26 @@
         <v>26</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>668</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>21</v>
       </c>
@@ -4960,13 +5093,13 @@
         <v>21</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>21</v>
+        <v>866</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -4974,55 +5107,55 @@
         <v>26</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="H24" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -5030,55 +5163,55 @@
         <v>26</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="s">
         <v>676</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -5086,55 +5219,55 @@
         <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -5142,55 +5275,55 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="F27" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -5198,55 +5331,55 @@
         <v>26</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
@@ -5254,55 +5387,55 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="s">
         <v>687</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -5310,55 +5443,55 @@
         <v>26</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="s">
         <v>690</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -5366,55 +5499,55 @@
         <v>26</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="H31" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -5422,25 +5555,25 @@
         <v>26</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="H32" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
@@ -5464,13 +5597,13 @@
         <v>21</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>21</v>
+        <v>875</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -5478,55 +5611,55 @@
         <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="H33" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R33" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -5534,55 +5667,55 @@
         <v>26</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="H34" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="s">
         <v>697</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -5590,55 +5723,55 @@
         <v>26</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="H35" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H35" s="3" t="s">
+      <c r="I35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="s">
         <v>700</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -5646,55 +5779,55 @@
         <v>26</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="F36" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H36" s="3" t="s">
+      <c r="I36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -5702,55 +5835,55 @@
         <v>26</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="H37" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" s="3" t="s">
         <v>705</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -5758,55 +5891,55 @@
         <v>26</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H38" s="3" t="s">
+      <c r="I38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -5814,55 +5947,55 @@
         <v>26</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="H39" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -5870,55 +6003,55 @@
         <v>26</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="H40" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -5926,55 +6059,55 @@
         <v>26</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="H41" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R41" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -5982,55 +6115,55 @@
         <v>26</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F42" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R42" s="3" t="s">
         <v>716</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -6038,55 +6171,55 @@
         <v>26</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="E43" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="H43" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="s">
         <v>718</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -6094,55 +6227,55 @@
         <v>26</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="E44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="H44" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R44" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -6150,55 +6283,55 @@
         <v>26</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -6206,122 +6339,122 @@
         <v>26</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R46" s="3" t="s">
         <v>724</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F47" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="s">
         <v>726</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>23</v>
@@ -6339,45 +6472,45 @@
         <v>21</v>
       </c>
       <c r="I48" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J48" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="K48" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P48" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>268</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>23</v>
@@ -6395,45 +6528,45 @@
         <v>21</v>
       </c>
       <c r="I49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J49" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="K49" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P49" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>271</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>23</v>
@@ -6451,45 +6584,45 @@
         <v>21</v>
       </c>
       <c r="I50" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="J50" s="3" t="s">
+      <c r="K50" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O50" s="3" t="s">
+      <c r="P50" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="P50" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="Q50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>23</v>
@@ -6507,45 +6640,45 @@
         <v>21</v>
       </c>
       <c r="I51" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="J51" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="J51" s="3" t="s">
+      <c r="K51" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P51" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="K51" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="Q51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>23</v>
@@ -6563,45 +6696,45 @@
         <v>21</v>
       </c>
       <c r="I52" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="L52" s="3" t="s">
+      <c r="M52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P52" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>23</v>
@@ -6619,45 +6752,45 @@
         <v>21</v>
       </c>
       <c r="I53" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="K53" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="K53" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O53" s="3" t="s">
+      <c r="P53" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="P53" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="Q53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>23</v>
@@ -6675,45 +6808,45 @@
         <v>21</v>
       </c>
       <c r="I54" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="J54" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="J54" s="3" t="s">
+      <c r="K54" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O54" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O54" s="3" t="s">
+      <c r="P54" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>300</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>23</v>
@@ -6731,45 +6864,45 @@
         <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J55" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="J55" s="3" t="s">
+      <c r="K55" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N55" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="K55" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N55" s="3" t="s">
+      <c r="O55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P55" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="O55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>306</v>
-      </c>
       <c r="Q55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>23</v>
@@ -6787,45 +6920,45 @@
         <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="J56" s="3" t="s">
+      <c r="K56" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N56" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="K56" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N56" s="3" t="s">
+      <c r="O56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P56" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="O56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="Q56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>23</v>
@@ -6843,45 +6976,45 @@
         <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="J57" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="J57" s="3" t="s">
+      <c r="K57" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>317</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>318</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>319</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>23</v>
@@ -6899,45 +7032,45 @@
         <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="J58" s="3" t="s">
+      <c r="K58" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N58" s="3" t="s">
+      <c r="O58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>325</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>23</v>
@@ -6955,45 +7088,45 @@
         <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J59" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="K59" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N59" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" s="3" t="s">
+      <c r="O59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P59" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>329</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>331</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>23</v>
@@ -7011,101 +7144,101 @@
         <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="J60" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="J60" s="3" t="s">
+      <c r="K60" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P60" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>334</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="3" t="s">
+      <c r="J61" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O61" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="J61" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O61" s="3" t="s">
+      <c r="P61" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="P61" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="Q61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>24</v>
@@ -7123,45 +7256,45 @@
         <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N62" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N62" s="3" t="s">
+      <c r="O62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P62" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>344</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>24</v>
@@ -7179,45 +7312,45 @@
         <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O63" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O63" s="3" t="s">
+      <c r="P63" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="P63" s="3" t="s">
-        <v>349</v>
-      </c>
       <c r="Q63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>24</v>
@@ -7235,45 +7368,45 @@
         <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N64" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N64" s="3" t="s">
+      <c r="O64" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="O64" s="3" t="s">
+      <c r="P64" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="P64" s="3" t="s">
-        <v>355</v>
-      </c>
       <c r="Q64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>24</v>
@@ -7291,45 +7424,45 @@
         <v>21</v>
       </c>
       <c r="I65" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N65" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N65" s="3" t="s">
+      <c r="O65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P65" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="O65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>360</v>
-      </c>
       <c r="Q65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>24</v>
@@ -7347,45 +7480,45 @@
         <v>21</v>
       </c>
       <c r="I66" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N66" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N66" s="3" t="s">
+      <c r="O66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P66" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>365</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>366</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>24</v>
@@ -7403,45 +7536,45 @@
         <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="K67" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O67" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="K67" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O67" s="3" t="s">
+      <c r="P67" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="P67" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="Q67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>24</v>
@@ -7459,45 +7592,45 @@
         <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O68" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J68" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O68" s="3" t="s">
+      <c r="P68" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="P68" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="Q68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>24</v>
@@ -7515,45 +7648,45 @@
         <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O69" s="3" t="s">
+      <c r="P69" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="P69" s="3" t="s">
-        <v>381</v>
-      </c>
       <c r="Q69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>24</v>
@@ -7571,45 +7704,45 @@
         <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="J70" s="3" t="s">
+      <c r="K70" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="K70" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O70" s="3" t="s">
+      <c r="P70" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="Q70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>24</v>
@@ -7627,45 +7760,45 @@
         <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="J71" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="J71" s="3" t="s">
+      <c r="K71" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="K71" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="L71" s="3" t="s">
+      <c r="M71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O71" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="M71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O71" s="3" t="s">
+      <c r="P71" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="P71" s="3" t="s">
-        <v>393</v>
-      </c>
       <c r="Q71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>24</v>
@@ -7683,45 +7816,45 @@
         <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N72" s="3" t="s">
+      <c r="O72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P72" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>398</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>24</v>
@@ -7739,45 +7872,45 @@
         <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="J73" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="J73" s="3" t="s">
+      <c r="K73" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O73" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="K73" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O73" s="3" t="s">
+      <c r="P73" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="P73" s="3" t="s">
-        <v>404</v>
-      </c>
       <c r="Q73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>406</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>24</v>
@@ -7795,101 +7928,101 @@
         <v>21</v>
       </c>
       <c r="I74" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="J74" s="3" t="s">
+      <c r="K74" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O74" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="K74" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="P74" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="Q74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I75" s="3" t="s">
+      <c r="J75" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P75" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="J75" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P75" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="Q75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>25</v>
@@ -7907,45 +8040,45 @@
         <v>21</v>
       </c>
       <c r="I76" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N76" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N76" s="3" t="s">
+      <c r="O76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P76" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>419</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>25</v>
@@ -7963,45 +8096,45 @@
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N77" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="J77" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N77" s="3" t="s">
+      <c r="O77" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="O77" s="3" t="s">
+      <c r="P77" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="P77" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="Q77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>25</v>
@@ -8019,45 +8152,45 @@
         <v>21</v>
       </c>
       <c r="I78" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O78" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="J78" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="L78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O78" s="3" t="s">
+      <c r="P78" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="P78" s="3" t="s">
-        <v>430</v>
-      </c>
       <c r="Q78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>25</v>
@@ -8075,45 +8208,45 @@
         <v>21</v>
       </c>
       <c r="I79" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N79" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="J79" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N79" s="3" t="s">
+      <c r="O79" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="O79" s="3" t="s">
+      <c r="P79" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="P79" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="Q79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>25</v>
@@ -8131,45 +8264,45 @@
         <v>21</v>
       </c>
       <c r="I80" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O80" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="J80" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O80" s="3" t="s">
+      <c r="P80" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="P80" s="3" t="s">
-        <v>441</v>
-      </c>
       <c r="Q80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>25</v>
@@ -8187,45 +8320,45 @@
         <v>21</v>
       </c>
       <c r="I81" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N81" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N81" s="3" t="s">
+      <c r="O81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P81" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>446</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>25</v>
@@ -8243,45 +8376,45 @@
         <v>21</v>
       </c>
       <c r="I82" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="J82" s="3" t="s">
+      <c r="K82" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M82" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="3" t="s">
+      <c r="N82" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="N82" s="3" t="s">
+      <c r="O82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P82" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="O82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P82" s="3" t="s">
-        <v>453</v>
-      </c>
       <c r="Q82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>455</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>25</v>
@@ -8299,45 +8432,45 @@
         <v>21</v>
       </c>
       <c r="I83" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="J83" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N83" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P83" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>25</v>
@@ -8355,45 +8488,45 @@
         <v>21</v>
       </c>
       <c r="I84" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="J84" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="J84" s="3" t="s">
+      <c r="K84" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="K84" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="L84" s="3" t="s">
+      <c r="M84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O84" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="M84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O84" s="3" t="s">
+      <c r="P84" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="P84" s="3" t="s">
-        <v>466</v>
-      </c>
       <c r="Q84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>25</v>
@@ -8411,45 +8544,45 @@
         <v>21</v>
       </c>
       <c r="I85" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N85" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="J85" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="L85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N85" s="3" t="s">
+      <c r="O85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P85" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="O85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P85" s="3" t="s">
-        <v>471</v>
-      </c>
       <c r="Q85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>25</v>
@@ -8467,45 +8600,45 @@
         <v>21</v>
       </c>
       <c r="I86" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N86" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="J86" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="L86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N86" s="3" t="s">
+      <c r="O86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P86" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="O86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P86" s="3" t="s">
-        <v>476</v>
-      </c>
       <c r="Q86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>25</v>
@@ -8523,45 +8656,45 @@
         <v>21</v>
       </c>
       <c r="I87" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="J87" s="3" t="s">
+      <c r="K87" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O87" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="L87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O87" s="3" t="s">
+      <c r="P87" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="P87" s="3" t="s">
-        <v>482</v>
-      </c>
       <c r="Q87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>25</v>
@@ -8579,101 +8712,101 @@
         <v>21</v>
       </c>
       <c r="I88" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="L88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N88" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="J88" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="L88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N88" s="3" t="s">
+      <c r="O88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P88" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="O88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>487</v>
-      </c>
       <c r="Q88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="3" t="s">
+      <c r="J89" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N89" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N89" s="3" t="s">
+      <c r="O89" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="O89" s="3" t="s">
+      <c r="P89" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>493</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>22</v>
@@ -8691,45 +8824,45 @@
         <v>21</v>
       </c>
       <c r="I90" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="L90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M90" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="J90" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="L90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M90" s="3" t="s">
+      <c r="N90" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="N90" s="3" t="s">
+      <c r="O90" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="O90" s="3" t="s">
+      <c r="P90" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="P90" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="Q90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>22</v>
@@ -8747,45 +8880,45 @@
         <v>21</v>
       </c>
       <c r="I91" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M91" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M91" s="3" t="s">
+      <c r="N91" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="O91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>507</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>508</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>22</v>
@@ -8803,45 +8936,45 @@
         <v>21</v>
       </c>
       <c r="I92" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="L92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="J92" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="L92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M92" s="3" t="s">
+      <c r="N92" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="N92" s="3" t="s">
+      <c r="O92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P92" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="O92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>513</v>
-      </c>
       <c r="Q92" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>22</v>
@@ -8859,45 +8992,45 @@
         <v>21</v>
       </c>
       <c r="I93" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="L93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M93" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="J93" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" s="3" t="s">
+      <c r="N93" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="N93" s="3" t="s">
+      <c r="O93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P93" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="O93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>518</v>
-      </c>
       <c r="Q93" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R93" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>22</v>
@@ -8915,45 +9048,45 @@
         <v>21</v>
       </c>
       <c r="I94" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M94" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>525</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>527</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>22</v>
@@ -8971,45 +9104,45 @@
         <v>21</v>
       </c>
       <c r="I95" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="L95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M95" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="J95" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="L95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M95" s="3" t="s">
+      <c r="N95" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="N95" s="3" t="s">
+      <c r="O95" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P95" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="O95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>531</v>
-      </c>
       <c r="Q95" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>532</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>533</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>22</v>
@@ -9027,45 +9160,45 @@
         <v>21</v>
       </c>
       <c r="I96" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M96" s="3" t="s">
+      <c r="N96" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="O96" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="O96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>538</v>
-      </c>
       <c r="Q96" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>22</v>
@@ -9083,45 +9216,45 @@
         <v>21</v>
       </c>
       <c r="I97" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="L97" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="J97" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="L97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M97" s="3" t="s">
+      <c r="N97" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="N97" s="3" t="s">
+      <c r="O97" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="O97" s="3" t="s">
+      <c r="P97" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="P97" s="3" t="s">
-        <v>545</v>
-      </c>
       <c r="Q97" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>22</v>
@@ -9139,45 +9272,45 @@
         <v>21</v>
       </c>
       <c r="I98" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="L98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="J98" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="L98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M98" s="3" t="s">
+      <c r="N98" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="N98" s="3" t="s">
+      <c r="O98" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P98" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="O98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P98" s="3" t="s">
-        <v>551</v>
-      </c>
       <c r="Q98" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>22</v>
@@ -9195,45 +9328,45 @@
         <v>21</v>
       </c>
       <c r="I99" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="J99" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="J99" s="3" t="s">
+      <c r="K99" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="K99" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="L99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M99" s="3" t="s">
+      <c r="N99" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O99" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="N99" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O99" s="3" t="s">
+      <c r="P99" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="P99" s="3" t="s">
-        <v>558</v>
-      </c>
       <c r="Q99" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>22</v>
@@ -9251,45 +9384,45 @@
         <v>21</v>
       </c>
       <c r="I100" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M100" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>565</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>22</v>
@@ -9307,45 +9440,45 @@
         <v>21</v>
       </c>
       <c r="I101" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M101" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>572</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>574</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>22</v>
@@ -9363,39 +9496,39 @@
         <v>21</v>
       </c>
       <c r="I102" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="J102" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="J102" s="3" t="s">
+      <c r="K102" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" s="3" t="s">
+      <c r="N102" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="N102" s="3" t="s">
+      <c r="O102" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="O102" s="3" t="s">
+      <c r="P102" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>580</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>21</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>33</v>
@@ -9413,10 +9546,10 @@
         <v>36</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="M103" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N103" s="5" t="s">
         <v>37</v>
@@ -9425,12 +9558,12 @@
         <v>38</v>
       </c>
       <c r="R103" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>39</v>
@@ -9442,16 +9575,16 @@
         <v>22</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K104" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="M104" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="N104" s="5" t="s">
         <v>31</v>
@@ -9460,12 +9593,12 @@
         <v>41</v>
       </c>
       <c r="R104" s="5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>42</v>
@@ -9477,16 +9610,16 @@
         <v>22</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K105" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="M105" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="N105" s="5" t="s">
         <v>44</v>
@@ -9498,12 +9631,12 @@
         <v>46</v>
       </c>
       <c r="R105" s="5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>47</v>
@@ -9521,10 +9654,10 @@
         <v>50</v>
       </c>
       <c r="K106" s="5" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="N106" s="5" t="s">
         <v>51</v>
@@ -9533,238 +9666,238 @@
         <v>52</v>
       </c>
       <c r="R106" s="5" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>589</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J107" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K107" s="5" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="M107" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="N107" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="N107" s="5" t="s">
+      <c r="O107" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="O107" s="5" t="s">
+      <c r="P107" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="P107" s="5" t="s">
-        <v>594</v>
-      </c>
       <c r="R107" s="5" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B108" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>595</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>596</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K108" s="5" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="M108" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="N108" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="N108" s="5" t="s">
+      <c r="O108" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="O108" s="5" t="s">
+      <c r="P108" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="P108" s="5" t="s">
-        <v>601</v>
-      </c>
       <c r="R108" s="5" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>602</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>603</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="J109" s="5" t="s">
         <v>30</v>
       </c>
       <c r="K109" s="5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="L109" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="M109" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="M109" s="5" t="s">
+      <c r="N109" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="N109" s="5" t="s">
+      <c r="O109" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="O109" s="5" t="s">
+      <c r="P109" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="P109" s="5" t="s">
-        <v>609</v>
-      </c>
       <c r="R109" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>610</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>611</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K110" s="5" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="M110" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="N110" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="N110" s="5" t="s">
+      <c r="O110" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="O110" s="5" t="s">
+      <c r="P110" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="P110" s="5" t="s">
-        <v>616</v>
-      </c>
       <c r="R110" s="5" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B111" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>617</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>618</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K111" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="M111" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="N111" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="N111" s="5" t="s">
+      <c r="O111" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="O111" s="5" t="s">
+      <c r="P111" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="P111" s="5" t="s">
-        <v>623</v>
-      </c>
       <c r="R111" s="5" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>624</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>625</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>22</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>29</v>
       </c>
       <c r="K112" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="M112" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="N112" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="N112" s="5" t="s">
+      <c r="O112" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="O112" s="5" t="s">
+      <c r="P112" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="P112" s="5" t="s">
-        <v>630</v>
-      </c>
       <c r="R112" s="5" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
   </sheetData>
@@ -9819,7 +9952,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
@@ -9834,22 +9967,22 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
@@ -9859,7 +9992,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
@@ -9884,7 +10017,7 @@
     </row>
     <row r="21" spans="1:1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -9899,7 +10032,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
@@ -9909,17 +10042,17 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
@@ -9934,7 +10067,7 @@
     </row>
     <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>729</v>
+        <v>891</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
@@ -9992,19 +10125,19 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>79</v>
+        <v>892</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA41CF1-A6D9-4CDE-8C8E-295D1186E4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FF36AD-3FA8-4571-8E24-6B62C899D9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="942">
   <si>
     <t>類型</t>
   </si>
@@ -3126,14 +3126,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>atkPct:0.9;matkPct:0.9;elemDmgFire:0.45;elemDmgIce:0.45;elemDmgLightning:0.45;elemDmgPoison:0.45;elemDmgLight:0.45;elemDmgDark:0.45;elemDmgEarth:0.45;elemDmgWind:0.45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.9、魔法攻擊×0.9、火屬性傷害提升×0.45、冰屬性傷害提升×0.45、雷屬性傷害提升×0.45、毒屬性傷害提升×0.45、聖屬性傷害提升×0.45、暗屬性傷害提升×0.45、地屬性傷害提升×0.45、風屬性傷害提升×0.45｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>atkPct:1.05;critDmg:1.05;bossDmg:1.05;aoeDmg:0.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3603,6 +3595,17 @@
   </si>
   <si>
     <t>風味文字：圖鑑與詳情顯示的一句話，可留空。符文列＝符文庫詳情裡形容這顆符文的文字；符文真言列＝圖鑑裡那組真言的一句話。效果說明文字由資料自動產生，不需要另外寫。</t>
+  </si>
+  <si>
+    <t>atkPct:0.9;matkPct:0.9;elemDmgAll:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.9、魔法攻擊×0.9、全屬性傷害提升×0.45｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>　　符文專用的合成屬性：elemDmgAll＝全屬性傷害提升（火冰雷毒聖暗地風八種元素傷害提升各加同樣的值；符文列與真言的屬性加成都能填）。</t>
   </si>
 </sst>
 </file>
@@ -4059,10 +4062,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>8</v>
@@ -4797,40 +4800,40 @@
         <v>652</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" s="3" t="s">
         <v>857</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4859,40 +4862,40 @@
         <v>100</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4921,40 +4924,40 @@
         <v>184</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T17" s="3" t="s">
         <v>863</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4983,40 +4986,40 @@
         <v>653</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T18" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -5045,10 +5048,10 @@
         <v>655</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>21</v>
@@ -5072,13 +5075,13 @@
         <v>21</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -5107,10 +5110,10 @@
         <v>657</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>21</v>
@@ -5134,13 +5137,13 @@
         <v>21</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -5169,10 +5172,10 @@
         <v>659</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>21</v>
@@ -5196,13 +5199,13 @@
         <v>21</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -5231,40 +5234,40 @@
         <v>660</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T22" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -5293,10 +5296,10 @@
         <v>659</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>21</v>
@@ -5320,13 +5323,13 @@
         <v>21</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -5355,40 +5358,40 @@
         <v>661</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T24" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -5417,40 +5420,40 @@
         <v>663</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T25" s="3" t="s">
         <v>883</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -5479,40 +5482,40 @@
         <v>665</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T26" s="3" t="s">
         <v>886</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5541,10 +5544,10 @@
         <v>667</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>21</v>
@@ -5568,13 +5571,13 @@
         <v>21</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5603,10 +5606,10 @@
         <v>669</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>21</v>
@@ -5630,13 +5633,13 @@
         <v>21</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5665,10 +5668,10 @@
         <v>670</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>21</v>
@@ -5692,13 +5695,13 @@
         <v>21</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5727,40 +5730,40 @@
         <v>672</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T30" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5789,10 +5792,10 @@
         <v>673</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>21</v>
@@ -5816,13 +5819,13 @@
         <v>21</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="S31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5851,10 +5854,10 @@
         <v>662</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>21</v>
@@ -5878,13 +5881,13 @@
         <v>21</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5913,10 +5916,10 @@
         <v>674</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>21</v>
@@ -5940,13 +5943,13 @@
         <v>21</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5975,40 +5978,40 @@
         <v>675</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T34" s="3" t="s">
         <v>904</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -6037,40 +6040,40 @@
         <v>677</v>
       </c>
       <c r="I35" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T35" s="3" t="s">
         <v>907</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -6099,40 +6102,40 @@
         <v>679</v>
       </c>
       <c r="I36" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T36" s="3" t="s">
         <v>910</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -6161,10 +6164,10 @@
         <v>196</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>21</v>
@@ -6188,13 +6191,13 @@
         <v>21</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="S37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -6223,10 +6226,10 @@
         <v>682</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>21</v>
@@ -6250,13 +6253,13 @@
         <v>21</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="S38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -6285,40 +6288,40 @@
         <v>683</v>
       </c>
       <c r="I39" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T39" s="3" t="s">
         <v>917</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>846</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6347,40 +6350,40 @@
         <v>677</v>
       </c>
       <c r="I40" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T40" s="3" t="s">
         <v>920</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -6409,10 +6412,10 @@
         <v>681</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>21</v>
@@ -6436,13 +6439,13 @@
         <v>21</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="S41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -6471,10 +6474,10 @@
         <v>686</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>21</v>
@@ -6498,13 +6501,13 @@
         <v>21</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -6533,10 +6536,10 @@
         <v>687</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>21</v>
@@ -6560,13 +6563,13 @@
         <v>21</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6595,10 +6598,10 @@
         <v>688</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>21</v>
@@ -6622,13 +6625,13 @@
         <v>21</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
@@ -6657,10 +6660,10 @@
         <v>658</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>21</v>
@@ -6684,13 +6687,13 @@
         <v>21</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
@@ -6719,10 +6722,10 @@
         <v>688</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>21</v>
@@ -6746,13 +6749,13 @@
         <v>21</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
@@ -6781,10 +6784,10 @@
         <v>685</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>21</v>
@@ -6808,13 +6811,13 @@
         <v>21</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -10135,7 +10138,7 @@
         <v>50</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>808</v>
+        <v>939</v>
       </c>
       <c r="O106" s="5" t="s">
         <v>584</v>
@@ -10147,7 +10150,7 @@
         <v>52</v>
       </c>
       <c r="T106" s="5" t="s">
-        <v>809</v>
+        <v>940</v>
       </c>
     </row>
     <row r="107" spans="1:20" x14ac:dyDescent="0.25">
@@ -10170,7 +10173,7 @@
         <v>30</v>
       </c>
       <c r="M107" s="5" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="O107" s="5" t="s">
         <v>588</v>
@@ -10185,7 +10188,7 @@
         <v>591</v>
       </c>
       <c r="T107" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="108" spans="1:20" x14ac:dyDescent="0.25">
@@ -10208,7 +10211,7 @@
         <v>32</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="O108" s="5" t="s">
         <v>595</v>
@@ -10223,7 +10226,7 @@
         <v>598</v>
       </c>
       <c r="T108" s="5" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="109" spans="1:20" x14ac:dyDescent="0.25">
@@ -10246,7 +10249,7 @@
         <v>30</v>
       </c>
       <c r="M109" s="5" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="N109" s="5" t="s">
         <v>602</v>
@@ -10264,7 +10267,7 @@
         <v>606</v>
       </c>
       <c r="T109" s="5" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="110" spans="1:20" x14ac:dyDescent="0.25">
@@ -10287,7 +10290,7 @@
         <v>27</v>
       </c>
       <c r="M110" s="5" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="O110" s="5" t="s">
         <v>610</v>
@@ -10302,7 +10305,7 @@
         <v>613</v>
       </c>
       <c r="T110" s="5" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="111" spans="1:20" x14ac:dyDescent="0.25">
@@ -10325,7 +10328,7 @@
         <v>27</v>
       </c>
       <c r="M111" s="5" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="O111" s="5" t="s">
         <v>617</v>
@@ -10340,7 +10343,7 @@
         <v>620</v>
       </c>
       <c r="T111" s="5" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="112" spans="1:20" x14ac:dyDescent="0.25">
@@ -10363,7 +10366,7 @@
         <v>29</v>
       </c>
       <c r="M112" s="5" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="O112" s="5" t="s">
         <v>624</v>
@@ -10378,7 +10381,7 @@
         <v>627</v>
       </c>
       <c r="T112" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
   </sheetData>
@@ -10390,7 +10393,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="125.625" customWidth="1"/>
@@ -10498,7 +10501,7 @@
     </row>
     <row r="21" spans="1:1" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -10508,17 +10511,17 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
@@ -10558,76 +10561,81 @@
     </row>
     <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>67</v>
+        <v>941</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="33" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>940</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>78</v>
       </c>
     </row>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\tmp\rune-unlock-authoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FF36AD-3FA8-4571-8E24-6B62C899D9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28B8A0A6-64E6-4BAD-B0DC-8744FE093EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Runes" sheetId="1" r:id="rId1"/>
     <sheet name="欄位說明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runes!$A$1:$T$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Runes!$A$1:$U$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="944">
   <si>
     <t>類型</t>
   </si>
@@ -3606,6 +3606,12 @@
   </si>
   <si>
     <t>　　符文專用的合成屬性：elemDmgAll＝全屬性傷害提升（火冰雷毒聖暗地風八種元素傷害提升各加同樣的值；符文列與真言的屬性加成都能填）。</t>
+  </si>
+  <si>
+    <t>封魔塔解鎖層數</t>
+  </si>
+  <si>
+    <t>封魔塔解鎖層數：非負整數；通關該層 BOSS 即永久解鎖配方與效果（正式／內測皆適用）。留白或 0＝僅自行成功成形解鎖。超過目前塔上限仍可自行成形。已解鎖不因門檻調高而撤銷。</t>
   </si>
 </sst>
 </file>
@@ -3660,7 +3666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3677,6 +3683,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4013,30 +4025,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}">
-  <dimension ref="A1:T112"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U112"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" customWidth="1"/>
-    <col min="5" max="5" width="14.625" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="9.625" customWidth="1"/>
-    <col min="9" max="10" width="14.625" style="5" customWidth="1"/>
-    <col min="11" max="12" width="24.625" customWidth="1"/>
-    <col min="13" max="13" width="40.625" customWidth="1"/>
-    <col min="14" max="14" width="14.625" customWidth="1"/>
-    <col min="15" max="15" width="22.625" customWidth="1"/>
-    <col min="16" max="16" width="36.625" customWidth="1"/>
-    <col min="17" max="17" width="60.625" customWidth="1"/>
-    <col min="18" max="18" width="36.625" customWidth="1"/>
-    <col min="19" max="19" width="10.625" customWidth="1"/>
-    <col min="20" max="20" width="50.625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" customWidth="1"/>
+    <col min="9" max="10" width="14.6640625" style="5" customWidth="1"/>
+    <col min="11" max="12" width="24.6640625" customWidth="1"/>
+    <col min="13" max="13" width="40.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" customWidth="1"/>
+    <col min="15" max="15" width="22.6640625" customWidth="1"/>
+    <col min="16" max="16" width="36.6640625" customWidth="1"/>
+    <col min="17" max="17" width="60.6640625" customWidth="1"/>
+    <col min="18" max="18" width="36.6640625" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" customWidth="1"/>
+    <col min="20" max="20" width="50.6640625" customWidth="1"/>
+    <col min="21" max="21" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4097,8 +4110,11 @@
       <c r="T1" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" s="2" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -4155,8 +4171,9 @@
       <c r="T2" s="3" t="s">
         <v>635</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U2" s="6"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -4213,8 +4230,9 @@
       <c r="T3" s="3" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U3" s="6"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -4245,8 +4263,9 @@
       <c r="T4" s="3" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U4" s="6"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
@@ -4277,8 +4296,9 @@
       <c r="T5" s="3" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U5" s="6"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -4309,8 +4329,9 @@
       <c r="T6" s="3" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U6" s="6"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
@@ -4367,8 +4388,9 @@
       <c r="T7" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U7" s="6"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -4425,8 +4447,9 @@
       <c r="T8" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U8" s="6"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -4483,8 +4506,9 @@
       <c r="T9" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U9" s="6"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -4541,8 +4565,9 @@
       <c r="T10" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U10" s="6"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -4599,8 +4624,9 @@
       <c r="T11" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U11" s="6"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>18</v>
       </c>
@@ -4657,8 +4683,9 @@
       <c r="T12" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U12" s="6"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
@@ -4715,8 +4742,9 @@
       <c r="T13" s="3" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U13" s="6"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>110</v>
       </c>
@@ -4773,8 +4801,9 @@
       <c r="T14" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U14" s="6"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -4835,8 +4864,9 @@
       <c r="T15" s="3" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U15" s="6"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>26</v>
       </c>
@@ -4897,8 +4927,9 @@
       <c r="T16" s="3" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U16" s="6"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -4959,8 +4990,9 @@
       <c r="T17" s="3" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U17" s="6"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
@@ -5021,8 +5053,9 @@
       <c r="T18" s="3" t="s">
         <v>866</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="6"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
@@ -5083,8 +5116,9 @@
       <c r="T19" s="3" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U19" s="6"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>26</v>
       </c>
@@ -5145,8 +5179,9 @@
       <c r="T20" s="3" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U20" s="6"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>26</v>
       </c>
@@ -5207,8 +5242,9 @@
       <c r="T21" s="3" t="s">
         <v>872</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U21" s="6"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>26</v>
       </c>
@@ -5269,8 +5305,9 @@
       <c r="T22" s="3" t="s">
         <v>875</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U22" s="6"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
@@ -5331,8 +5368,9 @@
       <c r="T23" s="3" t="s">
         <v>877</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U23" s="6"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
@@ -5393,8 +5431,9 @@
       <c r="T24" s="3" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U24" s="6"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>26</v>
       </c>
@@ -5455,8 +5494,9 @@
       <c r="T25" s="3" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U25" s="6"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
@@ -5517,8 +5557,9 @@
       <c r="T26" s="3" t="s">
         <v>886</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U26" s="6"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -5579,8 +5620,9 @@
       <c r="T27" s="3" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U27" s="6"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
@@ -5641,8 +5683,9 @@
       <c r="T28" s="3" t="s">
         <v>890</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U28" s="6"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>26</v>
       </c>
@@ -5703,8 +5746,9 @@
       <c r="T29" s="3" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U29" s="6"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>26</v>
       </c>
@@ -5765,8 +5809,9 @@
       <c r="T30" s="3" t="s">
         <v>895</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U30" s="6"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>26</v>
       </c>
@@ -5827,8 +5872,9 @@
       <c r="T31" s="3" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U31" s="6"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>26</v>
       </c>
@@ -5889,8 +5935,9 @@
       <c r="T32" s="3" t="s">
         <v>899</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U32" s="6"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>26</v>
       </c>
@@ -5951,8 +5998,9 @@
       <c r="T33" s="3" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U33" s="6"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>26</v>
       </c>
@@ -6013,8 +6061,9 @@
       <c r="T34" s="3" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U34" s="6"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>26</v>
       </c>
@@ -6075,8 +6124,9 @@
       <c r="T35" s="3" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U35" s="6"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>26</v>
       </c>
@@ -6137,8 +6187,9 @@
       <c r="T36" s="3" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U36" s="6"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>26</v>
       </c>
@@ -6199,8 +6250,9 @@
       <c r="T37" s="3" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U37" s="6"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>26</v>
       </c>
@@ -6261,8 +6313,9 @@
       <c r="T38" s="3" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U38" s="6"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>26</v>
       </c>
@@ -6323,8 +6376,9 @@
       <c r="T39" s="3" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U39" s="6"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>26</v>
       </c>
@@ -6385,8 +6439,9 @@
       <c r="T40" s="3" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U40" s="6"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>26</v>
       </c>
@@ -6447,8 +6502,9 @@
       <c r="T41" s="3" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U41" s="6"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>26</v>
       </c>
@@ -6509,8 +6565,9 @@
       <c r="T42" s="3" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U42" s="6"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>26</v>
       </c>
@@ -6571,8 +6628,9 @@
       <c r="T43" s="3" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U43" s="6"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>26</v>
       </c>
@@ -6633,8 +6691,9 @@
       <c r="T44" s="3" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U44" s="6"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>26</v>
       </c>
@@ -6695,8 +6754,9 @@
       <c r="T45" s="3" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U45" s="6"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>26</v>
       </c>
@@ -6757,8 +6817,9 @@
       <c r="T46" s="3" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U46" s="6"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>255</v>
       </c>
@@ -6819,8 +6880,9 @@
       <c r="T47" s="3" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U47" s="6"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>79</v>
       </c>
@@ -6877,8 +6939,11 @@
       <c r="T48" s="3" t="s">
         <v>693</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U48" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>79</v>
       </c>
@@ -6935,8 +7000,11 @@
       <c r="T49" s="3" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U49" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>79</v>
       </c>
@@ -6993,8 +7061,11 @@
       <c r="T50" s="3" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U50" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>79</v>
       </c>
@@ -7051,8 +7122,11 @@
       <c r="T51" s="3" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U51" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>79</v>
       </c>
@@ -7109,8 +7183,11 @@
       <c r="T52" s="3" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U52" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>79</v>
       </c>
@@ -7167,8 +7244,11 @@
       <c r="T53" s="3" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U53" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>79</v>
       </c>
@@ -7225,8 +7305,11 @@
       <c r="T54" s="3" t="s">
         <v>705</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U54" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>79</v>
       </c>
@@ -7283,8 +7366,11 @@
       <c r="T55" s="3" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U55" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>79</v>
       </c>
@@ -7341,8 +7427,11 @@
       <c r="T56" s="3" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U56" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>79</v>
       </c>
@@ -7399,8 +7488,11 @@
       <c r="T57" s="3" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U57" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>79</v>
       </c>
@@ -7457,8 +7549,11 @@
       <c r="T58" s="3" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U58" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>79</v>
       </c>
@@ -7515,8 +7610,11 @@
       <c r="T59" s="3" t="s">
         <v>715</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U59" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>79</v>
       </c>
@@ -7573,8 +7671,11 @@
       <c r="T60" s="3" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U60" s="6">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>79</v>
       </c>
@@ -7631,8 +7732,11 @@
       <c r="T61" s="3" t="s">
         <v>719</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U61" s="6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>79</v>
       </c>
@@ -7689,8 +7793,11 @@
       <c r="T62" s="3" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U62" s="6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>79</v>
       </c>
@@ -7747,8 +7854,11 @@
       <c r="T63" s="3" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U63" s="6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>79</v>
       </c>
@@ -7805,8 +7915,11 @@
       <c r="T64" s="3" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U64" s="6">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>79</v>
       </c>
@@ -7863,8 +7976,11 @@
       <c r="T65" s="3" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U65" s="6">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>79</v>
       </c>
@@ -7921,8 +8037,11 @@
       <c r="T66" s="3" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U66" s="6">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>79</v>
       </c>
@@ -7979,8 +8098,11 @@
       <c r="T67" s="3" t="s">
         <v>731</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U67" s="6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>79</v>
       </c>
@@ -8037,8 +8159,11 @@
       <c r="T68" s="3" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U68" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>79</v>
       </c>
@@ -8095,8 +8220,11 @@
       <c r="T69" s="3" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U69" s="6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>79</v>
       </c>
@@ -8153,8 +8281,11 @@
       <c r="T70" s="3" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U70" s="6">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>79</v>
       </c>
@@ -8211,8 +8342,11 @@
       <c r="T71" s="3" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U71" s="6">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>79</v>
       </c>
@@ -8269,8 +8403,11 @@
       <c r="T72" s="3" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U72" s="6">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>79</v>
       </c>
@@ -8327,8 +8464,11 @@
       <c r="T73" s="3" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U73" s="6">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>79</v>
       </c>
@@ -8385,8 +8525,11 @@
       <c r="T74" s="3" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U74" s="6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>79</v>
       </c>
@@ -8443,8 +8586,11 @@
       <c r="T75" s="3" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U75" s="6">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>79</v>
       </c>
@@ -8501,8 +8647,11 @@
       <c r="T76" s="3" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U76" s="6">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>79</v>
       </c>
@@ -8559,8 +8708,11 @@
       <c r="T77" s="3" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U77" s="6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>79</v>
       </c>
@@ -8617,8 +8769,11 @@
       <c r="T78" s="3" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U78" s="6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>79</v>
       </c>
@@ -8675,8 +8830,11 @@
       <c r="T79" s="3" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U79" s="6">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>79</v>
       </c>
@@ -8733,8 +8891,11 @@
       <c r="T80" s="3" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U80" s="6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>79</v>
       </c>
@@ -8791,8 +8952,11 @@
       <c r="T81" s="3" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U81" s="6">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>79</v>
       </c>
@@ -8849,8 +9013,11 @@
       <c r="T82" s="3" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U82" s="6">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>79</v>
       </c>
@@ -8907,8 +9074,11 @@
       <c r="T83" s="3" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U83" s="6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>79</v>
       </c>
@@ -8965,8 +9135,11 @@
       <c r="T84" s="3" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U84" s="6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>79</v>
       </c>
@@ -9023,8 +9196,11 @@
       <c r="T85" s="3" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U85" s="6">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>79</v>
       </c>
@@ -9081,8 +9257,11 @@
       <c r="T86" s="3" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U86" s="6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>79</v>
       </c>
@@ -9139,8 +9318,11 @@
       <c r="T87" s="3" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U87" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>79</v>
       </c>
@@ -9197,8 +9379,11 @@
       <c r="T88" s="3" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U88" s="6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>79</v>
       </c>
@@ -9255,8 +9440,11 @@
       <c r="T89" s="3" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U89" s="6">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>79</v>
       </c>
@@ -9313,8 +9501,11 @@
       <c r="T90" s="3" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U90" s="6">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>79</v>
       </c>
@@ -9371,8 +9562,11 @@
       <c r="T91" s="3" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U91" s="6">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>79</v>
       </c>
@@ -9429,8 +9623,11 @@
       <c r="T92" s="3" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U92" s="6">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>79</v>
       </c>
@@ -9487,8 +9684,11 @@
       <c r="T93" s="3" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U93" s="6">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>79</v>
       </c>
@@ -9545,8 +9745,11 @@
       <c r="T94" s="3" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U94" s="6">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>79</v>
       </c>
@@ -9603,8 +9806,11 @@
       <c r="T95" s="3" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U95" s="6">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>79</v>
       </c>
@@ -9661,8 +9867,11 @@
       <c r="T96" s="3" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U96" s="6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>79</v>
       </c>
@@ -9719,8 +9928,11 @@
       <c r="T97" s="3" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U97" s="6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>79</v>
       </c>
@@ -9777,8 +9989,11 @@
       <c r="T98" s="3" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U98" s="6">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>79</v>
       </c>
@@ -9835,8 +10050,11 @@
       <c r="T99" s="3" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U99" s="6">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>79</v>
       </c>
@@ -9893,8 +10111,11 @@
       <c r="T100" s="3" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U100" s="6">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>79</v>
       </c>
@@ -9951,8 +10172,11 @@
       <c r="T101" s="3" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U101" s="6">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>79</v>
       </c>
@@ -10009,8 +10233,11 @@
       <c r="T102" s="3" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U102" s="6">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>578</v>
       </c>
@@ -10044,8 +10271,11 @@
       <c r="T103" s="5" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U103" s="7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>578</v>
       </c>
@@ -10079,8 +10309,11 @@
       <c r="T104" s="5" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U104" s="7">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>578</v>
       </c>
@@ -10117,8 +10350,11 @@
       <c r="T105" s="5" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U105" s="7">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>578</v>
       </c>
@@ -10152,8 +10388,11 @@
       <c r="T106" s="5" t="s">
         <v>940</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U106" s="7">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>578</v>
       </c>
@@ -10190,8 +10429,11 @@
       <c r="T107" s="5" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U107" s="7">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>578</v>
       </c>
@@ -10228,8 +10470,11 @@
       <c r="T108" s="5" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U108" s="7">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>578</v>
       </c>
@@ -10269,8 +10514,11 @@
       <c r="T109" s="5" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U109" s="7">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>578</v>
       </c>
@@ -10307,8 +10555,11 @@
       <c r="T110" s="5" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U110" s="7">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>578</v>
       </c>
@@ -10345,8 +10596,11 @@
       <c r="T111" s="5" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U111" s="7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>578</v>
       </c>
@@ -10383,9 +10637,12 @@
       <c r="T112" s="5" t="s">
         <v>819</v>
       </c>
+      <c r="U112" s="7">
+        <v>195</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T102" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}"/>
+  <autoFilter ref="A1:U112" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10393,250 +10650,255 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
-  <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A49"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="47" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>943</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392428F6-DEFC-4831-810D-9DBAC9EB1F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC157A2-E885-4B3D-BECD-A6237E284A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -6784,7 +6784,7 @@
         <v>1</v>
       </c>
       <c r="E48" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>20</v>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="E49" s="6">
         <f>E48+2</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>20</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="E50" s="6">
         <f t="shared" ref="E50:E112" si="0">E49+2</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>20</v>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="E51" s="6">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>20</v>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="E52" s="6">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>20</v>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="E53" s="6">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>20</v>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="E54" s="6">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>20</v>
@@ -7218,7 +7218,7 @@
       </c>
       <c r="E55" s="6">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>20</v>
@@ -7280,7 +7280,7 @@
       </c>
       <c r="E56" s="6">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>20</v>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="E57" s="6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>20</v>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="E58" s="6">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>20</v>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="E59" s="6">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>20</v>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="E60" s="6">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>20</v>
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E61" s="6">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>20</v>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="E62" s="6">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>20</v>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="E63" s="6">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>20</v>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="E64" s="6">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>20</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="E65" s="6">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>20</v>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="E66" s="6">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>20</v>
@@ -7962,7 +7962,7 @@
       </c>
       <c r="E67" s="6">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>20</v>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="E68" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>20</v>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="E69" s="6">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>20</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="E70" s="6">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>20</v>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="E71" s="6">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>20</v>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="E72" s="6">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>20</v>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="E73" s="6">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>20</v>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E74" s="6">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>20</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="E75" s="6">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>20</v>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E76" s="6">
         <f t="shared" si="0"/>
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>20</v>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="E77" s="6">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>20</v>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="E78" s="6">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>20</v>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="E79" s="6">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>20</v>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="E80" s="6">
         <f t="shared" si="0"/>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>20</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="E81" s="6">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>20</v>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="E82" s="6">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>20</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="E83" s="6">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>20</v>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="E84" s="6">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>20</v>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="E85" s="6">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>20</v>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="E86" s="6">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>20</v>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="E87" s="6">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>20</v>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="E88" s="6">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>20</v>
@@ -9326,7 +9326,7 @@
       </c>
       <c r="E89" s="6">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>20</v>
@@ -9388,7 +9388,7 @@
       </c>
       <c r="E90" s="6">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>20</v>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="E91" s="6">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>20</v>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="E92" s="6">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>20</v>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="E93" s="6">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>20</v>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="E94" s="6">
         <f t="shared" si="0"/>
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>20</v>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="E95" s="6">
         <f t="shared" si="0"/>
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>20</v>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="E96" s="6">
         <f t="shared" si="0"/>
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>20</v>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="E97" s="6">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>20</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="E98" s="6">
         <f t="shared" si="0"/>
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>20</v>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="E99" s="6">
         <f t="shared" si="0"/>
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>20</v>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E100" s="6">
         <f t="shared" si="0"/>
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>20</v>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="E101" s="6">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>20</v>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="E102" s="6">
         <f t="shared" si="0"/>
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>20</v>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="E103" s="6">
         <f t="shared" si="0"/>
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>31</v>
@@ -10233,7 +10233,7 @@
       </c>
       <c r="E104" s="6">
         <f t="shared" si="0"/>
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>547</v>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="E105" s="6">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>549</v>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="E106" s="6">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>45</v>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E107" s="6">
         <f t="shared" si="0"/>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>554</v>
@@ -10395,7 +10395,7 @@
       </c>
       <c r="E108" s="6">
         <f t="shared" si="0"/>
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>561</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="E109" s="6">
         <f t="shared" si="0"/>
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>568</v>
@@ -10482,7 +10482,7 @@
       </c>
       <c r="E110" s="6">
         <f t="shared" si="0"/>
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L110" s="5" t="s">
         <v>576</v>
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E111" s="6">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>583</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="E112" s="6">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>590</v>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\.codex\visualizations\2026\10\19\01a154b8-8fd9-7253-8f40-4499a22fa170\earthguard-task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC157A2-E885-4B3D-BECD-A6237E284A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D2C13E-C7DE-4829-B475-94B78A0ACD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Runes" sheetId="1" r:id="rId1"/>
@@ -2970,10 +2970,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>屬性：生命值×1.5、全局減傷×0.9、全屬性抗性×0.9｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的無敵時間內，每殺死 1 個敵人則無敵時間 +0.5 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>atkPct:0.9;aspd:0.9;aoeDmg:0.6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3487,6 +3483,10 @@
   </si>
   <si>
     <t>階／級距</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×1.5、全局減傷×0.9、全屬性抗性×0.9｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3542,7 +3542,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3570,11 +3570,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3914,30 +3911,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}">
   <dimension ref="A1:U112"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="18.375" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="9.625" customWidth="1"/>
-    <col min="8" max="8" width="14.625" customWidth="1"/>
-    <col min="9" max="9" width="9.625" customWidth="1"/>
-    <col min="10" max="11" width="14.625" style="5" customWidth="1"/>
-    <col min="12" max="13" width="24.625" customWidth="1"/>
-    <col min="14" max="14" width="40.625" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
-    <col min="16" max="16" width="22.625" customWidth="1"/>
-    <col min="17" max="17" width="36.625" customWidth="1"/>
-    <col min="18" max="18" width="60.625" customWidth="1"/>
-    <col min="19" max="19" width="36.625" customWidth="1"/>
-    <col min="20" max="20" width="10.625" customWidth="1"/>
-    <col min="21" max="21" width="50.625" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="10" max="11" width="14.6640625" style="5" customWidth="1"/>
+    <col min="12" max="13" width="24.6640625" customWidth="1"/>
+    <col min="14" max="14" width="40.6640625" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="16" width="22.6640625" customWidth="1"/>
+    <col min="17" max="17" width="36.6640625" customWidth="1"/>
+    <col min="18" max="18" width="60.6640625" customWidth="1"/>
+    <col min="19" max="19" width="36.6640625" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" customWidth="1"/>
+    <col min="21" max="21" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3948,10 +3945,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3966,10 +3963,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>821</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>7</v>
@@ -4002,7 +3999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -4061,7 +4058,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -4120,7 +4117,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
@@ -4153,7 +4150,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -4186,7 +4183,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -4219,7 +4216,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -4278,7 +4275,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
@@ -4337,7 +4334,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
@@ -4396,7 +4393,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -4455,7 +4452,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
@@ -4514,7 +4511,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
@@ -4573,7 +4570,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
@@ -4632,7 +4629,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>106</v>
       </c>
@@ -4691,7 +4688,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -4718,43 +4715,43 @@
         <v>619</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -4781,43 +4778,43 @@
         <v>96</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="L16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
@@ -4844,43 +4841,43 @@
         <v>168</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
@@ -4907,43 +4904,43 @@
         <v>620</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
@@ -4970,43 +4967,43 @@
         <v>622</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
@@ -5033,43 +5030,43 @@
         <v>624</v>
       </c>
       <c r="J20" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -5096,43 +5093,43 @@
         <v>626</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>838</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
@@ -5159,43 +5156,43 @@
         <v>627</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -5222,43 +5219,43 @@
         <v>626</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
@@ -5285,43 +5282,43 @@
         <v>628</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>846</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
@@ -5348,43 +5345,43 @@
         <v>630</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="L25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>22</v>
       </c>
@@ -5411,43 +5408,43 @@
         <v>632</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
@@ -5474,43 +5471,43 @@
         <v>634</v>
       </c>
       <c r="J27" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>22</v>
       </c>
@@ -5537,43 +5534,43 @@
         <v>636</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
@@ -5600,43 +5597,43 @@
         <v>637</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
@@ -5663,43 +5660,43 @@
         <v>639</v>
       </c>
       <c r="J30" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U30" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="L30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>22</v>
       </c>
@@ -5726,43 +5723,43 @@
         <v>640</v>
       </c>
       <c r="J31" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>863</v>
       </c>
-      <c r="K31" s="3" t="s">
-        <v>861</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>22</v>
       </c>
@@ -5789,43 +5786,43 @@
         <v>629</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>22</v>
       </c>
@@ -5852,43 +5849,43 @@
         <v>641</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>22</v>
       </c>
@@ -5915,43 +5912,43 @@
         <v>642</v>
       </c>
       <c r="J34" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="L34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>22</v>
       </c>
@@ -5978,43 +5975,43 @@
         <v>644</v>
       </c>
       <c r="J35" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="L35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>22</v>
       </c>
@@ -6041,43 +6038,43 @@
         <v>646</v>
       </c>
       <c r="J36" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="L36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>22</v>
       </c>
@@ -6104,43 +6101,43 @@
         <v>178</v>
       </c>
       <c r="J37" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U37" s="3" t="s">
         <v>878</v>
       </c>
-      <c r="K37" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>22</v>
       </c>
@@ -6167,43 +6164,43 @@
         <v>649</v>
       </c>
       <c r="J38" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U38" s="3" t="s">
         <v>880</v>
       </c>
-      <c r="K38" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="T38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>22</v>
       </c>
@@ -6230,43 +6227,43 @@
         <v>650</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="L39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U39" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="L39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>22</v>
       </c>
@@ -6293,43 +6290,43 @@
         <v>644</v>
       </c>
       <c r="J40" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="L40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="L40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>22</v>
       </c>
@@ -6356,43 +6353,43 @@
         <v>648</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K41" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U41" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
@@ -6419,43 +6416,43 @@
         <v>653</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>22</v>
       </c>
@@ -6482,43 +6479,43 @@
         <v>654</v>
       </c>
       <c r="J43" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>892</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>22</v>
       </c>
@@ -6545,43 +6542,43 @@
         <v>655</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>22</v>
       </c>
@@ -6608,10 +6605,10 @@
         <v>625</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>20</v>
@@ -6635,16 +6632,16 @@
         <v>20</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>22</v>
       </c>
@@ -6671,10 +6668,10 @@
         <v>655</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>20</v>
@@ -6698,16 +6695,16 @@
         <v>20</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>223</v>
       </c>
@@ -6734,43 +6731,43 @@
         <v>652</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>75</v>
       </c>
@@ -6831,7 +6828,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>75</v>
       </c>
@@ -6893,7 +6890,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>75</v>
       </c>
@@ -6955,7 +6952,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>75</v>
       </c>
@@ -7017,7 +7014,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>75</v>
       </c>
@@ -7079,7 +7076,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>75</v>
       </c>
@@ -7141,7 +7138,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>75</v>
       </c>
@@ -7203,7 +7200,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>75</v>
       </c>
@@ -7265,7 +7262,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>75</v>
       </c>
@@ -7327,7 +7324,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>75</v>
       </c>
@@ -7389,7 +7386,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>75</v>
       </c>
@@ -7451,7 +7448,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>75</v>
       </c>
@@ -7513,7 +7510,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>75</v>
       </c>
@@ -7575,7 +7572,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>75</v>
       </c>
@@ -7637,7 +7634,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>75</v>
       </c>
@@ -7699,7 +7696,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>75</v>
       </c>
@@ -7761,7 +7758,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>75</v>
       </c>
@@ -7823,7 +7820,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>75</v>
       </c>
@@ -7885,7 +7882,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>75</v>
       </c>
@@ -7947,7 +7944,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>75</v>
       </c>
@@ -8009,7 +8006,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>75</v>
       </c>
@@ -8071,7 +8068,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>75</v>
       </c>
@@ -8133,7 +8130,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>75</v>
       </c>
@@ -8195,7 +8192,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>75</v>
       </c>
@@ -8257,7 +8254,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>75</v>
       </c>
@@ -8319,7 +8316,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>75</v>
       </c>
@@ -8381,7 +8378,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>75</v>
       </c>
@@ -8443,7 +8440,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>75</v>
       </c>
@@ -8505,7 +8502,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>75</v>
       </c>
@@ -8567,7 +8564,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>75</v>
       </c>
@@ -8629,7 +8626,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>75</v>
       </c>
@@ -8691,7 +8688,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>75</v>
       </c>
@@ -8753,7 +8750,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>75</v>
       </c>
@@ -8815,7 +8812,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>75</v>
       </c>
@@ -8877,7 +8874,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>75</v>
       </c>
@@ -8939,7 +8936,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>75</v>
       </c>
@@ -9001,7 +8998,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>75</v>
       </c>
@@ -9063,7 +9060,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>75</v>
       </c>
@@ -9125,7 +9122,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>75</v>
       </c>
@@ -9187,7 +9184,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>75</v>
       </c>
@@ -9249,7 +9246,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>75</v>
       </c>
@@ -9311,7 +9308,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>75</v>
       </c>
@@ -9373,7 +9370,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>75</v>
       </c>
@@ -9435,7 +9432,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>75</v>
       </c>
@@ -9497,7 +9494,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>75</v>
       </c>
@@ -9559,7 +9556,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>75</v>
       </c>
@@ -9621,7 +9618,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>75</v>
       </c>
@@ -9683,7 +9680,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>75</v>
       </c>
@@ -9745,7 +9742,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>75</v>
       </c>
@@ -9807,7 +9804,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>75</v>
       </c>
@@ -9869,7 +9866,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>75</v>
       </c>
@@ -9931,7 +9928,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>75</v>
       </c>
@@ -9993,7 +9990,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>75</v>
       </c>
@@ -10055,7 +10052,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>75</v>
       </c>
@@ -10117,7 +10114,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>75</v>
       </c>
@@ -10176,10 +10173,10 @@
         <v>20</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
         <v>545</v>
       </c>
@@ -10203,7 +10200,7 @@
         <v>32</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="P103" s="5" t="s">
         <v>546</v>
@@ -10215,10 +10212,10 @@
         <v>34</v>
       </c>
       <c r="U103" s="5" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
         <v>545</v>
       </c>
@@ -10242,7 +10239,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="P104" s="5" t="s">
         <v>548</v>
@@ -10254,10 +10251,10 @@
         <v>37</v>
       </c>
       <c r="U104" s="5" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
         <v>545</v>
       </c>
@@ -10281,7 +10278,7 @@
         <v>24</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P105" s="5" t="s">
         <v>550</v>
@@ -10296,10 +10293,10 @@
         <v>42</v>
       </c>
       <c r="U105" s="5" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>545</v>
       </c>
@@ -10323,7 +10320,7 @@
         <v>46</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="P106" s="5" t="s">
         <v>551</v>
@@ -10335,10 +10332,10 @@
         <v>48</v>
       </c>
       <c r="U106" s="5" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
         <v>545</v>
       </c>
@@ -10362,7 +10359,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="P107" s="5" t="s">
         <v>555</v>
@@ -10377,10 +10374,10 @@
         <v>558</v>
       </c>
       <c r="U107" s="5" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
         <v>545</v>
       </c>
@@ -10404,7 +10401,7 @@
         <v>28</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="P108" s="5" t="s">
         <v>562</v>
@@ -10419,10 +10416,10 @@
         <v>565</v>
       </c>
       <c r="U108" s="5" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
         <v>545</v>
       </c>
@@ -10446,7 +10443,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O109" s="5" t="s">
         <v>569</v>
@@ -10464,10 +10461,10 @@
         <v>573</v>
       </c>
       <c r="U109" s="5" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>545</v>
       </c>
@@ -10491,7 +10488,7 @@
         <v>23</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="P110" s="5" t="s">
         <v>577</v>
@@ -10506,10 +10503,10 @@
         <v>580</v>
       </c>
       <c r="U110" s="5" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
         <v>545</v>
       </c>
@@ -10533,7 +10530,7 @@
         <v>23</v>
       </c>
       <c r="N111" s="5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P111" s="5" t="s">
         <v>584</v>
@@ -10548,10 +10545,10 @@
         <v>587</v>
       </c>
       <c r="U111" s="5" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
         <v>545</v>
       </c>
@@ -10575,7 +10572,7 @@
         <v>25</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="P112" s="5" t="s">
         <v>591</v>
@@ -10590,7 +10587,7 @@
         <v>594</v>
       </c>
       <c r="U112" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -10603,254 +10600,254 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="125.625" customWidth="1"/>
+    <col min="1" max="1" width="125.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\.codex\visualizations\2026\10\19\01a154b8-8fd9-7253-8f40-4499a22fa170\earthguard-task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D2C13E-C7DE-4829-B475-94B78A0ACD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99158D9C-8524-41D6-9123-1A6E5C2CB5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
@@ -406,10 +406,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>4.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>進度（地圖序號＋關卡比例）每 +1 對應的最高掉落階增量（解鎖速度，不影響稀有度）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3487,6 +3483,10 @@
   </si>
   <si>
     <t>屬性：生命值×1.5、全局減傷×0.9、全屬性抗性×0.9｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3945,10 +3945,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3963,10 +3963,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>820</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>7</v>
@@ -4055,7 +4055,7 @@
         <v>76</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -4114,7 +4114,7 @@
         <v>92</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -4122,10 +4122,10 @@
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>607</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="6"/>
@@ -4144,10 +4144,10 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>609</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -4155,10 +4155,10 @@
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>612</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="6"/>
@@ -4180,7 +4180,7 @@
         <v>21</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -4188,10 +4188,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>615</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="6"/>
@@ -4210,10 +4210,10 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -4682,10 +4682,10 @@
         <v>20</v>
       </c>
       <c r="T14" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
@@ -4693,62 +4693,62 @@
         <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="D15" s="9">
         <v>1</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J15" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
@@ -4756,62 +4756,62 @@
         <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="D16" s="9">
         <v>2</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>92</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>96</v>
       </c>
       <c r="J16" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>825</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.3">
@@ -4819,62 +4819,62 @@
         <v>22</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="D17" s="9">
         <v>3</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="I17" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>827</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>828</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
@@ -4882,62 +4882,62 @@
         <v>22</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="D18" s="9">
         <v>4</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="J18" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>831</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
@@ -4945,62 +4945,62 @@
         <v>22</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="D19" s="9">
         <v>5</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="H19" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>622</v>
-      </c>
       <c r="J19" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>833</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
@@ -5008,62 +5008,62 @@
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D20" s="9">
         <v>6</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>624</v>
-      </c>
       <c r="J20" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>835</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.3">
@@ -5071,62 +5071,62 @@
         <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="D21" s="9">
         <v>7</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>626</v>
-      </c>
       <c r="J21" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>837</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.3">
@@ -5134,62 +5134,62 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D22" s="9">
         <v>8</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
@@ -5197,62 +5197,62 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="D23" s="9">
         <v>9</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="H23" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>626</v>
-      </c>
       <c r="J23" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.3">
@@ -5260,62 +5260,62 @@
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D24" s="9">
         <v>10</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="I24" s="3" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>845</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.3">
@@ -5323,62 +5323,62 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D25" s="9">
         <v>11</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="H25" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="J25" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>848</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="T25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
@@ -5386,62 +5386,62 @@
         <v>22</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>155</v>
       </c>
       <c r="D26" s="9">
         <v>12</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>632</v>
-      </c>
       <c r="J26" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>850</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>851</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.3">
@@ -5449,62 +5449,62 @@
         <v>22</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D27" s="9">
         <v>13</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>634</v>
-      </c>
       <c r="J27" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>853</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.3">
@@ -5512,62 +5512,62 @@
         <v>22</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D28" s="9">
         <v>14</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="J28" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>855</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>848</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
@@ -5575,62 +5575,62 @@
         <v>22</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="D29" s="9">
         <v>15</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J29" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>857</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
@@ -5638,62 +5638,62 @@
         <v>22</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="D30" s="9">
         <v>16</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>639</v>
-      </c>
       <c r="J30" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>859</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="L30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U30" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="T30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
@@ -5701,62 +5701,62 @@
         <v>22</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="D31" s="9">
         <v>17</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H31" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="I31" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J31" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="T31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>862</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="T31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
@@ -5764,62 +5764,62 @@
         <v>22</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>180</v>
       </c>
       <c r="D32" s="9">
         <v>18</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="I32" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="J32" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>864</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.3">
@@ -5827,62 +5827,62 @@
         <v>22</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="D33" s="9">
         <v>19</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J33" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.3">
@@ -5890,62 +5890,62 @@
         <v>22</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>187</v>
       </c>
       <c r="D34" s="9">
         <v>20</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="I34" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>642</v>
-      </c>
       <c r="J34" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="K34" s="3" t="s">
+      <c r="L34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="T34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>869</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
@@ -5953,62 +5953,62 @@
         <v>22</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D35" s="9">
         <v>21</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="I35" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>644</v>
-      </c>
       <c r="J35" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="K35" s="3" t="s">
+      <c r="L35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>872</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.3">
@@ -6016,62 +6016,62 @@
         <v>22</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="D36" s="9">
         <v>22</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G36" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>646</v>
-      </c>
       <c r="J36" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>874</v>
       </c>
-      <c r="K36" s="3" t="s">
+      <c r="L36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.3">
@@ -6079,62 +6079,62 @@
         <v>22</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="D37" s="9">
         <v>23</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J37" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U37" s="3" t="s">
         <v>877</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="T37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.3">
@@ -6142,62 +6142,62 @@
         <v>22</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>201</v>
       </c>
       <c r="D38" s="9">
         <v>24</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G38" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>649</v>
-      </c>
       <c r="J38" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U38" s="3" t="s">
         <v>879</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="T38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.3">
@@ -6205,62 +6205,62 @@
         <v>22</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="D39" s="9">
         <v>25</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J39" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="K39" s="3" t="s">
+      <c r="L39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U39" s="3" t="s">
         <v>882</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.3">
@@ -6268,62 +6268,62 @@
         <v>22</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>207</v>
       </c>
       <c r="D40" s="9">
         <v>26</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="I40" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="J40" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="L40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>885</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="T40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.3">
@@ -6331,62 +6331,62 @@
         <v>22</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D41" s="9">
         <v>27</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K41" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U41" s="3" t="s">
         <v>887</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
@@ -6394,62 +6394,62 @@
         <v>22</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>213</v>
       </c>
       <c r="D42" s="9">
         <v>28</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="J42" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>889</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.3">
@@ -6457,62 +6457,62 @@
         <v>22</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="D43" s="9">
         <v>29</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="I43" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J43" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>891</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.3">
@@ -6520,62 +6520,62 @@
         <v>22</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="D44" s="9">
         <v>30</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="I44" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>893</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.3">
@@ -6583,32 +6583,32 @@
         <v>22</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="D45" s="9">
         <v>31</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>20</v>
@@ -6632,13 +6632,13 @@
         <v>20</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.3">
@@ -6646,32 +6646,32 @@
         <v>22</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="D46" s="9">
         <v>32</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>20</v>
@@ -6695,76 +6695,76 @@
         <v>20</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="D47" s="9">
         <v>33</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J47" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>897</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.3">
@@ -6772,10 +6772,10 @@
         <v>75</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="D48" s="9">
         <v>1</v>
@@ -6798,34 +6798,34 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="N48" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S48" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="T48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
@@ -6833,10 +6833,10 @@
         <v>75</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -6860,34 +6860,34 @@
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="N49" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S49" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="N49" s="3" t="s">
+      <c r="T49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>661</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
@@ -6895,10 +6895,10 @@
         <v>75</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="D50" s="9">
         <v>1</v>
@@ -6922,34 +6922,34 @@
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="M50" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="M50" s="3" t="s">
+      <c r="N50" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="N50" s="3" t="s">
+      <c r="S50" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>663</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R50" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="T50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
@@ -6957,10 +6957,10 @@
         <v>75</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="D51" s="9">
         <v>1</v>
@@ -6984,34 +6984,34 @@
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="M51" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="M51" s="3" t="s">
+      <c r="N51" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S51" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="N51" s="3" t="s">
+      <c r="T51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="T51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
@@ -7019,10 +7019,10 @@
         <v>75</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D52" s="9">
         <v>1</v>
@@ -7046,34 +7046,34 @@
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="N52" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="O52" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="N52" s="3" t="s">
+      <c r="P52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
@@ -7081,10 +7081,10 @@
         <v>75</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="D53" s="9">
         <v>1</v>
@@ -7108,34 +7108,34 @@
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="M53" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="N53" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="N53" s="3" t="s">
+      <c r="S53" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="T53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>669</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R53" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="T53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
@@ -7143,10 +7143,10 @@
         <v>75</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="D54" s="9">
         <v>1</v>
@@ -7170,34 +7170,34 @@
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="N54" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R54" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="N54" s="3" t="s">
+      <c r="S54" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
@@ -7205,10 +7205,10 @@
         <v>75</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="D55" s="9">
         <v>1</v>
@@ -7232,34 +7232,34 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="M55" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="M55" s="3" t="s">
+      <c r="N55" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="N55" s="3" t="s">
+      <c r="R55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="T55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="O55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q55" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="R55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="T55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.3">
@@ -7267,10 +7267,10 @@
         <v>75</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>272</v>
       </c>
       <c r="D56" s="9">
         <v>1</v>
@@ -7294,34 +7294,34 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="M56" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="M56" s="3" t="s">
+      <c r="N56" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="N56" s="3" t="s">
+      <c r="R56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U56" s="3" t="s">
         <v>675</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q56" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="T56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U56" s="3" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.3">
@@ -7329,10 +7329,10 @@
         <v>75</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>277</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>278</v>
       </c>
       <c r="D57" s="9">
         <v>1</v>
@@ -7356,34 +7356,34 @@
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="M57" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="M57" s="3" t="s">
+      <c r="N57" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S57" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="N57" s="3" t="s">
+      <c r="T57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U57" s="3" t="s">
         <v>677</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.3">
@@ -7391,10 +7391,10 @@
         <v>75</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="D58" s="9">
         <v>1</v>
@@ -7418,34 +7418,34 @@
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="N58" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="N58" s="3" t="s">
+      <c r="R58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U58" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.3">
@@ -7453,10 +7453,10 @@
         <v>75</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="D59" s="9">
         <v>1</v>
@@ -7480,34 +7480,34 @@
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="M59" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="N59" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="N59" s="3" t="s">
+      <c r="R59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U59" s="3" t="s">
         <v>681</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.3">
@@ -7515,10 +7515,10 @@
         <v>75</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="D60" s="9">
         <v>1</v>
@@ -7542,34 +7542,34 @@
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="M60" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="N60" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S60" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="N60" s="3" t="s">
+      <c r="T60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U60" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U60" s="3" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.3">
@@ -7577,10 +7577,10 @@
         <v>75</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="D61" s="9">
         <v>1</v>
@@ -7604,34 +7604,34 @@
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R61" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="M61" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="N61" s="3" t="s">
+      <c r="S61" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U61" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="O61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R61" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="S61" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="T61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U61" s="3" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.3">
@@ -7639,10 +7639,10 @@
         <v>75</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="D62" s="9">
         <v>2</v>
@@ -7666,34 +7666,34 @@
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q62" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="N62" s="3" t="s">
+      <c r="R62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>687</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.3">
@@ -7701,10 +7701,10 @@
         <v>75</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -7728,34 +7728,34 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R63" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="M63" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N63" s="3" t="s">
+      <c r="S63" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U63" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="O63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R63" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="S63" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="T63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U63" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.3">
@@ -7763,10 +7763,10 @@
         <v>75</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="D64" s="9">
         <v>2</v>
@@ -7790,34 +7790,34 @@
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="M64" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="N64" s="3" t="s">
+      <c r="R64" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="T64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U64" s="3" t="s">
         <v>691</v>
-      </c>
-      <c r="O64" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q64" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="R64" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="T64" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U64" s="3" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.3">
@@ -7825,10 +7825,10 @@
         <v>75</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="D65" s="9">
         <v>2</v>
@@ -7852,34 +7852,34 @@
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="M65" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N65" s="3" t="s">
+      <c r="R65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U65" s="3" t="s">
         <v>693</v>
-      </c>
-      <c r="O65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q65" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="R65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S65" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="T65" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U65" s="3" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>75</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="D66" s="9">
         <v>2</v>
@@ -7914,34 +7914,34 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="N66" s="3" t="s">
+      <c r="R66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U66" s="3" t="s">
         <v>695</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U66" s="3" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.3">
@@ -7949,10 +7949,10 @@
         <v>75</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>331</v>
       </c>
       <c r="D67" s="9">
         <v>2</v>
@@ -7976,34 +7976,34 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="M67" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="M67" s="3" t="s">
+      <c r="N67" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="N67" s="3" t="s">
+      <c r="S67" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U67" s="3" t="s">
         <v>697</v>
-      </c>
-      <c r="O67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R67" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="S67" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="T67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U67" s="3" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.3">
@@ -8011,10 +8011,10 @@
         <v>75</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="D68" s="9">
         <v>2</v>
@@ -8038,34 +8038,34 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R68" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="M68" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="N68" s="3" t="s">
+      <c r="S68" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U68" s="3" t="s">
         <v>699</v>
-      </c>
-      <c r="O68" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q68" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R68" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="T68" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U68" s="3" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.3">
@@ -8073,10 +8073,10 @@
         <v>75</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="D69" s="9">
         <v>2</v>
@@ -8100,34 +8100,34 @@
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R69" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="M69" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="N69" s="3" t="s">
+      <c r="S69" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="T69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U69" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="O69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R69" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="T69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U69" s="3" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.3">
@@ -8135,10 +8135,10 @@
         <v>75</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D70" s="9">
         <v>2</v>
@@ -8162,34 +8162,34 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="M70" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="M70" s="3" t="s">
+      <c r="N70" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="N70" s="3" t="s">
+      <c r="S70" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U70" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="O70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R70" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="T70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U70" s="3" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.3">
@@ -8197,10 +8197,10 @@
         <v>75</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="D71" s="9">
         <v>2</v>
@@ -8224,34 +8224,34 @@
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="M71" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="M71" s="3" t="s">
+      <c r="N71" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="O71" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="N71" s="3" t="s">
+      <c r="P71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R71" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="T71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U71" s="3" t="s">
         <v>705</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q71" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R71" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="T71" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U71" s="3" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.3">
@@ -8259,10 +8259,10 @@
         <v>75</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="D72" s="9">
         <v>2</v>
@@ -8286,34 +8286,34 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="N72" s="3" t="s">
+      <c r="R72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U72" s="3" t="s">
         <v>707</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.3">
@@ -8321,10 +8321,10 @@
         <v>75</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="D73" s="9">
         <v>2</v>
@@ -8348,34 +8348,34 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="M73" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="M73" s="3" t="s">
+      <c r="N73" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R73" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="N73" s="3" t="s">
+      <c r="S73" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U73" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="O73" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q73" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R73" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="T73" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U73" s="3" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.3">
@@ -8383,10 +8383,10 @@
         <v>75</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="D74" s="9">
         <v>2</v>
@@ -8410,34 +8410,34 @@
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="M74" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="M74" s="3" t="s">
+      <c r="N74" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R74" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="N74" s="3" t="s">
+      <c r="S74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="T74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U74" s="3" t="s">
         <v>711</v>
-      </c>
-      <c r="O74" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q74" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R74" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="S74" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="T74" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U74" s="3" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.3">
@@ -8445,10 +8445,10 @@
         <v>75</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>376</v>
       </c>
       <c r="D75" s="9">
         <v>2</v>
@@ -8472,34 +8472,34 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="M75" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="N75" s="3" t="s">
+      <c r="T75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U75" s="3" t="s">
         <v>713</v>
-      </c>
-      <c r="O75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="T75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U75" s="3" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.3">
@@ -8507,10 +8507,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>380</v>
       </c>
       <c r="D76" s="9">
         <v>3</v>
@@ -8534,34 +8534,34 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N76" s="3" t="s">
+      <c r="R76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U76" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.3">
@@ -8569,10 +8569,10 @@
         <v>75</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="D77" s="9">
         <v>3</v>
@@ -8596,34 +8596,34 @@
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="M77" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N77" s="3" t="s">
+      <c r="R77" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="T77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U77" s="3" t="s">
         <v>717</v>
-      </c>
-      <c r="O77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q77" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="R77" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="S77" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="T77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U77" s="3" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.3">
@@ -8631,10 +8631,10 @@
         <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>391</v>
       </c>
       <c r="D78" s="9">
         <v>3</v>
@@ -8658,34 +8658,34 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R78" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="M78" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="N78" s="3" t="s">
+      <c r="S78" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U78" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="O78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R78" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="S78" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="T78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U78" s="3" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.3">
@@ -8693,10 +8693,10 @@
         <v>75</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="D79" s="9">
         <v>3</v>
@@ -8720,34 +8720,34 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="M79" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="N79" s="3" t="s">
+      <c r="R79" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="S79" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U79" s="3" t="s">
         <v>721</v>
-      </c>
-      <c r="O79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q79" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="R79" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="S79" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="T79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U79" s="3" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.3">
@@ -8755,10 +8755,10 @@
         <v>75</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="D80" s="9">
         <v>3</v>
@@ -8782,34 +8782,34 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R80" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="M80" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="N80" s="3" t="s">
+      <c r="S80" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="T80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U80" s="3" t="s">
         <v>723</v>
-      </c>
-      <c r="O80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R80" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="S80" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="T80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U80" s="3" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.3">
@@ -8817,10 +8817,10 @@
         <v>75</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="D81" s="9">
         <v>3</v>
@@ -8844,34 +8844,34 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N81" s="3" t="s">
+      <c r="R81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U81" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.3">
@@ -8879,10 +8879,10 @@
         <v>75</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="D82" s="9">
         <v>3</v>
@@ -8906,34 +8906,34 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="M82" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="M82" s="3" t="s">
+      <c r="N82" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P82" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="N82" s="3" t="s">
+      <c r="Q82" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="R82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S82" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="T82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U82" s="3" t="s">
         <v>727</v>
-      </c>
-      <c r="O82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P82" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="Q82" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="R82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S82" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="T82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U82" s="3" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.3">
@@ -8941,10 +8941,10 @@
         <v>75</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>419</v>
       </c>
       <c r="D83" s="9">
         <v>3</v>
@@ -8968,34 +8968,34 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q83" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="R83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U83" s="3" t="s">
         <v>729</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.3">
@@ -9003,10 +9003,10 @@
         <v>75</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="D84" s="9">
         <v>3</v>
@@ -9030,34 +9030,34 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="M84" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="M84" s="3" t="s">
+      <c r="N84" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="O84" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="N84" s="3" t="s">
+      <c r="P84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R84" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U84" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="O84" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="P84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R84" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="S84" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="T84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U84" s="3" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.3">
@@ -9065,10 +9065,10 @@
         <v>75</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="D85" s="9">
         <v>3</v>
@@ -9092,34 +9092,34 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q85" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="M85" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N85" s="3" t="s">
+      <c r="R85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S85" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="T85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U85" s="3" t="s">
         <v>733</v>
-      </c>
-      <c r="O85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q85" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="R85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S85" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="T85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U85" s="3" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.3">
@@ -9127,10 +9127,10 @@
         <v>75</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>437</v>
       </c>
       <c r="D86" s="9">
         <v>3</v>
@@ -9154,34 +9154,34 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q86" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="M86" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="N86" s="3" t="s">
+      <c r="R86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="T86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U86" s="3" t="s">
         <v>735</v>
-      </c>
-      <c r="O86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q86" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="R86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S86" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="T86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U86" s="3" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.3">
@@ -9189,10 +9189,10 @@
         <v>75</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="D87" s="9">
         <v>3</v>
@@ -9216,34 +9216,34 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="M87" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="M87" s="3" t="s">
+      <c r="N87" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R87" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="N87" s="3" t="s">
+      <c r="S87" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="T87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U87" s="3" t="s">
         <v>737</v>
-      </c>
-      <c r="O87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R87" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="S87" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="T87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U87" s="3" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.3">
@@ -9251,10 +9251,10 @@
         <v>75</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="D88" s="9">
         <v>3</v>
@@ -9278,34 +9278,34 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="M88" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="N88" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="O88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q88" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="M88" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="N88" s="3" t="s">
+      <c r="R88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S88" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="T88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U88" s="3" t="s">
         <v>739</v>
-      </c>
-      <c r="O88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q88" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="R88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S88" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="T88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U88" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.3">
@@ -9313,10 +9313,10 @@
         <v>75</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>452</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>453</v>
       </c>
       <c r="D89" s="9">
         <v>3</v>
@@ -9340,34 +9340,34 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q89" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N89" s="3" t="s">
+      <c r="R89" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U89" s="3" t="s">
         <v>741</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.3">
@@ -9375,10 +9375,10 @@
         <v>75</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>459</v>
       </c>
       <c r="D90" s="9">
         <v>4</v>
@@ -9402,34 +9402,34 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="M90" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="N90" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="O90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P90" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="M90" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N90" s="3" t="s">
+      <c r="Q90" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="R90" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="S90" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="T90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U90" s="3" t="s">
         <v>743</v>
-      </c>
-      <c r="O90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="Q90" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="R90" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="S90" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="T90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U90" s="3" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.3">
@@ -9437,10 +9437,10 @@
         <v>75</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="D91" s="9">
         <v>4</v>
@@ -9464,34 +9464,34 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P91" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N91" s="3" t="s">
+      <c r="Q91" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U91" s="3" t="s">
         <v>745</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.3">
@@ -9499,10 +9499,10 @@
         <v>75</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>473</v>
       </c>
       <c r="D92" s="9">
         <v>4</v>
@@ -9526,34 +9526,34 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="M92" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="N92" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="O92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P92" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="M92" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N92" s="3" t="s">
+      <c r="Q92" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="R92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S92" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="T92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U92" s="3" t="s">
         <v>747</v>
-      </c>
-      <c r="O92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q92" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="R92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S92" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="T92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U92" s="3" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.3">
@@ -9561,10 +9561,10 @@
         <v>75</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D93" s="9">
         <v>4</v>
@@ -9588,34 +9588,34 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="M93" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="N93" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="O93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P93" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="M93" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="N93" s="3" t="s">
+      <c r="Q93" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="R93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S93" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="T93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U93" s="3" t="s">
         <v>749</v>
-      </c>
-      <c r="O93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q93" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="R93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S93" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="T93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U93" s="3" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.3">
@@ -9623,10 +9623,10 @@
         <v>75</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>484</v>
       </c>
       <c r="D94" s="9">
         <v>4</v>
@@ -9650,34 +9650,34 @@
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P94" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="N94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U94" s="3" t="s">
         <v>751</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.3">
@@ -9685,10 +9685,10 @@
         <v>75</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="D95" s="9">
         <v>4</v>
@@ -9712,34 +9712,34 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="M95" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N95" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P95" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="M95" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N95" s="3" t="s">
+      <c r="Q95" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="R95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S95" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="T95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U95" s="3" t="s">
         <v>753</v>
-      </c>
-      <c r="O95" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q95" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="R95" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S95" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="T95" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U95" s="3" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.3">
@@ -9747,10 +9747,10 @@
         <v>75</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="D96" s="9">
         <v>4</v>
@@ -9774,34 +9774,34 @@
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P96" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N96" s="3" t="s">
+      <c r="Q96" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="R96" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="T96" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U96" s="3" t="s">
         <v>755</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="Q96" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="R96" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="S96" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="T96" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U96" s="3" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.3">
@@ -9809,10 +9809,10 @@
         <v>75</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>503</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="D97" s="9">
         <v>4</v>
@@ -9836,34 +9836,34 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="M97" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="N97" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="O97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P97" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="M97" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="N97" s="3" t="s">
+      <c r="Q97" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="R97" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="S97" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="T97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U97" s="3" t="s">
         <v>757</v>
-      </c>
-      <c r="O97" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P97" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="Q97" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="R97" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="S97" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="T97" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U97" s="3" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.3">
@@ -9871,10 +9871,10 @@
         <v>75</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="D98" s="9">
         <v>4</v>
@@ -9898,34 +9898,34 @@
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="M98" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="O98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P98" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="M98" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N98" s="3" t="s">
+      <c r="Q98" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="R98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S98" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="T98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U98" s="3" t="s">
         <v>759</v>
-      </c>
-      <c r="O98" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P98" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="Q98" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="R98" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S98" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="T98" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U98" s="3" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.3">
@@ -9933,10 +9933,10 @@
         <v>75</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>517</v>
       </c>
       <c r="D99" s="9">
         <v>4</v>
@@ -9960,34 +9960,34 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="M99" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="M99" s="3" t="s">
+      <c r="N99" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="O99" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P99" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="N99" s="3" t="s">
+      <c r="Q99" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R99" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="S99" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="T99" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U99" s="3" t="s">
         <v>761</v>
-      </c>
-      <c r="O99" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q99" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R99" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="S99" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="T99" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U99" s="3" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.3">
@@ -9995,10 +9995,10 @@
         <v>75</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="D100" s="9">
         <v>4</v>
@@ -10022,34 +10022,34 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
       <c r="L100" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P100" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="N100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U100" s="3" t="s">
         <v>763</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.3">
@@ -10057,10 +10057,10 @@
         <v>75</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="D101" s="9">
         <v>4</v>
@@ -10084,34 +10084,34 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P101" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U101" s="3" t="s">
         <v>765</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.3">
@@ -10119,10 +10119,10 @@
         <v>75</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="D102" s="9">
         <v>4</v>
@@ -10146,39 +10146,39 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="M102" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="M102" s="3" t="s">
+      <c r="N102" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P102" s="3" t="s">
+      <c r="Q102" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="Q102" s="3" t="s">
+      <c r="R102" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="R102" s="3" t="s">
+      <c r="S102" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>544</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>29</v>
@@ -10200,10 +10200,10 @@
         <v>32</v>
       </c>
       <c r="N103" s="5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P103" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q103" s="5" t="s">
         <v>33</v>
@@ -10212,12 +10212,12 @@
         <v>34</v>
       </c>
       <c r="U103" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>35</v>
@@ -10233,16 +10233,16 @@
         <v>117</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="M104" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="P104" s="5" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q104" s="5" t="s">
         <v>27</v>
@@ -10251,12 +10251,12 @@
         <v>37</v>
       </c>
       <c r="U104" s="5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>38</v>
@@ -10272,16 +10272,16 @@
         <v>119</v>
       </c>
       <c r="L105" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M105" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="P105" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q105" s="5" t="s">
         <v>40</v>
@@ -10293,12 +10293,12 @@
         <v>42</v>
       </c>
       <c r="U105" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>43</v>
@@ -10320,10 +10320,10 @@
         <v>46</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="P106" s="5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q106" s="5" t="s">
         <v>47</v>
@@ -10332,18 +10332,18 @@
         <v>48</v>
       </c>
       <c r="U106" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>552</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>553</v>
       </c>
       <c r="D107" s="10">
         <v>4</v>
@@ -10353,39 +10353,39 @@
         <v>123</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M107" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N107" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="P107" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q107" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="R107" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="S107" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="U107" s="5" t="s">
         <v>774</v>
-      </c>
-      <c r="P107" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="Q107" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="R107" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="S107" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="U107" s="5" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B108" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>560</v>
       </c>
       <c r="D108" s="10">
         <v>4</v>
@@ -10395,39 +10395,39 @@
         <v>125</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M108" s="5" t="s">
         <v>28</v>
       </c>
       <c r="N108" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="P108" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="Q108" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="R108" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="S108" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="U108" s="5" t="s">
         <v>776</v>
-      </c>
-      <c r="P108" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="Q108" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="R108" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="S108" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="U108" s="5" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>566</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>567</v>
       </c>
       <c r="D109" s="10">
         <v>4</v>
@@ -10437,42 +10437,42 @@
         <v>127</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="M109" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N109" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="O109" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="P109" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q109" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="R109" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="S109" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="U109" s="5" t="s">
         <v>778</v>
-      </c>
-      <c r="O109" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="P109" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="Q109" s="5" t="s">
-        <v>571</v>
-      </c>
-      <c r="R109" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="S109" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="U109" s="5" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>574</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>575</v>
       </c>
       <c r="D110" s="10">
         <v>4</v>
@@ -10482,39 +10482,39 @@
         <v>129</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="M110" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N110" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="P110" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="Q110" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="R110" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="S110" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="U110" s="5" t="s">
         <v>780</v>
-      </c>
-      <c r="P110" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="Q110" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="R110" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="S110" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="U110" s="5" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B111" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="D111" s="10">
         <v>4</v>
@@ -10524,39 +10524,39 @@
         <v>131</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="M111" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N111" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="P111" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="Q111" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="R111" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="S111" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="U111" s="5" t="s">
         <v>782</v>
-      </c>
-      <c r="P111" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="Q111" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="R111" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="S111" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="U111" s="5" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>589</v>
       </c>
       <c r="D112" s="10">
         <v>4</v>
@@ -10566,28 +10566,28 @@
         <v>133</v>
       </c>
       <c r="L112" s="5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="M112" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N112" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="P112" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q112" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="R112" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="S112" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="U112" s="5" t="s">
         <v>784</v>
-      </c>
-      <c r="P112" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="Q112" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="R112" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="S112" s="5" t="s">
-        <v>594</v>
-      </c>
-      <c r="U112" s="5" t="s">
-        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
@@ -10657,22 +10657,22 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
@@ -10682,7 +10682,7 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
@@ -10707,7 +10707,7 @@
     </row>
     <row r="21" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
@@ -10717,22 +10717,22 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
@@ -10742,17 +10742,17 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
@@ -10767,12 +10767,12 @@
     </row>
     <row r="33" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
@@ -10832,12 +10832,12 @@
     </row>
     <row r="46" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
@@ -10847,7 +10847,7 @@
     </row>
     <row r="49" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/Runes.xlsx
+++ b/config/Excel/Runes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99158D9C-8524-41D6-9123-1A6E5C2CB5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C4956B-68BF-4C99-886C-5321E3731EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
+    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{E2A3353D-3676-49BE-B9BC-70AD992698D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Runes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="905">
   <si>
     <t>類型</t>
   </si>
@@ -126,9 +126,6 @@
     <t>twoHand</t>
   </si>
   <si>
-    <t>aspdMult:15</t>
-  </si>
-  <si>
     <t>staff2h</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>greatsword2h;axe2h</t>
   </si>
   <si>
-    <t>splashPct:50;dmgPerFoePct:6</t>
-  </si>
-  <si>
     <t>一人成軍，一劍橫掃萬軍。</t>
   </si>
   <si>
@@ -165,12 +159,6 @@
     <t>虛空行者</t>
   </si>
   <si>
-    <t>dmgPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":30,"cd":4,"acts":[{"act":"invuln","sec":1.5},{"act":"dmg","pct":150,"elem":"dark","to":"all"}]}]</t>
-  </si>
-  <si>
     <t>走進虛空的人，被攻擊的永遠是上一個位置。</t>
   </si>
   <si>
@@ -186,9 +174,6 @@
     <t>any</t>
   </si>
   <si>
-    <t>dmgPct:50;cdPct:20;aspdMult:15;manaCostRedPct:30</t>
-  </si>
-  <si>
     <t>最後一顆符文落下時，世界從頭開始。</t>
   </si>
   <si>
@@ -970,10 +955,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>thorns:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>皮膚堅如岩層，觸碰者必受其傷。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -994,10 +975,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"hit","chance":15,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>毒蛇的一吻，慢慢收走對手的生命。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1018,10 +995,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":90,"elem":"lightning","to":"target"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一聲輕雷，落在不經意的地方。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1066,10 +1039,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>killHealPct:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>以血起誓，生者共飲。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1110,10 +1079,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>killManaPct:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>源源不絕，如山間清泉。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1134,10 +1099,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>runeFindPct:8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>連廢墟裡的一粒塵埃，也要翻過三遍。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1174,10 +1135,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"cast","chance":15,"acts":[{"act":"mana","pctMax":12}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>星火燎原，施法者的靈感湧現。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1194,10 +1151,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspdMult:8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>快過風的刃，連風聲都追不上。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1214,10 +1167,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"hit","chance":15,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>神怒所至，雷霆不擇敵我之外。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1234,10 +1183,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgCtrlPct:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","chance":20,"acts":[{"act":"stun","sec":1.5}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1258,10 +1203,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>killHealPct:3;dmgSelfLowPct:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>越是瀕死，越是渴血。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1322,10 +1263,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"tick","every":10,"acts":[{"act":"heal","pctMax":8},{"act":"mana","pctMax":8}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>戴上旭日，每一刻都是黎明。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1342,10 +1279,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"cast","chance":25,"acts":[{"act":"dot","pct":60,"sec":4,"name":"poison","to":"all"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>施法之後，毒霧久久不散。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1362,10 +1295,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":3,"max":3}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一聲春雷，萬蟲驚動。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1386,14 +1315,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>thorns:12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":20,"cd":3,"acts":[{"act":"dmg","pct":100,"type":"phys","to":"attacker"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>以鐵起誓，傷我者必以鐵還之。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1410,10 +1331,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>runeFindPct:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>全押。贏了拿走一切，輸了也不過一場好戲。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1434,10 +1351,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"block","chance":40,"acts":[{"act":"dmg","pct":200,"type":"phys","to":"attacker"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>盾不是為了後退，是為了把力量還給對方。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1458,10 +1371,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"cast","chance":20,"acts":[{"act":"cdr","sec":1.5}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>咒語落下之後，還在空氣裡迴盪。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1494,10 +1403,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgPct:18;aspdMult:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>號角響起，審判降臨。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1514,14 +1419,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgLoHpPct:60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":8,"acts":[{"act":"execute","hpBelow":15}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一刀兩斷，魂亦分離。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1538,10 +1435,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"crit","chance":30,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"all"}]},{"on":"cast","chance":25,"acts":[{"act":"dmg","pct":100,"elem":"lightning","to":"rand","n":3}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>雷與風相纏，一環扣一環。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1558,14 +1451,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cdPct:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"kill","acts":[{"act":"cdr","sec":1}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>守望者拾起墜落的時間，替你多留一點。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1582,10 +1467,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"lowhp","below":30,"cd":90,"acts":[{"act":"invuln","sec":3},{"act":"heal","pctMax":30},{"act":"cleanse"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>退無可退之處，才是真正的開始。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1602,10 +1483,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgPerFoePct:5;splashPct:20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>獸群越多，獵人越是興奮。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1654,10 +1531,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>manaCostRedPct:40;killManaPct:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>魔力不是用完的，是流過的。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1678,14 +1551,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>thorns:35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"hurt","chance":25,"cd":2,"acts":[{"act":"dmg","pct":150,"type":"phys","to":"all"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>怒意生出荊棘，連空氣都帶刺。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1702,10 +1567,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgHiHpPct:40;dmgSoloPct:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>王座再高，也有人要把它拆了。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1722,10 +1583,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>killHealPct:6;dmgSelfFullPct:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>契約的對價是活著，且活得很好。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1746,10 +1603,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"tick","every":8,"acts":[{"act":"shield","pctMax":20,"sec":8}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>牆起，風止。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1766,10 +1619,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgPct:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>五元素各執一角，在指尖上取得平衡。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1786,10 +1635,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspdMult:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","every":6,"acts":[{"act":"castRandom"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1814,14 +1659,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgHiHpPct:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":220,"type":"phys","to":"all"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>大地在刀下裂開，裂縫一路追著敵人。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1842,14 +1679,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>aspdMult:18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":12,"sec":4,"max":4}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>風暴中央最安靜，刀卻最快。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1870,10 +1699,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>killHealPct:8;dmgSelfLowPct:60;dmgPct:30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>以血為祭，戰場上的每一滴都算數。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1890,10 +1715,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>reviveHpPct:60;reviveCdSec:180;reviveInvulnSec:3;reviveDmgPct:60;reviveDmgSec:10;reviveRefresh:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡只是下一次輪迴的開場白。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1914,10 +1735,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cdPct:45;maxHpPct:-20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"cast","chance":25,"acts":[{"act":"recast"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1942,10 +1759,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgPct:60;selfDrainPct:2;killHealPct:8;maxHpPct:-30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>血月當空，誰先流盡誰先倒下。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1966,10 +1779,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skillDmgPct:40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"hit","every":4,"acts":[{"act":"castRandom"}]},{"on":"cast","chance":15,"acts":[{"act":"recast"}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1994,14 +1803,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgCtrlPct:10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":120,"elem":"lightning","to":"rand","n":3}]},{"on":"crit","acts":[{"act":"stun","sec":1,"to":"all"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>帝王不需親自出手，雷霆自會代勞。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2022,10 +1823,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgSoloPct:80;dmgHiHpPct:40;cdPct:15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>孤狼只獵王者。獵物以外，一概不理。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2050,10 +1847,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":150,"elem":"random","to":"rand","n":5}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>夜空翻面，群星墜落成雨。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2074,10 +1867,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>skillDmgPct:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>[{"on":"cast","acts":[{"act":"buffRandom","sec":8,"from":[{"sid":"atkUp","val":25},{"sid":"aspdUp","val":25},{"sid":"critDmgUp","val":60},{"sid":"defUp","val":40},{"sid":"evasionUp","val":30},{"sid":"allDmgUp","val":20}]}]}]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2102,14 +1891,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dmgHiHpPct:50;dmgPct:25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[{"on":"crit","chance":20,"acts":[{"act":"dmg","pct":250,"type":"phys","to":"target"}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>巨龍的鱗片，就是為了被一劍貫穿而生。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2138,10 +1919,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>[{"on":"lowhp","below":40,"cd":60,"acts":[{"act":"shield","pctMax":40,"sec":6},{"act":"invuln","sec":2}]}]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>以出手的力量，換不會倒下的身軀。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2179,12 +1956,6 @@
     <t>thunderorbFallCount</t>
   </si>
   <si>
-    <t>dmgPct:18;splashPct:15</t>
-  </si>
-  <si>
-    <t>[{"on":"crit","chance":10,"acts":[{"act":"dmg","pct":250,"type":"phys","to":"all"}]}]</t>
-  </si>
-  <si>
     <t>舉刀之時，終局已定。</t>
   </si>
   <si>
@@ -2200,9 +1971,6 @@
     <t>thunderstrikeRebirth</t>
   </si>
   <si>
-    <t>cdPct:25;skillDmgPct:40</t>
-  </si>
-  <si>
     <t>[{"on":"cast","chance":20,"acts":[{"act":"recast"}]}]</t>
   </si>
   <si>
@@ -2218,18 +1986,9 @@
     <t>蒼穹;冰魄;輪迴;混沌;終焉</t>
   </si>
   <si>
-    <t>smite:20</t>
-  </si>
-  <si>
     <t>firehuntHunter</t>
   </si>
   <si>
-    <t>dmgHiHpPct:40</t>
-  </si>
-  <si>
-    <t>[{"on":"crit","chance":15,"acts":[{"act":"dmg","pct":350,"elem":"light","to":"target"}]}]</t>
-  </si>
-  <si>
     <t>審判不問理由，只問罪行。</t>
   </si>
   <si>
@@ -2245,9 +2004,6 @@
     <t>frostnovaWinterFrost</t>
   </si>
   <si>
-    <t>dmgCtrlPct:45</t>
-  </si>
-  <si>
     <t>[{"on":"hit","chance":15,"acts":[{"act":"stun","sec":1.5}]}]</t>
   </si>
   <si>
@@ -2266,12 +2022,6 @@
     <t>icearrowDeepFreeze</t>
   </si>
   <si>
-    <t>dmgHiHpPct:40;dmgCtrlPct:20</t>
-  </si>
-  <si>
-    <t>[{"on":"crit","chance":25,"acts":[{"act":"dmg","pct":200,"elem":"ice","to":"target"}]}]</t>
-  </si>
-  <si>
     <t>冰川緩慢，但它走過的地方什麼都不剩。</t>
   </si>
   <si>
@@ -2287,12 +2037,6 @@
     <t>waterballTornado</t>
   </si>
   <si>
-    <t>killManaPct:4;manaCostRedPct:25</t>
-  </si>
-  <si>
-    <t>[{"on":"tick","every":6,"acts":[{"act":"heal","pctMax":6},{"act":"mana","pctMax":10}]}]</t>
-  </si>
-  <si>
     <t>潮來潮去，每一次都帶走疲憊、留下力量。</t>
   </si>
   <si>
@@ -2470,10 +2214,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.41</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2482,10 +2222,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.48</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2498,546 +2234,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.52</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.57</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.61</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.63</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.67</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkFlat:1;matkFlat:1;hit:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1、魔法攻擊×1、命中率×0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defFlat:1.25;hpFlat:1.25;hpRegen:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理防禦×1.25、生命值×1.25、生命恢復/秒×0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkFlat:1.25;elemDmgIce:0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.25、冰屬性傷害提升×0.75｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>evasion:1;hpFlat:1;hit:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×1、生命值×1、命中率×0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>defPct:0.75;hpPct:0.6;pRes:0.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理防禦×0.75、生命值×0.6、物理抗性×0.4｜反震 3%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.6;elemDmgPoison:0.75;critRate:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.6、毒屬性傷害提升×0.75、暴擊率×0.5｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 60% 攻擊力，4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:0.75;elemDmgLightning:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×0.75、雷屬性傷害提升×1｜普通攻擊命中時有 8% 機率：對目標造成 90% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mpFlat:1;resLight:0.75;hpPct:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力值×1、聖光抗性×0.75、生命值×0.5｜擊殺敵人時回復 1% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lifesteal:1;atkPct:0.5;hit:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：吸血×1、物理攻擊×0.5、命中率×0.5｜擊殺敵人時回復 1% 最大生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:0.75;defPct:0.75;tenacity:0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×0.75、物理防禦×0.75、韌性×0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mpRegen:1;hpRegen:1;mpFlat:0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力恢復/秒×1、生命恢復/秒×1、法力值×0.75｜擊殺敵人時回復 2% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goldBonus:1;xpBonus:0.75;loot:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：金幣加成×1、經驗加成×0.75、掉寶率×0.6｜符文掉落率 +8%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.6;critDmg:0.6;pPen:0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.6、暴擊傷害×0.6、物理穿透×0.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:0.75;elemDmgFire:0.75;mpFlat:0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×0.75、火屬性傷害提升×0.75、法力值×0.75｜施放技能時有 15% 機率：回復 12% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:1.08;critRate:0.65;atkPct:0.65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×1.08、暴擊率×0.65、物理攻擊×0.65｜攻擊速度額外乘算 +8%（突破攻速上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.65;elemDmgLightning:1.08;critDmg:0.65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.65、雷屬性傷害提升×1.08、暴擊傷害×0.65｜普通攻擊命中時有 15% 機率：對所有敵人造成 120% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:0.87;elemDmgIce:1.3;cdr:0.43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×0.87、冰屬性傷害提升×1.3、冷卻縮減×0.43｜對暈眩或緩速中的敵人傷害 +15%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lifesteal:1.3;atkPct:0.87;critRate:0.43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：吸血×1.3、物理攻擊×0.87、暴擊率×0.43｜擊殺敵人時回復 3% 最大生命；生命低於 35% 時，傷害 +25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.3;defPct:1.3;pRes:0.43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.3、物理防禦×1.3、物理抗性×0.43｜單次受到的傷害最多只會是最大生命的 40%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>evasion:1.52;hit:0.87;hpPct:0.65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×1.52、命中率×0.87、生命值×0.65｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:0.87;mpFlat:1.3;resAll:0.43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×0.87、法力值×1.3、全屬性抗性×0.43｜每 10 秒：回復 8% 最大生命，回復 8% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:0.87;elemDmgPoison:1.3;mPen:0.13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×0.87、毒屬性傷害提升×1.3、魔法穿透×0.13｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 60% 攻擊力，4 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:1.3;critRate:0.87;atkPct:0.65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×1.3、暴擊率×0.87、物理攻擊×0.65｜普通攻擊暴擊時：獲得「攻速」+12%（3 秒，最多 3 層）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.08;defPct:0.87;pRes:0.43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.08、物理防禦×0.87、物理抗性×0.43｜反震 12%；受到傷害時有 20% 機率：對攻擊者造成 100% 物理傷害（內建冷卻 3 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>luck:1.3;critRate:0.87;critDmg:1.08;loot:0.87</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：幸運值×1.3、暴擊率×0.87、暴擊傷害×1.08、掉寶率×0.87｜符文掉落率 +15%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>blockRate:1.3;blockDmgRed:1.3;hpPct:0.87</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：格擋率×1.3、格擋減傷×1.3、生命值×0.87｜格擋成功時有 40% 機率：對攻擊者造成 200% 物理傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:1.3;mpFlat:1.3;cdr:0.87</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.3、法力值×1.3、冷卻縮減×0.87｜施放技能時有 20% 機率：所有技能冷卻縮短 1.5 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gemEff:1.3;affixCap:0.87;enhanceSuccess:1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：寶石鑲嵌效率×1.3、詞條上限率×0.87、強化成功率×1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:1.1;matkPct:1.1;critDmg:1.1;bossDmg:1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.1、魔法攻擊×1.1、暴擊傷害×1.1、對BOSS傷害×1.1｜造成的所有傷害 +18%；攻擊速度額外乘算 +10%（突破攻速上限）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:1.47;critDmg:1.47;eliteDmg:1.1;pPen:0.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.47、暴擊傷害×1.47、對菁英傷害×1.1、物理穿透×0.18｜對生命低於 30% 的敵人傷害 +60%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 15% 的非 BOSS 敵人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:1.1;elemDmgLightning:1.1;elemDmgWind:0.73;mPen:0.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.1、雷屬性傷害提升×1.1、風屬性傷害提升×0.73、魔法穿透×0.18｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 120% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 100% 雷電傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cdr:1.47;matkPct:1.1;mpRegen:1.1;hpPct:0.73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：冷卻縮減×1.47、魔法攻擊×1.1、法力恢復/秒×1.1、生命值×0.73｜所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 1 秒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.47;defPct:1.28;mdefPct:1.28;globalDmgRed:0.73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.47、物理防禦×1.28、魔法防禦×1.28、全局減傷×0.73｜生命低於 30% 時：無敵 3 秒，回復 30% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:0.92;atkPct:0.92;critRate:0.55;aoeDmg:0.73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×0.92、物理攻擊×0.92、暴擊率×0.55、範圍傷害×0.73｜場上每多一名敵人，傷害 +5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 20% 的傷害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>critRate:0.55;critDmg:0.73;atkPct:0.73;evasion:0.55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：暴擊率×0.55、暴擊傷害×0.73、物理攻擊×0.73、閃避率×0.55｜對生命高於 70% 的敵人傷害 +20%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：飛刀的彈射數 +2 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mpFlat:1.47;mpRegen:1.47;matkPct:0.92</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力值×1.47、法力恢復/秒×1.47、魔法攻擊×0.92｜技能法力消耗 -40%；擊殺敵人時回復 3% 最大法力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.28;defPct:1.28;pRes:0.73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.28、物理防禦×1.28、物理抗性×0.73｜反震 35%；受到傷害時有 25% 機率：對所有敵人造成 150% 物理傷害（內建冷卻 2 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bossDmg:1.83;eliteDmg:1.47;atkPct:0.92;matkPct:0.92</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：對BOSS傷害×1.83、對菁英傷害×1.47、物理攻擊×0.92、魔法攻擊×0.92｜對生命高於 70% 的敵人傷害 +40%；場上只有一名敵人時，傷害 +40%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.47;lifesteal:1.47;hpRegen:1.47</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.47、吸血×1.47、生命恢復/秒×1.47｜擊殺敵人時回復 6% 最大生命；生命高於 90% 時，傷害 +25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shieldEff:1.83;hpPct:1.1;globalDmgRed:0.92</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：護盾效率×1.83、生命值×1.1、全局減傷×0.92｜每 8 秒：獲得相當於 20% 最大生命的護盾（8 秒）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>elemDmgFire:0.66;elemDmgIce:0.66;elemDmgLightning:0.66;elemDmgWind:0.66;elemDmgPoison:0.66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：火屬性傷害提升×0.66、冰屬性傷害提升×0.66、雷屬性傷害提升×0.66、風屬性傷害提升×0.66、毒屬性傷害提升×0.66｜造成的所有傷害 +10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:1.47;critRate:1.1;hit:0.73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×1.47、暴擊率×1.1、命中率×0.73｜攻擊速度額外乘算 +15%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:1.2;eliteDmg:0.9;pPen:0.18;critDmg:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.2、對菁英傷害×0.9、物理穿透×0.18、暴擊傷害×0.9｜對生命高於 70% 的敵人傷害 +30%；普通攻擊命中時有 8% 機率：對所有敵人造成 220% 物理傷害；傳奇特效【大地之心】：當你的生命護盾降至 0 時獲得無敵 2 秒；此效果每 30 秒只能觸發 1 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:1.35;critRate:1.05;atkPct:1.05;aoeDmg:0.75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×1.35、暴擊率×1.05、物理攻擊×1.05、範圍傷害×0.75｜攻擊速度額外乘算 +18%（突破攻速上限）；普通攻擊暴擊時：獲得「攻速」+12%（4 秒，最多 4 層）；傳奇特效【風暴核心】：【暴風神體】的持續時間 +50%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:1.35;lifesteal:1.35;critDmg:1.35;hpPct:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.35、吸血×1.35、暴擊傷害×1.35、生命值×0.9｜擊殺敵人時回復 8% 最大生命；生命低於 35% 時，傷害 +60%；造成的所有傷害 +30%；傳奇特效【毒血祭】：血刃斬的中毒每感染 1 個敵人就使自身生命值 -1%，但造成的中毒與流血傷害提高 50%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.2;defPct:1.2;mdefPct:1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.2、物理防禦×1.2、魔法防禦×1.2｜死亡時以 60% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +60%，冷卻 180 秒；傳奇特效【堅韌誓言】：反擊 100 次後獲得無敵狀態，持續 3 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cdr:1.5;mpRegen:1.5;matkPct:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：冷卻縮減×1.5、法力恢復/秒×1.5、魔法攻擊×0.9｜所有技能冷卻時間 -45%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能；傳奇特效【虛空漲落】：【虛空斬】的持續時間 +3 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.9;matkPct:0.9;critDmg:0.9;lifesteal:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.9、魔法攻擊×0.9、暴擊傷害×0.9、吸血×0.6｜造成的所有傷害 +60%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 8% 最大生命；最大生命 -30%（乘算，代價）；傳奇特效【燃血】：【血飲術】每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:0.9;atkPct:0.9;matkPct:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×0.9、物理攻擊×0.9、魔法攻擊×0.9｜技能傷害 +40%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能；傳奇特效【分裂者】：飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:0.9;elemDmgLightning:1.05;critRate:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×0.9、雷屬性傷害提升×1.05、暴擊率×0.6｜對暈眩或緩速中的敵人傷害 +10%；每 3 秒：對隨機 3 名敵人造成 120% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒；傳奇特效【過載】：同一個敵人受到 5 次連鎖閃電的彈射後產生爆炸，對周圍 6 米內的敵人造成 200% 雷電傷害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>critDmg:1.05;atkPct:0.9;bossDmg:1.05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：暴擊傷害×1.05、物理攻擊×0.9、對BOSS傷害×1.05｜場上只有一名敵人時，傷害 +80%；對生命高於 70% 的敵人傷害 +40%；所有技能冷卻時間 -15%（乘算，突破冷卻縮減上限）；傳奇特效【貫日之刺】：四方突刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:1.05;elemDmgFire:0.75;elemDmgIce:0.75;mPen:0.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.05、火屬性傷害提升×0.75、冰屬性傷害提升×0.75、魔法穿透×0.18｜每 3 秒：對隨機 5 名敵人造成 150% 隨機元素傷害；傳奇特效【爆裂】：【火球爆裂】會額外產生 3 個小火球。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>resAll:0.9;luck:1.2;critRate:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：全屬性抗性×0.9、幸運值×1.2、暴擊率×0.9｜技能傷害 +25%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）；傳奇特效【腐化】：在泥沼術範圍內所有受到控場的敵人，受到的傷害 +30%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.75;bossDmg:1.5;critDmg:0.75;pPen:0.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.75、對BOSS傷害×1.5、暴擊傷害×0.75、物理穿透×0.24｜對生命高於 70% 的敵人傷害 +50%；造成的所有傷害 +25%；普通攻擊暴擊時有 20% 機率：對目標造成 250% 物理傷害；傳奇特效【斬殺】：疾風斬有 35% 機率可立即殺死生命值 20% 以下的非 BOSS 敵人。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hpPct:1.5;globalDmgRed:0.9;resAll:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.9;aspd:0.9;aoeDmg:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.9、攻擊速度×0.9、範圍傷害×0.6｜普通攻擊同時對其他所有敵人造成 50% 的傷害；場上每多一名敵人，傷害 +6%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aspd:0.9;critRate:0.9;atkPct:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：攻擊速度×0.9、暴擊率×0.9、物理攻擊×0.9｜攻擊速度額外乘算 +15%（突破攻速上限）；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>evasion:1.8;hit:1.2;hpPct:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：閃避率×1.8、命中率×1.2、生命值×0.9｜造成的所有傷害 +25%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 150% 暗影傷害（內建冷卻 4 秒）；傳奇特效【斷空刃】：【暴風真空刃】每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:1.05;critDmg:1.05;bossDmg:1.05;aoeDmg:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×1.05、暴擊傷害×1.05、對BOSS傷害×1.05、範圍傷害×0.6｜造成的所有傷害 +18%；普通攻擊同時對其他所有敵人造成 15% 的傷害；普通攻擊暴擊時有 10% 機率：對所有敵人造成 250% 物理傷害；傳奇特效【雷殞落】：【雷殞天落】降下的雷球數量 +1 顆。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:1.5;elemDmgLightning:0.75;elemDmgWind:0.75;cdr:1.05;mPen:0.18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.5、雷屬性傷害提升×0.75、風屬性傷害提升×0.75、冷卻縮減×1.05、魔法穿透×0.18｜所有技能冷卻時間 -25%（乘算，突破冷卻縮減上限）；技能傷害 +40%；施放技能時有 20% 機率：免費再施放一次剛施放的技能；傳奇特效【雷之再生】：【迅雷重生】的機率提高至 100%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct:0.9;bossDmg:1.5;elemDmgLight:0.9;critRate:0.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.9、對BOSS傷害×1.5、聖屬性傷害提升×0.9、暴擊率×0.6｜天罰 20%；對生命高於 70% 的敵人傷害 +40%；普通攻擊暴擊時有 15% 機率：對目標造成 350% 聖光傷害；傳奇特效【狩獵者】：你的火狩數量減半（無條件進位，至少 1 團），但造成的傷害額外 +150%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:1.35;elemDmgIce:1.5;cdr:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.35、冰屬性傷害提升×1.5、冷卻縮減×0.9｜對暈眩或緩速中的敵人傷害 +45%；普通攻擊命中時有 15% 機率：目標暈眩 1.5 秒；傳奇特效【凜冬寒霜】：暴風雪持續時間內會不斷對範圍內的敵人施加寒霜狀態，且寒霜狀態傷害 +30%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>matkPct:1.05;elemDmgIce:0.9;critDmg:0.9;bossDmg:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：魔法攻擊×1.05、冰屬性傷害提升×0.9、暴擊傷害×0.9、對BOSS傷害×0.9｜對生命高於 70% 的敵人傷害 +40%；對暈眩或緩速中的敵人傷害 +20%；普通攻擊暴擊時有 25% 機率：對目標造成 200% 冰霜傷害；傳奇特效【深度凍結】：寒冰箭擊中暈眩或凍結的敵人造成的傷害 +50%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>mpRegen:1.5;hpRegen:1.5;matkPct:0.9;cdr:0.9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：法力恢復/秒×1.5、生命恢復/秒×1.5、魔法攻擊×0.9、冷卻縮減×0.9｜擊殺敵人時回復 4% 最大法力；技能法力消耗 -25%；每 6 秒：回復 6% 最大生命，回復 10% 最大法力；傳奇特效【水龍勢】：水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>黑暗裡最先亮起的一點微光，指引落點，也教人閃身而過。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3182,20 +2382,9 @@
     <t>0.2</t>
   </si>
   <si>
-    <t>武器：命中率×1｜防具：閃避率×0.3｜飾品：金幣加成×0.2（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>atkFlat</t>
   </si>
   <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>武器：物理攻擊×1｜防具：物理防禦×0.3｜飾品：物理攻擊×0.5（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgVsIce</t>
   </si>
   <si>
@@ -3219,10 +2408,6 @@
     <t>vit</t>
   </si>
   <si>
-    <t>武器：物理穿透×0.06｜防具：物理防禦×0.29｜飾品：耐力×0.3（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgVsPoison</t>
   </si>
   <si>
@@ -3243,10 +2428,6 @@
     <t>0.4</t>
   </si>
   <si>
-    <t>武器：吸血×0.33｜防具：生命恢復/秒×0.33｜飾品：吸魔×0.4（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgVsLight</t>
   </si>
   <si>
@@ -3270,10 +2451,6 @@
     <t>0.35</t>
   </si>
   <si>
-    <t>武器：暴擊傷害×0.36｜防具：物理抗性×0.09｜飾品：韌性×0.35（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -3352,141 +2529,955 @@
     <t>0.45</t>
   </si>
   <si>
-    <t>武器：對BOSS傷害×0.42｜防具：護盾效率×0.42｜飾品：經驗加成×0.45（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>dmgVsEarth</t>
   </si>
   <si>
     <t>0.29</t>
   </si>
   <si>
-    <t>武器：地屬性傷害提升×0.41｜防具：生命值×0.45｜飾品：對地屬性敵人傷害×0.29（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>critDmg</t>
   </si>
   <si>
-    <t>武器：物理攻擊×0.48｜防具：全局減傷×0.4｜飾品：暴擊傷害×0.3（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>resAll</t>
   </si>
   <si>
-    <t>武器：暴擊傷害×0.5｜防具：全屬性抗性×0.22｜飾品：全屬性抗性×0.3（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>mPen</t>
   </si>
   <si>
     <t>0.12</t>
   </si>
   <si>
-    <t>武器：魔法攻擊×0.49｜防具：格擋減傷×0.49｜飾品：魔法穿透×0.12（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>aoeDmg</t>
   </si>
   <si>
+    <t>loot</t>
+  </si>
+  <si>
+    <t>lifesteal</t>
+  </si>
+  <si>
+    <t>atkPct</t>
+  </si>
+  <si>
+    <t>bossDmg</t>
+  </si>
+  <si>
+    <t>武器詞條／武器倍率：符文鑲在武器（主手、副手、雙手）時給的屬性（詞條鍵見 Equipment_Affix 表的詞條池）。倍率＝「詞條可能範圍的下限」的幾倍：裝備詳情提示的「可能出現的詞條 [2828 ~ 4241]」，2828 就是 1 倍，不再另乘 1.2。數值隨裝備等級、稀有度、強化成長；雙手武器的詞條本身 ×2，符文跟著 ×2。</t>
+  </si>
+  <si>
+    <t>防具詞條／防具倍率：符文鑲在防具（頭、肩、胸、腰、手、腕、腿、靴八件）時給的屬性，規則同上，但不乘雙手倍率。</t>
+  </si>
+  <si>
+    <t>飾品詞條／飾品倍率：符文鑲在飾品（戒指兩枚、項鍊）時給的屬性，規則同上，但不乘雙手倍率。</t>
+  </si>
+  <si>
+    <t>　　每顆符文在三個部位各有一條屬性，固定一條、不能加第二條；倍率必須大於 0。</t>
+  </si>
+  <si>
+    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率＝「基礎值」（同符文列：詞條可能範圍的下限）的幾倍，與符文不同的是不乘雙手倍率（雙手武器的優勢是 5 孔）；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
+  </si>
+  <si>
+    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。符文列＝符文庫詳情裡形容這顆符文的文字；符文真言列＝圖鑑裡那組真言的一句話。效果說明文字由資料自動產生，不需要另外寫。</t>
+  </si>
+  <si>
+    <t>　　符文專用的合成屬性：elemDmgAll＝全屬性傷害提升（火冰雷毒聖暗地風八種元素傷害提升各加同樣的值；符文列與真言的屬性加成都能填）。</t>
+  </si>
+  <si>
+    <t>封魔塔解鎖層數</t>
+  </si>
+  <si>
+    <t>封魔塔解鎖層數：非負整數；通關該層 BOSS 即永久解鎖配方與效果（正式／內測皆適用）。留白或 0＝僅自行成功成形解鎖。超過目前塔上限仍可自行成形。已解鎖不因門檻調高而撤銷。</t>
+  </si>
+  <si>
+    <t>階／級距</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×0.45｜防具：全屬性抗性×0.28｜飾品：魔法攻擊×0.45（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：吸血×0.45｜防具：生命恢復/秒×0.45｜飾品：吸血×0.4（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×0.47｜防具：生命值×0.45｜飾品：物理攻擊×0.4（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：命中率×0.3｜防具：閃避率×0.3｜飾品：金幣加成×0.2（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×0.3｜防具：物理防禦×0.3｜飾品：物理攻擊×0.2（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：吸血×0.25｜防具：生命恢復/秒×0.25｜飾品：吸魔×0.25（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×0.33｜防具：物理抗性×0.09｜飾品：韌性×0.35（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：地屬性傷害提升×0.41｜防具：生命值×0.4｜飾品：對地屬性敵人傷害×0.29（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對BOSS傷害×0.35｜防具：護盾效率×0.35｜飾品：經驗加成×0.35（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：範圍傷害×0.4｜防具：控制時間縮減×0.4｜飾品：範圍傷害×0.3（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊率×0.45｜防具：物理防禦×0.45｜飾品：幸運值×0.45（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對普通敵人傷害×0.5｜防具：閃避率×0.57｜飾品：掉寶率×0.4（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×0.43｜防具：護盾效率×0.56｜飾品：暴擊傷害×0.38（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：對BOSS傷害×0.6｜防具：全局減傷×0.45｜飾品：對BOSS傷害×0.5（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理穿透×0.06｜防具：物理防禦×0.29｜飾品：體質×0.3（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：物理攻擊×0.42｜防具：全局減傷×0.4｜飾品：暴擊傷害×0.3（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：暴擊傷害×0.4｜防具：全屬性抗性×0.22｜飾品：全屬性抗性×0.3（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器：魔法攻擊×0.4｜防具：格擋減傷×0.49｜飾品：魔法穿透×0.12（×倍＝詞條可能範圍下限的倍數）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>0.6</t>
-  </si>
-  <si>
-    <t>武器：範圍傷害×0.52｜防具：控制時間縮減×0.42｜飾品：範圍傷害×0.6（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>武器：暴擊率×0.54｜防具：物理防禦×0.5｜飾品：幸運值×0.54（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>loot</t>
-  </si>
-  <si>
-    <t>武器：對普通敵人傷害×0.57｜防具：閃避率×0.57｜飾品：掉寶率×0.4（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lifesteal</t>
-  </si>
-  <si>
-    <t>武器：吸血×0.59｜防具：生命恢復/秒×0.59｜飾品：吸血×0.5（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atkPct</t>
-  </si>
-  <si>
-    <t>武器：物理攻擊×0.61｜防具：生命值×0.61｜飾品：物理攻擊×0.45（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：魔法攻擊×0.63｜防具：全屬性抗性×0.28｜飾品：魔法攻擊×0.45（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器：暴擊傷害×0.67｜防具：護盾效率×0.61｜飾品：暴擊傷害×0.5（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bossDmg</t>
-  </si>
-  <si>
-    <t>武器：對BOSS傷害×0.75｜防具：全局減傷×0.54｜飾品：對BOSS傷害×0.6（×倍＝詞條可能範圍下限的倍數）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>武器詞條／武器倍率：符文鑲在武器（主手、副手、雙手）時給的屬性（詞條鍵見 Equipment_Affix 表的詞條池）。倍率＝「詞條可能範圍的下限」的幾倍：裝備詳情提示的「可能出現的詞條 [2828 ~ 4241]」，2828 就是 1 倍，不再另乘 1.2。數值隨裝備等級、稀有度、強化成長；雙手武器的詞條本身 ×2，符文跟著 ×2。</t>
-  </si>
-  <si>
-    <t>防具詞條／防具倍率：符文鑲在防具（頭、肩、胸、腰、手、腕、腿、靴八件）時給的屬性，規則同上，但不乘雙手倍率。</t>
-  </si>
-  <si>
-    <t>飾品詞條／飾品倍率：符文鑲在飾品（戒指兩枚、項鍊）時給的屬性，規則同上，但不乘雙手倍率。</t>
-  </si>
-  <si>
-    <t>　　每顆符文在三個部位各有一條屬性，固定一條、不能加第二條；倍率必須大於 0。</t>
-  </si>
-  <si>
-    <t>屬性加成：「詞條鍵:倍率」用「;」分隔，例如 atkPct:1.2;critRate:1。倍率＝「基礎值」（同符文列：詞條可能範圍的下限）的幾倍，與符文不同的是不乘雙手倍率（雙手武器的優勢是 5 孔）；負數＝代價。同一組符文真言穿在多件裝備上時，各件的屬性都計。</t>
-  </si>
-  <si>
-    <t>風味文字：圖鑑與詳情顯示的一句話，可留空。符文列＝符文庫詳情裡形容這顆符文的文字；符文真言列＝圖鑑裡那組真言的一句話。效果說明文字由資料自動產生，不需要另外寫。</t>
-  </si>
-  <si>
-    <t>atkPct:0.9;matkPct:0.9;elemDmgAll:0.45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：物理攻擊×0.9、魔法攻擊×0.9、全屬性傷害提升×0.45｜造成的所有傷害 +50%；所有技能冷卻時間 -20%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +15%（突破攻速上限）；技能法力消耗 -30%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>　　符文專用的合成屬性：elemDmgAll＝全屬性傷害提升（火冰雷毒聖暗地風八種元素傷害提升各加同樣的值；符文列與真言的屬性加成都能填）。</t>
-  </si>
-  <si>
-    <t>封魔塔解鎖層數</t>
-  </si>
-  <si>
-    <t>封魔塔解鎖層數：非負整數；通關該層 BOSS 即永久解鎖配方與效果（正式／內測皆適用）。留白或 0＝僅自行成功成形解鎖。超過目前塔上限仍可自行成形。已解鎖不因門檻調高而撤銷。</t>
-  </si>
-  <si>
-    <t>階／級距</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>屬性：生命值×1.5、全局減傷×0.9、全屬性抗性×0.9｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 40% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：【天地共生】復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkFlat:0.5;matkFlat:0.5;hit:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.5、魔法攻擊×0.5、命中率×0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defFlat:0.625;hpFlat:0.625;hpRegen:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×0.625、生命值×0.625、生命恢復/秒×0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkFlat:0.625;elemDmgIce:0.375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.625、冰屬性傷害提升×0.375｜普通攻擊命中時有 10% 機率：目標緩速 2 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion:0.5;hpFlat:0.5;hit:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×0.5、生命值×0.5、命中率×0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defPct:0.375;hpPct:0.3;pRes:0.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorns:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理防禦×0.375、生命值×0.3、物理抗性×0.2｜反震 1.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.3;elemDmgPoison:0.375;critRate:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":15,"acts":[{"act":"dot","pct":30,"sec":4,"name":"poison"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.3、毒屬性傷害提升×0.375、暴擊率×0.25｜普通攻擊命中時有 15% 機率：對目標施加中毒（每秒 30% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.375;elemDmgLightning:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":45,"elem":"lightning","to":"target"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.375、雷屬性傷害提升×0.5｜普通攻擊命中時有 8% 機率：對目標造成 45% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpFlat:0.5;resLight:0.375;hpPct:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killManaPct:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×0.5、聖光抗性×0.375、生命值×0.25｜擊殺敵人時回復 0.5% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifesteal:0.5;atkPct:0.25;hit:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killHealPct:0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×0.5、物理攻擊×0.25、命中率×0.25｜擊殺敵人時回復 0.5% 最大生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.375;defPct:0.375;tenacity:0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.375、物理防禦×0.375、韌性×0.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpRegen:0.5;hpRegen:0.5;mpFlat:0.375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×0.5、生命恢復/秒×0.5、法力值×0.375｜擊殺敵人時回復 1% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goldBonus:0.5;xpBonus:0.375;loot:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>runeFindPct:4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：金幣加成×0.5、經驗加成×0.375、掉寶率×0.3｜符文掉落率 +4%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.3;critDmg:0.3;pPen:0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.3、暴擊傷害×0.3、物理穿透×0.05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.375;elemDmgFire:0.375;mpFlat:0.375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":15,"acts":[{"act":"mana","pctMax":6}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.375、火屬性傷害提升×0.375、法力值×0.375｜施放技能時有 15% 機率：回復 6% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.54;critRate:0.325;atkPct:0.325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspdMult:4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.54、暴擊率×0.325、物理攻擊×0.325｜攻擊速度額外乘算 +4%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.325;elemDmgLightning:0.54;critDmg:0.325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":15,"acts":[{"act":"dmg","pct":60,"elem":"lightning","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.325、雷屬性傷害提升×0.54、暴擊傷害×0.325｜普通攻擊命中時有 15% 機率：對所有敵人造成 60% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.435;elemDmgIce:0.65;cdr:0.215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgCtrlPct:7.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.435、冰屬性傷害提升×0.65、冷卻縮減×0.215｜對暈眩或緩速中的敵人傷害 +7.5%；普通攻擊命中時有 20% 機率：目標暈眩 1.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lifesteal:0.65;atkPct:0.435;critRate:0.215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killHealPct:1.5;dmgSelfLowPct:12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：吸血×0.65、物理攻擊×0.435、暴擊率×0.215｜擊殺敵人時回復 1.5% 最大生命；生命低於 35% 時，傷害 +12.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.65;defPct:0.65;pRes:0.215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.65、物理防禦×0.65、物理抗性×0.215｜單次受到的傷害最多只會是最大生命的 40%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion:0.76;hit:0.435;hpPct:0.325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×0.76、命中率×0.435、生命值×0.325｜受到傷害時有 15% 機率：無敵 1 秒（內建冷卻 10 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.435;mpFlat:0.65;resAll:0.215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":10,"acts":[{"act":"heal","pctMax":4},{"act":"mana","pctMax":4}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.435、法力值×0.65、全屬性抗性×0.215｜每 10 秒：回復 4% 最大生命，回復 4% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.435;elemDmgPoison:0.65;mPen:0.065</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":25,"acts":[{"act":"dot","pct":30,"sec":4,"name":"poison","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.435、毒屬性傷害提升×0.65、魔法穿透×0.065｜施放技能時有 25% 機率：對所有敵人施加中毒（每秒 30% 攻擊力，4 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.65;critRate:0.435;atkPct:0.325</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":6,"sec":3,"max":3}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.65、暴擊率×0.435、物理攻擊×0.325｜普通攻擊暴擊時：獲得「攻速」+6%（3 秒，最多 3 層）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.54;defPct:0.435;pRes:0.215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorns:6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":20,"cd":3,"acts":[{"act":"dmg","pct":50,"type":"phys","to":"attacker"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.54、物理防禦×0.435、物理抗性×0.215｜反震 6%；受到傷害時有 20% 機率：對攻擊者造成 50% 物理傷害（內建冷卻 3 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>luck:0.65;critRate:0.435;critDmg:0.54;loot:0.435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>runeFindPct:7.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：幸運值×0.65、暴擊率×0.435、暴擊傷害×0.54、掉寶率×0.435｜符文掉落率 +7.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockRate:0.65;blockDmgRed:0.65;hpPct:0.435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"block","chance":40,"acts":[{"act":"dmg","pct":100,"type":"phys","to":"attacker"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：格擋率×0.65、格擋減傷×0.65、生命值×0.435｜格擋成功時有 40% 機率：對攻擊者造成 100% 物理傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.65;mpFlat:0.65;cdr:0.435</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"cast","chance":20,"acts":[{"act":"cdr","sec":0.75}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.65、法力值×0.65、冷卻縮減×0.435｜施放技能時有 20% 機率：所有技能冷卻縮短 0.75 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gemEff:0.65;affixCap:0.435;enhanceSuccess:0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：寶石鑲嵌效率×0.65、詞條上限率×0.435、強化成功率×0.65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.55;matkPct:0.55;critDmg:0.55;bossDmg:0.55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPct:9;aspdMult:5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.55、魔法攻擊×0.55、暴擊傷害×0.55、對BOSS傷害×0.55｜造成的所有傷害 +9%；攻擊速度額外乘算 +5%（突破攻速上限）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.735;critDmg:0.735;eliteDmg:0.55;pPen:0.09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgLoHpPct:30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":8,"acts":[{"act":"execute","hpBelow":7.5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.735、暴擊傷害×0.735、對菁英傷害×0.55、物理穿透×0.09｜對生命低於 30% 的敵人傷害 +30%；普通攻擊命中時有 8% 機率：直接斬殺生命低於 7.5% 的非 BOSS 敵人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.55;elemDmgLightning:0.55;elemDmgWind:0.365;mPen:0.09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":30,"acts":[{"act":"dmg","pct":60,"elem":"lightning","to":"all"}]},{"on":"cast","chance":25,"acts":[{"act":"dmg","pct":50,"elem":"lightning","to":"rand","n":3}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.55、雷屬性傷害提升×0.55、風屬性傷害提升×0.365、魔法穿透×0.09｜普通攻擊暴擊時有 30% 機率：對所有敵人造成 60% 雷電傷害；施放技能時有 25% 機率：對隨機 3 名敵人造成 50% 雷電傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdr:0.735;matkPct:0.55;mpRegen:0.55;hpPct:0.365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdPct:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"kill","acts":[{"act":"cdr","sec":0.5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×0.735、魔法攻擊×0.55、法力恢復/秒×0.55、生命值×0.365｜所有技能冷卻時間 -10%（乘算，突破冷卻縮減上限）；擊殺敵人時：所有技能冷卻縮短 0.5 秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.735;defPct:0.64;mdefPct:0.64;globalDmgRed:0.365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"lowhp","below":30,"cd":90,"acts":[{"act":"invuln","sec":3},{"act":"heal","pctMax":15},{"act":"cleanse"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.735、物理防禦×0.64、魔法防禦×0.64、全局減傷×0.365｜生命低於 30% 時：無敵 3 秒，回復 15% 最大生命，淨化負面狀態（內建冷卻 90 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.46;atkPct:0.46;critRate:0.275;aoeDmg:0.365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPerFoePct:2.5;splashPct:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.46、物理攻擊×0.46、暴擊率×0.275、範圍傷害×0.365｜場上每多一名敵人，傷害 +2.5%（最多計 10 名）；普通攻擊同時對其他所有敵人造成 10% 的傷害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critRate:0.275;critDmg:0.365;atkPct:0.365;evasion:0.275</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgHiHpPct:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊率×0.275、暴擊傷害×0.365、物理攻擊×0.365、閃避率×0.275｜對生命高於 70% 的敵人傷害 +10%；傳奇特效【影刃】：射出的飛刀數量 +2 把。；傳奇特效【連鎖】：每把飛刀有 25% 機率再彈射 2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpFlat:0.735;mpRegen:0.735;matkPct:0.46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manaCostRedPct:20;killManaPct:1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力值×0.735、法力恢復/秒×0.735、魔法攻擊×0.46｜技能法力消耗 -20%；擊殺敵人時回復 1.5% 最大法力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.64;defPct:0.64;pRes:0.365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>thorns:17.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":25,"cd":2,"acts":[{"act":"dmg","pct":75,"type":"phys","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.64、物理防禦×0.64、物理抗性×0.365｜反震 17.5%；受到傷害時有 25% 機率：對所有敵人造成 75% 物理傷害（內建冷卻 2 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bossDmg:0.915;eliteDmg:0.735;atkPct:0.46;matkPct:0.46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgHiHpPct:20;dmgSoloPct:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：對BOSS傷害×0.915、對菁英傷害×0.735、物理攻擊×0.46、魔法攻擊×0.46｜對生命高於 70% 的敵人傷害 +20%；場上只有一名敵人時，傷害 +20%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.735;lifesteal:0.735;hpRegen:0.735</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killHealPct:3;dmgSelfFullPct:12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.735、吸血×0.735、生命恢復/秒×0.735｜擊殺敵人時回復 3% 最大生命；生命高於 90% 時，傷害 +12.5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shieldEff:0.915;hpPct:0.55;globalDmgRed:0.46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":8,"acts":[{"act":"shield","pctMax":10,"sec":8}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：護盾效率×0.915、生命值×0.55、全局減傷×0.46｜每 8 秒：獲得相當於 10% 最大生命的護盾（8 秒）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elemDmgFire:0.33;elemDmgIce:0.33;elemDmgLightning:0.33;elemDmgWind:0.33;elemDmgPoison:0.33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPct:5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：火屬性傷害提升×0.33、冰屬性傷害提升×0.33、雷屬性傷害提升×0.33、風屬性傷害提升×0.33、毒屬性傷害提升×0.33｜造成的所有傷害 +5%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.735;critRate:0.55;hit:0.365</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspdMult:7.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.735、暴擊率×0.55、命中率×0.365｜攻擊速度額外乘算 +7.5%（突破攻速上限）；每 6 次普通攻擊命中：免費施放一個隨機的已裝配技能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.6;eliteDmg:0.45;pPen:0.09;critDmg:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgHiHpPct:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hit","chance":8,"acts":[{"act":"dmg","pct":110,"type":"phys","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.6、對菁英傷害×0.45、物理穿透×0.09、暴擊傷害×0.45｜對生命高於 70% 的敵人傷害 +15%；普通攻擊命中時有 8% 機率：對所有敵人造成 110% 物理傷害；傳奇特效【大地之心】：當你的生命護盾降至 0 時獲得無敵 3 秒；此效果每 60 秒只能觸發 1 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.675;critRate:0.525;atkPct:0.525;aoeDmg:0.375</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspdMult:9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","acts":[{"act":"buff","sid":"aspdUp","val":6,"sec":4,"max":4}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.675、暴擊率×0.525、物理攻擊×0.525、範圍傷害×0.375｜攻擊速度額外乘算 +9%（突破攻速上限）；普通攻擊暴擊時：獲得「攻速」+6%（4 秒，最多 4 層）；傳奇特效【風暴核心】：暴風神體的持續時間 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.675;lifesteal:0.675;critDmg:0.675;hpPct:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killHealPct:4;dmgSelfLowPct:30;dmgPct:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.675、吸血×0.675、暴擊傷害×0.675、生命值×0.45｜擊殺敵人時回復 4% 最大生命；生命低於 35% 時，傷害 +30%；造成的所有傷害 +15%；傳奇特效【毒血祭】：血刃斬的中毒每感染 1 個敵人就使自身生命值 -0.5%，但造成的中毒與流血傷害提高 50%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.6;defPct:0.6;mdefPct:0.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reviveHpPct:30;reviveCdSec:180;reviveInvulnSec:3;reviveDmgPct:30;reviveDmgSec:10;reviveRefresh:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.6、物理防禦×0.6、魔法防禦×0.6｜死亡時以 30% 生命復活並淨化，無敵 3 秒，所有技能冷卻重置，之後 10 秒內傷害 +30%，冷卻 180 秒；傳奇特效【堅韌誓言】：反擊 200 次後獲得無敵狀態，持續 3 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdr:0.75;mpRegen:0.75;matkPct:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdPct:22.5;maxHpPct:-20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：冷卻縮減×0.75、法力恢復/秒×0.75、魔法攻擊×0.45｜所有技能冷卻時間 -22.5%（乘算，突破冷卻縮減上限）；最大生命 -20%（乘算，代價）；施放技能時有 25% 機率：免費再施放一次剛施放的技能；傳奇特效【虛空漲落】：虛空斬的持續時間 +3 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.45;matkPct:0.45;critDmg:0.45;lifesteal:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPct:30;selfDrainPct:2;killHealPct:4;maxHpPct:-30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.45、魔法攻擊×0.45、暴擊傷害×0.45、吸血×0.3｜造成的所有傷害 +30%；代價：每秒損失 2% 最大生命（不會致死）；擊殺敵人時回復 4% 最大生命；最大生命 -30%（乘算，代價）；傳奇特效【燃血】：血飲術每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.45;atkPct:0.45;matkPct:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillDmgPct:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.45、物理攻擊×0.45、魔法攻擊×0.45｜技能傷害 +20%；每 4 次普通攻擊命中：免費施放一個隨機的已裝配技能；施放技能時有 15% 機率：免費再施放一次剛施放的技能；傳奇特效【分裂者】：飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.45;elemDmgLightning:0.525;critRate:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgCtrlPct:5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":60,"elem":"lightning","to":"rand","n":3}]},{"on":"crit","acts":[{"act":"stun","sec":1,"to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.45、雷屬性傷害提升×0.525、暴擊率×0.3｜對暈眩或緩速中的敵人傷害 +5%；每 3 秒：對隨機 3 名敵人造成 60% 雷電傷害；普通攻擊暴擊時：所有敵人暈眩 1 秒；傳奇特效【過載】：同一個敵人受到 10 次連鎖閃電的彈射後產生爆炸，對周圍 10 米內的敵人造成 400% 雷電傷害。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critDmg:0.525;atkPct:0.45;bossDmg:0.525</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgSoloPct:40;dmgHiHpPct:20;cdPct:7.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：暴擊傷害×0.525、物理攻擊×0.45、對BOSS傷害×0.525｜場上只有一名敵人時，傷害 +40%；對生命高於 70% 的敵人傷害 +20%；所有技能冷卻時間 -7.5%（乘算，突破冷卻縮減上限）；傳奇特效【貫日之刺】：突刺有 25% 機率使敵人重傷，使其受到的傷害 +20%，持續 5 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.525;elemDmgFire:0.375;elemDmgIce:0.375;mPen:0.09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":3,"acts":[{"act":"dmg","pct":75,"elem":"random","to":"rand","n":5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.525、火屬性傷害提升×0.375、冰屬性傷害提升×0.375、魔法穿透×0.09｜每 3 秒：對隨機 5 名敵人造成 75% 隨機元素傷害；傳奇特效【爆裂】：火球爆裂會額外產生 3 個小火球。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resAll:0.45;luck:0.6;critRate:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>skillDmgPct:12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：全屬性抗性×0.45、幸運值×0.6、暴擊率×0.45｜技能傷害 +12.5%；施放技能時：隨機獲得一種增益（攻擊／攻速／爆傷／防禦／閃避／所有傷害，8 秒）；傳奇特效【腐化】：在泥沼術範圍內所有受到控場的敵人，受到的傷害 +20%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.375;bossDmg:0.75;critDmg:0.375;pPen:0.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgHiHpPct:25;dmgPct:12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":20,"acts":[{"act":"dmg","pct":125,"type":"phys","to":"target"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.375、對BOSS傷害×0.75、暴擊傷害×0.375、物理穿透×0.12｜對生命高於 70% 的敵人傷害 +25%；造成的所有傷害 +12.5%；普通攻擊暴擊時有 20% 機率：對目標造成 125% 物理傷害；傳奇特效【斬殺】：疾風斬有 20% 機率可立即殺死生命值 10% 以下的非 BOSS 敵人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpPct:0.75;globalDmgRed:0.45;resAll:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"lowhp","below":40,"cd":60,"acts":[{"act":"shield","pctMax":20,"sec":6},{"act":"invuln","sec":2}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：生命值×0.75、全局減傷×0.45、全屬性抗性×0.45｜單次受到的傷害最多只會是最大生命的 15%；造成的所有傷害 -20%；生命低於 40% 時：獲得相當於 20% 最大生命的護盾（6 秒），無敵 2 秒（內建冷卻 60 秒）；傳奇特效【不滅意志】：天地共生復活後的減傷時間內，每殺死 1 個敵人則減傷時間 +0.5 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.45;aspd:0.45;aoeDmg:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>splashPct:25;dmgPerFoePct:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.45、攻擊速度×0.45、範圍傷害×0.3｜普通攻擊同時對其他所有敵人造成 25% 的傷害；場上每多一名敵人，傷害 +3%（最多計 10 名）；傳奇特效【裂空飛斬】：迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspd:0.45;critRate:0.45;atkPct:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：攻擊速度×0.45、暴擊率×0.45、物理攻擊×0.45｜攻擊速度額外乘算 +7.5%（突破攻速上限）；傳奇特效【殺千刀】：雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evasion:0.9;hit:0.6;hpPct:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPct:12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"hurt","chance":30,"cd":4,"acts":[{"act":"invuln","sec":1.5},{"act":"dmg","pct":75,"elem":"dark","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：閃避率×0.9、命中率×0.6、生命值×0.45｜造成的所有傷害 +12.5%；受到傷害時有 30% 機率：無敵 1.5 秒，對所有敵人造成 75% 暗影傷害（內建冷卻 4 秒）；傳奇特效【斷空刃】：暴風真空刃每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.45;matkPct:0.45;elemDmgAll:0.225</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPct:25;cdPct:10;aspdMult:7.5;manaCostRedPct:15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.45、魔法攻擊×0.45、全屬性傷害提升×0.225｜造成的所有傷害 +25%；所有技能冷卻時間 -10%（乘算，突破冷卻縮減上限）；攻擊速度額外乘算 +7.5%（突破攻速上限）；技能法力消耗 -15%；傳奇特效【火龍共鳴】：場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +10%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.525;critDmg:0.525;bossDmg:0.525;aoeDmg:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgPct:9;splashPct:7.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":10,"acts":[{"act":"dmg","pct":125,"type":"phys","to":"all"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.525、暴擊傷害×0.525、對BOSS傷害×0.525、範圍傷害×0.3｜造成的所有傷害 +9%；普通攻擊同時對其他所有敵人造成 7.5% 的傷害；普通攻擊暴擊時有 10% 機率：對所有敵人造成 125% 物理傷害；傳奇特效【雷殞落】：雷殞天落降下的雷球數量 +1 顆。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.75;elemDmgLightning:0.375;elemDmgWind:0.375;cdr:0.525;mPen:0.09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cdPct:12.5;skillDmgPct:20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.75、雷屬性傷害提升×0.375、風屬性傷害提升×0.375、冷卻縮減×0.525、魔法穿透×0.09｜所有技能冷卻時間 -12.5%（乘算，突破冷卻縮減上限）；技能傷害 +20%；施放技能時有 20% 機率：免費再施放一次剛施放的技能；傳奇特效【雷之再生】：迅雷重生的機率提高至 100%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atkPct:0.45;bossDmg:0.75;elemDmgLight:0.45;critRate:0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>smite:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":15,"acts":[{"act":"dmg","pct":175,"elem":"light","to":"target"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：物理攻擊×0.45、對BOSS傷害×0.75、聖屬性傷害提升×0.45、暴擊率×0.3｜天罰 10%；對生命高於 70% 的敵人傷害 +20%；普通攻擊暴擊時有 15% 機率：對目標造成 175% 聖光傷害；傳奇特效【狩獵者】：你的火狩數量減半（無條件進位，至少 1 團），但造成的傷害額外 +150%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.675;elemDmgIce:0.75;cdr:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgCtrlPct:22.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.675、冰屬性傷害提升×0.75、冷卻縮減×0.45｜對暈眩或緩速中的敵人傷害 +22.5%；普通攻擊命中時有 15% 機率：目標暈眩 1.5 秒；傳奇特效【凜冬寒霜】：暴風雪對帶有寒霜狀態的敵人，每層寒霜傷害 +5%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>matkPct:0.525;elemDmgIce:0.45;critDmg:0.45;bossDmg:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dmgHiHpPct:20;dmgCtrlPct:10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"crit","chance":25,"acts":[{"act":"dmg","pct":100,"elem":"ice","to":"target"}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：魔法攻擊×0.525、冰屬性傷害提升×0.45、暴擊傷害×0.45、對BOSS傷害×0.45｜對生命高於 70% 的敵人傷害 +20%；對暈眩或緩速中的敵人傷害 +10%；普通攻擊暴擊時有 25% 機率：對目標造成 100% 冰霜傷害；傳奇特效【深度凍結】：寒冰箭擊中暈眩或凍結的敵人造成的傷害 +30%。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mpRegen:0.75;hpRegen:0.75;matkPct:0.45;cdr:0.45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>killManaPct:2;manaCostRedPct:12.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[{"on":"tick","every":6,"acts":[{"act":"heal","pctMax":3},{"act":"mana","pctMax":5}]}]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性：法力恢復/秒×0.75、生命恢復/秒×0.75、魔法攻擊×0.45、冷卻縮減×0.45｜擊殺敵人時回復 2% 最大法力；技能法力消耗 -12.5%；每 6 秒：回復 3% 最大生命，回復 5% 最大法力；傳奇特效【水龍勢】：水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3911,30 +3902,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF89A0-83BA-4F8D-98E0-5ED4EB2EEC35}">
   <dimension ref="A1:U112"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
-    <col min="10" max="11" width="14.6640625" style="5" customWidth="1"/>
-    <col min="12" max="13" width="24.6640625" customWidth="1"/>
-    <col min="14" max="14" width="40.6640625" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="16" width="22.6640625" customWidth="1"/>
-    <col min="17" max="17" width="36.6640625" customWidth="1"/>
-    <col min="18" max="18" width="60.6640625" customWidth="1"/>
-    <col min="19" max="19" width="36.6640625" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" customWidth="1"/>
-    <col min="21" max="21" width="50.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="2" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="9.625" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="9.625" customWidth="1"/>
+    <col min="10" max="11" width="14.625" style="5" customWidth="1"/>
+    <col min="12" max="13" width="24.625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="40.625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="22.625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="36.625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="60.625" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="36.625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="10.625" customWidth="1"/>
+    <col min="21" max="21" width="50.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3945,10 +3936,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>909</v>
+        <v>682</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>907</v>
+        <v>680</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3963,10 +3954,10 @@
         <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>818</v>
+        <v>614</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>819</v>
+        <v>615</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>7</v>
@@ -3999,7 +3990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -4052,21 +4043,21 @@
         <v>20</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>20</v>
@@ -4111,21 +4102,21 @@
         <v>20</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>606</v>
+        <v>538</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>607</v>
+        <v>539</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="6"/>
@@ -4144,21 +4135,21 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>608</v>
+        <v>540</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>610</v>
+        <v>542</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>611</v>
+        <v>543</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="6"/>
@@ -4180,18 +4171,18 @@
         <v>21</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>613</v>
+        <v>545</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>614</v>
+        <v>546</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="6"/>
@@ -4210,21 +4201,21 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3" t="s">
-        <v>615</v>
+        <v>547</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>20</v>
@@ -4269,21 +4260,21 @@
         <v>20</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>20</v>
@@ -4328,21 +4319,21 @@
         <v>20</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>20</v>
@@ -4390,18 +4381,18 @@
         <v>21</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>20</v>
@@ -4446,21 +4437,21 @@
         <v>20</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>20</v>
@@ -4505,21 +4496,21 @@
         <v>20</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>20</v>
@@ -4564,21 +4555,21 @@
         <v>20</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>20</v>
@@ -4623,21 +4614,21 @@
         <v>20</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>20</v>
@@ -4682,43 +4673,43 @@
         <v>20</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>911</v>
+        <v>683</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D15" s="9">
         <v>1</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>618</v>
+        <v>550</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>820</v>
+        <v>616</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>821</v>
+        <v>617</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>20</v>
@@ -4742,46 +4733,46 @@
         <v>20</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>785</v>
+        <v>581</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D16" s="9">
         <v>2</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>823</v>
+        <v>618</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>824</v>
+        <v>699</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>20</v>
@@ -4805,46 +4796,46 @@
         <v>20</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>786</v>
+        <v>582</v>
       </c>
       <c r="T16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D17" s="9">
         <v>3</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>618</v>
+        <v>550</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>826</v>
+        <v>619</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>827</v>
+        <v>620</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>20</v>
@@ -4868,46 +4859,46 @@
         <v>20</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>787</v>
+        <v>583</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D18" s="9">
         <v>4</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>619</v>
+        <v>551</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>829</v>
+        <v>622</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>830</v>
+        <v>623</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>20</v>
@@ -4931,46 +4922,46 @@
         <v>20</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>788</v>
+        <v>584</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D19" s="9">
         <v>5</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>620</v>
+        <v>552</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>621</v>
+        <v>553</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>832</v>
+        <v>625</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>830</v>
+        <v>623</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>20</v>
@@ -4994,46 +4985,46 @@
         <v>20</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>789</v>
+        <v>585</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D20" s="9">
         <v>6</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>622</v>
+        <v>554</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>623</v>
+        <v>555</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>834</v>
+        <v>626</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>821</v>
+        <v>617</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>20</v>
@@ -5057,46 +5048,46 @@
         <v>20</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>790</v>
+        <v>586</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D21" s="9">
         <v>7</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>624</v>
+        <v>556</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>625</v>
+        <v>557</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>836</v>
+        <v>628</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>821</v>
+        <v>617</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>20</v>
@@ -5120,46 +5111,46 @@
         <v>20</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>791</v>
+        <v>587</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D22" s="9">
         <v>8</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>626</v>
+        <v>701</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>626</v>
+        <v>701</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>838</v>
+        <v>630</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>839</v>
+        <v>701</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>20</v>
@@ -5183,46 +5174,46 @@
         <v>20</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>792</v>
+        <v>588</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D23" s="9">
         <v>9</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>624</v>
+        <v>556</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>625</v>
+        <v>557</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>841</v>
+        <v>632</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>821</v>
+        <v>617</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>20</v>
@@ -5246,46 +5237,46 @@
         <v>20</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>793</v>
+        <v>589</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D24" s="9">
         <v>10</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>627</v>
+        <v>559</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>627</v>
+        <v>559</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>843</v>
+        <v>634</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>844</v>
+        <v>635</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>20</v>
@@ -5309,46 +5300,46 @@
         <v>20</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>794</v>
+        <v>590</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D25" s="9">
         <v>11</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>628</v>
+        <v>558</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>629</v>
+        <v>561</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>846</v>
+        <v>637</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>847</v>
+        <v>638</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>20</v>
@@ -5372,46 +5363,46 @@
         <v>20</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>795</v>
+        <v>591</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D26" s="9">
         <v>12</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>630</v>
+        <v>562</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>631</v>
+        <v>563</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>849</v>
+        <v>639</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>850</v>
+        <v>640</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>20</v>
@@ -5435,46 +5426,46 @@
         <v>20</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>796</v>
+        <v>592</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D27" s="9">
         <v>13</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>632</v>
+        <v>564</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>633</v>
+        <v>565</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>852</v>
+        <v>642</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>830</v>
+        <v>623</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>20</v>
@@ -5498,46 +5489,46 @@
         <v>20</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>797</v>
+        <v>593</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D28" s="9">
         <v>14</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>634</v>
+        <v>566</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>635</v>
+        <v>567</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>854</v>
+        <v>644</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>847</v>
+        <v>638</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>20</v>
@@ -5561,46 +5552,46 @@
         <v>20</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>798</v>
+        <v>594</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D29" s="9">
         <v>15</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>620</v>
+        <v>552</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>636</v>
+        <v>568</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>856</v>
+        <v>646</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>830</v>
+        <v>623</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>20</v>
@@ -5624,46 +5615,46 @@
         <v>20</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>799</v>
+        <v>595</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D30" s="9">
         <v>16</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>637</v>
+        <v>569</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>638</v>
+        <v>570</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>858</v>
+        <v>648</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>859</v>
+        <v>649</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>20</v>
@@ -5687,46 +5678,46 @@
         <v>20</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>800</v>
+        <v>596</v>
       </c>
       <c r="T30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D31" s="9">
         <v>17</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>626</v>
+        <v>558</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>639</v>
+        <v>571</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>861</v>
+        <v>651</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>859</v>
+        <v>649</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>20</v>
@@ -5750,46 +5741,46 @@
         <v>20</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>801</v>
+        <v>597</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D32" s="9">
         <v>18</v>
       </c>
       <c r="E32" s="6"/>
       <c r="F32" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>628</v>
+        <v>560</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>628</v>
+        <v>560</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>863</v>
+        <v>653</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>821</v>
+        <v>617</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>20</v>
@@ -5813,46 +5804,46 @@
         <v>20</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>802</v>
+        <v>598</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D33" s="9">
         <v>19</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>633</v>
+        <v>565</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>640</v>
+        <v>572</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>865</v>
+        <v>655</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>839</v>
+        <v>631</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>20</v>
@@ -5876,46 +5867,46 @@
         <v>20</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>803</v>
+        <v>599</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D34" s="9">
         <v>20</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>640</v>
+        <v>572</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>641</v>
+        <v>573</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>867</v>
+        <v>657</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>868</v>
+        <v>658</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>20</v>
@@ -5939,46 +5930,46 @@
         <v>20</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>804</v>
+        <v>600</v>
       </c>
       <c r="T34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U34" s="3" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D35" s="9">
         <v>21</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>642</v>
+        <v>551</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>643</v>
+        <v>551</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>870</v>
+        <v>660</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>871</v>
+        <v>551</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>20</v>
@@ -6002,46 +5993,46 @@
         <v>20</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>805</v>
+        <v>601</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D36" s="9">
         <v>22</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>644</v>
+        <v>575</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>645</v>
+        <v>172</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>873</v>
+        <v>662</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>874</v>
+        <v>663</v>
       </c>
       <c r="L36" s="3" t="s">
         <v>20</v>
@@ -6065,46 +6056,46 @@
         <v>20</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>806</v>
+        <v>602</v>
       </c>
       <c r="T36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U36" s="3" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D37" s="9">
         <v>23</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>646</v>
+        <v>574</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>876</v>
+        <v>664</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>830</v>
+        <v>623</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>20</v>
@@ -6128,46 +6119,46 @@
         <v>20</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>807</v>
+        <v>603</v>
       </c>
       <c r="T37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D38" s="9">
         <v>24</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>647</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>648</v>
+        <v>578</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>878</v>
+        <v>665</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>830</v>
+        <v>623</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>20</v>
@@ -6191,46 +6182,46 @@
         <v>20</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>808</v>
+        <v>604</v>
       </c>
       <c r="T38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U38" s="3" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D39" s="9">
         <v>25</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>649</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>649</v>
+        <v>579</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>880</v>
+        <v>666</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>881</v>
+        <v>667</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>20</v>
@@ -6254,46 +6245,46 @@
         <v>20</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>809</v>
+        <v>605</v>
       </c>
       <c r="T39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D40" s="9">
         <v>26</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>650</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>643</v>
+        <v>172</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>883</v>
+        <v>668</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>884</v>
+        <v>91</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>20</v>
@@ -6317,46 +6308,46 @@
         <v>20</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>810</v>
+        <v>606</v>
       </c>
       <c r="T40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D41" s="9">
         <v>27</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>651</v>
+        <v>576</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>647</v>
+        <v>576</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>863</v>
+        <v>653</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>886</v>
+        <v>576</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>20</v>
@@ -6380,46 +6371,46 @@
         <v>20</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>811</v>
+        <v>607</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D42" s="9">
         <v>28</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>652</v>
+        <v>577</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>652</v>
+        <v>580</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>888</v>
+        <v>669</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>839</v>
+        <v>631</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>20</v>
@@ -6443,46 +6434,46 @@
         <v>20</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>812</v>
+        <v>608</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U42" s="3" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D43" s="9">
         <v>29</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>653</v>
+        <v>576</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>653</v>
+        <v>576</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>890</v>
+        <v>670</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>824</v>
+        <v>172</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>20</v>
@@ -6506,46 +6497,46 @@
         <v>20</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>813</v>
+        <v>609</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D44" s="9">
         <v>30</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>654</v>
+        <v>686</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>654</v>
+        <v>576</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>892</v>
+        <v>671</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>871</v>
+        <v>172</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>20</v>
@@ -6569,46 +6560,46 @@
         <v>20</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>814</v>
+        <v>610</v>
       </c>
       <c r="T44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U44" s="3" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D45" s="9">
         <v>31</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>655</v>
+        <v>576</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>624</v>
+        <v>556</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>856</v>
+        <v>646</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>871</v>
+        <v>661</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>20</v>
@@ -6632,46 +6623,46 @@
         <v>20</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>815</v>
+        <v>611</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U45" s="3" t="s">
-        <v>894</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D46" s="9">
         <v>32</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>656</v>
+        <v>705</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>654</v>
+        <v>706</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>876</v>
+        <v>664</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>824</v>
+        <v>567</v>
       </c>
       <c r="L46" s="3" t="s">
         <v>20</v>
@@ -6695,46 +6686,46 @@
         <v>20</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>816</v>
+        <v>612</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D47" s="9">
         <v>33</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>657</v>
+        <v>707</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>651</v>
+        <v>576</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>896</v>
+        <v>672</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>884</v>
+        <v>577</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>20</v>
@@ -6758,24 +6749,24 @@
         <v>20</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>817</v>
+        <v>613</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U47" s="3" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D48" s="9">
         <v>1</v>
@@ -6798,13 +6789,13 @@
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>658</v>
+        <v>708</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>20</v>
@@ -6819,24 +6810,24 @@
         <v>20</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -6860,13 +6851,13 @@
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>20</v>
@@ -6881,24 +6872,24 @@
         <v>20</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D50" s="9">
         <v>1</v>
@@ -6922,45 +6913,45 @@
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="T50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U50" s="3" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="O50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R50" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="T50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="D51" s="9">
         <v>1</v>
@@ -6984,13 +6975,13 @@
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N51" s="3" t="s">
-        <v>664</v>
+        <v>714</v>
       </c>
       <c r="O51" s="3" t="s">
         <v>20</v>
@@ -7005,24 +6996,24 @@
         <v>20</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="T51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U51" s="3" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D52" s="9">
         <v>1</v>
@@ -7046,16 +7037,16 @@
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>666</v>
+        <v>716</v>
       </c>
       <c r="O52" s="3" t="s">
-        <v>250</v>
+        <v>717</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>20</v>
@@ -7067,24 +7058,24 @@
         <v>20</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D53" s="9">
         <v>1</v>
@@ -7108,13 +7099,13 @@
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N53" s="3" t="s">
-        <v>668</v>
+        <v>719</v>
       </c>
       <c r="O53" s="3" t="s">
         <v>20</v>
@@ -7126,27 +7117,27 @@
         <v>20</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>256</v>
+        <v>720</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="T53" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U53" s="3" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="D54" s="9">
         <v>1</v>
@@ -7170,13 +7161,13 @@
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>670</v>
+        <v>722</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>20</v>
@@ -7188,27 +7179,27 @@
         <v>20</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>262</v>
+        <v>723</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="T54" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U54" s="3" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D55" s="9">
         <v>1</v>
@@ -7232,13 +7223,13 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="N55" s="3" t="s">
-        <v>672</v>
+        <v>725</v>
       </c>
       <c r="O55" s="3" t="s">
         <v>20</v>
@@ -7247,30 +7238,30 @@
         <v>20</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>268</v>
+        <v>726</v>
       </c>
       <c r="R55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="T55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D56" s="9">
         <v>1</v>
@@ -7294,13 +7285,13 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>674</v>
+        <v>728</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>20</v>
@@ -7309,30 +7300,30 @@
         <v>20</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>274</v>
+        <v>729</v>
       </c>
       <c r="R56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="T56" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D57" s="9">
         <v>1</v>
@@ -7356,13 +7347,13 @@
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>676</v>
+        <v>731</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>20</v>
@@ -7377,24 +7368,24 @@
         <v>20</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D58" s="9">
         <v>1</v>
@@ -7418,13 +7409,13 @@
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>678</v>
+        <v>733</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>20</v>
@@ -7433,30 +7424,30 @@
         <v>20</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="D59" s="9">
         <v>1</v>
@@ -7480,13 +7471,13 @@
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>680</v>
+        <v>735</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>20</v>
@@ -7495,30 +7486,30 @@
         <v>20</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>291</v>
+        <v>736</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="D60" s="9">
         <v>1</v>
@@ -7542,13 +7533,13 @@
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>682</v>
+        <v>738</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>20</v>
@@ -7563,24 +7554,24 @@
         <v>20</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D61" s="9">
         <v>1</v>
@@ -7604,13 +7595,13 @@
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N61" s="3" t="s">
-        <v>684</v>
+        <v>740</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>20</v>
@@ -7622,27 +7613,27 @@
         <v>20</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>301</v>
+        <v>741</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="T61" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D62" s="9">
         <v>2</v>
@@ -7666,13 +7657,13 @@
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="N62" s="3" t="s">
-        <v>686</v>
+        <v>743</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>20</v>
@@ -7681,30 +7672,30 @@
         <v>20</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>306</v>
+        <v>744</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -7728,13 +7719,13 @@
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N63" s="3" t="s">
-        <v>688</v>
+        <v>746</v>
       </c>
       <c r="O63" s="3" t="s">
         <v>20</v>
@@ -7746,27 +7737,27 @@
         <v>20</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>311</v>
+        <v>747</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="T63" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D64" s="9">
         <v>2</v>
@@ -7790,13 +7781,13 @@
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>690</v>
+        <v>749</v>
       </c>
       <c r="O64" s="3" t="s">
         <v>20</v>
@@ -7805,30 +7796,30 @@
         <v>20</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>316</v>
+        <v>750</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="T64" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="D65" s="9">
         <v>2</v>
@@ -7852,13 +7843,13 @@
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N65" s="3" t="s">
-        <v>692</v>
+        <v>752</v>
       </c>
       <c r="O65" s="3" t="s">
         <v>20</v>
@@ -7867,30 +7858,30 @@
         <v>20</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>322</v>
+        <v>753</v>
       </c>
       <c r="R65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="T65" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="D66" s="9">
         <v>2</v>
@@ -7914,13 +7905,13 @@
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N66" s="3" t="s">
-        <v>694</v>
+        <v>755</v>
       </c>
       <c r="O66" s="3" t="s">
         <v>20</v>
@@ -7929,30 +7920,30 @@
         <v>20</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="R66" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="D67" s="9">
         <v>2</v>
@@ -7976,13 +7967,13 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>331</v>
+        <v>315</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>332</v>
+        <v>316</v>
       </c>
       <c r="N67" s="3" t="s">
-        <v>696</v>
+        <v>757</v>
       </c>
       <c r="O67" s="3" t="s">
         <v>20</v>
@@ -7994,27 +7985,27 @@
         <v>20</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="T67" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>335</v>
+        <v>319</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="D68" s="9">
         <v>2</v>
@@ -8038,13 +8029,13 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>698</v>
+        <v>759</v>
       </c>
       <c r="O68" s="3" t="s">
         <v>20</v>
@@ -8056,27 +8047,27 @@
         <v>20</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>338</v>
+        <v>760</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="T68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="D69" s="9">
         <v>2</v>
@@ -8100,13 +8091,13 @@
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>700</v>
+        <v>762</v>
       </c>
       <c r="O69" s="3" t="s">
         <v>20</v>
@@ -8118,27 +8109,27 @@
         <v>20</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>343</v>
+        <v>763</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="T69" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D70" s="9">
         <v>2</v>
@@ -8162,13 +8153,13 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>702</v>
+        <v>765</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>20</v>
@@ -8180,27 +8171,27 @@
         <v>20</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>348</v>
+        <v>766</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="T70" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U70" s="3" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="D71" s="9">
         <v>2</v>
@@ -8224,16 +8215,16 @@
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>704</v>
+        <v>768</v>
       </c>
       <c r="O71" s="3" t="s">
-        <v>354</v>
+        <v>769</v>
       </c>
       <c r="P71" s="3" t="s">
         <v>20</v>
@@ -8242,27 +8233,27 @@
         <v>20</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>355</v>
+        <v>770</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="T71" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U71" s="3" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="D72" s="9">
         <v>2</v>
@@ -8286,13 +8277,13 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="N72" s="3" t="s">
-        <v>706</v>
+        <v>772</v>
       </c>
       <c r="O72" s="3" t="s">
         <v>20</v>
@@ -8301,30 +8292,30 @@
         <v>20</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>360</v>
+        <v>773</v>
       </c>
       <c r="R72" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U72" s="3" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="D73" s="9">
         <v>2</v>
@@ -8348,13 +8339,13 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="N73" s="3" t="s">
-        <v>708</v>
+        <v>775</v>
       </c>
       <c r="O73" s="3" t="s">
         <v>20</v>
@@ -8366,27 +8357,27 @@
         <v>20</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>366</v>
+        <v>776</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="T73" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U73" s="3" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="D74" s="9">
         <v>2</v>
@@ -8410,13 +8401,13 @@
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="N74" s="3" t="s">
-        <v>710</v>
+        <v>778</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>20</v>
@@ -8428,27 +8419,27 @@
         <v>20</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>372</v>
+        <v>779</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="T74" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U74" s="3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="D75" s="9">
         <v>2</v>
@@ -8472,13 +8463,13 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N75" s="3" t="s">
-        <v>712</v>
+        <v>781</v>
       </c>
       <c r="O75" s="3" t="s">
         <v>20</v>
@@ -8493,24 +8484,24 @@
         <v>20</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="T75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U75" s="3" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="D76" s="9">
         <v>3</v>
@@ -8534,13 +8525,13 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>714</v>
+        <v>783</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>20</v>
@@ -8549,30 +8540,30 @@
         <v>20</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>381</v>
+        <v>784</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U76" s="3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="D77" s="9">
         <v>3</v>
@@ -8596,13 +8587,13 @@
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>716</v>
+        <v>786</v>
       </c>
       <c r="O77" s="3" t="s">
         <v>20</v>
@@ -8611,30 +8602,30 @@
         <v>20</v>
       </c>
       <c r="Q77" s="3" t="s">
-        <v>386</v>
+        <v>787</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>387</v>
+        <v>788</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>388</v>
+        <v>361</v>
       </c>
       <c r="T77" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U77" s="3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="D78" s="9">
         <v>3</v>
@@ -8658,13 +8649,13 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N78" s="3" t="s">
-        <v>718</v>
+        <v>790</v>
       </c>
       <c r="O78" s="3" t="s">
         <v>20</v>
@@ -8676,27 +8667,27 @@
         <v>20</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>392</v>
+        <v>791</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="T78" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>394</v>
+        <v>366</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>395</v>
+        <v>367</v>
       </c>
       <c r="D79" s="9">
         <v>3</v>
@@ -8720,45 +8711,45 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3" t="s">
-        <v>396</v>
+        <v>368</v>
       </c>
       <c r="M79" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="R79" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="S79" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="T79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U79" s="3" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="N79" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="O79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q79" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="R79" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="S79" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="T79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="U79" s="3" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A80" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="D80" s="9">
         <v>3</v>
@@ -8782,13 +8773,13 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3" t="s">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>722</v>
+        <v>797</v>
       </c>
       <c r="O80" s="3" t="s">
         <v>20</v>
@@ -8800,27 +8791,27 @@
         <v>20</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>403</v>
+        <v>798</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="T80" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U80" s="3" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>405</v>
+        <v>374</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>406</v>
+        <v>375</v>
       </c>
       <c r="D81" s="9">
         <v>3</v>
@@ -8844,13 +8835,13 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>724</v>
+        <v>800</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>20</v>
@@ -8859,30 +8850,30 @@
         <v>20</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>408</v>
+        <v>801</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U81" s="3" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="D82" s="9">
         <v>3</v>
@@ -8906,45 +8897,45 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3" t="s">
-        <v>412</v>
+        <v>380</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>726</v>
+        <v>803</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>415</v>
+        <v>804</v>
       </c>
       <c r="R82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="T82" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U82" s="3" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="D83" s="9">
         <v>3</v>
@@ -8968,13 +8959,13 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3" t="s">
-        <v>419</v>
+        <v>387</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>420</v>
+        <v>388</v>
       </c>
       <c r="N83" s="3" t="s">
-        <v>728</v>
+        <v>806</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>20</v>
@@ -8983,30 +8974,30 @@
         <v>20</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>421</v>
+        <v>807</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>422</v>
+        <v>389</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U83" s="3" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>423</v>
+        <v>390</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="D84" s="9">
         <v>3</v>
@@ -9030,16 +9021,16 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>426</v>
+        <v>393</v>
       </c>
       <c r="N84" s="3" t="s">
-        <v>730</v>
+        <v>809</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>427</v>
+        <v>810</v>
       </c>
       <c r="P84" s="3" t="s">
         <v>20</v>
@@ -9048,27 +9039,27 @@
         <v>20</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>428</v>
+        <v>811</v>
       </c>
       <c r="S84" s="3" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="T84" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U84" s="3" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="D85" s="9">
         <v>3</v>
@@ -9092,13 +9083,13 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3" t="s">
-        <v>432</v>
+        <v>397</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N85" s="3" t="s">
-        <v>732</v>
+        <v>813</v>
       </c>
       <c r="O85" s="3" t="s">
         <v>20</v>
@@ -9107,30 +9098,30 @@
         <v>20</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>433</v>
+        <v>814</v>
       </c>
       <c r="R85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="T85" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U85" s="3" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="D86" s="9">
         <v>3</v>
@@ -9154,13 +9145,13 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="N86" s="3" t="s">
-        <v>734</v>
+        <v>816</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>20</v>
@@ -9169,30 +9160,30 @@
         <v>20</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>438</v>
+        <v>817</v>
       </c>
       <c r="R86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>439</v>
+        <v>402</v>
       </c>
       <c r="T86" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U86" s="3" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="D87" s="9">
         <v>3</v>
@@ -9216,13 +9207,13 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3" t="s">
-        <v>442</v>
+        <v>405</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="N87" s="3" t="s">
-        <v>736</v>
+        <v>819</v>
       </c>
       <c r="O87" s="3" t="s">
         <v>20</v>
@@ -9234,27 +9225,27 @@
         <v>20</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>444</v>
+        <v>820</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>445</v>
+        <v>407</v>
       </c>
       <c r="T87" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U87" s="3" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="D88" s="9">
         <v>3</v>
@@ -9278,13 +9269,13 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="N88" s="3" t="s">
-        <v>738</v>
+        <v>822</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>20</v>
@@ -9293,30 +9284,30 @@
         <v>20</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>449</v>
+        <v>823</v>
       </c>
       <c r="R88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S88" s="3" t="s">
-        <v>450</v>
+        <v>411</v>
       </c>
       <c r="T88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U88" s="3" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>451</v>
+        <v>412</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>452</v>
+        <v>413</v>
       </c>
       <c r="D89" s="9">
         <v>3</v>
@@ -9340,13 +9331,13 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3" t="s">
-        <v>453</v>
+        <v>414</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>740</v>
+        <v>825</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>20</v>
@@ -9355,30 +9346,30 @@
         <v>20</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>454</v>
+        <v>826</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="S89" s="3" t="s">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U89" s="3" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>457</v>
+        <v>417</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="D90" s="9">
         <v>4</v>
@@ -9402,45 +9393,45 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3" t="s">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>742</v>
+        <v>828</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>461</v>
+        <v>829</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>462</v>
+        <v>830</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
       <c r="T90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U90" s="3" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>464</v>
+        <v>422</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="D91" s="9">
         <v>4</v>
@@ -9464,45 +9455,45 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3" t="s">
-        <v>466</v>
+        <v>424</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>744</v>
+        <v>832</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P91" s="3" t="s">
-        <v>467</v>
+        <v>425</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>468</v>
+        <v>833</v>
       </c>
       <c r="R91" s="3" t="s">
-        <v>469</v>
+        <v>834</v>
       </c>
       <c r="S91" s="3" t="s">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U91" s="3" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>471</v>
+        <v>427</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>472</v>
+        <v>428</v>
       </c>
       <c r="D92" s="9">
         <v>4</v>
@@ -9526,45 +9517,45 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="3" t="s">
-        <v>473</v>
+        <v>429</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>746</v>
+        <v>836</v>
       </c>
       <c r="O92" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>474</v>
+        <v>430</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>475</v>
+        <v>837</v>
       </c>
       <c r="R92" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>476</v>
+        <v>431</v>
       </c>
       <c r="T92" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U92" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D93" s="9">
         <v>4</v>
@@ -9588,45 +9579,45 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3" t="s">
-        <v>478</v>
+        <v>433</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>748</v>
+        <v>839</v>
       </c>
       <c r="O93" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="Q93" s="3" t="s">
-        <v>480</v>
+        <v>840</v>
       </c>
       <c r="R93" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S93" s="3" t="s">
-        <v>481</v>
+        <v>435</v>
       </c>
       <c r="T93" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U93" s="3" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>482</v>
+        <v>436</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="D94" s="9">
         <v>4</v>
@@ -9650,45 +9641,45 @@
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="3" t="s">
-        <v>484</v>
+        <v>438</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>750</v>
+        <v>842</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>485</v>
+        <v>439</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>486</v>
+        <v>843</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>487</v>
+        <v>440</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>488</v>
+        <v>441</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U94" s="3" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>490</v>
+        <v>443</v>
       </c>
       <c r="D95" s="9">
         <v>4</v>
@@ -9712,45 +9703,45 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3" t="s">
-        <v>491</v>
+        <v>444</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>752</v>
+        <v>845</v>
       </c>
       <c r="O95" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>493</v>
+        <v>846</v>
       </c>
       <c r="R95" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>494</v>
+        <v>446</v>
       </c>
       <c r="T95" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U95" s="3" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>495</v>
+        <v>447</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="D96" s="9">
         <v>4</v>
@@ -9774,45 +9765,45 @@
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="3" t="s">
-        <v>497</v>
+        <v>449</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>754</v>
+        <v>848</v>
       </c>
       <c r="O96" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>498</v>
+        <v>450</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>499</v>
+        <v>849</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>500</v>
+        <v>451</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>501</v>
+        <v>452</v>
       </c>
       <c r="T96" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U96" s="3" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>502</v>
+        <v>453</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>503</v>
+        <v>454</v>
       </c>
       <c r="D97" s="9">
         <v>4</v>
@@ -9836,45 +9827,45 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3" t="s">
-        <v>504</v>
+        <v>455</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>756</v>
+        <v>851</v>
       </c>
       <c r="O97" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>505</v>
+        <v>456</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>506</v>
+        <v>852</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>507</v>
+        <v>853</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="T97" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U97" s="3" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="D98" s="9">
         <v>4</v>
@@ -9898,45 +9889,45 @@
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="3" t="s">
-        <v>511</v>
+        <v>460</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>758</v>
+        <v>855</v>
       </c>
       <c r="O98" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>512</v>
+        <v>461</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>513</v>
+        <v>856</v>
       </c>
       <c r="R98" s="3" t="s">
         <v>20</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>514</v>
+        <v>462</v>
       </c>
       <c r="T98" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U98" s="3" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>515</v>
+        <v>463</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>516</v>
+        <v>464</v>
       </c>
       <c r="D99" s="9">
         <v>4</v>
@@ -9960,45 +9951,45 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="3" t="s">
-        <v>517</v>
+        <v>465</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>518</v>
+        <v>466</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>760</v>
+        <v>858</v>
       </c>
       <c r="O99" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>519</v>
+        <v>467</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>20</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>520</v>
+        <v>859</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>521</v>
+        <v>468</v>
       </c>
       <c r="T99" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U99" s="3" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>522</v>
+        <v>469</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>523</v>
+        <v>470</v>
       </c>
       <c r="D100" s="9">
         <v>4</v>
@@ -10022,45 +10013,45 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
       <c r="L100" s="3" t="s">
-        <v>524</v>
+        <v>471</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>762</v>
+        <v>861</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P100" s="3" t="s">
-        <v>525</v>
+        <v>472</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>526</v>
+        <v>862</v>
       </c>
       <c r="R100" s="3" t="s">
-        <v>527</v>
+        <v>473</v>
       </c>
       <c r="S100" s="3" t="s">
-        <v>528</v>
+        <v>474</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U100" s="3" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>529</v>
+        <v>475</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>530</v>
+        <v>476</v>
       </c>
       <c r="D101" s="9">
         <v>4</v>
@@ -10084,45 +10075,45 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101" s="3" t="s">
-        <v>531</v>
+        <v>477</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>764</v>
+        <v>864</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P101" s="3" t="s">
-        <v>532</v>
+        <v>478</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>533</v>
+        <v>865</v>
       </c>
       <c r="R101" s="3" t="s">
-        <v>534</v>
+        <v>866</v>
       </c>
       <c r="S101" s="3" t="s">
-        <v>535</v>
+        <v>479</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U101" s="3" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>536</v>
+        <v>480</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>537</v>
+        <v>481</v>
       </c>
       <c r="D102" s="9">
         <v>4</v>
@@ -10146,45 +10137,45 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3" t="s">
-        <v>538</v>
+        <v>482</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>539</v>
+        <v>483</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>766</v>
+        <v>868</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>540</v>
+        <v>484</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>541</v>
+        <v>485</v>
       </c>
       <c r="R102" s="3" t="s">
-        <v>542</v>
+        <v>869</v>
       </c>
       <c r="S102" s="3" t="s">
-        <v>543</v>
+        <v>486</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="U102" s="3" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B103" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="D103" s="10">
         <v>4</v>
@@ -10194,36 +10185,36 @@
         <v>115</v>
       </c>
       <c r="L103" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M103" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="M103" s="5" t="s">
+      <c r="N103" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="P103" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q103" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="S103" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N103" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="P103" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="Q103" s="5" t="s">
+      <c r="U103" s="5" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="S103" s="5" t="s">
+      <c r="C104" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="U103" s="5" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A104" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="D104" s="10">
         <v>4</v>
@@ -10233,36 +10224,36 @@
         <v>117</v>
       </c>
       <c r="L104" s="5" t="s">
-        <v>546</v>
+        <v>489</v>
       </c>
       <c r="M104" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N104" s="5" t="s">
-        <v>769</v>
+        <v>874</v>
       </c>
       <c r="P104" s="5" t="s">
-        <v>547</v>
+        <v>490</v>
       </c>
       <c r="Q104" s="5" t="s">
-        <v>27</v>
+        <v>826</v>
       </c>
       <c r="S104" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="U104" s="5" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="U104" s="5" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="D105" s="10">
         <v>4</v>
@@ -10272,39 +10263,39 @@
         <v>119</v>
       </c>
       <c r="L105" s="5" t="s">
-        <v>548</v>
+        <v>491</v>
       </c>
       <c r="M105" s="5" t="s">
         <v>24</v>
       </c>
       <c r="N105" s="5" t="s">
-        <v>771</v>
+        <v>876</v>
       </c>
       <c r="P105" s="5" t="s">
-        <v>549</v>
+        <v>492</v>
       </c>
       <c r="Q105" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="R105" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="S105" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="U105" s="5" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>40</v>
-      </c>
-      <c r="R105" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="S105" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U105" s="5" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A106" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>44</v>
       </c>
       <c r="D106" s="10">
         <v>4</v>
@@ -10314,36 +10305,36 @@
         <v>121</v>
       </c>
       <c r="L106" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M106" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="N106" s="5" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="P106" s="5" t="s">
-        <v>550</v>
+        <v>493</v>
       </c>
       <c r="Q106" s="5" t="s">
-        <v>47</v>
+        <v>881</v>
       </c>
       <c r="S106" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="U106" s="5" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>551</v>
+        <v>494</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>552</v>
+        <v>495</v>
       </c>
       <c r="D107" s="10">
         <v>4</v>
@@ -10353,39 +10344,39 @@
         <v>123</v>
       </c>
       <c r="L107" s="5" t="s">
-        <v>553</v>
+        <v>496</v>
       </c>
       <c r="M107" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N107" s="5" t="s">
-        <v>773</v>
+        <v>883</v>
       </c>
       <c r="P107" s="5" t="s">
-        <v>554</v>
+        <v>497</v>
       </c>
       <c r="Q107" s="5" t="s">
-        <v>555</v>
+        <v>884</v>
       </c>
       <c r="R107" s="5" t="s">
-        <v>556</v>
+        <v>885</v>
       </c>
       <c r="S107" s="5" t="s">
-        <v>557</v>
+        <v>498</v>
       </c>
       <c r="U107" s="5" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>558</v>
+        <v>499</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>559</v>
+        <v>500</v>
       </c>
       <c r="D108" s="10">
         <v>4</v>
@@ -10395,39 +10386,39 @@
         <v>125</v>
       </c>
       <c r="L108" s="5" t="s">
-        <v>560</v>
+        <v>501</v>
       </c>
       <c r="M108" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N108" s="5" t="s">
-        <v>775</v>
+        <v>887</v>
       </c>
       <c r="P108" s="5" t="s">
-        <v>561</v>
+        <v>502</v>
       </c>
       <c r="Q108" s="5" t="s">
-        <v>562</v>
+        <v>888</v>
       </c>
       <c r="R108" s="5" t="s">
-        <v>563</v>
+        <v>503</v>
       </c>
       <c r="S108" s="5" t="s">
-        <v>564</v>
+        <v>504</v>
       </c>
       <c r="U108" s="5" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>565</v>
+        <v>505</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>566</v>
+        <v>506</v>
       </c>
       <c r="D109" s="10">
         <v>4</v>
@@ -10437,42 +10428,42 @@
         <v>127</v>
       </c>
       <c r="L109" s="5" t="s">
-        <v>567</v>
+        <v>507</v>
       </c>
       <c r="M109" s="5" t="s">
         <v>26</v>
       </c>
       <c r="N109" s="5" t="s">
-        <v>777</v>
+        <v>890</v>
       </c>
       <c r="O109" s="5" t="s">
-        <v>568</v>
+        <v>891</v>
       </c>
       <c r="P109" s="5" t="s">
-        <v>569</v>
+        <v>508</v>
       </c>
       <c r="Q109" s="5" t="s">
-        <v>570</v>
+        <v>383</v>
       </c>
       <c r="R109" s="5" t="s">
-        <v>571</v>
+        <v>892</v>
       </c>
       <c r="S109" s="5" t="s">
-        <v>572</v>
+        <v>509</v>
       </c>
       <c r="U109" s="5" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>573</v>
+        <v>510</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>574</v>
+        <v>511</v>
       </c>
       <c r="D110" s="10">
         <v>4</v>
@@ -10482,39 +10473,39 @@
         <v>129</v>
       </c>
       <c r="L110" s="5" t="s">
-        <v>575</v>
+        <v>512</v>
       </c>
       <c r="M110" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N110" s="5" t="s">
-        <v>779</v>
+        <v>894</v>
       </c>
       <c r="P110" s="5" t="s">
-        <v>576</v>
+        <v>513</v>
       </c>
       <c r="Q110" s="5" t="s">
-        <v>577</v>
+        <v>895</v>
       </c>
       <c r="R110" s="5" t="s">
-        <v>578</v>
+        <v>514</v>
       </c>
       <c r="S110" s="5" t="s">
-        <v>579</v>
+        <v>515</v>
       </c>
       <c r="U110" s="5" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>580</v>
+        <v>516</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>581</v>
+        <v>517</v>
       </c>
       <c r="D111" s="10">
         <v>4</v>
@@ -10524,39 +10515,39 @@
         <v>131</v>
       </c>
       <c r="L111" s="5" t="s">
-        <v>582</v>
+        <v>518</v>
       </c>
       <c r="M111" s="5" t="s">
         <v>23</v>
       </c>
       <c r="N111" s="5" t="s">
-        <v>781</v>
+        <v>897</v>
       </c>
       <c r="P111" s="5" t="s">
-        <v>583</v>
+        <v>519</v>
       </c>
       <c r="Q111" s="5" t="s">
-        <v>584</v>
+        <v>898</v>
       </c>
       <c r="R111" s="5" t="s">
-        <v>585</v>
+        <v>899</v>
       </c>
       <c r="S111" s="5" t="s">
-        <v>586</v>
+        <v>520</v>
       </c>
       <c r="U111" s="5" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>544</v>
+        <v>487</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>588</v>
+        <v>522</v>
       </c>
       <c r="D112" s="10">
         <v>4</v>
@@ -10566,28 +10557,28 @@
         <v>133</v>
       </c>
       <c r="L112" s="5" t="s">
-        <v>589</v>
+        <v>523</v>
       </c>
       <c r="M112" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N112" s="5" t="s">
-        <v>783</v>
+        <v>901</v>
       </c>
       <c r="P112" s="5" t="s">
-        <v>590</v>
+        <v>524</v>
       </c>
       <c r="Q112" s="5" t="s">
-        <v>591</v>
+        <v>902</v>
       </c>
       <c r="R112" s="5" t="s">
-        <v>592</v>
+        <v>903</v>
       </c>
       <c r="S112" s="5" t="s">
-        <v>593</v>
+        <v>525</v>
       </c>
       <c r="U112" s="5" t="s">
-        <v>784</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -10600,254 +10591,254 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3E58011-FC67-4D87-BC14-C3FC38733444}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="125.6640625" customWidth="1"/>
+    <col min="1" max="1" width="125.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="18" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="21" spans="1:1" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+    <row r="32" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+    <row r="33" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+    <row r="36" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>901</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+    <row r="38" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="39" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
+    <row r="40" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
+    <row r="41" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+    <row r="42" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="48.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
+    <row r="44" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
+    <row r="45" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
+    <row r="46" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="33" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>908</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
